--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -157,7 +157,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bases, the POI, the grid (SCR and X/R, or short-circuit MVA, or R/X), the gen-tie, the operating point and the PSCAD run settings.</t>
+          <t xml:space="preserve">Bases, the POI, the grid (SCR and X/R, or short-circuit MVA, or R/X), the gen-tie, the operating point, the plant controller and the PSCAD run settings.</t>
         </is>
       </c>
     </row>
@@ -170,120 +170,128 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
+      <c r="A8" s="4"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">One row per main power transformer; HV winding first. Three windings: TV kV, the three impedances and their bases. Parallel units: identical units in parallel. Tie: a line of its own from HV to it.</t>
+          <t xml:space="preserve">Plant controller (PSS/E .dyr): REPC_A = a REPCA1 on each generator, each holding the POI; REPC_B = one controller for the whole plant (hybrid PV + BESS): PLNTBU1 at the POI, and on each generator a REAX4BU1 that takes its share of the plant's Q (Qmax / sum of Qmax) and P (Pmax / sum of Pmax). REGC_A / REPC_A records: standard = REGCA1 / REPCA1 from the PSS/E library; USRMDL = REGCAU1 / REPCAU1.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generators</t>
+          <t xml:space="preserve">MPT</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">One row per generator (PV, BESS, wind, synchronous ...): the units (count and one unit's data; the model is their aggregate), its GSU (one GSU's data and the count), its collector (FEEDERS: the WECC equivalent of its rows in Feeders; EQUIVALENT: R X B given; NONE), how it shares the POI's Q, and its PSCAD model (vendor library and definition, or blank for a voltage source at the solved terminal voltage: a network check against PSS/E).</t>
+          <t xml:space="preserve">One row per main power transformer; HV winding first. Three windings: TV kV, the three impedances and their bases. Parallel units: identical units in parallel. Tie: a line of its own from HV to it.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeders</t>
+          <t xml:space="preserve">Generators</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The collector feeders section by section from the collector bus out: cable, length and the units tapped at the section's far end. A daisy chain needs no From section; a lateral names the section it leaves from (its far end); 0 = straight from the collector bus. Copies: identical feeders. WECC equivalent: Zeq = sum(Zi Wi^2) / W^2, Beq = sum(Bi), Wi = MW of the units downstream of section i.</t>
+          <t xml:space="preserve">One row per generator (PV, BESS, wind, synchronous ...): the units (count and one unit's data; the model is their aggregate), its GSU (one GSU's data and the count), its collector (FEEDERS: the WECC equivalent of its rows in Feeders; EQUIVALENT: R X B given; NONE), how it shares the POI's Q, its electrical control model in the .dyr (REEC_A: REECA1, PV and wind; REEC_C: REECCU1, BESS; REEC_D: REECDU1, PV, BESS and WT4) and its PSCAD model (vendor library and definition, or blank for a voltage source at the solved terminal voltage: a network check against PSS/E).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable data per length (R, X in ohm; C in uF or B in uS) and the length unit they are per.</t>
+          <t xml:space="preserve">The collector feeders section by section from the collector bus out: cable, length and the units tapped at the section's far end. A daisy chain needs no From section; a lateral names the section it leaves from (its far end); 0 = straight from the collector bus. Copies: identical feeders. WECC equivalent: Zeq = sum(Zi Wi^2) / W^2, Beq = sum(Bi), Wi = MW of the units downstream of section i.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector systems shared by more than one generator: name and the bus it starts from. Their Feeders rows say whose units each section carries (Units of); the generators on it Connect to its name.</t>
+          <t xml:space="preserve">Cable data per length (R, X in ohm; C in uF or B in uS) and the length unit they are per.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliary loads (constant impedance, MW and MVAr at 1 pu) and shunts (MVAr at 1 pu: + capacitor, - reactor) on any bus.</t>
+          <t xml:space="preserve">Collector systems shared by more than one generator: name and the bus it starts from. Their Feeders rows say whose units each section carries (Units of); the generators on it Connect to its name.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus numbers or names of your own, by role (the report lists every role and its number).</t>
+          <t xml:space="preserve">Auxiliary loads (constant impedance, MW and MVAr at 1 pu) and shunts (MVAr at 1 pu: + capacitor, - reactor) on any bus.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any parameter of the WECC-approved generic models, by generator, model and PSS/E name (IB for the infinite bus). PV and WT4: REGCA1 + REECA1 + REPCA1 (REGC_A, REEC_A, REPC_A); BESS: REGCAU1 + REECCU1 + REPCAU1 (REGC_A, REEC_C, REPC_A -- USRMDL records: the WECC user-model DLL must be loaded, ADDLIB_IDV / DLLS in the script); WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1; SYNC: GENROU SEXS TGOV1. The report lists every model's parameters with the values used.</t>
+          <t xml:space="preserve">Bus numbers or names of your own, by role (the report lists every role and its number).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Records of your own (vendor or user models), one per row, ending in /. {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} and {&lt;bus role&gt;} are filled in. Type USER generators have only these. Models in user DLLs: list the DLLs in DLLS in the script for the PSS/E check.</t>
+          <t xml:space="preserve">Any parameter of the WECC-approved generic models, by generator, model and PSS/E name or position (ICON2, CON14) -- IB for the infinite bus, PLANT for the plant controller. Inverters: REGCA1 (REGC_A) + REECA1 / REECCU1 / REECDU1 (REEC_A / C / D) + REPCA1 (REPC_A) or REAX4BU1 (with PLNTBU1, REPC_B); WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1; SYNC: GENROU SEXS TGOV1. REECCU1, REECDU1, PLNTBU1, REAX4BU1 (and REGCAU1, REPCAU1) are user models: the WECC user-model DLL must be loaded for the PSS/E check (ADDLIB_IDV / DLLS in the script). The report lists every model's parameters with the values used.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Records of your own (vendor or user models), one per row, ending in /. {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} and {&lt;bus role&gt;} are filled in. Type USER generators have only these. Models in user DLLs: list the DLLs in DLLS in the script for the PSS/E check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Parameters of each generator's vendor PSCAD model, as PSCAD takes them.</t>
         </is>
@@ -327,17 +335,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># IB for the infinite bus</t>
+          <t xml:space="preserve"># IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PV/WT4: REGCA1 REECA1 REPCA1 | BESS: REGCAU1 REECCU1 REPCAU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all)</t>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
         </is>
       </c>
       <c r="D2" s="2"/>
@@ -345,12 +353,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PV</t>
+          <t xml:space="preserve">PLANT</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">REPCA1</t>
+          <t xml:space="preserve">PLNTBU1</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -360,6 +368,26 @@
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REECCU1</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOCini</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -468,7 +496,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
     </row>
@@ -515,7 +543,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Example_PV_BESS</t>
+          <t xml:space="preserve">Hybrid_PV100_BESS100</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -586,7 +614,7 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <v>345.0</v>
+        <v>230.0</v>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
@@ -717,7 +745,7 @@
         </is>
       </c>
       <c r="B14" s="3">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -749,7 +777,7 @@
         </is>
       </c>
       <c r="B16" s="3">
-        <v>0.0287</v>
+        <v>0.072</v>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
@@ -769,7 +797,7 @@
         </is>
       </c>
       <c r="B17" s="3">
-        <v>0.37</v>
+        <v>0.495</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
@@ -789,7 +817,7 @@
         </is>
       </c>
       <c r="B18" s="3">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
@@ -888,7 +916,7 @@
         </is>
       </c>
       <c r="B24" s="3">
-        <v>600.0</v>
+        <v>400.0</v>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
@@ -1014,51 +1042,45 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD time step</t>
-        </is>
-      </c>
-      <c r="B31" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">us</t>
+          <t xml:space="preserve">Plant controller</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REPC_B</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 10 (the vendor model's own requirement wins)</t>
+          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD duration</t>
-        </is>
-      </c>
-      <c r="B32" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
+          <t xml:space="preserve">REGC_A / REPC_A records</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 5</t>
+          <t xml:space="preserve">standard: REGCA1 / REPCA1 (PSS/E library) | USRMDL: REGCAU1 / REPCAU1 (the WECC user-model DLL) (blank = standard)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD plot step</t>
+          <t xml:space="preserve">PSCAD time step</t>
         </is>
       </c>
       <c r="B33" s="3">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
@@ -1067,49 +1089,95 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 100</t>
+          <t xml:space="preserve">blank = 10 (the vendor model's own requirement wins)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD meter at POI</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">PSCAD duration</t>
+        </is>
+      </c>
+      <c r="B34" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
+          <t xml:space="preserve">blank = 5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD plot step</t>
+        </is>
+      </c>
+      <c r="B35" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">us</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD meter at POI</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD libraries</t>
         </is>
       </c>
-      <c r="B35" s="3"/>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B37" s="3"/>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B15">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B25">
       <formula1>"Q,PF,V"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B34">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B31">
+      <formula1>"REPC_A,REPC_B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B32">
+      <formula1>"standard,USRMDL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B36">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1413,19 +1481,19 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>345.0</v>
+        <v>230.0</v>
       </c>
       <c r="C3" s="3">
         <v>34.5</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3">
-        <v>280.0</v>
+        <v>225.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -1433,7 +1501,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="inlineStr">
@@ -1450,7 +1518,7 @@
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3">
-        <v>280.0</v>
+        <v>225.0</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1502,9 +1570,10 @@
     <col min="29" max="29" width="8" customWidth="1"/>
     <col min="30" max="30" width="8" customWidth="1"/>
     <col min="31" max="31" width="6" customWidth="1"/>
-    <col min="32" max="32" width="18" customWidth="1"/>
-    <col min="33" max="33" width="16" customWidth="1"/>
-    <col min="34" max="34" width="9" customWidth="1"/>
+    <col min="32" max="32" width="9" customWidth="1"/>
+    <col min="33" max="33" width="18" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
+    <col min="35" max="35" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1665,15 +1734,20 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Electrical control</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD AC port</t>
         </is>
@@ -1817,15 +1891,20 @@
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
@@ -1853,7 +1932,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
         <v>4.2</v>
@@ -1915,9 +1994,14 @@
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_A</t>
+        </is>
+      </c>
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1944,19 +2028,19 @@
         <v>25</v>
       </c>
       <c r="F4" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="G4" s="3">
         <v>4.0</v>
       </c>
-      <c r="G4" s="3">
-        <v>3.6</v>
-      </c>
       <c r="H4" s="3">
-        <v>-3.6</v>
+        <v>-4.0</v>
       </c>
       <c r="I4" s="3">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="J4" s="3">
-        <v>-1.74</v>
+        <v>-1.83</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3">
@@ -1972,7 +2056,7 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3">
-        <v>4.0</v>
+        <v>4.4</v>
       </c>
       <c r="S4" s="3">
         <v>34.5</v>
@@ -1994,31 +2078,26 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT</t>
-        </is>
-      </c>
-      <c r="Z4" s="3">
-        <v>0.004</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>0.003</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>0.015</v>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
+          <t xml:space="preserve">FEEDERS</t>
+        </is>
+      </c>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_C</t>
+        </is>
+      </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B500">
       <formula1>"PV,BESS,WT4,WT3,SYNC,USER"</formula1>
     </dataValidation>
@@ -2030,6 +2109,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC3:AC500">
       <formula1>"pu,ohm"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF3:AF500">
+      <formula1>"REEC_A,REEC_C,REEC_D"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -2173,7 +2255,7 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -2185,7 +2267,7 @@
         </is>
       </c>
       <c r="G3" s="3">
-        <v>2.0</v>
+        <v>1.6</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2210,7 +2292,7 @@
         </is>
       </c>
       <c r="C4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3">
         <v>2</v>
@@ -2222,7 +2304,7 @@
         </is>
       </c>
       <c r="G4" s="3">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2230,7 +2312,7 @@
         </is>
       </c>
       <c r="I4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -2247,7 +2329,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -2259,7 +2341,7 @@
         </is>
       </c>
       <c r="G5" s="3">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2349,7 @@
         </is>
       </c>
       <c r="I5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -2284,7 +2366,7 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>4</v>
@@ -2296,7 +2378,7 @@
         </is>
       </c>
       <c r="G6" s="3">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2304,7 +2386,7 @@
         </is>
       </c>
       <c r="I6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -2321,7 +2403,7 @@
         </is>
       </c>
       <c r="C7" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3">
         <v>5</v>
@@ -2333,7 +2415,7 @@
         </is>
       </c>
       <c r="G7" s="3">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2423,7 @@
         </is>
       </c>
       <c r="I7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -2358,7 +2440,7 @@
         </is>
       </c>
       <c r="C8" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="3">
         <v>6</v>
@@ -2370,7 +2452,7 @@
         </is>
       </c>
       <c r="G8" s="3">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2378,10 +2460,232 @@
         </is>
       </c>
       <c r="I8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="C9" s="3">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000AL</t>
+        </is>
+      </c>
+      <c r="G9" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="C10" s="3">
+        <v>5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500AL</t>
+        </is>
+      </c>
+      <c r="G10" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="C11" s="3">
+        <v>5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500AL</t>
+        </is>
+      </c>
+      <c r="G11" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="C12" s="3">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/0AL</t>
+        </is>
+      </c>
+      <c r="G12" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="C13" s="3">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/0AL</t>
+        </is>
+      </c>
+      <c r="G13" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+      <c r="C14" s="3">
+        <v>5</v>
+      </c>
+      <c r="D14" s="3">
+        <v>6</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/0AL</t>
+        </is>
+      </c>
+      <c r="G14" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="I14" s="3">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2671,10 +2975,10 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D3" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -197,7 +197,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">One row per generator (PV, BESS, wind, synchronous ...): the units (count and one unit's data; the model is their aggregate), its GSU (one GSU's data and the count), its collector (FEEDERS: the WECC equivalent of its rows in Feeders; EQUIVALENT: R X B given; NONE), how it shares the POI's Q, its electrical control model in the .dyr (REEC_A: REECA1, PV and wind; REEC_C: REECCU1, BESS; REEC_D: REECDU1, PV, BESS and WT4) and its PSCAD model (vendor library and definition, or blank for a voltage source at the solved terminal voltage: a network check against PSS/E).</t>
+          <t xml:space="preserve">One row per generator (PV, BESS, wind, synchronous ...): the units (count and one unit's data; the model is their aggregate), its GSU (one GSU's data and the count), its collector (FEEDERS: the WECC equivalent of its rows in Feeders; EQUIVALENT: R X B given; NONE), how it shares the POI's Q, its electrical control model in the .dyr (REEC_A: REECA1, PV and wind; REEC_C: REECCU1, BESS; REEC_D: REECDU1, PV, BESS and WT4) and its PSCAD model (vendor library and definition, or blank for a voltage source at the solved terminal voltage: a network check against PSS/E), where the inverter connects (LV or MV side of the GSU) and how the collector is drawn in PSCAD (EQUIVALENT or DETAILED).</t>
         </is>
       </c>
     </row>
@@ -293,7 +293,19 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameters of each generator's vendor PSCAD model, as PSCAD takes them.</t>
+          <t xml:space="preserve">Parameters of each generator's vendor PSCAD model (UDM), as PSCAD takes them. Filled in for each inverter it stands for (DETAILED: each node): {UNITS} units, {MVA} their MVA, {P_MW} {Q_MVAR} their P and Q where it connects, {P_PU} {Q_PU} on {MVA}, {UNIT_MVA} {UNIT_P_MW} {UNIT_Q_MVAR} one unit's, {V_PU} {V_KV} {KV} {ANGLE} the voltage there, its base and PSCAD angle, {P_INV_MW} {Q_INV_MVAR} {V_INV_PU} at the inverters' own terminals (a UDM on the MV side), {FREQ} -- e.g. Ninv = {UNITS}, Vt0 = {V_PU}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and connect your UDM to its node label (the report and the build log list every inverter node). PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn.</t>
         </is>
       </c>
     </row>
@@ -479,7 +491,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, ...)</t>
+          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
         </is>
       </c>
     </row>
@@ -496,7 +508,24 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">{UNITS}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#PV</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vt0</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_PU} [pu]</t>
         </is>
       </c>
     </row>
@@ -1574,6 +1603,8 @@
     <col min="33" max="33" width="18" customWidth="1"/>
     <col min="34" max="34" width="16" customWidth="1"/>
     <col min="35" max="35" width="9" customWidth="1"/>
+    <col min="36" max="36" width="8" customWidth="1"/>
+    <col min="37" max="37" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1752,6 +1783,16 @@
           <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD inverter at</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD collector</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1907,6 +1948,16 @@
       <c r="AI2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIVALENT: one pi section, as PSS/E | DETAILED: every Feeders section, a GSU and an inverter at every node with units (blank = EQUIVALENT)</t>
         </is>
       </c>
     </row>
@@ -2002,6 +2053,16 @@
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETAILED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2095,9 +2156,19 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETAILED</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B500">
       <formula1>"PV,BESS,WT4,WT3,SYNC,USER"</formula1>
     </dataValidation>
@@ -2112,6 +2183,12 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF3:AF500">
       <formula1>"REEC_A,REEC_C,REEC_D"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AJ3:AJ500">
+      <formula1>"LV,MV"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AK3:AK500">
+      <formula1>"EQUIVALENT,DETAILED"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>
@@ -2873,6 +2950,7 @@
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2886,6 +2964,11 @@
           <t xml:space="preserve">Connect to</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD collector</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2898,8 +2981,18 @@
           <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUIVALENT | DETAILED: every section, a GSU and an inverter per generator at every node (blank = EQUIVALENT)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C500">
+      <formula1>"EQUIVALENT,DETAILED"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -305,7 +305,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and connect your UDM to its node label (the report and the build log list every inverter node). PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn.</t>
+          <t xml:space="preserve">The .pscx is built in the same run when PSCAD 5 and its Python library mhi.pscad (pip install mhi.pscad) are on the PC; otherwise run &lt;name&gt;_build_pscad.py where they are. The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and connect your UDM to its node label (the report and the build log list every inverter node). PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn.</t>
         </is>
       </c>
     </row>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -305,7 +305,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The .pscx is built in the same run when PSCAD 5 and its Python library mhi.pscad (pip install mhi.pscad) are on the PC; otherwise run &lt;name&gt;_build_pscad.py where they are. The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and connect your UDM to its node label (the report and the build log list every inverter node). PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn.</t>
+          <t xml:space="preserve">The .pscx is built in the same run when PSCAD 5 and its Python library mhi.pscad (pip install mhi.pscad) are on the PC; otherwise run &lt;name&gt;_build_pscad.py where they are. The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and wire your UDM in its place (the report and the build log list every inverter node). PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn. It is drawn as a single-line diagram with wires, left to right from the grid; where PSCAD's R, L and C are single-phase, each is drawn three times between breakouts.</t>
         </is>
       </c>
     </row>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -1182,18 +1182,110 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD fault at POI</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault time</t>
+        </is>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault duration</t>
+        </is>
+      </c>
+      <c r="B39" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = 0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault type</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABCG</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault resistance</t>
+        </is>
+      </c>
+      <c r="B41" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = 0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD libraries</t>
         </is>
       </c>
-      <c r="B37" s="3"/>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B42" s="3"/>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B15">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
@@ -1208,6 +1300,12 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B36">
       <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B37">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B40">
+      <formula1>"ABCG,ABC,AG,BG,CG,ABG,BCG,ACG,AB,BC,AC"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -224,7 +224,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E (.raw, .dyr) and PSCAD (.pscx) models of a plant from one workbook -- smib_build.py, 2026-10-14</t>
+          <t xml:space="preserve">PSS/E (.raw, .dyr) and PSCAD (.pscx) models of a plant from one workbook -- smib_build.py, 2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="10"/>
@@ -260,7 +260,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plant: Model type -- SMIB: one equivalent feeder per MPT, each generator one machine | DETAILED: every feeder section, the units at each node a machine of their own. PSS/E and PSCAD are built alike.</t>
+          <t xml:space="preserve">Plant: Model type -- SMIB: each generator one machine on its own equivalent feeder | DETAILED: every feeder section, the units at each node a machine of their own. PSS/E and PSCAD are built alike.</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="69.0" customHeight="1">
+    <row r="38" ht="56.0" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">MODEL TYPE</t>
@@ -655,7 +655,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plant: Model type sets PSS/E and PSCAD alike. SMIB (default): the collectors on one MPT winding are one equivalent feeder (WECC, each collector weighed by its MW), each generator one machine behind one GSU at its far end. DETAILED: every feeder section is a branch (identical feeder copies lumped), the units of a generator at each node a machine of their own behind their own GSU; a generator's Dyr_Params, Dyr_Records and PSCAD_Params rows apply to all its machines.</t>
+          <t xml:space="preserve">Plant: Model type sets PSS/E and PSCAD alike. SMIB (default): each generator is one machine behind one GSU on a collector equivalent of its own (WECC, each feeder weighed by its MW) from its MPT winding. DETAILED: every feeder section is a branch (identical feeder copies lumped), the units of a generator at each node a machine of their own behind their own GSU; a generator's Dyr_Params, Dyr_Records and PSCAD_Params rows apply to all its machines.</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMIB: one equivalent feeder (WECC) per MPT, each generator one machine behind one GSU | DETAILED: every feeder section, the units at each node a machine of their own behind their own GSU -- PSS/E and PSCAD alike (blank = SMIB)</t>
+          <t xml:space="preserve">SMIB: each generator one machine behind one GSU on its own equivalent feeder (WECC) from its MPT | DETAILED: every feeder section, the units at each node a machine of their own behind their own GSU -- PSS/E and PSCAD alike (blank = SMIB)</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -6273,7 +6273,7 @@
       <c r="A163" s="8"/>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:COLL</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C163" s="8"/>
@@ -6282,7 +6282,7 @@
       <c r="F163" s="8"/>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMIB: the far end of the MPT's one equivalent feeder</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H163" s="8"/>
@@ -6291,7 +6291,7 @@
       <c r="A164" s="8"/>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C164" s="8"/>
@@ -6300,7 +6300,7 @@
       <c r="F164" s="8"/>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end (SMIB without merging)</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H164" s="8"/>
@@ -6309,7 +6309,7 @@
       <c r="A165" s="8"/>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
         </is>
       </c>
       <c r="C165" s="8"/>
@@ -6318,7 +6318,7 @@
       <c r="F165" s="8"/>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">a generator's terminal</t>
         </is>
       </c>
       <c r="H165" s="8"/>
@@ -6327,7 +6327,7 @@
       <c r="A166" s="8"/>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C166" s="8"/>
@@ -6336,7 +6336,7 @@
       <c r="F166" s="8"/>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
         </is>
       </c>
       <c r="H166" s="8"/>
@@ -6345,7 +6345,7 @@
       <c r="A167" s="8"/>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
         </is>
       </c>
       <c r="C167" s="8"/>
@@ -6354,42 +6354,50 @@
       <c r="F167" s="8"/>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
         </is>
       </c>
       <c r="H167" s="8"/>
     </row>
-    <row r="168">
-      <c r="A168" s="8"/>
-      <c r="B168" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
-        </is>
-      </c>
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
-      <c r="F168" s="8"/>
-      <c r="G168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
-        </is>
-      </c>
-      <c r="H168" s="8"/>
-    </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
         </is>
       </c>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
-      <c r="G169" s="7"/>
-      <c r="H169" s="7"/>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
+      <c r="H168" s="7"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{UNITS}</t>
+        </is>
+      </c>
+      <c r="C169" s="8"/>
+      <c r="D169" s="8"/>
+      <c r="E169" s="8"/>
+      <c r="F169" s="8"/>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the units the inverter stands for</t>
+        </is>
+      </c>
+      <c r="H169" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="8" t="inlineStr">
@@ -6399,7 +6407,7 @@
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNITS}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C170" s="8"/>
@@ -6408,7 +6416,7 @@
       <c r="F170" s="8"/>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H170" s="13" t="inlineStr">
@@ -6425,7 +6433,7 @@
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C171" s="8"/>
@@ -6434,7 +6442,7 @@
       <c r="F171" s="8"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
@@ -6451,7 +6459,7 @@
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_MW}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C172" s="8"/>
@@ -6460,7 +6468,7 @@
       <c r="F172" s="8"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
@@ -6477,7 +6485,7 @@
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C173" s="8"/>
@@ -6486,7 +6494,7 @@
       <c r="F173" s="8"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H173" s="13" t="inlineStr">
@@ -6503,7 +6511,7 @@
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C174" s="8"/>
@@ -6512,7 +6520,7 @@
       <c r="F174" s="8"/>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H174" s="13" t="inlineStr">
@@ -6529,7 +6537,7 @@
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C175" s="8"/>
@@ -6538,7 +6546,7 @@
       <c r="F175" s="8"/>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H175" s="13" t="inlineStr">
@@ -6555,7 +6563,7 @@
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C176" s="8"/>
@@ -6564,7 +6572,7 @@
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H176" s="13" t="inlineStr">
@@ -6581,7 +6589,7 @@
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C177" s="8"/>
@@ -6590,7 +6598,7 @@
       <c r="F177" s="8"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -6607,7 +6615,7 @@
       </c>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C178" s="8"/>
@@ -6616,7 +6624,7 @@
       <c r="F178" s="8"/>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H178" s="13" t="inlineStr">
@@ -6633,7 +6641,7 @@
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C179" s="8"/>
@@ -6642,7 +6650,7 @@
       <c r="F179" s="8"/>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H179" s="13" t="inlineStr">
@@ -6659,7 +6667,7 @@
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C180" s="8"/>
@@ -6668,7 +6676,7 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -6685,7 +6693,7 @@
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -6694,7 +6702,7 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H181" s="13" t="inlineStr">
@@ -6711,7 +6719,7 @@
       </c>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C182" s="8"/>
@@ -6720,7 +6728,7 @@
       <c r="F182" s="8"/>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">frequency (Hz)</t>
         </is>
       </c>
       <c r="H182" s="13" t="inlineStr">
@@ -6737,7 +6745,7 @@
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{P_INV_MW}</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -6746,7 +6754,7 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
         </is>
       </c>
       <c r="H183" s="13" t="inlineStr">
@@ -6763,7 +6771,7 @@
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
         </is>
       </c>
       <c r="C184" s="8"/>
@@ -6772,7 +6780,7 @@
       <c r="F184" s="8"/>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">Q there (MVAr)</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
@@ -6789,7 +6797,7 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{V_INV_PU}</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -6798,36 +6806,10 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
       <c r="H185" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B186" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
-        </is>
-      </c>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
-      <c r="F186" s="8"/>
-      <c r="G186" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the voltage there (pu)</t>
-        </is>
-      </c>
-      <c r="H186" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -6849,7 +6831,7 @@
     <mergeCell ref="A149:H149"/>
     <mergeCell ref="A152:H152"/>
     <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A169:H169"/>
+    <mergeCell ref="A168:H168"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
@@ -6863,7 +6845,7 @@
     <hyperlink ref="A144" location="'Dyr_Params'!A1" display="Dyr_Params"/>
     <hyperlink ref="A149" location="'Dyr_Records'!A1" display="Dyr_Records"/>
     <hyperlink ref="A152" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A169" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A168" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -17529,7 +17511,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMIB: one equivalent feeder (WECC) per MPT, each generator one machine behind one GSU | DETAILED: every feeder section, the units at each node a machine of their own behind their own GSU -- PSS/E and PSCAD alike (blank = SMIB)</t>
+          <t xml:space="preserve">SMIB: each generator one machine behind one GSU on its own equivalent feeder (WECC) from its MPT | DETAILED: every feeder section, the units at each node a machine of their own behind their own GSU -- PSS/E and PSCAD alike (blank = SMIB)</t>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
@@ -22474,7 +22456,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MPT1:COLL</t>
+          <t xml:space="preserve">PV:MV</t>
         </is>
       </c>
       <c r="B7" s="3"/>
@@ -22492,14 +22474,18 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BESS:LV</t>
+          <t xml:space="preserve">BESS:MV</t>
         </is>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS:LV</t>
+        </is>
+      </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -2705,62 +2705,62 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD lines as</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_lines</t>
+        </is>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI | RLC</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30.0" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD fault at POI</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_fault</t>
         </is>
       </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="17.0" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault time</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_fault_s</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100: none in the run</t>
-        </is>
-      </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault duration</t>
+          <t xml:space="preserve">PSCAD fault time</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_fault_dur_s</t>
+          <t xml:space="preserve">pscad_fault_s</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2792,89 +2792,89 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
+          <t xml:space="preserve">100: none in the run</t>
         </is>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17.0" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault duration</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_fault_dur_s</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 0.15</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="43.0" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45" ht="43.0" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault type</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_fault_type</t>
         </is>
       </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="D45" s="8"/>
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="17.0" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault resistance</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_fault_ohm</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.01</t>
-        </is>
-      </c>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 0.01</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -2891,71 +2891,79 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD libraries</t>
+          <t xml:space="preserve">PSCAD fault resistance</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_libraries</t>
-        </is>
-      </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
+          <t xml:space="preserve">pscad_fault_ohm</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.01</t>
+        </is>
+      </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = 0.01</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17.0" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD libraries</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_libraries</t>
+        </is>
+      </c>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
         </is>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-    </row>
-    <row r="48" ht="17.0" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
     </row>
     <row r="49" ht="17.0" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
@@ -2965,18 +2973,22 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV kV</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hv_kv</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
+        </is>
+      </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -2991,12 +3003,12 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV kV</t>
+          <t xml:space="preserve">HV kV</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_kv</t>
+          <t xml:space="preserve">hv_kv</t>
         </is>
       </c>
       <c r="D50" s="8"/>
@@ -3017,26 +3029,18 @@
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TV kV</t>
+          <t xml:space="preserve">LV kV</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tv_kv</t>
+          <t xml:space="preserve">lv_kv</t>
         </is>
       </c>
       <c r="D51" s="8"/>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">two windings</t>
-        </is>
-      </c>
+      <c r="E51" s="8"/>
       <c r="F51" s="8"/>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tertiary / 2nd LV winding; blank = two windings</t>
-        </is>
-      </c>
+      <c r="G51" s="8"/>
       <c r="H51" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3051,20 +3055,24 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">TV kV</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mva</t>
+          <t xml:space="preserve">tv_kv</t>
         </is>
       </c>
       <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">two windings</t>
+        </is>
+      </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
+          <t xml:space="preserve">tertiary / 2nd LV winding; blank = two windings</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -3081,12 +3089,12 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV MVA</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_mva</t>
+          <t xml:space="preserve">mva</t>
         </is>
       </c>
       <c r="D53" s="8"/>
@@ -3094,7 +3102,7 @@
       <c r="F53" s="8"/>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -3111,12 +3119,12 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TV MVA</t>
+          <t xml:space="preserve">LV MVA</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tv_mva</t>
+          <t xml:space="preserve">lv_mva</t>
         </is>
       </c>
       <c r="D54" s="8"/>
@@ -3141,12 +3149,12 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV %</t>
+          <t xml:space="preserve">TV MVA</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_hl_pct</t>
+          <t xml:space="preserve">tv_mva</t>
         </is>
       </c>
       <c r="D55" s="8"/>
@@ -3154,7 +3162,7 @@
       <c r="F55" s="8"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on its base MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -3171,12 +3179,12 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV %</t>
+          <t xml:space="preserve">Z HV-LV %</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_ht_pct</t>
+          <t xml:space="preserve">z_hl_pct</t>
         </is>
       </c>
       <c r="D56" s="8"/>
@@ -3184,7 +3192,7 @@
       <c r="F56" s="8"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">on its base MVA</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -3201,12 +3209,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV %</t>
+          <t xml:space="preserve">Z HV-TV %</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_lt_pct</t>
+          <t xml:space="preserve">z_ht_pct</t>
         </is>
       </c>
       <c r="D57" s="8"/>
@@ -3231,24 +3239,20 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV base MVA</t>
+          <t xml:space="preserve">Z LV-TV %</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_hl_mva</t>
+          <t xml:space="preserve">z_lt_pct</t>
         </is>
       </c>
       <c r="D58" s="8"/>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -3265,12 +3269,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-LV base MVA</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_ht_mva</t>
+          <t xml:space="preserve">base_hl_mva</t>
         </is>
       </c>
       <c r="D59" s="8"/>
@@ -3299,12 +3303,12 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-TV base MVA</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_lt_mva</t>
+          <t xml:space="preserve">base_ht_mva</t>
         </is>
       </c>
       <c r="D60" s="8"/>
@@ -3333,20 +3337,24 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X/R</t>
+          <t xml:space="preserve">Z LV-TV base MVA</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_r</t>
+          <t xml:space="preserve">base_lt_mva</t>
         </is>
       </c>
       <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each impedance</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -3363,12 +3371,12 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load loss kW</t>
+          <t xml:space="preserve">X/R</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">load_loss_kw</t>
+          <t xml:space="preserve">x_r</t>
         </is>
       </c>
       <c r="D62" s="8"/>
@@ -3376,7 +3384,7 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
+          <t xml:space="preserve">each impedance</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -3393,12 +3401,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector group</t>
+          <t xml:space="preserve">Load loss kW</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vector</t>
+          <t xml:space="preserve">load_loss_kw</t>
         </is>
       </c>
       <c r="D63" s="8"/>
@@ -3406,7 +3414,7 @@
       <c r="F63" s="8"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
+          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -3423,24 +3431,20 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV tap</t>
+          <t xml:space="preserve">Vector group</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tap</t>
+          <t xml:space="preserve">vector</t>
         </is>
       </c>
       <c r="D64" s="8"/>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E64" s="8"/>
       <c r="F64" s="8"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
+          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -3457,12 +3461,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel units</t>
+          <t xml:space="preserve">HV tap</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">count</t>
+          <t xml:space="preserve">tap</t>
         </is>
       </c>
       <c r="D65" s="8"/>
@@ -3474,7 +3478,7 @@
       <c r="F65" s="8"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical units (blank = 1)</t>
+          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -3491,24 +3495,24 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No-load loss %</t>
+          <t xml:space="preserve">Parallel units</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nll_pct</t>
+          <t xml:space="preserve">count</t>
         </is>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">of MVA (blank = 0)</t>
+          <t xml:space="preserve">identical units (blank = 1)</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -3525,12 +3529,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnetising current %</t>
+          <t xml:space="preserve">No-load loss %</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">im_pct</t>
+          <t xml:space="preserve">nll_pct</t>
         </is>
       </c>
       <c r="D67" s="8"/>
@@ -3559,24 +3563,24 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rating MVA</t>
+          <t xml:space="preserve">Magnetising current %</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_mva</t>
+          <t xml:space="preserve">im_pct</t>
         </is>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -3593,24 +3597,24 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length</t>
+          <t xml:space="preserve">Rating MVA</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_length</t>
+          <t xml:space="preserve">rate_mva</t>
         </is>
       </c>
       <c r="D69" s="8"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3627,22 +3631,26 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length unit</t>
+          <t xml:space="preserve">Tie length</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_unit</t>
+          <t xml:space="preserve">tie_length</t>
         </is>
       </c>
       <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G70" s="8"/>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+        </is>
+      </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3657,22 +3665,22 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie R per length</t>
+          <t xml:space="preserve">Tie length unit</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_r_per</t>
+          <t xml:space="preserve">tie_unit</t>
         </is>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
+      <c r="G71" s="8"/>
       <c r="H71" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3687,12 +3695,12 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie X per length</t>
+          <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_per</t>
+          <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
       <c r="D72" s="8"/>
@@ -3717,12 +3725,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie B per length</t>
+          <t xml:space="preserve">Tie X per length</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_per</t>
+          <t xml:space="preserve">tie_x_per</t>
         </is>
       </c>
       <c r="D73" s="8"/>
@@ -3730,7 +3738,7 @@
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -3747,128 +3755,124 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie rating MVA</t>
+          <t xml:space="preserve">Tie B per length</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_rate_mva</t>
+          <t xml:space="preserve">tie_b_per</t>
         </is>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uS</t>
+        </is>
+      </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+    <row r="75" ht="17.0" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tie rating MVA</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_rate_mva</t>
+        </is>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-    </row>
-    <row r="76" ht="17.0" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+    </row>
+    <row r="77" ht="17.0" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
-        </is>
-      </c>
-      <c r="H76" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30.0" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F77" s="8"/>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
+        </is>
+      </c>
+      <c r="H77" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30.0" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
-        </is>
-      </c>
-      <c r="H77" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="17.0" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -3885,20 +3889,24 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F79" s="8"/>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
@@ -3915,12 +3923,12 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D80" s="8"/>
@@ -3928,7 +3936,7 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number of units</t>
+          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -3945,24 +3953,20 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit MVA</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_mva</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D81" s="8"/>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from P and Q</t>
-        </is>
-      </c>
+      <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+          <t xml:space="preserve">number of units</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -3979,18 +3983,26 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmax MW</t>
+          <t xml:space="preserve">Unit MVA</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmax_mw</t>
+          <t xml:space="preserve">unit_mva</t>
         </is>
       </c>
       <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from P and Q</t>
+        </is>
+      </c>
       <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+        </is>
+      </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4005,26 +4017,18 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmin MW</t>
+          <t xml:space="preserve">Unit Pmax MW</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmin_mw</t>
+          <t xml:space="preserve">unit_pmax_mw</t>
         </is>
       </c>
       <c r="D83" s="8"/>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
+      <c r="E83" s="8"/>
       <c r="F83" s="8"/>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
-        </is>
-      </c>
+      <c r="G83" s="8"/>
       <c r="H83" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4039,24 +4043,24 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmax MVAr</t>
+          <t xml:space="preserve">Unit Pmin MW</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmax_mvar</t>
+          <t xml:space="preserve">unit_pmin_mw</t>
         </is>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Unit PF</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F84" s="8"/>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = from Unit PF</t>
+          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -4073,24 +4077,24 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmin MVAr</t>
+          <t xml:space="preserve">Unit Qmax MVAr</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmin_mvar</t>
+          <t xml:space="preserve">unit_qmax_mvar</t>
         </is>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Qmax</t>
+          <t xml:space="preserve">from Unit PF</t>
         </is>
       </c>
       <c r="F85" s="8"/>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = -Qmax</t>
+          <t xml:space="preserve">blank = from Unit PF</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4107,24 +4111,24 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit PF</t>
+          <t xml:space="preserve">Unit Qmin MVAr</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pf</t>
+          <t xml:space="preserve">unit_qmin_mvar</t>
         </is>
       </c>
       <c r="D86" s="8"/>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95</t>
+          <t xml:space="preserve">-Qmax</t>
         </is>
       </c>
       <c r="F86" s="8"/>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
+          <t xml:space="preserve">blank = -Qmax</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
@@ -4141,24 +4145,24 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminal kV</t>
+          <t xml:space="preserve">Unit PF</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kv</t>
+          <t xml:space="preserve">unit_pf</t>
         </is>
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">0.95</t>
         </is>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = GSU LV kV</t>
+          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4167,7 +4171,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="30.0" customHeight="1">
+    <row r="88" ht="17.0" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4175,58 +4179,58 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispatch MW</t>
+          <t xml:space="preserve">Terminal kV</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dispatch_mw</t>
+          <t xml:space="preserve">kv</t>
         </is>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="F88" s="8"/>
       <c r="G88" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = GSU LV kV</t>
+        </is>
+      </c>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30.0" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dispatch MW</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dispatch_mw</t>
+        </is>
+      </c>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+        </is>
+      </c>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
-        </is>
-      </c>
-      <c r="H88" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="17.0" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q mode</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">q_mode</t>
-        </is>
-      </c>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share | fixed</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
@@ -4243,24 +4247,24 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Q mode</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_q_mvar</t>
+          <t xml:space="preserve">q_mode</t>
         </is>
       </c>
       <c r="D90" s="8"/>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">share | fixed</t>
+        </is>
+      </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
+          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4277,20 +4281,24 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed PF</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_pf</t>
+          <t xml:space="preserve">fixed_q_mvar</t>
         </is>
       </c>
       <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
       <c r="F91" s="8"/>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
+          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -4307,24 +4315,20 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU count</t>
+          <t xml:space="preserve">Fixed PF</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_count</t>
+          <t xml:space="preserve">fixed_pf</t>
         </is>
       </c>
       <c r="D92" s="8"/>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Units</t>
-        </is>
-      </c>
+      <c r="E92" s="8"/>
       <c r="F92" s="8"/>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = Units</t>
+          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
@@ -4333,7 +4337,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="30.0" customHeight="1">
+    <row r="93" ht="17.0" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4341,52 +4345,60 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU MVA</t>
+          <t xml:space="preserve">GSU count</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_mva</t>
+          <t xml:space="preserve">gsu_count</t>
         </is>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">no GSU (units on the MV bus</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = Units</t>
+        </is>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30.0" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSU MVA</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gsu_mva</t>
+        </is>
+      </c>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no GSU (units on the MV bus</t>
+        </is>
+      </c>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
         </is>
       </c>
-      <c r="H93" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="17.0" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GSU HV kV</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gsu_hv_kv</t>
-        </is>
-      </c>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
       <c r="H94" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4401,12 +4413,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">GSU HV kV</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_lv_kv</t>
+          <t xml:space="preserve">gsu_hv_kv</t>
         </is>
       </c>
       <c r="D95" s="8"/>
@@ -4427,22 +4439,18 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU Z %</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_z_pct</t>
+          <t xml:space="preserve">gsu_lv_kv</t>
         </is>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">on GSU MVA</t>
-        </is>
-      </c>
+      <c r="G96" s="8"/>
       <c r="H96" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4457,18 +4465,22 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU X/R</t>
+          <t xml:space="preserve">GSU Z %</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_x_r</t>
+          <t xml:space="preserve">gsu_z_pct</t>
         </is>
       </c>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on GSU MVA</t>
+        </is>
+      </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4483,12 +4495,12 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU vector group</t>
+          <t xml:space="preserve">GSU X/R</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_vector</t>
+          <t xml:space="preserve">gsu_x_r</t>
         </is>
       </c>
       <c r="D98" s="8"/>
@@ -4509,26 +4521,18 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV tap</t>
+          <t xml:space="preserve">GSU vector group</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_tap</t>
+          <t xml:space="preserve">gsu_vector</t>
         </is>
       </c>
       <c r="D99" s="8"/>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E99" s="8"/>
       <c r="F99" s="8"/>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 1</t>
-        </is>
-      </c>
+      <c r="G99" s="8"/>
       <c r="H99" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4543,24 +4547,24 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">GSU HV tap</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">gsu_tap</t>
         </is>
       </c>
       <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
-        </is>
-      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F100" s="8"/>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H100" s="13" t="inlineStr">
@@ -4577,20 +4581,24 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector R</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_r</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
+        </is>
+      </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT</t>
+          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
@@ -4607,12 +4615,12 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector X</t>
+          <t xml:space="preserve">Collector R</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_x</t>
+          <t xml:space="preserve">coll_r</t>
         </is>
       </c>
       <c r="D102" s="8"/>
@@ -4637,12 +4645,12 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector B</t>
+          <t xml:space="preserve">Collector X</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_b</t>
+          <t xml:space="preserve">coll_x</t>
         </is>
       </c>
       <c r="D103" s="8"/>
@@ -4650,7 +4658,7 @@
       <c r="F103" s="8"/>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT, total charging</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
@@ -4667,24 +4675,20 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector units</t>
+          <t xml:space="preserve">Collector B</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_units</t>
+          <t xml:space="preserve">coll_b</t>
         </is>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu | ohm</t>
-        </is>
-      </c>
+      <c r="F104" s="8"/>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
+          <t xml:space="preserve">EQUIVALENT, total charging</t>
         </is>
       </c>
       <c r="H104" s="13" t="inlineStr">
@@ -4701,25 +4705,29 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZSORCE X pu</t>
+          <t xml:space="preserve">Collector units</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zsorce_x</t>
+          <t xml:space="preserve">coll_units</t>
         </is>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu | ohm</t>
+        </is>
+      </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
         </is>
       </c>
       <c r="H105" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4731,12 +4739,12 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WMOD</t>
+          <t xml:space="preserve">ZSORCE X pu</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wmod</t>
+          <t xml:space="preserve">zsorce_x</t>
         </is>
       </c>
       <c r="D106" s="8"/>
@@ -4744,84 +4752,80 @@
       <c r="F106" s="8"/>
       <c r="G106" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+        </is>
+      </c>
+      <c r="H106" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="17.0" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WMOD</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wmod</t>
+        </is>
+      </c>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
         </is>
       </c>
-      <c r="H106" s="13" t="inlineStr">
+      <c r="H107" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="30.0" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+    <row r="108" ht="30.0" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B107" s="12" t="inlineStr">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Electrical control</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">reec</t>
-        </is>
-      </c>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
-        </is>
-      </c>
-      <c r="F107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
-        </is>
-      </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
-        </is>
-      </c>
-      <c r="H107" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="17.0" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B108" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD library</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_library</t>
         </is>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
-      <c r="F108" s="8"/>
+          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
+        </is>
+      </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
+          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
       <c r="H108" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
@@ -4833,24 +4837,24 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD definition</t>
+          <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_definition</t>
+          <t xml:space="preserve">pscad_library</t>
         </is>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a source: network check</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F109" s="8"/>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
+          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
@@ -4867,24 +4871,24 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD AC port</t>
+          <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_ac_port</t>
+          <t xml:space="preserve">pscad_definition</t>
         </is>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its 3-phase port</t>
+          <t xml:space="preserve">a source: network check</t>
         </is>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
       <c r="H110" s="13" t="inlineStr">
@@ -4893,7 +4897,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="30.0" customHeight="1">
+    <row r="111" ht="17.0" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4901,79 +4905,83 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD inverter at</t>
+          <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_inv_at</t>
+          <t xml:space="preserve">pscad_ac_port</t>
         </is>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">its 3-phase port</t>
+        </is>
+      </c>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+        </is>
+      </c>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30.0" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD inverter at</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_inv_at</t>
+        </is>
+      </c>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">LV</t>
         </is>
       </c>
-      <c r="F111" s="8" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV | MV</t>
         </is>
       </c>
-      <c r="G111" s="8" t="inlineStr">
+      <c r="G112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
       </c>
-      <c r="H111" s="13" t="inlineStr">
+      <c r="H112" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-    </row>
-    <row r="113" ht="17.0" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collector</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collector</t>
-        </is>
-      </c>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
-        </is>
-      </c>
-      <c r="H113" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
     </row>
     <row r="114" ht="17.0" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
@@ -4983,12 +4991,12 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeder</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">feeder</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D114" s="8"/>
@@ -4996,7 +5004,7 @@
       <c r="F114" s="8"/>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">feeder name</t>
+          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
         </is>
       </c>
       <c r="H114" s="13" t="inlineStr">
@@ -5013,24 +5021,20 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copies</t>
+          <t xml:space="preserve">Feeder</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">copies</t>
+          <t xml:space="preserve">feeder</t>
         </is>
       </c>
       <c r="D115" s="8"/>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E115" s="8"/>
       <c r="F115" s="8"/>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
+          <t xml:space="preserve">feeder name</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
@@ -5047,20 +5051,24 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section</t>
+          <t xml:space="preserve">Copies</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">section</t>
+          <t xml:space="preserve">copies</t>
         </is>
       </c>
       <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F116" s="8"/>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+          <t xml:space="preserve">identical feeders (blank = 1)</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
@@ -5069,7 +5077,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="30.0" customHeight="1">
+    <row r="117" ht="17.0" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5077,24 +5085,20 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">From section</t>
+          <t xml:space="preserve">Section</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_section</t>
+          <t xml:space="preserve">section</t>
         </is>
       </c>
       <c r="D117" s="8"/>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the one before (daisy chain</t>
-        </is>
-      </c>
+      <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
@@ -5103,7 +5107,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="17.0" customHeight="1">
+    <row r="118" ht="30.0" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5111,20 +5115,24 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">From section</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">from_section</t>
         </is>
       </c>
       <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the one before (daisy chain</t>
+        </is>
+      </c>
       <c r="F118" s="8"/>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Cables</t>
+          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
@@ -5141,18 +5149,22 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">length</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
-      <c r="G119" s="8"/>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from Cables</t>
+        </is>
+      </c>
       <c r="H119" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5167,30 +5179,18 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">length</t>
         </is>
       </c>
       <c r="D120" s="8"/>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = km</t>
-        </is>
-      </c>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
       <c r="H120" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5205,20 +5205,28 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units at end</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units tapped at the far end</t>
+          <t xml:space="preserve">blank = km</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
@@ -5235,12 +5243,12 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units of</t>
+          <t xml:space="preserve">Units at end</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units_of</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D122" s="8"/>
@@ -5248,7 +5256,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
+          <t xml:space="preserve">units tapped at the far end</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
@@ -5265,75 +5273,75 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel cables</t>
+          <t xml:space="preserve">Units of</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parallel</t>
+          <t xml:space="preserve">units_of</t>
         </is>
       </c>
       <c r="D123" s="8"/>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E123" s="8"/>
       <c r="F123" s="8"/>
       <c r="G123" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="17.0" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parallel cables</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parallel</t>
+        </is>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F124" s="8"/>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
-      <c r="H123" s="13" t="inlineStr">
+      <c r="H124" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-    </row>
-    <row r="125" ht="17.0" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cable</t>
-        </is>
-      </c>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cable type</t>
-        </is>
-      </c>
-      <c r="H125" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
     </row>
     <row r="126" ht="17.0" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
@@ -5343,24 +5351,20 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
-      <c r="F126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+      <c r="F126" s="8"/>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per</t>
+          <t xml:space="preserve">cable type</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
@@ -5377,20 +5381,24 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R per length</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_per</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
+          <t xml:space="preserve">the values are per</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
@@ -5407,12 +5415,12 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D128" s="8"/>
@@ -5420,7 +5428,7 @@
       <c r="F128" s="8"/>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
@@ -5437,12 +5445,12 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">X per length</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">x_per</t>
         </is>
       </c>
       <c r="D129" s="8"/>
@@ -5450,7 +5458,7 @@
       <c r="F129" s="8"/>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -5467,12 +5475,12 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">C per length</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">c_per</t>
         </is>
       </c>
       <c r="D130" s="8"/>
@@ -5480,58 +5488,58 @@
       <c r="F130" s="8"/>
       <c r="G130" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">uF</t>
+        </is>
+      </c>
+      <c r="H130" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="17.0" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B per length</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b_per</t>
+        </is>
+      </c>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">uS, instead of C</t>
         </is>
       </c>
-      <c r="H130" s="13" t="inlineStr">
+      <c r="H131" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Collectors</t>
         </is>
       </c>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-    </row>
-    <row r="132" ht="17.0" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B132" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
-        </is>
-      </c>
-      <c r="H132" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
     </row>
     <row r="133" ht="17.0" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
@@ -5541,12 +5549,12 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D133" s="8"/>
@@ -5554,62 +5562,58 @@
       <c r="F133" s="8"/>
       <c r="G133" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="17.0" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collectors</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connect to</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">connect</t>
+        </is>
+      </c>
+      <c r="D134" s="8"/>
+      <c r="E134" s="8"/>
+      <c r="F134" s="8"/>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
-      <c r="H133" s="13" t="inlineStr">
+      <c r="H134" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-    </row>
-    <row r="135" ht="17.0" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loads_Shunts</t>
-        </is>
-      </c>
-      <c r="B135" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kind</t>
-        </is>
-      </c>
-      <c r="C135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
-        </is>
-      </c>
-      <c r="H135" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B135" s="7"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
     </row>
     <row r="136" ht="17.0" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
@@ -5619,20 +5623,24 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">At bus</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -5649,12 +5657,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mw</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D137" s="8"/>
@@ -5662,7 +5670,7 @@
       <c r="F137" s="8"/>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
@@ -5679,12 +5687,12 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">MW</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">mw</t>
         </is>
       </c>
       <c r="D138" s="8"/>
@@ -5692,7 +5700,7 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
@@ -5709,67 +5717,67 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">mvar</t>
         </is>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
-      <c r="G139" s="8"/>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+        </is>
+      </c>
       <c r="H139" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
+    <row r="140" ht="17.0" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="8"/>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
-    </row>
-    <row r="141" ht="17.0" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B141" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus</t>
-        </is>
-      </c>
-      <c r="C141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bus</t>
-        </is>
-      </c>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
-        </is>
-      </c>
-      <c r="H141" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="7"/>
+      <c r="H141" s="7"/>
     </row>
     <row r="142" ht="17.0" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
@@ -5779,24 +5787,20 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">Bus</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">bus</t>
         </is>
       </c>
       <c r="D142" s="8"/>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic</t>
-        </is>
-      </c>
+      <c r="E142" s="8"/>
       <c r="F142" s="8"/>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -5805,7 +5809,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="30.0" customHeight="1">
+    <row r="143" ht="17.0" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
@@ -5813,90 +5817,94 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Number</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
+          <t xml:space="preserve">automatic</t>
         </is>
       </c>
       <c r="F143" s="8"/>
       <c r="G143" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = automatic</t>
+        </is>
+      </c>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="30.0" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
+      <c r="F144" s="8"/>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = automatic (12 characters at most)</t>
         </is>
       </c>
-      <c r="H143" s="13" t="inlineStr">
+      <c r="H144" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B144" s="7"/>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
-      <c r="G144" s="7"/>
-      <c r="H144" s="7"/>
-    </row>
-    <row r="145" ht="17.0" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
+    </row>
+    <row r="146" ht="17.0" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B145" s="12" t="inlineStr">
+      <c r="B146" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Generator</t>
         </is>
       </c>
-      <c r="C145" s="8" t="inlineStr">
+      <c r="C146" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
-        </is>
-      </c>
-      <c r="H145" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="30.0" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B146" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Model</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D146" s="8"/>
@@ -5904,7 +5912,7 @@
       <c r="F146" s="8"/>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
         </is>
       </c>
       <c r="H146" s="13" t="inlineStr">
@@ -5913,7 +5921,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="17.0" customHeight="1">
+    <row r="147" ht="30.0" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
@@ -5921,12 +5929,12 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Model</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D147" s="8"/>
@@ -5934,7 +5942,7 @@
       <c r="F147" s="8"/>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -5951,71 +5959,67 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
-      <c r="G148" s="8"/>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+        </is>
+      </c>
       <c r="H148" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
+    <row r="149" ht="17.0" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D149" s="8"/>
+      <c r="E149" s="8"/>
+      <c r="F149" s="8"/>
+      <c r="G149" s="8"/>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
-      <c r="B149" s="7"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="7"/>
-    </row>
-    <row r="150" ht="17.0" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B150" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generator</t>
-        </is>
-      </c>
-      <c r="C150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the plant</t>
-        </is>
-      </c>
-      <c r="F150" s="8"/>
-      <c r="G150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = the plant</t>
-        </is>
-      </c>
-      <c r="H150" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
+      <c r="B150" s="7"/>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
     </row>
     <row r="151" ht="17.0" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
@@ -6025,67 +6029,75 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">record</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the plant</t>
+        </is>
+      </c>
       <c r="F151" s="8"/>
       <c r="G151" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = the plant</t>
+        </is>
+      </c>
+      <c r="H151" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="17.0" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Record</t>
+        </is>
+      </c>
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">record</t>
+        </is>
+      </c>
+      <c r="D152" s="8"/>
+      <c r="E152" s="8"/>
+      <c r="F152" s="8"/>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
         </is>
       </c>
-      <c r="H151" s="13" t="inlineStr">
+      <c r="H152" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B152" s="7"/>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-      <c r="G152" s="7"/>
-      <c r="H152" s="7"/>
-    </row>
-    <row r="153" ht="17.0" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B153" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generator</t>
-        </is>
-      </c>
-      <c r="C153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D153" s="8"/>
-      <c r="E153" s="8"/>
-      <c r="F153" s="8"/>
-      <c r="G153" s="8"/>
-      <c r="H153" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
     </row>
     <row r="154" ht="17.0" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
@@ -6095,22 +6107,18 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
-      <c r="G154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
-        </is>
-      </c>
+      <c r="G154" s="8"/>
       <c r="H154" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
@@ -6125,12 +6133,12 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D155" s="8"/>
@@ -6138,52 +6146,64 @@
       <c r="F155" s="8"/>
       <c r="G155" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H155" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="17.0" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="8"/>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
         </is>
       </c>
-      <c r="H155" s="13" t="inlineStr">
+      <c r="H156" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
         </is>
       </c>
-      <c r="B156" s="7"/>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
-      <c r="G156" s="7"/>
-      <c r="H156" s="7"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="8"/>
-      <c r="B157" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
-      <c r="F157" s="8"/>
-      <c r="G157" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H157" s="8"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7"/>
     </row>
     <row r="158">
       <c r="A158" s="8"/>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C158" s="8"/>
@@ -6192,7 +6212,7 @@
       <c r="F158" s="8"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the point of interconnection</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H158" s="8"/>
@@ -6201,7 +6221,7 @@
       <c r="A159" s="8"/>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C159" s="8"/>
@@ -6210,7 +6230,7 @@
       <c r="F159" s="8"/>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H159" s="8"/>
@@ -6219,7 +6239,7 @@
       <c r="A160" s="8"/>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C160" s="8"/>
@@ -6228,7 +6248,7 @@
       <c r="F160" s="8"/>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
         </is>
       </c>
       <c r="H160" s="8"/>
@@ -6237,7 +6257,7 @@
       <c r="A161" s="8"/>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C161" s="8"/>
@@ -6246,7 +6266,7 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+          <t xml:space="preserve">an MPT's LV winding</t>
         </is>
       </c>
       <c r="H161" s="8"/>
@@ -6255,7 +6275,7 @@
       <c r="A162" s="8"/>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C162" s="8"/>
@@ -6264,7 +6284,7 @@
       <c r="F162" s="8"/>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
         </is>
       </c>
       <c r="H162" s="8"/>
@@ -6273,7 +6293,7 @@
       <c r="A163" s="8"/>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C163" s="8"/>
@@ -6282,7 +6302,7 @@
       <c r="F163" s="8"/>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
         </is>
       </c>
       <c r="H163" s="8"/>
@@ -6291,7 +6311,7 @@
       <c r="A164" s="8"/>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C164" s="8"/>
@@ -6300,7 +6320,7 @@
       <c r="F164" s="8"/>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H164" s="8"/>
@@ -6309,7 +6329,7 @@
       <c r="A165" s="8"/>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C165" s="8"/>
@@ -6318,7 +6338,7 @@
       <c r="F165" s="8"/>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H165" s="8"/>
@@ -6327,7 +6347,7 @@
       <c r="A166" s="8"/>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
         </is>
       </c>
       <c r="C166" s="8"/>
@@ -6336,7 +6356,7 @@
       <c r="F166" s="8"/>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">a generator's terminal</t>
         </is>
       </c>
       <c r="H166" s="8"/>
@@ -6345,7 +6365,7 @@
       <c r="A167" s="8"/>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C167" s="8"/>
@@ -6354,50 +6374,42 @@
       <c r="F167" s="8"/>
       <c r="G167" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H167" s="8"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="8"/>
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+        </is>
+      </c>
+      <c r="C168" s="8"/>
+      <c r="D168" s="8"/>
+      <c r="E168" s="8"/>
+      <c r="F168" s="8"/>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
         </is>
       </c>
-      <c r="H167" s="8"/>
-    </row>
-    <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="7" t="inlineStr">
+      <c r="H168" s="8"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
         </is>
       </c>
-      <c r="B168" s="7"/>
-      <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
-      <c r="G168" s="7"/>
-      <c r="H168" s="7"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B169" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{UNITS}</t>
-        </is>
-      </c>
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
-      <c r="F169" s="8"/>
-      <c r="G169" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H169" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="7"/>
+      <c r="H169" s="7"/>
     </row>
     <row r="170">
       <c r="A170" s="8" t="inlineStr">
@@ -6407,7 +6419,7 @@
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C170" s="8"/>
@@ -6416,7 +6428,7 @@
       <c r="F170" s="8"/>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H170" s="13" t="inlineStr">
@@ -6433,7 +6445,7 @@
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_MW}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C171" s="8"/>
@@ -6442,7 +6454,7 @@
       <c r="F171" s="8"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
@@ -6459,7 +6471,7 @@
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C172" s="8"/>
@@ -6468,7 +6480,7 @@
       <c r="F172" s="8"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
@@ -6485,7 +6497,7 @@
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C173" s="8"/>
@@ -6494,7 +6506,7 @@
       <c r="F173" s="8"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H173" s="13" t="inlineStr">
@@ -6511,7 +6523,7 @@
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C174" s="8"/>
@@ -6520,7 +6532,7 @@
       <c r="F174" s="8"/>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H174" s="13" t="inlineStr">
@@ -6537,7 +6549,7 @@
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C175" s="8"/>
@@ -6546,7 +6558,7 @@
       <c r="F175" s="8"/>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H175" s="13" t="inlineStr">
@@ -6563,7 +6575,7 @@
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C176" s="8"/>
@@ -6572,7 +6584,7 @@
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H176" s="13" t="inlineStr">
@@ -6589,7 +6601,7 @@
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C177" s="8"/>
@@ -6598,7 +6610,7 @@
       <c r="F177" s="8"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -6615,7 +6627,7 @@
       </c>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C178" s="8"/>
@@ -6624,7 +6636,7 @@
       <c r="F178" s="8"/>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H178" s="13" t="inlineStr">
@@ -6641,7 +6653,7 @@
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C179" s="8"/>
@@ -6650,7 +6662,7 @@
       <c r="F179" s="8"/>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H179" s="13" t="inlineStr">
@@ -6667,7 +6679,7 @@
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C180" s="8"/>
@@ -6676,7 +6688,7 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -6693,7 +6705,7 @@
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -6702,7 +6714,7 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H181" s="13" t="inlineStr">
@@ -6719,7 +6731,7 @@
       </c>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C182" s="8"/>
@@ -6728,7 +6740,7 @@
       <c r="F182" s="8"/>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H182" s="13" t="inlineStr">
@@ -6745,7 +6757,7 @@
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -6754,7 +6766,7 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">frequency (Hz)</t>
         </is>
       </c>
       <c r="H183" s="13" t="inlineStr">
@@ -6771,7 +6783,7 @@
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{P_INV_MW}</t>
         </is>
       </c>
       <c r="C184" s="8"/>
@@ -6780,7 +6792,7 @@
       <c r="F184" s="8"/>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
@@ -6797,7 +6809,7 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -6806,10 +6818,36 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H185" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B186" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C186" s="8"/>
+      <c r="D186" s="8"/>
+      <c r="E186" s="8"/>
+      <c r="F186" s="8"/>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H185" s="13" t="inlineStr">
+      <c r="H186" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -6820,32 +6858,32 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A112:H112"/>
-    <mergeCell ref="A124:H124"/>
-    <mergeCell ref="A131:H131"/>
-    <mergeCell ref="A134:H134"/>
-    <mergeCell ref="A140:H140"/>
-    <mergeCell ref="A144:H144"/>
-    <mergeCell ref="A149:H149"/>
-    <mergeCell ref="A152:H152"/>
-    <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A168:H168"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A113:H113"/>
+    <mergeCell ref="A125:H125"/>
+    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A135:H135"/>
+    <mergeCell ref="A141:H141"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A153:H153"/>
+    <mergeCell ref="A157:H157"/>
+    <mergeCell ref="A169:H169"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
-    <hyperlink ref="A47" location="'MPT'!A1" display="MPT"/>
-    <hyperlink ref="A75" location="'Generators'!A1" display="Generators"/>
-    <hyperlink ref="A112" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A124" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A131" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A134" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A140" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A144" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A149" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A152" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A168" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A48" location="'MPT'!A1" display="MPT"/>
+    <hyperlink ref="A76" location="'Generators'!A1" display="Generators"/>
+    <hyperlink ref="A113" location="'Feeders'!A1" display="Feeders"/>
+    <hyperlink ref="A125" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A132" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A135" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A141" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A145" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A150" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A153" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A169" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -18521,69 +18559,73 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="44" ht="43.0" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD lines as</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI | RLC</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD FAULT AT THE POI</t>
         </is>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="45" ht="30.0" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" ht="30.0" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault at POI</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">YES</t>
         </is>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
-        </is>
-      </c>
-      <c r="G45" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="17.0" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault time</t>
-        </is>
-      </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100: none in the run</t>
-        </is>
-      </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
@@ -18595,12 +18637,10 @@
     <row r="47" ht="17.0" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault duration</t>
-        </is>
-      </c>
-      <c r="B47" s="3">
-        <v>0.15</v>
-      </c>
+          <t xml:space="preserve">PSCAD fault time</t>
+        </is>
+      </c>
+      <c r="B47" s="3"/>
       <c r="C47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">s</t>
@@ -18608,114 +18648,145 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
+          <t xml:space="preserve">100: none in the run</t>
         </is>
       </c>
       <c r="E47" s="8"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17.0" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault duration</t>
+        </is>
+      </c>
+      <c r="B48" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
+      <c r="E48" s="8"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 0.15</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="43.0" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="49" ht="43.0" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault type</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="C49" s="8"/>
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="17.0" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="50" ht="17.0" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault resistance</t>
         </is>
       </c>
-      <c r="B49" s="3">
+      <c r="B50" s="3">
         <v>0.01</v>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">0.01</t>
         </is>
       </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="E50" s="8"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 0.01</t>
         </is>
       </c>
-      <c r="G49" s="13" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD LIBRARIES</t>
         </is>
       </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-    </row>
-    <row r="51" ht="17.0" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+    </row>
+    <row r="52" ht="17.0" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD libraries</t>
         </is>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="B52" s="3"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -18729,10 +18800,10 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A51:G51"/>
   </mergeCells>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4">
       <formula1>"SMIB,DETAILED"</formula1>
     </dataValidation>
@@ -18751,10 +18822,13 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B43">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B45">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B44">
+      <formula1>"PI,RLC"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B46">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B48">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B49">
       <formula1>"ABCG,ABC,AG,BG,CG,ABG,BCG,ACG,AB,BC,AC"</formula1>
     </dataValidation>
   </dataValidations>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -10,12 +10,13 @@
     <sheet name="Cables" sheetId="6" r:id="rId6"/>
     <sheet name="Collectors" sheetId="7" r:id="rId7"/>
     <sheet name="Loads_Shunts" sheetId="8" r:id="rId8"/>
-    <sheet name="Bus_Numbers" sheetId="9" r:id="rId9"/>
-    <sheet name="Dyr_Params" sheetId="10" r:id="rId10"/>
-    <sheet name="Dyr_Records" sheetId="11" r:id="rId11"/>
-    <sheet name="PSCAD_Params" sheetId="12" r:id="rId12"/>
-    <sheet name="Input_Reference" sheetId="13" r:id="rId13"/>
-    <sheet name="Dynamic_Models" sheetId="14" r:id="rId14"/>
+    <sheet name="Machines" sheetId="9" r:id="rId9"/>
+    <sheet name="Bus_Numbers" sheetId="10" r:id="rId10"/>
+    <sheet name="Dyr_Params" sheetId="11" r:id="rId11"/>
+    <sheet name="Dyr_Records" sheetId="12" r:id="rId12"/>
+    <sheet name="PSCAD_Params" sheetId="13" r:id="rId13"/>
+    <sheet name="Input_Reference" sheetId="14" r:id="rId14"/>
+    <sheet name="Dynamic_Models" sheetId="15" r:id="rId15"/>
   </sheets>
 </workbook>
 </file>
@@ -420,12 +421,12 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bus numbers and names of your own (blank = automatic)</t>
+          <t xml:space="preserve">DETAILED: each machine's own Pgen, P and Q limits, MBASE and ID</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -437,12 +438,12 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">any dynamic model parameter, by generator, model and name</t>
+          <t xml:space="preserve">bus numbers and names of your own (blank = automatic)</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -454,12 +455,12 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">.dyr records of your own (vendor models)</t>
+          <t xml:space="preserve">any dynamic model parameter, by generator, model and name</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -471,12 +472,12 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the vendor PSCAD model's parameters, by generator</t>
+          <t xml:space="preserve">.dyr records of your own (vendor models)</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -488,320 +489,349 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Input_Reference</t>
+          <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">every input: what it is, its unit, the default when blank, the choices, which model uses it</t>
+          <t xml:space="preserve">the vendor PSCAD model's parameters, by generator</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference</t>
+          <t xml:space="preserve">input</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Input_Reference</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">every input: what it is, its unit, the default when blank, the choices, which model uses it</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Dynamic_Models</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">every dynamic model's parameters: position, default and meaning</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">reference</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="25"/>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">COLOURS</t>
         </is>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">your inputs</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">note</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">what to enter, the default when blank</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Column</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">column titles</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">SECTION</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">a group of items</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">which model an input goes into</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="32"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">GUIDE</t>
         </is>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-    </row>
-    <row r="33" ht="17.0" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+    </row>
+    <row r="34" ht="17.0" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">SMIB INPUT</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Fill in the sheets, save, then run:   python smib_build.py &lt;this workbook&gt;.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="43.0" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It writes the PSS/E model (.raw rev 33 and .dyr; with PSS/E found, a solved .sav and a flat-run check) and the PSCAD build script (run it where PSCAD 5 and its Python automation library mhi.pscad are: it builds the .pscx), with a report of every equivalent, the load flow and anything to check.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30.0" customHeight="1">
+    <row r="35" ht="43.0" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">It writes the PSS/E model (.raw rev 33 and .dyr; with PSS/E found, a solved .sav and a flat-run check) and the PSCAD build script (run it where PSCAD 5 and its Python automation library mhi.pscad are: it builds the .pscx), with a report of every equivalent, the load flow and anything to check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30.0" customHeight="1">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Blank cells take the default in the column note (row 2 of each sheet). Any row whose first cell starts with # is skipped (row 2 is one).</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="56.0" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+    <row r="37" ht="56.0" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">BUSES</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Name a bus by its role: POI | HV (the gen-tie's end; the POI when there is no gen-tie) | &lt;MPT&gt; or &lt;MPT&gt;:LV | &lt;MPT&gt;:TV (3-winding) | &lt;MPT&gt;:HV (an MPT with a tie of its own) | &lt;shared collector&gt; (its far end) | &lt;generator&gt;:MV (GSU HV side) | &lt;generator&gt; or &lt;generator&gt;:LV (terminal) | IB (infinite bus). Numbers are automatic from First bus number; Bus_Numbers sets any one.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30.0" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="38" ht="30.0" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Bases, the POI, the grid (SCR and X/R, or short-circuit MVA, or R/X), the gen-tie, the operating point, the plant controller and the PSCAD run settings.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="56.0" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="39" ht="56.0" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">MODEL TYPE</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant: Model type sets PSS/E and PSCAD alike. SMIB (default): each generator is one machine behind one GSU on a collector equivalent of its own (WECC, each feeder weighed by its MW) from its MPT winding. DETAILED: every feeder section is a branch (identical feeder copies lumped), the units of a generator at each node a machine of their own behind their own GSU; a generator's Dyr_Params, Dyr_Records and PSCAD_Params rows apply to all its machines.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="43.0" customHeight="1">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control mode Q: the plant holds the POI voltage with Q at POI into the grid; PF: with that power factor; V: the plant holds the POI voltage with the infinite bus at Grid voltage. The infinite-bus voltage (and the generators' Q) come out of the load flow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="56.0" customHeight="1">
+    <row r="40" ht="43.0" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control mode Q: the plant holds the POI voltage with Q at POI into the grid; PF: with that power factor; V: the plant holds the POI voltage with the infinite bus at Grid voltage. The infinite-bus voltage (and the generators' Q) come out of the load flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="56.0" customHeight="1">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Plant controller (PSS/E .dyr): REPC_A = a REPCA1 on each generator, each holding the POI; REPC_B = one controller for the whole plant (hybrid PV + BESS): PLNTBU1 at the POI, and on each generator a REAX4BU1 that takes its share of the plant's Q (Qmax / sum of Qmax) and P (Pmax / sum of Pmax). REGC_A / REPC_A records: standard = REGCA1 / REPCA1 from the PSS/E library; USRMDL = REGCAU1 / REPCAU1.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="42" ht="30.0" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">One row per main power transformer; HV winding first. Three windings: TV kV, the three impedances and their bases. Parallel units: identical units in parallel. Tie: a line of its own from HV to it.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="82.0" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+    <row r="43" ht="82.0" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">One row per generator (PV, BESS, wind, synchronous ...): the units (count and one unit's data; the model is their aggregate), its GSU (one GSU's data and the count), its collector (FEEDERS: the WECC equivalent of its rows in Feeders; EQUIVALENT: R X B given; NONE), how it shares the POI's Q, its electrical control model in the .dyr (REEC_A: REECA1, PV and wind; REEC_C: REECCU1, BESS; REEC_D: REECDU1, PV, BESS and WT4) and its PSCAD model (vendor library and definition, or blank for a voltage source at the solved terminal voltage: a network check against PSS/E) and where the inverter connects (LV or MV side of the GSU).</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="56.0" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="44" ht="56.0" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">The collector feeders section by section from the collector bus out: cable, length and the units tapped at the section's far end. A daisy chain needs no From section; a lateral names the section it leaves from (its far end); 0 = straight from the collector bus. Copies: identical feeders. WECC equivalent: Zeq = sum(Zi Wi^2) / W^2, Beq = sum(Bi), Wi = MW of the units downstream of section i.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="17.0" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+    <row r="45" ht="17.0" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Cable data per length (R, X in ohm; C in uF or B in uS) and the length unit they are per.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30.0" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collector systems shared by more than one generator: name and the bus it starts from. Their Feeders rows say whose units each section carries (Units of); the generators on it Connect to its name.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30.0" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Collectors</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collector systems shared by more than one generator: name and the bus it starts from. Their Feeders rows say whose units each section carries (Units of); the generators on it Connect to its name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30.0" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Auxiliary loads (constant impedance, MW and MVAr at 1 pu) and shunts (MVAr at 1 pu: + capacitor, - reactor) on any bus.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="17.0" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="48" ht="56.0" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETAILED model only: a machine's own Pgen, Pmax, Pmin, Qmax, Qmin, fixed Q, MBASE and ID in place of its share of its generator's (the GUI's 'List the DETAILED machines' fills in their names and values). Scale up (GUI) or --scale: a test plant -- MPTs (copies of the first, with its generators), feeders per MPT, GSUs per feeder and inverters per GSU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17.0" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus numbers or names of your own, by role (the report lists every role and its number).</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="82.0" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="50" ht="82.0" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Any parameter of the WECC-approved generic models, by generator, model and PSS/E name or position (ICON2, CON14) -- IB for the infinite bus, PLANT for the plant controller. Inverters: REGCA1 (REGC_A) + REECA1 / REECCU1 / REECDU1 (REEC_A / C / D) + REPCA1 (REPC_A) or REAX4BU1 (with PLNTBU1, REPC_B); WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1; SYNC: GENROU SEXS TGOV1. REECCU1, REECDU1, PLNTBU1, REAX4BU1 (and REGCAU1, REPCAU1) are user models: the WECC user-model DLL must be loaded for the PSS/E check (ADDLIB_IDV / DLLS in the script). The report lists every model's parameters with the values used.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="43.0" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="51" ht="43.0" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Records of your own (vendor or user models), one per row, ending in /. {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} and {&lt;bus role&gt;} are filled in. Type USER generators have only these. Models in user DLLs: list the DLLs in DLLS in the script for the PSS/E check.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="69.0" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
+    <row r="52" ht="69.0" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Parameters of each generator's vendor PSCAD model (UDM), as PSCAD takes them. Filled in for each inverter it stands for (DETAILED: each node): {UNITS} units, {MVA} their MVA, {P_MW} {Q_MVAR} their P and Q where it connects, {P_PU} {Q_PU} on {MVA}, {UNIT_MVA} {UNIT_P_MW} {UNIT_Q_MVAR} one unit's, {V_PU} {V_KV} {KV} {ANGLE} the voltage there, its base and PSCAD angle, {P_INV_MW} {Q_INV_MVAR} {V_INV_PU} at the inverters' own terminals (a UDM on the MV side), {FREQ} -- e.g. Ninv = {UNITS}, Vt0 = {V_PU}.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="108.0" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
+    <row r="53" ht="108.0" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">The .pscx is built in the same run when PSCAD 5 and its Python library mhi.pscad (pip install mhi.pscad) are on the PC; otherwise run &lt;name&gt;_build_pscad.py where they are. The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and wire your UDM in its place (the report and the build log list every inverter node). PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn. It is drawn as a single-line diagram with wires, left to right from the grid; where PSCAD's R, L and C are single-phase, each is drawn three times between breakouts.</t>
         </is>
@@ -813,8 +843,8 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A11" location="'Plant'!A1" display="Plant"/>
@@ -824,12 +854,13 @@
     <hyperlink ref="A15" location="'Cables'!A1" display="Cables"/>
     <hyperlink ref="A16" location="'Collectors'!A1" display="Collectors"/>
     <hyperlink ref="A17" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A18" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A19" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A20" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A21" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A22" location="'Input_Reference'!A1" display="Input_Reference"/>
-    <hyperlink ref="A23" location="'Dynamic_Models'!A1" display="Dynamic_Models"/>
+    <hyperlink ref="A18" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A19" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A20" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A21" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A22" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A23" location="'Input_Reference'!A1" display="Input_Reference"/>
+    <hyperlink ref="A24" location="'Dynamic_Models'!A1" display="Dynamic_Models"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -837,6 +868,191 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52.0" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = automatic</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IB</t>
+        </is>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POI</t>
+        </is>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HV</t>
+        </is>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT1:LV</t>
+        </is>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PV:MV</t>
+        </is>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PV:LV</t>
+        </is>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS:MV</t>
+        </is>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BESS:LV</t>
+        </is>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
@@ -1044,7 +1260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
@@ -1174,7 +1390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
@@ -1351,7 +1567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
@@ -5768,7 +5984,7 @@
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B141" s="7"/>
@@ -5779,20 +5995,20 @@
       <c r="G141" s="7"/>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" ht="17.0" customHeight="1">
+    <row r="142" ht="30.0" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus</t>
+          <t xml:space="preserve">Machine</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bus</t>
+          <t xml:space="preserve">machine</t>
         </is>
       </c>
       <c r="D142" s="8"/>
@@ -5800,7 +6016,7 @@
       <c r="F142" s="8"/>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -5812,29 +6028,29 @@
     <row r="143" ht="17.0" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic</t>
+          <t xml:space="preserve">its generator's</t>
         </is>
       </c>
       <c r="F143" s="8"/>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr">
@@ -5846,29 +6062,29 @@
     <row r="144" ht="30.0" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F144" s="8"/>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
@@ -5877,198 +6093,238 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B145" s="7"/>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7"/>
-      <c r="G145" s="7"/>
-      <c r="H145" s="7"/>
+    <row r="145" ht="17.0" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pmax MW</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pmax_mw</t>
+        </is>
+      </c>
+      <c r="D145" s="8"/>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Pmax</t>
+        </is>
+      </c>
+      <c r="F145" s="8"/>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+        </is>
+      </c>
+      <c r="H145" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="17.0" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Pmin MW</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">pmin_mw</t>
         </is>
       </c>
       <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Pmin</t>
+        </is>
+      </c>
       <c r="F146" s="8"/>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
         </is>
       </c>
       <c r="H146" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="17.0" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Model</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">model</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Qmax</t>
+        </is>
+      </c>
       <c r="F147" s="8"/>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="148" ht="17.0" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Qmin MVAr</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">qmin_mvar</t>
         </is>
       </c>
       <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Qmin</t>
+        </is>
+      </c>
       <c r="F148" s="8"/>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="30.0" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">q_mvar</t>
         </is>
       </c>
       <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as its generator's Q mode</t>
+        </is>
+      </c>
       <c r="F149" s="8"/>
-      <c r="G149" s="8"/>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+        </is>
+      </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B150" s="7"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-      <c r="G150" s="7"/>
-      <c r="H150" s="7"/>
-    </row>
-    <row r="151" ht="17.0" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B151" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generator</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the plant</t>
-        </is>
-      </c>
-      <c r="F151" s="8"/>
-      <c r="G151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = the plant</t>
-        </is>
-      </c>
-      <c r="H151" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="17.0" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBASE MVA</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mbase_mva</t>
+        </is>
+      </c>
+      <c r="D150" s="8"/>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit MVA</t>
+        </is>
+      </c>
+      <c r="F150" s="8"/>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit MVA</t>
+        </is>
+      </c>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B151" s="7"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
     </row>
     <row r="152" ht="17.0" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record</t>
+          <t xml:space="preserve">Bus</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">record</t>
+          <t xml:space="preserve">bus</t>
         </is>
       </c>
       <c r="D152" s="8"/>
@@ -6076,99 +6332,111 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B153" s="7"/>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
-      <c r="H153" s="7"/>
-    </row>
-    <row r="154" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="17.0" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D153" s="8"/>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic</t>
+        </is>
+      </c>
+      <c r="F153" s="8"/>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = automatic</t>
+        </is>
+      </c>
+      <c r="H153" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="30.0" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
       <c r="F154" s="8"/>
-      <c r="G154" s="8"/>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
+        </is>
+      </c>
       <c r="H154" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="17.0" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B155" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parameter</t>
-        </is>
-      </c>
-      <c r="C155" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parameter</t>
-        </is>
-      </c>
-      <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
-      <c r="F155" s="8"/>
-      <c r="G155" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
-        </is>
-      </c>
-      <c r="H155" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B155" s="7"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
     </row>
     <row r="156" ht="17.0" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D156" s="8"/>
@@ -6176,214 +6444,298 @@
       <c r="F156" s="8"/>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
         </is>
       </c>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
-        </is>
-      </c>
-      <c r="B157" s="7"/>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-      <c r="G157" s="7"/>
-      <c r="H157" s="7"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="8"/>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30.0" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Model</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model</t>
+        </is>
+      </c>
+      <c r="D157" s="8"/>
+      <c r="E157" s="8"/>
+      <c r="F157" s="8"/>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+        </is>
+      </c>
+      <c r="H157" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="17.0" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C158" s="8"/>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H158" s="8"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="8"/>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+        </is>
+      </c>
+      <c r="H158" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="17.0" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI</t>
-        </is>
-      </c>
-      <c r="C159" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
-      <c r="G159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the point of interconnection</t>
-        </is>
-      </c>
-      <c r="H159" s="8"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="8"/>
-      <c r="B160" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HV</t>
-        </is>
-      </c>
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
-      <c r="F160" s="8"/>
-      <c r="G160" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
-        </is>
-      </c>
-      <c r="H160" s="8"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="8"/>
+      <c r="G159" s="8"/>
+      <c r="H159" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
+      <c r="B160" s="7"/>
+      <c r="C160" s="7"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+    </row>
+    <row r="161" ht="17.0" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
-        </is>
-      </c>
-      <c r="C161" s="8"/>
+          <t xml:space="preserve">Generator</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator</t>
+        </is>
+      </c>
       <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the plant</t>
+        </is>
+      </c>
       <c r="F161" s="8"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
-        </is>
-      </c>
-      <c r="H161" s="8"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="8"/>
+          <t xml:space="preserve">blank = the plant</t>
+        </is>
+      </c>
+      <c r="H161" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="17.0" customHeight="1">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
-        </is>
-      </c>
-      <c r="C162" s="8"/>
+          <t xml:space="preserve">Record</t>
+        </is>
+      </c>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">record</t>
+        </is>
+      </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
-        </is>
-      </c>
-      <c r="H162" s="8"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="8"/>
-      <c r="B163" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
-        </is>
-      </c>
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
-      <c r="G163" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
-        </is>
-      </c>
-      <c r="H163" s="8"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="8"/>
+          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
+        </is>
+      </c>
+      <c r="H162" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
+    </row>
+    <row r="164" ht="17.0" customHeight="1">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
-        </is>
-      </c>
-      <c r="C164" s="8"/>
+          <t xml:space="preserve">Generator</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator</t>
+        </is>
+      </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
-      <c r="G164" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a shared collector's far end</t>
-        </is>
-      </c>
-      <c r="H164" s="8"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="8"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="17.0" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
-        </is>
-      </c>
-      <c r="C165" s="8"/>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
-        </is>
-      </c>
-      <c r="H165" s="8"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="8"/>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H165" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="17.0" customHeight="1">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
-        </is>
-      </c>
-      <c r="C166" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
-        </is>
-      </c>
-      <c r="H166" s="8"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="8"/>
-      <c r="B167" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
-        </is>
-      </c>
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
-      <c r="F167" s="8"/>
-      <c r="G167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
-        </is>
-      </c>
-      <c r="H167" s="8"/>
+          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+        </is>
+      </c>
+      <c r="H166" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
+        </is>
+      </c>
+      <c r="B167" s="7"/>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
     </row>
     <row r="168">
       <c r="A168" s="8"/>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C168" s="8"/>
@@ -6392,34 +6744,34 @@
       <c r="F168" s="8"/>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H168" s="8"/>
     </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
-        </is>
-      </c>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
-      <c r="G169" s="7"/>
-      <c r="H169" s="7"/>
+    <row r="169">
+      <c r="A169" s="8"/>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POI</t>
+        </is>
+      </c>
+      <c r="C169" s="8"/>
+      <c r="D169" s="8"/>
+      <c r="E169" s="8"/>
+      <c r="F169" s="8"/>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the point of interconnection</t>
+        </is>
+      </c>
+      <c r="H169" s="8"/>
     </row>
     <row r="170">
-      <c r="A170" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A170" s="8"/>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNITS}</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C170" s="8"/>
@@ -6428,24 +6780,16 @@
       <c r="F170" s="8"/>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H170" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
+        </is>
+      </c>
+      <c r="H170" s="8"/>
     </row>
     <row r="171">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A171" s="8"/>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C171" s="8"/>
@@ -6454,24 +6798,16 @@
       <c r="F171" s="8"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
-        </is>
-      </c>
-      <c r="H171" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">an MPT's LV winding</t>
+        </is>
+      </c>
+      <c r="H171" s="8"/>
     </row>
     <row r="172">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A172" s="8"/>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_MW}</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C172" s="8"/>
@@ -6480,24 +6816,16 @@
       <c r="F172" s="8"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
-        </is>
-      </c>
-      <c r="H172" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+        </is>
+      </c>
+      <c r="H172" s="8"/>
     </row>
     <row r="173">
-      <c r="A173" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A173" s="8"/>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C173" s="8"/>
@@ -6506,24 +6834,16 @@
       <c r="F173" s="8"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
-        </is>
-      </c>
-      <c r="H173" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+        </is>
+      </c>
+      <c r="H173" s="8"/>
     </row>
     <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A174" s="8"/>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C174" s="8"/>
@@ -6532,24 +6852,16 @@
       <c r="F174" s="8"/>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
-        </is>
-      </c>
-      <c r="H174" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">a shared collector's far end</t>
+        </is>
+      </c>
+      <c r="H174" s="8"/>
     </row>
     <row r="175">
-      <c r="A175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A175" s="8"/>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C175" s="8"/>
@@ -6558,24 +6870,16 @@
       <c r="F175" s="8"/>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
-        </is>
-      </c>
-      <c r="H175" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">a generator's GSU HV side</t>
+        </is>
+      </c>
+      <c r="H175" s="8"/>
     </row>
     <row r="176">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A176" s="8"/>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
         </is>
       </c>
       <c r="C176" s="8"/>
@@ -6584,24 +6888,16 @@
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
-        </is>
-      </c>
-      <c r="H176" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">a generator's terminal</t>
+        </is>
+      </c>
+      <c r="H176" s="8"/>
     </row>
     <row r="177">
-      <c r="A177" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A177" s="8"/>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C177" s="8"/>
@@ -6610,24 +6906,16 @@
       <c r="F177" s="8"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
-        </is>
-      </c>
-      <c r="H177" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H177" s="8"/>
     </row>
     <row r="178">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A178" s="8"/>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
         </is>
       </c>
       <c r="C178" s="8"/>
@@ -6636,40 +6924,24 @@
       <c r="F178" s="8"/>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
-        </is>
-      </c>
-      <c r="H178" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B179" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{V_PU}</t>
-        </is>
-      </c>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
-      <c r="G179" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
-        </is>
-      </c>
-      <c r="H179" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+        </is>
+      </c>
+      <c r="H178" s="8"/>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
+        </is>
+      </c>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
+      <c r="G179" s="7"/>
+      <c r="H179" s="7"/>
     </row>
     <row r="180">
       <c r="A180" s="8" t="inlineStr">
@@ -6679,7 +6951,7 @@
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C180" s="8"/>
@@ -6688,7 +6960,7 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
@@ -6705,7 +6977,7 @@
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -6714,7 +6986,7 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H181" s="13" t="inlineStr">
@@ -6731,7 +7003,7 @@
       </c>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C182" s="8"/>
@@ -6740,7 +7012,7 @@
       <c r="F182" s="8"/>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H182" s="13" t="inlineStr">
@@ -6757,7 +7029,7 @@
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -6766,7 +7038,7 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H183" s="13" t="inlineStr">
@@ -6783,7 +7055,7 @@
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C184" s="8"/>
@@ -6792,7 +7064,7 @@
       <c r="F184" s="8"/>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
@@ -6809,7 +7081,7 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -6818,7 +7090,7 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H185" s="13" t="inlineStr">
@@ -6835,7 +7107,7 @@
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C186" s="8"/>
@@ -6844,17 +7116,277 @@
       <c r="F186" s="8"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">one unit's MVA</t>
+        </is>
+      </c>
+      <c r="H186" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B187" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
+        </is>
+      </c>
+      <c r="C187" s="8"/>
+      <c r="D187" s="8"/>
+      <c r="E187" s="8"/>
+      <c r="F187" s="8"/>
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one unit's P (MW)</t>
+        </is>
+      </c>
+      <c r="H187" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B188" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+        </is>
+      </c>
+      <c r="C188" s="8"/>
+      <c r="D188" s="8"/>
+      <c r="E188" s="8"/>
+      <c r="F188" s="8"/>
+      <c r="G188" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
+        </is>
+      </c>
+      <c r="H188" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B189" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_PU}</t>
+        </is>
+      </c>
+      <c r="C189" s="8"/>
+      <c r="D189" s="8"/>
+      <c r="E189" s="8"/>
+      <c r="F189" s="8"/>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
+        </is>
+      </c>
+      <c r="H189" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B190" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_KV}</t>
+        </is>
+      </c>
+      <c r="C190" s="8"/>
+      <c r="D190" s="8"/>
+      <c r="E190" s="8"/>
+      <c r="F190" s="8"/>
+      <c r="G190" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the same in kV</t>
+        </is>
+      </c>
+      <c r="H190" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{KV}</t>
+        </is>
+      </c>
+      <c r="C191" s="8"/>
+      <c r="D191" s="8"/>
+      <c r="E191" s="8"/>
+      <c r="F191" s="8"/>
+      <c r="G191" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">that bus's base kV</t>
+        </is>
+      </c>
+      <c r="H191" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B192" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{ANGLE}</t>
+        </is>
+      </c>
+      <c r="C192" s="8"/>
+      <c r="D192" s="8"/>
+      <c r="E192" s="8"/>
+      <c r="F192" s="8"/>
+      <c r="G192" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+        </is>
+      </c>
+      <c r="H192" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{FREQ}</t>
+        </is>
+      </c>
+      <c r="C193" s="8"/>
+      <c r="D193" s="8"/>
+      <c r="E193" s="8"/>
+      <c r="F193" s="8"/>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frequency (Hz)</t>
+        </is>
+      </c>
+      <c r="H193" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B194" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{P_INV_MW}</t>
+        </is>
+      </c>
+      <c r="C194" s="8"/>
+      <c r="D194" s="8"/>
+      <c r="E194" s="8"/>
+      <c r="F194" s="8"/>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+        </is>
+      </c>
+      <c r="H194" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B195" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
+        </is>
+      </c>
+      <c r="C195" s="8"/>
+      <c r="D195" s="8"/>
+      <c r="E195" s="8"/>
+      <c r="F195" s="8"/>
+      <c r="G195" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H195" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B196" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C196" s="8"/>
+      <c r="D196" s="8"/>
+      <c r="E196" s="8"/>
+      <c r="F196" s="8"/>
+      <c r="G196" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H186" s="13" t="inlineStr">
+      <c r="H196" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -6865,11 +7397,12 @@
     <mergeCell ref="A132:H132"/>
     <mergeCell ref="A135:H135"/>
     <mergeCell ref="A141:H141"/>
-    <mergeCell ref="A145:H145"/>
-    <mergeCell ref="A150:H150"/>
-    <mergeCell ref="A153:H153"/>
-    <mergeCell ref="A157:H157"/>
-    <mergeCell ref="A169:H169"/>
+    <mergeCell ref="A151:H151"/>
+    <mergeCell ref="A155:H155"/>
+    <mergeCell ref="A160:H160"/>
+    <mergeCell ref="A163:H163"/>
+    <mergeCell ref="A167:H167"/>
+    <mergeCell ref="A179:H179"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
@@ -6879,18 +7412,19 @@
     <hyperlink ref="A125" location="'Cables'!A1" display="Cables"/>
     <hyperlink ref="A132" location="'Collectors'!A1" display="Collectors"/>
     <hyperlink ref="A135" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A141" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A145" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A150" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A153" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A169" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A141" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A151" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A155" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A160" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A163" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A179" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
@@ -22452,176 +22986,330 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus</t>
+          <t xml:space="preserve">Machine</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="52.0" customHeight="1">
+          <t xml:space="preserve">Pgen MW</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pmax MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pmin MW</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qmax MVAr</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qmin MVAr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed Q MVAr</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBASE MVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100.0" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+          <t xml:space="preserve"># DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit MVA</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
+      <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI</t>
-        </is>
-      </c>
+      <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HV</t>
-        </is>
-      </c>
+      <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT1:LV</t>
-        </is>
-      </c>
+      <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV:MV</t>
-        </is>
-      </c>
+      <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV:LV</t>
-        </is>
-      </c>
+      <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BESS:MV</t>
-        </is>
-      </c>
+      <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BESS:LV</t>
-        </is>
-      </c>
+      <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="82.0" customHeight="1">
+    <row r="50" ht="108.0" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
@@ -797,7 +797,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any parameter of the WECC-approved generic models, by generator, model and PSS/E name or position (ICON2, CON14) -- IB for the infinite bus, PLANT for the plant controller. Inverters: REGCA1 (REGC_A) + REECA1 / REECCU1 / REECDU1 (REEC_A / C / D) + REPCA1 (REPC_A) or REAX4BU1 (with PLNTBU1, REPC_B); WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1; SYNC: GENROU SEXS TGOV1. REECCU1, REECDU1, PLNTBU1, REAX4BU1 (and REGCAU1, REPCAU1) are user models: the WECC user-model DLL must be loaded for the PSS/E check (ADDLIB_IDV / DLLS in the script). The report lists every model's parameters with the values used.</t>
+          <t xml:space="preserve">Any parameter of the WECC-approved generic models, by generator, model and PSS/E name or position (ICON2, CON14) -- IB for the infinite bus, PLANT for the plant controller. Inverters: REGCA1 (REGC_A) + REECA1 / REECCU1 / REECDU1 (REEC_A / C / D) + REPCA1 (REPC_A) or REAX4BU1 (with PLNTBU1, REPC_B); WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1; SYNC: GENROU SEXS TGOV1. REECCU1, REECDU1, PLNTBU1, REAX4BU1 (and REGCAU1, REPCAU1) are user models: the WECC user-model DLL must be loaded for the PSS/E check (ADDLIB_IDV / DLLS in the script). The report lists every model's parameters with the values used. In the GUI, the Dyr_Params tab shows every model's parameters with the values the .dyr gets, a column per generator: double-click one to change it (it becomes a row here), clear it to go back to the default.</t>
         </is>
       </c>
     </row>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -1783,28 +1783,28 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frequency</t>
+          <t xml:space="preserve">Build PSS/E .raw</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">freq_hz</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hz</t>
-        </is>
-      </c>
+          <t xml:space="preserve">out_raw</t>
+        </is>
+      </c>
+      <c r="D8" s="8"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="F8" s="8"/>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 60</t>
+          <t xml:space="preserve">YES = the load-flow case (blank = YES)</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -1821,20 +1821,28 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">First bus number</t>
+          <t xml:space="preserve">Build PSS/E .dyr</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">first_bus</t>
+          <t xml:space="preserve">out_dyr</t>
         </is>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">buses are numbered from here + 1 (Bus_Numbers sets any one)</t>
+          <t xml:space="preserve">YES = the dynamic models (blank = YES)</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1851,26 +1859,30 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI kV</t>
+          <t xml:space="preserve">Build PSCAD model</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">poi_kv</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kV</t>
-        </is>
-      </c>
+          <t xml:space="preserve">out_pscad</t>
+        </is>
+      </c>
+      <c r="D10" s="8"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">required</t>
-        </is>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES = the PSCAD build script, its data and the .pscx (blank = YES)</t>
+        </is>
+      </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -1885,20 +1897,28 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI name</t>
+          <t xml:space="preserve">Frequency</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">poi_name</t>
-        </is>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+          <t xml:space="preserve">freq_hz</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hz</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
+        </is>
+      </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 characters at most</t>
+          <t xml:space="preserve">blank = 60</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -1915,12 +1935,12 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid SCR</t>
+          <t xml:space="preserve">First bus number</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">grid_scr</t>
+          <t xml:space="preserve">first_bus</t>
         </is>
       </c>
       <c r="D12" s="8"/>
@@ -1928,7 +1948,7 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base</t>
+          <t xml:space="preserve">buses are numbered from here + 1 (Bus_Numbers sets any one)</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
@@ -1945,16 +1965,24 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid X/R</t>
+          <t xml:space="preserve">POI kV</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">grid_x_r</t>
-        </is>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+          <t xml:space="preserve">poi_kv</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kV</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">required</t>
+        </is>
+      </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="13" t="inlineStr">
@@ -1971,28 +1999,20 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCR base</t>
+          <t xml:space="preserve">POI name</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">scr_base_mw</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MW</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the generators' Pmax</t>
-        </is>
-      </c>
+          <t xml:space="preserve">poi_name</t>
+        </is>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the generators' Pmax</t>
+          <t xml:space="preserve">12 characters at most</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -2009,24 +2029,20 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid short-circuit MVA</t>
+          <t xml:space="preserve">Grid SCR</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">grid_sc_mva</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">grid_scr</t>
+        </is>
+      </c>
+      <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of the SCR (with Grid X/R)</t>
+          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
@@ -2043,26 +2059,18 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid R</t>
+          <t xml:space="preserve">Grid X/R</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">grid_r_pu</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
+          <t xml:space="preserve">grid_x_r</t>
+        </is>
+      </c>
+      <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">instead of the SCR: Thevenin R on the system base</t>
-        </is>
-      </c>
+      <c r="G16" s="8"/>
       <c r="H16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -2077,24 +2085,28 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid X</t>
+          <t xml:space="preserve">SCR base</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">grid_x_pu</t>
+          <t xml:space="preserve">scr_base_mw</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
-      <c r="E17" s="8"/>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the generators' Pmax</t>
+        </is>
+      </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of the SCR: Thevenin X on the system base</t>
+          <t xml:space="preserve">blank = the generators' Pmax</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -2103,7 +2115,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30.0" customHeight="1">
+    <row r="18" ht="17.0" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2111,24 +2123,24 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie length</t>
+          <t xml:space="preserve">Grid short-circuit MVA</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_length</t>
-        </is>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no gen-tie (the MPTs on the POI bus</t>
-        </is>
-      </c>
+          <t xml:space="preserve">grid_sc_mva</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
+      <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI to the substation HV bus; blank = no gen-tie (the MPTs on the POI bus)</t>
+          <t xml:space="preserve">instead of the SCR (with Grid X/R)</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -2145,28 +2157,24 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie length unit</t>
+          <t xml:space="preserve">Grid R</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_unit</t>
-        </is>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+          <t xml:space="preserve">grid_r_pu</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu</t>
+        </is>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km, mi, kft, m, ft (blank = km)</t>
+          <t xml:space="preserve">instead of the SCR: Thevenin R on the system base</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
@@ -2183,24 +2191,24 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie R per length</t>
+          <t xml:space="preserve">Grid X</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_r_per</t>
+          <t xml:space="preserve">grid_x_pu</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">pu</t>
         </is>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit</t>
+          <t xml:space="preserve">instead of the SCR: Thevenin X on the system base</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -2209,7 +2217,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="17.0" customHeight="1">
+    <row r="21" ht="30.0" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2217,24 +2225,24 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie X per length</t>
+          <t xml:space="preserve">Gen-tie length</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_per</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
-      <c r="E21" s="8"/>
+          <t xml:space="preserve">tie_length</t>
+        </is>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no gen-tie (the MPTs on the POI bus</t>
+        </is>
+      </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit</t>
+          <t xml:space="preserve">POI to the substation HV bus; blank = no gen-tie (the MPTs on the POI bus)</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -2251,24 +2259,28 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie B per length</t>
+          <t xml:space="preserve">Gen-tie length unit</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_per</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">uS</t>
-        </is>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+          <t xml:space="preserve">tie_unit</t>
+        </is>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit (total charging)</t>
+          <t xml:space="preserve">km, mi, kft, m, ft (blank = km)</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
@@ -2285,24 +2297,24 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie C per length</t>
+          <t xml:space="preserve">Gen-tie R per length</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_c_per</t>
+          <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of B</t>
+          <t xml:space="preserve">one circuit, per length unit</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -2319,12 +2331,12 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie R total</t>
+          <t xml:space="preserve">Gen-tie X per length</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_r_ohm</t>
+          <t xml:space="preserve">tie_x_per</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -2336,7 +2348,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of per length (one circuit)</t>
+          <t xml:space="preserve">one circuit, per length unit</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -2353,22 +2365,26 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie X total</t>
+          <t xml:space="preserve">Gen-tie B per length</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_ohm</t>
+          <t xml:space="preserve">tie_b_per</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">uS</t>
         </is>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one circuit, per length unit (total charging)</t>
+        </is>
+      </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -2383,22 +2399,26 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie B total</t>
+          <t xml:space="preserve">Gen-tie C per length</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_us</t>
+          <t xml:space="preserve">tie_c_per</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
+          <t xml:space="preserve">uF</t>
         </is>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instead of B</t>
+        </is>
+      </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -2413,24 +2433,24 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie circuits</t>
+          <t xml:space="preserve">Gen-tie R total</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_parallel</t>
-        </is>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">tie_r_ohm</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical circuits in parallel (blank = 1)</t>
+          <t xml:space="preserve">instead of per length (one circuit)</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -2447,33 +2467,29 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie rating</t>
+          <t xml:space="preserve">Gen-tie X total</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_rate_mva</t>
+          <t xml:space="preserve">tie_x_ohm</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one circuit</t>
-        </is>
-      </c>
+      <c r="G28" s="8"/>
       <c r="H28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30.0" customHeight="1">
+    <row r="29" ht="17.0" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2481,26 +2497,22 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control mode</t>
+          <t xml:space="preserve">Gen-tie B total</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">control_mode</t>
-        </is>
-      </c>
-      <c r="D29" s="8"/>
+          <t xml:space="preserve">tie_b_us</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uS</t>
+        </is>
+      </c>
       <c r="E29" s="8"/>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q | PF | V</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage</t>
-        </is>
-      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
       <c r="H29" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -2515,28 +2527,24 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI voltage</t>
+          <t xml:space="preserve">Gen-tie circuits</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">v_poi_pu</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
+          <t xml:space="preserve">tie_parallel</t>
+        </is>
+      </c>
+      <c r="D30" s="8"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
+          <t xml:space="preserve">identical circuits in parallel (blank = 1)</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -2553,28 +2561,24 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at POI</t>
+          <t xml:space="preserve">Gen-tie rating</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_poi_mvar</t>
+          <t xml:space="preserve">tie_rate_mva</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
+      <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
+          <t xml:space="preserve">one circuit</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -2583,7 +2587,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="17.0" customHeight="1">
+    <row r="32" ht="30.0" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2591,20 +2595,24 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PF at POI</t>
+          <t xml:space="preserve">Control mode</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pf_poi</t>
+          <t xml:space="preserve">control_mode</t>
         </is>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q | PF | V</t>
+        </is>
+      </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
+          <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -2621,12 +2629,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid voltage</t>
+          <t xml:space="preserve">POI voltage</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">v_grid_pu</t>
+          <t xml:space="preserve">v_poi_pu</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2642,7 +2650,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
+          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -2651,7 +2659,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="30.0" customHeight="1">
+    <row r="34" ht="17.0" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2659,28 +2667,28 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at POI</t>
+          <t xml:space="preserve">Q at POI</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">p_poi_mw</t>
+          <t xml:space="preserve">q_poi_mvar</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each generator at its dispatch</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
+          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
@@ -2689,7 +2697,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="30.0" customHeight="1">
+    <row r="35" ht="17.0" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2697,37 +2705,29 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plant controller</t>
+          <t xml:space="preserve">PF at POI</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">plant_ctrl</t>
+          <t xml:space="preserve">pf_poi</t>
         </is>
       </c>
       <c r="D35" s="8"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPC_A</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPC_A | REPC_B</t>
-        </is>
-      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
+          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17.0" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2735,33 +2735,33 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGC_A / REPC_A records</t>
+          <t xml:space="preserve">Grid voltage</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">regc_repc</t>
-        </is>
-      </c>
-      <c r="D36" s="8"/>
+          <t xml:space="preserve">v_grid_pu</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">standard | USRMDL</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="F36" s="8"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard: REGCA1 / REPCA1 (PSS/E library) | USRMDL: REGCAU1 / REPCAU1 (the WECC user-model DLL) (blank = standard)</t>
+          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2773,210 +2773,218 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD time step</t>
+          <t xml:space="preserve">P at POI</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_time_step_us</t>
+          <t xml:space="preserve">p_poi_mw</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">us</t>
+          <t xml:space="preserve">MW</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 (the vendor model's own requirement wins</t>
+          <t xml:space="preserve">each generator at its dispatch</t>
         </is>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30.0" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant controller</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plant_ctrl</t>
+        </is>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REPC_A</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REPC_A | REPC_B</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30.0" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGC_A / REPC_A records</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regc_repc</t>
+        </is>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard | USRMDL</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard: REGCA1 / REPCA1 (PSS/E library) | USRMDL: REGCAU1 / REPCAU1 (the WECC user-model DLL) (blank = standard)</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30.0" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD time step</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_time_step_us</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">us</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10 (the vendor model's own requirement wins</t>
+        </is>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 10 (the vendor model's own requirement wins)</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="17.0" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="41" ht="17.0" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD duration</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_duration_s</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">s</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="F41" s="8"/>
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 5</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="17.0" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="42" ht="17.0" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD plot step</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_plot_step_us</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">us</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">100</t>
         </is>
       </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="F42" s="8"/>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 100</t>
-        </is>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="17.0" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD meter at POI</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_meter</t>
-        </is>
-      </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES | NO</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD lines as</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_lines</t>
-        </is>
-      </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI | RLC</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30.0" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault at POI</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_fault</t>
-        </is>
-      </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES | NO</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -2993,28 +3001,24 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault time</t>
+          <t xml:space="preserve">PSCAD meter at POI</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_fault_s</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100: none in the run</t>
-        </is>
-      </c>
-      <c r="F43" s="8"/>
+          <t xml:space="preserve">pscad_meter</t>
+        </is>
+      </c>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+          <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -3023,7 +3027,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="17.0" customHeight="1">
+    <row r="44" ht="30.0" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -3031,28 +3035,28 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault duration</t>
+          <t xml:space="preserve">PSCAD lines as</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_fault_dur_s</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
+          <t xml:space="preserve">pscad_lines</t>
+        </is>
+      </c>
+      <c r="D44" s="8"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
-        </is>
-      </c>
-      <c r="F44" s="8"/>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI | RLC</t>
+        </is>
+      </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 0.15</t>
+          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -3061,7 +3065,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="43.0" customHeight="1">
+    <row r="45" ht="30.0" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -3069,28 +3073,24 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault type</t>
+          <t xml:space="preserve">PSCAD fault at POI</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_fault_type</t>
+          <t xml:space="preserve">pscad_fault</t>
         </is>
       </c>
       <c r="D45" s="8"/>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ABCG</t>
-        </is>
-      </c>
+      <c r="E45" s="8"/>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
+          <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
+          <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -3107,28 +3107,28 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault resistance</t>
+          <t xml:space="preserve">PSCAD fault time</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_fault_ohm</t>
+          <t xml:space="preserve">pscad_fault_s</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">s</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.01</t>
+          <t xml:space="preserve">100: none in the run</t>
         </is>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 0.01</t>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -3145,20 +3145,28 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD libraries</t>
+          <t xml:space="preserve">PSCAD fault duration</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_libraries</t>
-        </is>
-      </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
+          <t xml:space="preserve">pscad_fault_dur_s</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
+          <t xml:space="preserve">blank = 0.15</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -3167,101 +3175,125 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
+    <row r="48" ht="43.0" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault type</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_fault_type</t>
+        </is>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABCG</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="17.0" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MPT</t>
+          <t xml:space="preserve">Plant</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">PSCAD fault resistance</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
+          <t xml:space="preserve">pscad_fault_ohm</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.01</t>
+        </is>
+      </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
+          <t xml:space="preserve">blank = 0.01</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17.0" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MPT</t>
+          <t xml:space="preserve">Plant</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV kV</t>
+          <t xml:space="preserve">PSCAD libraries</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hv_kv</t>
+          <t xml:space="preserve">pscad_libraries</t>
         </is>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
+        </is>
+      </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="17.0" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LV kV</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lv_kv</t>
-        </is>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
     </row>
     <row r="52" ht="17.0" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
@@ -3271,24 +3303,20 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TV kV</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tv_kv</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D52" s="8"/>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">two windings</t>
-        </is>
-      </c>
+      <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tertiary / 2nd LV winding; blank = two windings</t>
+          <t xml:space="preserve">MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -3305,22 +3333,18 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">HV kV</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mva</t>
+          <t xml:space="preserve">hv_kv</t>
         </is>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
-        </is>
-      </c>
+      <c r="G53" s="8"/>
       <c r="H53" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3335,22 +3359,18 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV MVA</t>
+          <t xml:space="preserve">LV kV</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_mva</t>
+          <t xml:space="preserve">lv_kv</t>
         </is>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 windings</t>
-        </is>
-      </c>
+      <c r="G54" s="8"/>
       <c r="H54" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3365,20 +3385,24 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TV MVA</t>
+          <t xml:space="preserve">TV kV</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tv_mva</t>
+          <t xml:space="preserve">tv_kv</t>
         </is>
       </c>
       <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">two windings</t>
+        </is>
+      </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">tertiary / 2nd LV winding; blank = two windings</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -3395,12 +3419,12 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV %</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_hl_pct</t>
+          <t xml:space="preserve">mva</t>
         </is>
       </c>
       <c r="D56" s="8"/>
@@ -3408,7 +3432,7 @@
       <c r="F56" s="8"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on its base MVA</t>
+          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -3425,12 +3449,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV %</t>
+          <t xml:space="preserve">LV MVA</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_ht_pct</t>
+          <t xml:space="preserve">lv_mva</t>
         </is>
       </c>
       <c r="D57" s="8"/>
@@ -3455,12 +3479,12 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV %</t>
+          <t xml:space="preserve">TV MVA</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_lt_pct</t>
+          <t xml:space="preserve">tv_mva</t>
         </is>
       </c>
       <c r="D58" s="8"/>
@@ -3485,24 +3509,20 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV base MVA</t>
+          <t xml:space="preserve">Z HV-LV %</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_hl_mva</t>
+          <t xml:space="preserve">z_hl_pct</t>
         </is>
       </c>
       <c r="D59" s="8"/>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">on its base MVA</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -3519,24 +3539,20 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-TV %</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_ht_mva</t>
+          <t xml:space="preserve">z_ht_pct</t>
         </is>
       </c>
       <c r="D60" s="8"/>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E60" s="8"/>
       <c r="F60" s="8"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -3553,24 +3569,20 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV base MVA</t>
+          <t xml:space="preserve">Z LV-TV %</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_lt_mva</t>
+          <t xml:space="preserve">z_lt_pct</t>
         </is>
       </c>
       <c r="D61" s="8"/>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E61" s="8"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -3587,20 +3599,24 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X/R</t>
+          <t xml:space="preserve">Z HV-LV base MVA</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_r</t>
+          <t xml:space="preserve">base_hl_mva</t>
         </is>
       </c>
       <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F62" s="8"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each impedance</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -3617,20 +3633,24 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load loss kW</t>
+          <t xml:space="preserve">Z HV-TV base MVA</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">load_loss_kw</t>
+          <t xml:space="preserve">base_ht_mva</t>
         </is>
       </c>
       <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F63" s="8"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -3647,20 +3667,24 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector group</t>
+          <t xml:space="preserve">Z LV-TV base MVA</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vector</t>
+          <t xml:space="preserve">base_lt_mva</t>
         </is>
       </c>
       <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -3677,24 +3701,20 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV tap</t>
+          <t xml:space="preserve">X/R</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tap</t>
+          <t xml:space="preserve">x_r</t>
         </is>
       </c>
       <c r="D65" s="8"/>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
+          <t xml:space="preserve">each impedance</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -3711,24 +3731,20 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel units</t>
+          <t xml:space="preserve">Load loss kW</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">count</t>
+          <t xml:space="preserve">load_loss_kw</t>
         </is>
       </c>
       <c r="D66" s="8"/>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E66" s="8"/>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical units (blank = 1)</t>
+          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -3745,24 +3761,20 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No-load loss %</t>
+          <t xml:space="preserve">Vector group</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nll_pct</t>
+          <t xml:space="preserve">vector</t>
         </is>
       </c>
       <c r="D67" s="8"/>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
+      <c r="E67" s="8"/>
       <c r="F67" s="8"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">of MVA (blank = 0)</t>
+          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -3779,24 +3791,24 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnetising current %</t>
+          <t xml:space="preserve">HV tap</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">im_pct</t>
+          <t xml:space="preserve">tap</t>
         </is>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">of MVA (blank = 0)</t>
+          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -3813,24 +3825,24 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rating MVA</t>
+          <t xml:space="preserve">Parallel units</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_mva</t>
+          <t xml:space="preserve">count</t>
         </is>
       </c>
       <c r="D69" s="8"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">identical units (blank = 1)</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3847,24 +3859,24 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length</t>
+          <t xml:space="preserve">No-load loss %</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_length</t>
+          <t xml:space="preserve">nll_pct</t>
         </is>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+          <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -3881,22 +3893,26 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length unit</t>
+          <t xml:space="preserve">Magnetising current %</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_unit</t>
+          <t xml:space="preserve">im_pct</t>
         </is>
       </c>
       <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G71" s="8"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">of MVA (blank = 0)</t>
+        </is>
+      </c>
       <c r="H71" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3911,20 +3927,24 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie R per length</t>
+          <t xml:space="preserve">Rating MVA</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_r_per</t>
+          <t xml:space="preserve">rate_mva</t>
         </is>
       </c>
       <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -3941,20 +3961,24 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie X per length</t>
+          <t xml:space="preserve">Tie length</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_per</t>
+          <t xml:space="preserve">tie_length</t>
         </is>
       </c>
       <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -3971,22 +3995,22 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie B per length</t>
+          <t xml:space="preserve">Tie length unit</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_per</t>
+          <t xml:space="preserve">tie_unit</t>
         </is>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">uS</t>
-        </is>
-      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
+      <c r="G74" s="8"/>
       <c r="H74" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4001,52 +4025,72 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie rating MVA</t>
+          <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_rate_mva</t>
+          <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
+    <row r="76" ht="17.0" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tie X per length</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_x_per</t>
+        </is>
+      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="17.0" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generators</t>
+          <t xml:space="preserve">MPT</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Tie B per length</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">tie_b_per</t>
         </is>
       </c>
       <c r="D77" s="8"/>
@@ -4054,7 +4098,7 @@
       <c r="F77" s="8"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
+          <t xml:space="preserve">uS</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -4063,73 +4107,45 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="30.0" customHeight="1">
+    <row r="78" ht="17.0" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generators</t>
+          <t xml:space="preserve">MPT</t>
         </is>
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type</t>
+          <t xml:space="preserve">Tie rating MVA</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">tie_rate_mva</t>
         </is>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
-        </is>
-      </c>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
       <c r="H78" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="17.0" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 1</t>
-        </is>
-      </c>
-      <c r="H79" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
     </row>
     <row r="80" ht="17.0" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
@@ -4139,12 +4155,12 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D80" s="8"/>
@@ -4152,7 +4168,7 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
+          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -4161,7 +4177,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="17.0" customHeight="1">
+    <row r="81" ht="30.0" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4169,20 +4185,24 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units</t>
+          <t xml:space="preserve">Type</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
+        </is>
+      </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number of units</t>
+          <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -4199,24 +4219,24 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit MVA</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_mva</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from P and Q</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
@@ -4233,18 +4253,22 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmax MW</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmax_mw</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
+        </is>
+      </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4259,24 +4283,20 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmin MW</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmin_mw</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D84" s="8"/>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
+      <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
+          <t xml:space="preserve">number of units</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -4293,24 +4313,24 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmax MVAr</t>
+          <t xml:space="preserve">Unit MVA</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmax_mvar</t>
+          <t xml:space="preserve">unit_mva</t>
         </is>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Unit PF</t>
+          <t xml:space="preserve">from P and Q</t>
         </is>
       </c>
       <c r="F85" s="8"/>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = from Unit PF</t>
+          <t xml:space="preserve">one unit (blank = from P and Q)</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4327,26 +4347,18 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmin MVAr</t>
+          <t xml:space="preserve">Unit Pmax MW</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmin_mvar</t>
+          <t xml:space="preserve">unit_pmax_mw</t>
         </is>
       </c>
       <c r="D86" s="8"/>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-Qmax</t>
-        </is>
-      </c>
+      <c r="E86" s="8"/>
       <c r="F86" s="8"/>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = -Qmax</t>
-        </is>
-      </c>
+      <c r="G86" s="8"/>
       <c r="H86" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4361,24 +4373,24 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit PF</t>
+          <t xml:space="preserve">Unit Pmin MW</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pf</t>
+          <t xml:space="preserve">unit_pmin_mw</t>
         </is>
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
+          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4395,24 +4407,24 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminal kV</t>
+          <t xml:space="preserve">Unit Qmax MVAr</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kv</t>
+          <t xml:space="preserve">unit_qmax_mvar</t>
         </is>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">from Unit PF</t>
         </is>
       </c>
       <c r="F88" s="8"/>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = GSU LV kV</t>
+          <t xml:space="preserve">blank = from Unit PF</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
@@ -4421,7 +4433,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="30.0" customHeight="1">
+    <row r="89" ht="17.0" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4429,24 +4441,24 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispatch MW</t>
+          <t xml:space="preserve">Unit Qmin MVAr</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dispatch_mw</t>
+          <t xml:space="preserve">unit_qmin_mvar</t>
         </is>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+          <t xml:space="preserve">-Qmax</t>
         </is>
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
+          <t xml:space="preserve">blank = -Qmax</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
@@ -4463,24 +4475,24 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode</t>
+          <t xml:space="preserve">Unit PF</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mode</t>
+          <t xml:space="preserve">unit_pf</t>
         </is>
       </c>
       <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share | fixed</t>
-        </is>
-      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.95</t>
+        </is>
+      </c>
+      <c r="F90" s="8"/>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
+          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4497,24 +4509,24 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Terminal kV</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_q_mvar</t>
+          <t xml:space="preserve">kv</t>
         </is>
       </c>
       <c r="D91" s="8"/>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="F91" s="8"/>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
+          <t xml:space="preserve">blank = GSU LV kV</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -4523,7 +4535,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="17.0" customHeight="1">
+    <row r="92" ht="30.0" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4531,20 +4543,24 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed PF</t>
+          <t xml:space="preserve">Dispatch MW</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_pf</t>
+          <t xml:space="preserve">dispatch_mw</t>
         </is>
       </c>
       <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+        </is>
+      </c>
       <c r="F92" s="8"/>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
+          <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
@@ -4561,24 +4577,24 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU count</t>
+          <t xml:space="preserve">Q mode</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_count</t>
+          <t xml:space="preserve">q_mode</t>
         </is>
       </c>
       <c r="D93" s="8"/>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Units</t>
-        </is>
-      </c>
-      <c r="F93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">share | fixed</t>
+        </is>
+      </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = Units</t>
+          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
@@ -4587,7 +4603,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="30.0" customHeight="1">
+    <row r="94" ht="17.0" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4595,24 +4611,24 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU MVA</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_mva</t>
+          <t xml:space="preserve">fixed_q_mvar</t>
         </is>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">no GSU (units on the MV bus</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
+          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
@@ -4629,18 +4645,22 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV kV</t>
+          <t xml:space="preserve">Fixed PF</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_hv_kv</t>
+          <t xml:space="preserve">fixed_pf</t>
         </is>
       </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
+        </is>
+      </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4655,25 +4675,33 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">GSU count</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_lv_kv</t>
+          <t xml:space="preserve">gsu_count</t>
         </is>
       </c>
       <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units</t>
+        </is>
+      </c>
       <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = Units</t>
+        </is>
+      </c>
       <c r="H96" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="17.0" customHeight="1">
+    <row r="97" ht="30.0" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4681,20 +4709,24 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU Z %</t>
+          <t xml:space="preserve">GSU MVA</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_z_pct</t>
+          <t xml:space="preserve">gsu_mva</t>
         </is>
       </c>
       <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no GSU (units on the MV bus</t>
+        </is>
+      </c>
       <c r="F97" s="8"/>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on GSU MVA</t>
+          <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
@@ -4711,12 +4743,12 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU X/R</t>
+          <t xml:space="preserve">GSU HV kV</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_x_r</t>
+          <t xml:space="preserve">gsu_hv_kv</t>
         </is>
       </c>
       <c r="D98" s="8"/>
@@ -4737,12 +4769,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU vector group</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_vector</t>
+          <t xml:space="preserve">gsu_lv_kv</t>
         </is>
       </c>
       <c r="D99" s="8"/>
@@ -4763,24 +4795,20 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV tap</t>
+          <t xml:space="preserve">GSU Z %</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_tap</t>
+          <t xml:space="preserve">gsu_z_pct</t>
         </is>
       </c>
       <c r="D100" s="8"/>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E100" s="8"/>
       <c r="F100" s="8"/>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">on GSU MVA</t>
         </is>
       </c>
       <c r="H100" s="13" t="inlineStr">
@@ -4797,26 +4825,18 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">GSU X/R</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">gsu_x_r</t>
         </is>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
-        </is>
-      </c>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
       <c r="H101" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4831,22 +4851,18 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector R</t>
+          <t xml:space="preserve">GSU vector group</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_r</t>
+          <t xml:space="preserve">gsu_vector</t>
         </is>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIVALENT</t>
-        </is>
-      </c>
+      <c r="G102" s="8"/>
       <c r="H102" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4861,20 +4877,24 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector X</t>
+          <t xml:space="preserve">GSU HV tap</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_x</t>
+          <t xml:space="preserve">gsu_tap</t>
         </is>
       </c>
       <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F103" s="8"/>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
@@ -4891,20 +4911,24 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector B</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_b</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
+      <c r="F104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
+        </is>
+      </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT, total charging</t>
+          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
         </is>
       </c>
       <c r="H104" s="13" t="inlineStr">
@@ -4921,24 +4945,20 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector units</t>
+          <t xml:space="preserve">Collector R</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_units</t>
+          <t xml:space="preserve">coll_r</t>
         </is>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
-      <c r="F105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu | ohm</t>
-        </is>
-      </c>
+      <c r="F105" s="8"/>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H105" s="13" t="inlineStr">
@@ -4955,12 +4975,12 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZSORCE X pu</t>
+          <t xml:space="preserve">Collector X</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zsorce_x</t>
+          <t xml:space="preserve">coll_x</t>
         </is>
       </c>
       <c r="D106" s="8"/>
@@ -4968,12 +4988,12 @@
       <c r="F106" s="8"/>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H106" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4985,12 +5005,12 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WMOD</t>
+          <t xml:space="preserve">Collector B</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wmod</t>
+          <t xml:space="preserve">coll_b</t>
         </is>
       </c>
       <c r="D107" s="8"/>
@@ -4998,16 +5018,16 @@
       <c r="F107" s="8"/>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
+          <t xml:space="preserve">EQUIVALENT, total charging</t>
         </is>
       </c>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="17.0" customHeight="1">
       <c r="A108" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5015,33 +5035,29 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical control</t>
+          <t xml:space="preserve">Collector units</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">reec</t>
+          <t xml:space="preserve">coll_units</t>
         </is>
       </c>
       <c r="D108" s="8"/>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
-        </is>
-      </c>
+      <c r="E108" s="8"/>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
+          <t xml:space="preserve">pu | ohm</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
+          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
         </is>
       </c>
       <c r="H108" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5053,29 +5069,25 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD library</t>
+          <t xml:space="preserve">ZSORCE X pu</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_library</t>
+          <t xml:space="preserve">zsorce_x</t>
         </is>
       </c>
       <c r="D109" s="8"/>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
+      <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
+          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
@@ -5087,33 +5099,29 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD definition</t>
+          <t xml:space="preserve">WMOD</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_definition</t>
+          <t xml:space="preserve">wmod</t>
         </is>
       </c>
       <c r="D110" s="8"/>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a source: network check</t>
-        </is>
-      </c>
+      <c r="E110" s="8"/>
       <c r="F110" s="8"/>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
+          <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
         </is>
       </c>
       <c r="H110" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30.0" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5121,33 +5129,37 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD AC port</t>
+          <t xml:space="preserve">Electrical control</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_ac_port</t>
+          <t xml:space="preserve">reec</t>
         </is>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its 3-phase port</t>
-        </is>
-      </c>
-      <c r="F111" s="8"/>
+          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
+        </is>
+      </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="17.0" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5155,28 +5167,24 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD inverter at</t>
+          <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_inv_at</t>
+          <t xml:space="preserve">pscad_library</t>
         </is>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LV | MV</t>
-        </is>
-      </c>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F112" s="8"/>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
+          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
@@ -5185,113 +5193,125 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
+    <row r="113" ht="17.0" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD definition</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_definition</t>
+        </is>
+      </c>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a source: network check</t>
+        </is>
+      </c>
+      <c r="F113" s="8"/>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
+        </is>
+      </c>
+      <c r="H113" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="17.0" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeders</t>
+          <t xml:space="preserve">Generators</t>
         </is>
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">pscad_ac_port</t>
         </is>
       </c>
       <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its 3-phase port</t>
+        </is>
+      </c>
       <c r="F114" s="8"/>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
+          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
       </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30.0" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD inverter at</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_inv_at</t>
+        </is>
+      </c>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV | MV</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B115" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeder</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feeder</t>
-        </is>
-      </c>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feeder name</t>
-        </is>
-      </c>
-      <c r="H115" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="17.0" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B116" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Copies</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copies</t>
-        </is>
-      </c>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F116" s="8"/>
-      <c r="G116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
-        </is>
-      </c>
-      <c r="H116" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B116" s="7"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7"/>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
     </row>
     <row r="117" ht="17.0" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
@@ -5301,12 +5321,12 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">section</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D117" s="8"/>
@@ -5314,7 +5334,7 @@
       <c r="F117" s="8"/>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
@@ -5323,7 +5343,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="30.0" customHeight="1">
+    <row r="118" ht="17.0" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5331,24 +5351,20 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">From section</t>
+          <t xml:space="preserve">Feeder</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_section</t>
+          <t xml:space="preserve">feeder</t>
         </is>
       </c>
       <c r="D118" s="8"/>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the one before (daisy chain</t>
-        </is>
-      </c>
+      <c r="E118" s="8"/>
       <c r="F118" s="8"/>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+          <t xml:space="preserve">feeder name</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
@@ -5365,20 +5381,24 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">Copies</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">copies</t>
         </is>
       </c>
       <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F119" s="8"/>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Cables</t>
+          <t xml:space="preserve">identical feeders (blank = 1)</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
@@ -5395,25 +5415,29 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length</t>
+          <t xml:space="preserve">Section</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">length</t>
+          <t xml:space="preserve">section</t>
         </is>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
-      <c r="G120" s="8"/>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+        </is>
+      </c>
       <c r="H120" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="17.0" customHeight="1">
+    <row r="121" ht="30.0" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5421,28 +5445,24 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">From section</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">from_section</t>
         </is>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+          <t xml:space="preserve">the one before (daisy chain</t>
+        </is>
+      </c>
+      <c r="F121" s="8"/>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = km</t>
+          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
@@ -5459,12 +5479,12 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units at end</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D122" s="8"/>
@@ -5472,7 +5492,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units tapped at the far end</t>
+          <t xml:space="preserve">from Cables</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
@@ -5489,22 +5509,18 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units of</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units_of</t>
+          <t xml:space="preserve">length</t>
         </is>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
-        </is>
-      </c>
+      <c r="G123" s="8"/>
       <c r="H123" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5519,24 +5535,28 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel cables</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parallel</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F124" s="8"/>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">blank = km</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
@@ -5545,34 +5565,50 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
+    <row r="125" ht="17.0" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units at end</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">units</t>
+        </is>
+      </c>
+      <c r="D125" s="8"/>
+      <c r="E125" s="8"/>
+      <c r="F125" s="8"/>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">units tapped at the far end</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="17.0" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">Units of</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">units_of</t>
         </is>
       </c>
       <c r="D126" s="8"/>
@@ -5580,7 +5616,7 @@
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable type</t>
+          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
@@ -5592,66 +5628,50 @@
     <row r="127" ht="17.0" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parallel cables</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parallel</t>
+        </is>
+      </c>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F127" s="8"/>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = 1</t>
+        </is>
+      </c>
+      <c r="H127" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Length unit</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unit</t>
-        </is>
-      </c>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the values are per</t>
-        </is>
-      </c>
-      <c r="H127" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="17.0" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R per length</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">r_per</t>
-        </is>
-      </c>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
-        </is>
-      </c>
-      <c r="H128" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B128" s="7"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7"/>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
     </row>
     <row r="129" ht="17.0" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
@@ -5661,12 +5681,12 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D129" s="8"/>
@@ -5674,7 +5694,7 @@
       <c r="F129" s="8"/>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">cable type</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -5691,20 +5711,24 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">the values are per</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
@@ -5721,12 +5745,12 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D131" s="8"/>
@@ -5734,7 +5758,7 @@
       <c r="F131" s="8"/>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS, instead of C</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
@@ -5743,34 +5767,50 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
+    <row r="132" ht="17.0" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X per length</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x_per</t>
+        </is>
+      </c>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="17.0" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">C per length</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">c_per</t>
         </is>
       </c>
       <c r="D133" s="8"/>
@@ -5778,7 +5818,7 @@
       <c r="F133" s="8"/>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
+          <t xml:space="preserve">uF</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
@@ -5790,17 +5830,17 @@
     <row r="134" ht="17.0" customHeight="1">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">B per length</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">b_per</t>
         </is>
       </c>
       <c r="D134" s="8"/>
@@ -5808,7 +5848,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
+          <t xml:space="preserve">uS, instead of C</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
@@ -5820,7 +5860,7 @@
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B135" s="7"/>
@@ -5834,29 +5874,25 @@
     <row r="136" ht="17.0" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
-      <c r="F136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
+      <c r="F136" s="8"/>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
+          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -5868,17 +5904,17 @@
     <row r="137" ht="17.0" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">At bus</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D137" s="8"/>
@@ -5886,7 +5922,7 @@
       <c r="F137" s="8"/>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
@@ -5895,35 +5931,19 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="17.0" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B138" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MW</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mw</t>
-        </is>
-      </c>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
-      <c r="G138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
-        </is>
-      </c>
-      <c r="H138" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B138" s="7"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
     </row>
     <row r="139" ht="17.0" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
@@ -5933,20 +5953,24 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
@@ -5963,52 +5987,72 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
-      <c r="G140" s="8"/>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+        </is>
+      </c>
       <c r="H140" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B141" s="7"/>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7"/>
-      <c r="G141" s="7"/>
-      <c r="H141" s="7"/>
-    </row>
-    <row r="142" ht="30.0" customHeight="1">
+    <row r="141" ht="17.0" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mw</t>
+        </is>
+      </c>
+      <c r="D141" s="8"/>
+      <c r="E141" s="8"/>
+      <c r="F141" s="8"/>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
+        </is>
+      </c>
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="17.0" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">machine</t>
+          <t xml:space="preserve">mvar</t>
         </is>
       </c>
       <c r="D142" s="8"/>
@@ -6016,7 +6060,7 @@
       <c r="F142" s="8"/>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -6028,97 +6072,65 @@
     <row r="143" ht="17.0" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D143" s="8"/>
+      <c r="E143" s="8"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8"/>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B143" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its generator's</t>
-        </is>
-      </c>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = its generator's</t>
-        </is>
-      </c>
-      <c r="H143" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="30.0" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+      <c r="B144" s="7"/>
+      <c r="C144" s="7"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="7"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
+    </row>
+    <row r="145" ht="30.0" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B144" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pgen MW</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pgen_mw</t>
-        </is>
-      </c>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
-        </is>
-      </c>
-      <c r="F144" s="8"/>
-      <c r="G144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
-        </is>
-      </c>
-      <c r="H144" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="17.0" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax MW</t>
+          <t xml:space="preserve">Machine</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmax_mw</t>
+          <t xml:space="preserve">machine</t>
         </is>
       </c>
       <c r="D145" s="8"/>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its units x Unit Pmax</t>
-        </is>
-      </c>
+      <c r="E145" s="8"/>
       <c r="F145" s="8"/>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="H145" s="13" t="inlineStr">
@@ -6135,24 +6147,24 @@
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmin MW</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmin_mw</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmin</t>
+          <t xml:space="preserve">its generator's</t>
         </is>
       </c>
       <c r="F146" s="8"/>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H146" s="13" t="inlineStr">
@@ -6161,7 +6173,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="17.0" customHeight="1">
+    <row r="147" ht="30.0" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6169,24 +6181,24 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmax MVAr</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmax_mvar</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmax</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F147" s="8"/>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -6203,24 +6215,24 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmin MVAr</t>
+          <t xml:space="preserve">Pmax MW</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmin_mvar</t>
+          <t xml:space="preserve">pmax_mw</t>
         </is>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmin</t>
+          <t xml:space="preserve">its units x Unit Pmax</t>
         </is>
       </c>
       <c r="F148" s="8"/>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
@@ -6229,7 +6241,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="30.0" customHeight="1">
+    <row r="149" ht="17.0" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6237,24 +6249,24 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Pmin MW</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mvar</t>
+          <t xml:space="preserve">pmin_mw</t>
         </is>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as its generator's Q mode</t>
+          <t xml:space="preserve">its units x Unit Pmin</t>
         </is>
       </c>
       <c r="F149" s="8"/>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
         </is>
       </c>
       <c r="H149" s="13" t="inlineStr">
@@ -6271,24 +6283,24 @@
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBASE MVA</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mbase_mva</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit MVA</t>
+          <t xml:space="preserve">its units x Unit Qmax</t>
         </is>
       </c>
       <c r="F150" s="8"/>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit MVA</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H150" s="13" t="inlineStr">
@@ -6297,42 +6309,66 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B151" s="7"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
-      <c r="H151" s="7"/>
-    </row>
-    <row r="152" ht="17.0" customHeight="1">
+    <row r="151" ht="17.0" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qmin MVAr</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">qmin_mvar</t>
+        </is>
+      </c>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Qmin</t>
+        </is>
+      </c>
+      <c r="F151" s="8"/>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+        </is>
+      </c>
+      <c r="H151" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="30.0" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bus</t>
+          <t xml:space="preserve">q_mvar</t>
         </is>
       </c>
       <c r="D152" s="8"/>
-      <c r="E152" s="8"/>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as its generator's Q mode</t>
+        </is>
+      </c>
       <c r="F152" s="8"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -6344,29 +6380,29 @@
     <row r="153" ht="17.0" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">MBASE MVA</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">mbase_mva</t>
         </is>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic</t>
+          <t xml:space="preserve">its units x Unit MVA</t>
         </is>
       </c>
       <c r="F153" s="8"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">blank = its units x Unit MVA</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
@@ -6375,143 +6411,131 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="30.0" customHeight="1">
-      <c r="A154" s="8" t="inlineStr">
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B154" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="C154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D154" s="8"/>
-      <c r="E154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
-        </is>
-      </c>
-      <c r="F154" s="8"/>
-      <c r="G154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
-        </is>
-      </c>
-      <c r="H154" s="13" t="inlineStr">
+      <c r="B154" s="7"/>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="7"/>
+      <c r="H154" s="7"/>
+    </row>
+    <row r="155" ht="17.0" customHeight="1">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bus</t>
+        </is>
+      </c>
+      <c r="D155" s="8"/>
+      <c r="E155" s="8"/>
+      <c r="F155" s="8"/>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+        </is>
+      </c>
+      <c r="H155" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
-    </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B155" s="7"/>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
-      <c r="H155" s="7"/>
     </row>
     <row r="156" ht="17.0" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Number</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic</t>
+        </is>
+      </c>
       <c r="F156" s="8"/>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+          <t xml:space="preserve">blank = automatic</t>
         </is>
       </c>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="157" ht="30.0" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Model</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">model</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
       <c r="F157" s="8"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="17.0" customHeight="1">
-      <c r="A158" s="8" t="inlineStr">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B158" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parameter</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parameter</t>
-        </is>
-      </c>
-      <c r="D158" s="8"/>
-      <c r="E158" s="8"/>
-      <c r="F158" s="8"/>
-      <c r="G158" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
-        </is>
-      </c>
-      <c r="H158" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
+      <c r="B158" s="7"/>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7"/>
     </row>
     <row r="159" ht="17.0" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
@@ -6521,64 +6545,80 @@
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
-      <c r="G159" s="8"/>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+        </is>
+      </c>
       <c r="H159" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B160" s="7"/>
-      <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
-      <c r="G160" s="7"/>
-      <c r="H160" s="7"/>
+    <row r="160" ht="30.0" customHeight="1">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Model</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model</t>
+        </is>
+      </c>
+      <c r="D160" s="8"/>
+      <c r="E160" s="8"/>
+      <c r="F160" s="8"/>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+        </is>
+      </c>
+      <c r="H160" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="17.0" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D161" s="8"/>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the plant</t>
-        </is>
-      </c>
+      <c r="E161" s="8"/>
       <c r="F161" s="8"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the plant</t>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
@@ -6590,27 +6630,23 @@
     <row r="162" ht="17.0" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">record</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
-      <c r="G162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
-        </is>
-      </c>
+      <c r="G162" s="8"/>
       <c r="H162" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
@@ -6620,7 +6656,7 @@
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B163" s="7"/>
@@ -6634,7 +6670,7 @@
     <row r="164" ht="17.0" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B164" s="12" t="inlineStr">
@@ -6648,29 +6684,37 @@
         </is>
       </c>
       <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the plant</t>
+        </is>
+      </c>
       <c r="F164" s="8"/>
-      <c r="G164" s="8"/>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = the plant</t>
+        </is>
+      </c>
       <c r="H164" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
     <row r="165" ht="17.0" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Record</t>
         </is>
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">record</t>
         </is>
       </c>
       <c r="D165" s="8"/>
@@ -6678,118 +6722,134 @@
       <c r="F165" s="8"/>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
+          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
         </is>
       </c>
       <c r="H165" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+    </row>
+    <row r="167" ht="17.0" customHeight="1">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generator</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator</t>
+        </is>
+      </c>
+      <c r="D167" s="8"/>
+      <c r="E167" s="8"/>
+      <c r="F167" s="8"/>
+      <c r="G167" s="8"/>
+      <c r="H167" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="17.0" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
+    <row r="168" ht="17.0" customHeight="1">
+      <c r="A168" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B166" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">value</t>
-        </is>
-      </c>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
-      <c r="G166" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
-        </is>
-      </c>
-      <c r="H166" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
-        </is>
-      </c>
-      <c r="B167" s="7"/>
-      <c r="C167" s="7"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-      <c r="G167" s="7"/>
-      <c r="H167" s="7"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="8"/>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C168" s="8"/>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
       <c r="F168" s="8"/>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H168" s="8"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="8"/>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="17.0" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI</t>
-        </is>
-      </c>
-      <c r="C169" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the point of interconnection</t>
-        </is>
-      </c>
-      <c r="H169" s="8"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="8"/>
-      <c r="B170" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HV</t>
-        </is>
-      </c>
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
-      <c r="F170" s="8"/>
-      <c r="G170" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
-        </is>
-      </c>
-      <c r="H170" s="8"/>
+          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+        </is>
+      </c>
+      <c r="H169" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
+        </is>
+      </c>
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="7"/>
+      <c r="H170" s="7"/>
     </row>
     <row r="171">
       <c r="A171" s="8"/>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C171" s="8"/>
@@ -6798,7 +6858,7 @@
       <c r="F171" s="8"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H171" s="8"/>
@@ -6807,7 +6867,7 @@
       <c r="A172" s="8"/>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C172" s="8"/>
@@ -6816,7 +6876,7 @@
       <c r="F172" s="8"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H172" s="8"/>
@@ -6825,7 +6885,7 @@
       <c r="A173" s="8"/>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C173" s="8"/>
@@ -6834,7 +6894,7 @@
       <c r="F173" s="8"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
         </is>
       </c>
       <c r="H173" s="8"/>
@@ -6843,7 +6903,7 @@
       <c r="A174" s="8"/>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C174" s="8"/>
@@ -6852,7 +6912,7 @@
       <c r="F174" s="8"/>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
+          <t xml:space="preserve">an MPT's LV winding</t>
         </is>
       </c>
       <c r="H174" s="8"/>
@@ -6861,7 +6921,7 @@
       <c r="A175" s="8"/>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C175" s="8"/>
@@ -6870,7 +6930,7 @@
       <c r="F175" s="8"/>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
         </is>
       </c>
       <c r="H175" s="8"/>
@@ -6879,7 +6939,7 @@
       <c r="A176" s="8"/>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C176" s="8"/>
@@ -6888,7 +6948,7 @@
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
         </is>
       </c>
       <c r="H176" s="8"/>
@@ -6897,7 +6957,7 @@
       <c r="A177" s="8"/>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C177" s="8"/>
@@ -6906,7 +6966,7 @@
       <c r="F177" s="8"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H177" s="8"/>
@@ -6915,7 +6975,7 @@
       <c r="A178" s="8"/>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C178" s="8"/>
@@ -6924,34 +6984,34 @@
       <c r="F178" s="8"/>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H178" s="8"/>
     </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
-        </is>
-      </c>
-      <c r="B179" s="7"/>
-      <c r="C179" s="7"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
-      <c r="G179" s="7"/>
-      <c r="H179" s="7"/>
+    <row r="179">
+      <c r="A179" s="8"/>
+      <c r="B179" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+        </is>
+      </c>
+      <c r="C179" s="8"/>
+      <c r="D179" s="8"/>
+      <c r="E179" s="8"/>
+      <c r="F179" s="8"/>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a generator's terminal</t>
+        </is>
+      </c>
+      <c r="H179" s="8"/>
     </row>
     <row r="180">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A180" s="8"/>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNITS}</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C180" s="8"/>
@@ -6960,24 +7020,16 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H180" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H180" s="8"/>
     </row>
     <row r="181">
-      <c r="A181" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A181" s="8"/>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -6986,40 +7038,24 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
-        </is>
-      </c>
-      <c r="H181" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B182" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{P_MW}</t>
-        </is>
-      </c>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
-      <c r="F182" s="8"/>
-      <c r="G182" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
-        </is>
-      </c>
-      <c r="H182" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+        </is>
+      </c>
+      <c r="H181" s="8"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
+        </is>
+      </c>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
+      <c r="G182" s="7"/>
+      <c r="H182" s="7"/>
     </row>
     <row r="183">
       <c r="A183" s="8" t="inlineStr">
@@ -7029,7 +7065,7 @@
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -7038,7 +7074,7 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H183" s="13" t="inlineStr">
@@ -7055,7 +7091,7 @@
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C184" s="8"/>
@@ -7064,7 +7100,7 @@
       <c r="F184" s="8"/>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H184" s="13" t="inlineStr">
@@ -7081,7 +7117,7 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -7090,7 +7126,7 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H185" s="13" t="inlineStr">
@@ -7107,7 +7143,7 @@
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C186" s="8"/>
@@ -7116,7 +7152,7 @@
       <c r="F186" s="8"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H186" s="13" t="inlineStr">
@@ -7133,7 +7169,7 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C187" s="8"/>
@@ -7142,7 +7178,7 @@
       <c r="F187" s="8"/>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H187" s="13" t="inlineStr">
@@ -7159,7 +7195,7 @@
       </c>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C188" s="8"/>
@@ -7168,7 +7204,7 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr">
@@ -7185,7 +7221,7 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C189" s="8"/>
@@ -7194,7 +7230,7 @@
       <c r="F189" s="8"/>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
@@ -7211,7 +7247,7 @@
       </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C190" s="8"/>
@@ -7220,7 +7256,7 @@
       <c r="F190" s="8"/>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H190" s="13" t="inlineStr">
@@ -7237,7 +7273,7 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C191" s="8"/>
@@ -7246,7 +7282,7 @@
       <c r="F191" s="8"/>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H191" s="13" t="inlineStr">
@@ -7263,7 +7299,7 @@
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C192" s="8"/>
@@ -7272,7 +7308,7 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
@@ -7289,7 +7325,7 @@
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C193" s="8"/>
@@ -7298,7 +7334,7 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H193" s="13" t="inlineStr">
@@ -7315,7 +7351,7 @@
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C194" s="8"/>
@@ -7324,7 +7360,7 @@
       <c r="F194" s="8"/>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H194" s="13" t="inlineStr">
@@ -7341,7 +7377,7 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -7350,7 +7386,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
@@ -7367,7 +7403,7 @@
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -7376,10 +7412,88 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">frequency (Hz)</t>
+        </is>
+      </c>
+      <c r="H196" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B197" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{P_INV_MW}</t>
+        </is>
+      </c>
+      <c r="C197" s="8"/>
+      <c r="D197" s="8"/>
+      <c r="E197" s="8"/>
+      <c r="F197" s="8"/>
+      <c r="G197" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+        </is>
+      </c>
+      <c r="H197" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B198" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
+        </is>
+      </c>
+      <c r="C198" s="8"/>
+      <c r="D198" s="8"/>
+      <c r="E198" s="8"/>
+      <c r="F198" s="8"/>
+      <c r="G198" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H198" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B199" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C199" s="8"/>
+      <c r="D199" s="8"/>
+      <c r="E199" s="8"/>
+      <c r="F199" s="8"/>
+      <c r="G199" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H196" s="13" t="inlineStr">
+      <c r="H199" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -7390,34 +7504,34 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="A113:H113"/>
-    <mergeCell ref="A125:H125"/>
-    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A116:H116"/>
+    <mergeCell ref="A128:H128"/>
     <mergeCell ref="A135:H135"/>
-    <mergeCell ref="A141:H141"/>
-    <mergeCell ref="A151:H151"/>
-    <mergeCell ref="A155:H155"/>
-    <mergeCell ref="A160:H160"/>
+    <mergeCell ref="A138:H138"/>
+    <mergeCell ref="A144:H144"/>
+    <mergeCell ref="A154:H154"/>
+    <mergeCell ref="A158:H158"/>
     <mergeCell ref="A163:H163"/>
-    <mergeCell ref="A167:H167"/>
-    <mergeCell ref="A179:H179"/>
+    <mergeCell ref="A166:H166"/>
+    <mergeCell ref="A170:H170"/>
+    <mergeCell ref="A182:H182"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
-    <hyperlink ref="A48" location="'MPT'!A1" display="MPT"/>
-    <hyperlink ref="A76" location="'Generators'!A1" display="Generators"/>
-    <hyperlink ref="A113" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A125" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A132" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A135" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A141" location="'Machines'!A1" display="Machines"/>
-    <hyperlink ref="A151" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A155" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A160" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A163" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A179" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A51" location="'MPT'!A1" display="MPT"/>
+    <hyperlink ref="A79" location="'Generators'!A1" display="Generators"/>
+    <hyperlink ref="A116" location="'Feeders'!A1" display="Feeders"/>
+    <hyperlink ref="A128" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A135" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A138" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A144" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A154" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A158" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A163" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A166" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A182" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -18126,26 +18240,28 @@
     <row r="6" ht="17.0" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frequency</t>
-        </is>
-      </c>
-      <c r="B6" s="3">
-        <v>60.0</v>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hz</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Build PSS/E .raw</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="C6" s="8"/>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
-        </is>
-      </c>
-      <c r="E6" s="8"/>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 60</t>
+          <t xml:space="preserve">YES = the load-flow case (blank = YES)</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
@@ -18157,18 +18273,28 @@
     <row r="7" ht="17.0" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">First bus number</t>
-        </is>
-      </c>
-      <c r="B7" s="3">
-        <v>1000</v>
+          <t xml:space="preserve">Build PSS/E .dyr</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
       </c>
       <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">buses are numbered from here + 1 (Bus_Numbers sets any one)</t>
+          <t xml:space="preserve">YES = the dynamic models (blank = YES)</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -18177,40 +18303,64 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI AND GRID (the infinite bus behind its Thevenin impedance)</t>
-        </is>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+    <row r="8" ht="17.0" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Build PSCAD model</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES = the PSCAD build script, its data and the .pscx (blank = YES)</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="17.0" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI kV</t>
+          <t xml:space="preserve">Frequency</t>
         </is>
       </c>
       <c r="B9" s="3">
-        <v>230.0</v>
+        <v>60.0</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kV</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">required</t>
+          <t xml:space="preserve">Hz</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = 60</t>
+        </is>
+      </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -18220,20 +18370,18 @@
     <row r="10" ht="17.0" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI name</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI</t>
-        </is>
+          <t xml:space="preserve">First bus number</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <v>1000</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 characters at most</t>
+          <t xml:space="preserve">buses are numbered from here + 1 (Bus_Numbers sets any one)</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -18242,44 +18390,38 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30.0" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grid SCR</t>
-        </is>
-      </c>
-      <c r="B11" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of SCR, short-circuit MVA or R + X</t>
-        </is>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POI AND GRID (the infinite bus behind its Thevenin impedance)</t>
+        </is>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" ht="17.0" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid X/R</t>
+          <t xml:space="preserve">POI kV</t>
         </is>
       </c>
       <c r="B12" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+        <v>230.0</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kV</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">required</t>
+        </is>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="2"/>
       <c r="G12" s="13" t="inlineStr">
@@ -18291,24 +18433,20 @@
     <row r="13" ht="17.0" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCR base</t>
-        </is>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MW</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the generators' Pmax</t>
-        </is>
-      </c>
+          <t xml:space="preserve">POI name</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POI</t>
+        </is>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the generators' Pmax</t>
+          <t xml:space="preserve">12 characters at most</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
@@ -18317,23 +18455,25 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="17.0" customHeight="1">
+    <row r="14" ht="30.0" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid short-circuit MVA</t>
-        </is>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
-      <c r="D14" s="8"/>
+          <t xml:space="preserve">Grid SCR</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of SCR, short-circuit MVA or R + X</t>
+        </is>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of the SCR (with Grid X/R)</t>
+          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -18345,22 +18485,16 @@
     <row r="15" ht="17.0" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid R</t>
-        </is>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Grid X/R</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">instead of the SCR: Thevenin R on the system base</t>
-        </is>
-      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -18370,20 +18504,24 @@
     <row r="16" ht="17.0" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid X</t>
+          <t xml:space="preserve">SCR base</t>
         </is>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
-      <c r="D16" s="8"/>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the generators' Pmax</t>
+        </is>
+      </c>
       <c r="E16" s="8"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of the SCR: Thevenin X on the system base</t>
+          <t xml:space="preserve">blank = the generators' Pmax</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -18392,38 +18530,48 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GEN-TIE (POI to the HV bus; blank = none)</t>
-        </is>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" ht="30.0" customHeight="1">
+    <row r="17" ht="17.0" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grid short-circuit MVA</t>
+        </is>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instead of the SCR (with Grid X/R)</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17.0" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie length</t>
-        </is>
-      </c>
-      <c r="B18" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no gen-tie (the MPTs on the POI bus</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Grid R</t>
+        </is>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu</t>
+        </is>
+      </c>
+      <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI to the substation HV bus; blank = no gen-tie (the MPTs on the POI bus)</t>
+          <t xml:space="preserve">instead of the SCR: Thevenin R on the system base</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -18435,28 +18583,20 @@
     <row r="19" ht="17.0" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie length unit</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Grid X</t>
+        </is>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu</t>
+        </is>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">km, mi, kft, m, ft (blank = km)</t>
+          <t xml:space="preserve">instead of the SCR: Thevenin X on the system base</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -18465,52 +18605,38 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="17.0" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gen-tie R per length</t>
-        </is>
-      </c>
-      <c r="B20" s="3">
-        <v>0.072</v>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one circuit, per length unit</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="17.0" customHeight="1">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEN-TIE (POI to the HV bus; blank = none)</t>
+        </is>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" ht="30.0" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie X per length</t>
+          <t xml:space="preserve">Gen-tie length</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <v>0.495</v>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
-      <c r="D21" s="8"/>
+        <v>5.0</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no gen-tie (the MPTs on the POI bus</t>
+        </is>
+      </c>
       <c r="E21" s="8"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit</t>
+          <t xml:space="preserve">POI to the substation HV bus; blank = no gen-tie (the MPTs on the POI bus)</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
@@ -18522,22 +18648,28 @@
     <row r="22" ht="17.0" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie B per length</t>
-        </is>
-      </c>
-      <c r="B22" s="3">
-        <v>3.35</v>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">uS</t>
-        </is>
-      </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+          <t xml:space="preserve">Gen-tie length unit</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit (total charging)</t>
+          <t xml:space="preserve">km, mi, kft, m, ft (blank = km)</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -18549,20 +18681,22 @@
     <row r="23" ht="17.0" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie C per length</t>
-        </is>
-      </c>
-      <c r="B23" s="3"/>
+          <t xml:space="preserve">Gen-tie R per length</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <v>0.072</v>
+      </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of B</t>
+          <t xml:space="preserve">one circuit, per length unit</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
@@ -18574,10 +18708,12 @@
     <row r="24" ht="17.0" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie R total</t>
-        </is>
-      </c>
-      <c r="B24" s="3"/>
+          <t xml:space="preserve">Gen-tie X per length</t>
+        </is>
+      </c>
+      <c r="B24" s="3">
+        <v>0.495</v>
+      </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm</t>
@@ -18587,7 +18723,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of per length (one circuit)</t>
+          <t xml:space="preserve">one circuit, per length unit</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -18599,18 +18735,24 @@
     <row r="25" ht="17.0" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie X total</t>
-        </is>
-      </c>
-      <c r="B25" s="3"/>
+          <t xml:space="preserve">Gen-tie B per length</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <v>3.35</v>
+      </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">uS</t>
         </is>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="2"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one circuit, per length unit (total charging)</t>
+        </is>
+      </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -18620,18 +18762,22 @@
     <row r="26" ht="17.0" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie B total</t>
+          <t xml:space="preserve">Gen-tie C per length</t>
         </is>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
+          <t xml:space="preserve">uF</t>
         </is>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="2"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instead of B</t>
+        </is>
+      </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -18641,22 +18787,20 @@
     <row r="27" ht="17.0" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie circuits</t>
-        </is>
-      </c>
-      <c r="B27" s="3">
-        <v>1</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Gen-tie R total</t>
+        </is>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical circuits in parallel (blank = 1)</t>
+          <t xml:space="preserve">instead of per length (one circuit)</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -18668,64 +18812,64 @@
     <row r="28" ht="17.0" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie rating</t>
-        </is>
-      </c>
-      <c r="B28" s="3">
-        <v>400.0</v>
-      </c>
+          <t xml:space="preserve">Gen-tie X total</t>
+        </is>
+      </c>
+      <c r="B28" s="3"/>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one circuit</t>
-        </is>
-      </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPERATING POINT (the load flow's targets at the POI)</t>
-        </is>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" ht="30.0" customHeight="1">
+    <row r="29" ht="17.0" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gen-tie B total</t>
+        </is>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uS</t>
+        </is>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17.0" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control mode</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q</t>
-        </is>
+          <t xml:space="preserve">Gen-tie circuits</t>
+        </is>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
       </c>
       <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q | PF | V</t>
-        </is>
-      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E30" s="8"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage</t>
+          <t xml:space="preserve">identical circuits in parallel (blank = 1)</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
@@ -18737,26 +18881,22 @@
     <row r="31" ht="17.0" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI voltage</t>
+          <t xml:space="preserve">Gen-tie rating</t>
         </is>
       </c>
       <c r="B31" s="3">
-        <v>1.0</v>
+        <v>400.0</v>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.0</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
+      <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
+          <t xml:space="preserve">one circuit</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -18765,52 +18905,40 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="17.0" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q at POI</t>
-        </is>
-      </c>
-      <c r="B32" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVAr</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17.0" customHeight="1">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPERATING POINT (the load flow's targets at the POI)</t>
+        </is>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" ht="30.0" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PF at POI</t>
-        </is>
-      </c>
-      <c r="B33" s="3">
-        <v>1.0</v>
+          <t xml:space="preserve">Control mode</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q</t>
+        </is>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q | PF | V</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
+          <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
@@ -18822,7 +18950,7 @@
     <row r="34" ht="17.0" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid voltage</t>
+          <t xml:space="preserve">POI voltage</t>
         </is>
       </c>
       <c r="B34" s="3">
@@ -18841,7 +18969,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
+          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
@@ -18850,27 +18978,29 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="30.0" customHeight="1">
+    <row r="35" ht="17.0" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at POI</t>
-        </is>
-      </c>
-      <c r="B35" s="3"/>
+          <t xml:space="preserve">Q at POI</t>
+        </is>
+      </c>
+      <c r="B35" s="3">
+        <v>0.0</v>
+      </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each generator at its dispatch</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
+          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -18879,89 +19009,93 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANT CONTROLLER (PSS/E .dyr)</t>
-        </is>
-      </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-    </row>
-    <row r="37" ht="30.0" customHeight="1">
+    <row r="36" ht="17.0" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PF at POI</t>
+        </is>
+      </c>
+      <c r="B36" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17.0" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plant controller</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPC_B</t>
-        </is>
-      </c>
-      <c r="C37" s="8"/>
+          <t xml:space="preserve">Grid voltage</t>
+        </is>
+      </c>
+      <c r="B37" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu</t>
+        </is>
+      </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REPC_A</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPC_A | REPC_B</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="E37" s="8"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
+          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30.0" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGC_A / REPC_A records</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">standard</t>
-        </is>
-      </c>
-      <c r="C38" s="8"/>
+          <t xml:space="preserve">P at POI</t>
+        </is>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">standard | USRMDL</t>
-        </is>
-      </c>
+          <t xml:space="preserve">each generator at its dispatch</t>
+        </is>
+      </c>
+      <c r="E38" s="8"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard: REGCA1 / REPCA1 (PSS/E library) | USRMDL: REGCAU1 / REPCAU1 (the WECC user-model DLL) (blank = standard)</t>
+          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD RUN</t>
+          <t xml:space="preserve">PLANT CONTROLLER (PSS/E .dyr)</t>
         </is>
       </c>
       <c r="B39" s="7"/>
@@ -18971,178 +19105,182 @@
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
     </row>
-    <row r="40" ht="43.0" customHeight="1">
+    <row r="40" ht="30.0" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Plant controller</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REPC_B</t>
+        </is>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REPC_A</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REPC_A | REPC_B</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGC_A / REPC_A records</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard | USRMDL</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard: REGCA1 / REPCA1 (PSS/E library) | USRMDL: REGCAU1 / REPCAU1 (the WECC user-model DLL) (blank = standard)</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD RUN</t>
+        </is>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+    </row>
+    <row r="43" ht="43.0" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD time step</t>
         </is>
       </c>
-      <c r="B40" s="3">
+      <c r="B43" s="3">
         <v>10.0</v>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">us</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10 (the vendor model's own requirement wins</t>
         </is>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="E43" s="8"/>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 10 (the vendor model's own requirement wins)</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="17.0" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="44" ht="17.0" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD duration</t>
         </is>
       </c>
-      <c r="B41" s="3">
+      <c r="B44" s="3">
         <v>5.0</v>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">s</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="E44" s="8"/>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 5</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="17.0" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+    <row r="45" ht="17.0" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD plot step</t>
         </is>
       </c>
-      <c r="B42" s="3">
+      <c r="B45" s="3">
         <v>100.0</v>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">us</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">100</t>
         </is>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E45" s="8"/>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 100</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="17.0" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="46" ht="17.0" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD meter at POI</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
-        </is>
-      </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES | NO</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="43.0" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD lines as</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI</t>
-        </is>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI | RLC</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
-        </is>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD FAULT AT THE POI</t>
-        </is>
-      </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-    </row>
-    <row r="46" ht="30.0" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault at POI</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -19159,100 +19297,82 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="43.0" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD lines as</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI | RLC</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD FAULT AT THE POI</t>
+        </is>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+    </row>
+    <row r="49" ht="30.0" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault at POI</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
-        </is>
-      </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="17.0" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault time</t>
-        </is>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100: none in the run</t>
-        </is>
-      </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
-        </is>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="17.0" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault duration</t>
-        </is>
-      </c>
-      <c r="B48" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.15</t>
-        </is>
-      </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 0.15</t>
-        </is>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="43.0" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault type</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ABCG</t>
-        </is>
-      </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ABCG</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -19264,63 +19384,156 @@
     <row r="50" ht="17.0" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault resistance</t>
-        </is>
-      </c>
-      <c r="B50" s="3">
-        <v>0.01</v>
-      </c>
+          <t xml:space="preserve">PSCAD fault time</t>
+        </is>
+      </c>
+      <c r="B50" s="3"/>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">s</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.01</t>
+          <t xml:space="preserve">100: none in the run</t>
         </is>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17.0" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault duration</t>
+        </is>
+      </c>
+      <c r="B51" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
+      <c r="E51" s="8"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = 0.15</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="43.0" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault type</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABCG</t>
+        </is>
+      </c>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABCG</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17.0" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault resistance</t>
+        </is>
+      </c>
+      <c r="B53" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.01</t>
+        </is>
+      </c>
+      <c r="E53" s="8"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 0.01</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD LIBRARIES</t>
         </is>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-    </row>
-    <row r="52" ht="17.0" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+    </row>
+    <row r="55" ht="17.0" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD libraries</t>
         </is>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="B55" s="3"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -19329,40 +19542,49 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A54:G54"/>
   </mergeCells>
-  <dataValidations count="9">
+  <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4">
       <formula1>"SMIB,DETAILED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B6">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B7">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B8">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B22">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B30">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B33">
       <formula1>"Q,PF,V"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B37">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B40">
       <formula1>"REPC_A,REPC_B"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B38">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B41">
       <formula1>"standard,USRMDL"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B43">
-      <formula1>"YES,NO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B44">
-      <formula1>"PI,RLC"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B46">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B47">
+      <formula1>"PI,RLC"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B49">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B52">
       <formula1>"ABCG,ABC,AG,BG,CG,ABG,BCG,ACG,AB,BC,AC"</formula1>
     </dataValidation>
   </dataValidations>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -825,7 +825,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="108.0" customHeight="1">
+    <row r="53" ht="160.0" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
@@ -833,7 +833,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">The .pscx is built in the same run when PSCAD 5 and its Python library mhi.pscad (pip install mhi.pscad) are on the PC; otherwise run &lt;name&gt;_build_pscad.py where they are. The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and wire your UDM in its place (the report and the build log list every inverter node). PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn. It is drawn as a single-line diagram with wires, left to right from the grid; where PSCAD's R, L and C are single-phase, each is drawn three times between breakouts.</t>
+          <t xml:space="preserve">The .pscx is built in the same run when PSCAD 5 and its Python library mhi.pscad (pip install mhi.pscad) are on the PC; otherwise run &lt;name&gt;_build_pscad.py where they are. The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and wire your UDM in its place (the report and the build log list every inverter node). Or set one UDM up in a case of its own (a vendor's test case) and give that case and the UDM's component ID (its Properties) in Generators: PSCAD source case, PSCAD component ID -- it is copied, with its settings, to every GSU of that generator (every machine of the DETAILED model), its definition and the case's resources (.lib, .obj) with it; PSCAD_Params rows ({UNITS}, {P_PU} ...) are set on each copy. PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn. It is drawn as a single-line diagram with wires, left to right from the grid; where PSCAD's R, L and C are single-phase, each is drawn three times between breakouts.</t>
         </is>
       </c>
     </row>
@@ -5269,109 +5269,109 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD source case</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_source</t>
+        </is>
+      </c>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a .pscx or .pslx (or a project open in PSCAD) with one UDM set up as you want it (with PSCAD component ID)</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="17.0" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD component ID</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_component_id</t>
+        </is>
+      </c>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">that UDM's ID in the source case: copied, with its settings, to every GSU of this generator</t>
+        </is>
+      </c>
+      <c r="H116" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="30.0" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD inverter at</t>
         </is>
       </c>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_inv_at</t>
         </is>
       </c>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8" t="inlineStr">
+      <c r="D117" s="8"/>
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV</t>
         </is>
       </c>
-      <c r="F115" s="8" t="inlineStr">
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV | MV</t>
         </is>
       </c>
-      <c r="G115" s="8" t="inlineStr">
+      <c r="G117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
       </c>
-      <c r="H115" s="13" t="inlineStr">
+      <c r="H117" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-    </row>
-    <row r="117" ht="17.0" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B117" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collector</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collector</t>
-        </is>
-      </c>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
-        </is>
-      </c>
-      <c r="H117" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="17.0" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B118" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeder</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feeder</t>
-        </is>
-      </c>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feeder name</t>
-        </is>
-      </c>
-      <c r="H118" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B118" s="7"/>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
     </row>
     <row r="119" ht="17.0" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
@@ -5381,24 +5381,20 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copies</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">copies</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D119" s="8"/>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E119" s="8"/>
       <c r="F119" s="8"/>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
+          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
@@ -5415,12 +5411,12 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section</t>
+          <t xml:space="preserve">Feeder</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">section</t>
+          <t xml:space="preserve">feeder</t>
         </is>
       </c>
       <c r="D120" s="8"/>
@@ -5428,7 +5424,7 @@
       <c r="F120" s="8"/>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+          <t xml:space="preserve">feeder name</t>
         </is>
       </c>
       <c r="H120" s="13" t="inlineStr">
@@ -5437,7 +5433,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="30.0" customHeight="1">
+    <row r="121" ht="17.0" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5445,24 +5441,24 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">From section</t>
+          <t xml:space="preserve">Copies</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_section</t>
+          <t xml:space="preserve">copies</t>
         </is>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the one before (daisy chain</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F121" s="8"/>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+          <t xml:space="preserve">identical feeders (blank = 1)</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
@@ -5479,12 +5475,12 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">Section</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">section</t>
         </is>
       </c>
       <c r="D122" s="8"/>
@@ -5492,7 +5488,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Cables</t>
+          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
@@ -5501,7 +5497,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="17.0" customHeight="1">
+    <row r="123" ht="30.0" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5509,18 +5505,26 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length</t>
+          <t xml:space="preserve">From section</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">length</t>
+          <t xml:space="preserve">from_section</t>
         </is>
       </c>
       <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the one before (daisy chain</t>
+        </is>
+      </c>
       <c r="F123" s="8"/>
-      <c r="G123" s="8"/>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+        </is>
+      </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5535,28 +5539,20 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D124" s="8"/>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+      <c r="E124" s="8"/>
+      <c r="F124" s="8"/>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = km</t>
+          <t xml:space="preserve">from Cables</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
@@ -5573,22 +5569,18 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units at end</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">length</t>
         </is>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">units tapped at the far end</t>
-        </is>
-      </c>
+      <c r="G125" s="8"/>
       <c r="H125" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5603,20 +5595,28 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units of</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units_of</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
+          <t xml:space="preserve">blank = km</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
@@ -5633,24 +5633,20 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel cables</t>
+          <t xml:space="preserve">Units at end</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parallel</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D127" s="8"/>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E127" s="8"/>
       <c r="F127" s="8"/>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">units tapped at the far end</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
@@ -5659,42 +5655,62 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B128" s="7"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
+    <row r="128" ht="17.0" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units of</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">units_of</t>
+        </is>
+      </c>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
+        </is>
+      </c>
+      <c r="H128" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="17.0" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">Parallel cables</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">parallel</t>
         </is>
       </c>
       <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F129" s="8"/>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable type</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -5703,39 +5719,19 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="17.0" customHeight="1">
-      <c r="A130" s="8" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B130" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Length unit</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unit</t>
-        </is>
-      </c>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the values are per</t>
-        </is>
-      </c>
-      <c r="H130" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B130" s="7"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
+      <c r="G130" s="7"/>
+      <c r="H130" s="7"/>
     </row>
     <row r="131" ht="17.0" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
@@ -5745,12 +5741,12 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R per length</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_per</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D131" s="8"/>
@@ -5758,7 +5754,7 @@
       <c r="F131" s="8"/>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
+          <t xml:space="preserve">cable type</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
@@ -5775,20 +5771,24 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">the values are per</t>
         </is>
       </c>
       <c r="H132" s="13" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D133" s="8"/>
@@ -5818,7 +5818,7 @@
       <c r="F133" s="8"/>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">X per length</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">x_per</t>
         </is>
       </c>
       <c r="D134" s="8"/>
@@ -5848,7 +5848,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS, instead of C</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
@@ -5857,34 +5857,50 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
+    <row r="135" ht="17.0" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C per length</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c_per</t>
+        </is>
+      </c>
+      <c r="D135" s="8"/>
+      <c r="E135" s="8"/>
+      <c r="F135" s="8"/>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uF</t>
+        </is>
+      </c>
+      <c r="H135" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="17.0" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">B per length</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">b_per</t>
         </is>
       </c>
       <c r="D136" s="8"/>
@@ -5892,85 +5908,81 @@
       <c r="F136" s="8"/>
       <c r="G136" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">uS, instead of C</t>
+        </is>
+      </c>
+      <c r="H136" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collectors</t>
+        </is>
+      </c>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
+    </row>
+    <row r="138" ht="17.0" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collectors</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D138" s="8"/>
+      <c r="E138" s="8"/>
+      <c r="F138" s="8"/>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">shared collector: its far-end bus has this name</t>
         </is>
       </c>
-      <c r="H136" s="13" t="inlineStr">
+      <c r="H138" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
-    </row>
-    <row r="137" ht="17.0" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B137" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connect to</t>
-        </is>
-      </c>
-      <c r="C137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">connect</t>
-        </is>
-      </c>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
-        </is>
-      </c>
-      <c r="H137" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loads_Shunts</t>
-        </is>
-      </c>
-      <c r="B138" s="7"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
     </row>
     <row r="139" ht="17.0" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
-      <c r="F139" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
+      <c r="F139" s="8"/>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
+          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
@@ -5979,35 +5991,19 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="17.0" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B140" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">At bus</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">at</t>
-        </is>
-      </c>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
-      <c r="G140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
-        </is>
-      </c>
-      <c r="H140" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B140" s="7"/>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
     </row>
     <row r="141" ht="17.0" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
@@ -6017,20 +6013,24 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mw</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D142" s="8"/>
@@ -6060,7 +6060,7 @@
       <c r="F142" s="8"/>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -6077,101 +6077,97 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">MW</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">mw</t>
         </is>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
-      <c r="G143" s="8"/>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
+        </is>
+      </c>
       <c r="H143" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B144" s="7"/>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
-      <c r="G144" s="7"/>
-      <c r="H144" s="7"/>
-    </row>
-    <row r="145" ht="30.0" customHeight="1">
+    <row r="144" ht="17.0" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVAr</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mvar</t>
+        </is>
+      </c>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+        </is>
+      </c>
+      <c r="H144" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="17.0" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">machine</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
-        </is>
-      </c>
+      <c r="G145" s="8"/>
       <c r="H145" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="17.0" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B146" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its generator's</t>
-        </is>
-      </c>
-      <c r="F146" s="8"/>
-      <c r="G146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = its generator's</t>
-        </is>
-      </c>
-      <c r="H146" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
     </row>
     <row r="147" ht="30.0" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
@@ -6181,24 +6177,20 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pgen MW</t>
+          <t xml:space="preserve">Machine</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pgen_mw</t>
+          <t xml:space="preserve">machine</t>
         </is>
       </c>
       <c r="D147" s="8"/>
-      <c r="E147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
-        </is>
-      </c>
+      <c r="E147" s="8"/>
       <c r="F147" s="8"/>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -6215,24 +6207,24 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax MW</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmax_mw</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmax</t>
+          <t xml:space="preserve">its generator's</t>
         </is>
       </c>
       <c r="F148" s="8"/>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
@@ -6241,7 +6233,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="17.0" customHeight="1">
+    <row r="149" ht="30.0" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6249,24 +6241,24 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmin MW</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmin_mw</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D149" s="8"/>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmin</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F149" s="8"/>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H149" s="13" t="inlineStr">
@@ -6283,24 +6275,24 @@
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmax MVAr</t>
+          <t xml:space="preserve">Pmax MW</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmax_mvar</t>
+          <t xml:space="preserve">pmax_mw</t>
         </is>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmax</t>
+          <t xml:space="preserve">its units x Unit Pmax</t>
         </is>
       </c>
       <c r="F150" s="8"/>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
         </is>
       </c>
       <c r="H150" s="13" t="inlineStr">
@@ -6317,24 +6309,24 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmin MVAr</t>
+          <t xml:space="preserve">Pmin MW</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmin_mvar</t>
+          <t xml:space="preserve">pmin_mw</t>
         </is>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmin</t>
+          <t xml:space="preserve">its units x Unit Pmin</t>
         </is>
       </c>
       <c r="F151" s="8"/>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -6343,7 +6335,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="30.0" customHeight="1">
+    <row r="152" ht="17.0" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6351,24 +6343,24 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mvar</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as its generator's Q mode</t>
+          <t xml:space="preserve">its units x Unit Qmax</t>
         </is>
       </c>
       <c r="F152" s="8"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -6385,24 +6377,24 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBASE MVA</t>
+          <t xml:space="preserve">Qmin MVAr</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mbase_mva</t>
+          <t xml:space="preserve">qmin_mvar</t>
         </is>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit MVA</t>
+          <t xml:space="preserve">its units x Unit Qmin</t>
         </is>
       </c>
       <c r="F153" s="8"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit MVA</t>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
@@ -6411,42 +6403,66 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="18" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B154" s="7"/>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
-      <c r="F154" s="7"/>
-      <c r="G154" s="7"/>
-      <c r="H154" s="7"/>
+    <row r="154" ht="30.0" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed Q MVAr</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q_mvar</t>
+        </is>
+      </c>
+      <c r="D154" s="8"/>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as its generator's Q mode</t>
+        </is>
+      </c>
+      <c r="F154" s="8"/>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+        </is>
+      </c>
+      <c r="H154" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="17.0" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus</t>
+          <t xml:space="preserve">MBASE MVA</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bus</t>
+          <t xml:space="preserve">mbase_mva</t>
         </is>
       </c>
       <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit MVA</t>
+        </is>
+      </c>
       <c r="F155" s="8"/>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+          <t xml:space="preserve">blank = its units x Unit MVA</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
@@ -6455,41 +6471,21 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="17.0" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B156" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number</t>
-        </is>
-      </c>
-      <c r="C156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic</t>
-        </is>
-      </c>
-      <c r="F156" s="8"/>
-      <c r="G156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = automatic</t>
-        </is>
-      </c>
-      <c r="H156" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="30.0" customHeight="1">
+      <c r="B156" s="7"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+    </row>
+    <row r="157" ht="17.0" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
@@ -6497,24 +6493,20 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Bus</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">bus</t>
         </is>
       </c>
       <c r="D157" s="8"/>
-      <c r="E157" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
-        </is>
-      </c>
+      <c r="E157" s="8"/>
       <c r="F157" s="8"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
@@ -6523,79 +6515,87 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="7"/>
-      <c r="H158" s="7"/>
-    </row>
-    <row r="159" ht="17.0" customHeight="1">
+    <row r="158" ht="17.0" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D158" s="8"/>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic</t>
+        </is>
+      </c>
+      <c r="F158" s="8"/>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = automatic</t>
+        </is>
+      </c>
+      <c r="H158" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="30.0" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
       <c r="F159" s="8"/>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
         </is>
       </c>
       <c r="H159" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="30.0" customHeight="1">
-      <c r="A160" s="8" t="inlineStr">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B160" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Model</t>
-        </is>
-      </c>
-      <c r="C160" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">model</t>
-        </is>
-      </c>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
-      <c r="F160" s="8"/>
-      <c r="G160" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
-        </is>
-      </c>
-      <c r="H160" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
+      <c r="B160" s="7"/>
+      <c r="C160" s="7"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
     </row>
     <row r="161" ht="17.0" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D161" s="8"/>
@@ -6618,7 +6618,7 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
@@ -6627,7 +6627,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="17.0" customHeight="1">
+    <row r="162" ht="30.0" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
@@ -6635,171 +6635,175 @@
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Model</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
-      <c r="G162" s="8"/>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+        </is>
+      </c>
       <c r="H162" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B163" s="7"/>
-      <c r="C163" s="7"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
-      <c r="G163" s="7"/>
-      <c r="H163" s="7"/>
+    <row r="163" ht="17.0" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
+      <c r="D163" s="8"/>
+      <c r="E163" s="8"/>
+      <c r="F163" s="8"/>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+        </is>
+      </c>
+      <c r="H163" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="17.0" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D164" s="8"/>
+      <c r="E164" s="8"/>
+      <c r="F164" s="8"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
-      <c r="B164" s="12" t="inlineStr">
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
+      <c r="H165" s="7"/>
+    </row>
+    <row r="166" ht="17.0" customHeight="1">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Generator</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C166" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">generator</t>
         </is>
       </c>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8" t="inlineStr">
+      <c r="D166" s="8"/>
+      <c r="E166" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">the plant</t>
         </is>
       </c>
-      <c r="F164" s="8"/>
-      <c r="G164" s="8" t="inlineStr">
+      <c r="F166" s="8"/>
+      <c r="G166" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = the plant</t>
         </is>
       </c>
-      <c r="H164" s="13" t="inlineStr">
+      <c r="H166" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
-    </row>
-    <row r="165" ht="17.0" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B165" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Record</t>
-        </is>
-      </c>
-      <c r="C165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">record</t>
-        </is>
-      </c>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
-        </is>
-      </c>
-      <c r="H165" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B166" s="7"/>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="7"/>
-      <c r="H166" s="7"/>
     </row>
     <row r="167" ht="17.0" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Record</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">record</t>
         </is>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
-      <c r="G167" s="8"/>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
+        </is>
+      </c>
       <c r="H167" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="17.0" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B168" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parameter</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parameter</t>
-        </is>
-      </c>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
-      <c r="F168" s="8"/>
-      <c r="G168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
-        </is>
-      </c>
-      <c r="H168" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
+      <c r="H168" s="7"/>
     </row>
     <row r="169" ht="17.0" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
@@ -6809,83 +6813,103 @@
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
-      <c r="G169" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
-        </is>
-      </c>
+      <c r="G169" s="8"/>
       <c r="H169" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
-        </is>
-      </c>
-      <c r="B170" s="7"/>
-      <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
-      <c r="G170" s="7"/>
-      <c r="H170" s="7"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="8"/>
+    <row r="170" ht="17.0" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
+      <c r="D170" s="8"/>
+      <c r="E170" s="8"/>
+      <c r="F170" s="8"/>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H170" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="17.0" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C171" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H171" s="8"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="8"/>
-      <c r="B172" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI</t>
-        </is>
-      </c>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
-      <c r="F172" s="8"/>
-      <c r="G172" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the point of interconnection</t>
-        </is>
-      </c>
-      <c r="H172" s="8"/>
+          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+        </is>
+      </c>
+      <c r="H171" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
+        </is>
+      </c>
+      <c r="B172" s="7"/>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7"/>
+      <c r="G172" s="7"/>
+      <c r="H172" s="7"/>
     </row>
     <row r="173">
       <c r="A173" s="8"/>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C173" s="8"/>
@@ -6894,7 +6918,7 @@
       <c r="F173" s="8"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H173" s="8"/>
@@ -6903,7 +6927,7 @@
       <c r="A174" s="8"/>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C174" s="8"/>
@@ -6912,7 +6936,7 @@
       <c r="F174" s="8"/>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H174" s="8"/>
@@ -6921,7 +6945,7 @@
       <c r="A175" s="8"/>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C175" s="8"/>
@@ -6930,7 +6954,7 @@
       <c r="F175" s="8"/>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
         </is>
       </c>
       <c r="H175" s="8"/>
@@ -6939,7 +6963,7 @@
       <c r="A176" s="8"/>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C176" s="8"/>
@@ -6948,7 +6972,7 @@
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+          <t xml:space="preserve">an MPT's LV winding</t>
         </is>
       </c>
       <c r="H176" s="8"/>
@@ -6957,7 +6981,7 @@
       <c r="A177" s="8"/>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C177" s="8"/>
@@ -6966,7 +6990,7 @@
       <c r="F177" s="8"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
         </is>
       </c>
       <c r="H177" s="8"/>
@@ -6975,7 +6999,7 @@
       <c r="A178" s="8"/>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C178" s="8"/>
@@ -6984,7 +7008,7 @@
       <c r="F178" s="8"/>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
         </is>
       </c>
       <c r="H178" s="8"/>
@@ -6993,7 +7017,7 @@
       <c r="A179" s="8"/>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C179" s="8"/>
@@ -7002,7 +7026,7 @@
       <c r="F179" s="8"/>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H179" s="8"/>
@@ -7011,7 +7035,7 @@
       <c r="A180" s="8"/>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C180" s="8"/>
@@ -7020,7 +7044,7 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H180" s="8"/>
@@ -7029,7 +7053,7 @@
       <c r="A181" s="8"/>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -7038,34 +7062,34 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+          <t xml:space="preserve">a generator's terminal</t>
         </is>
       </c>
       <c r="H181" s="8"/>
     </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
-        </is>
-      </c>
-      <c r="B182" s="7"/>
-      <c r="C182" s="7"/>
-      <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
-      <c r="F182" s="7"/>
-      <c r="G182" s="7"/>
-      <c r="H182" s="7"/>
+    <row r="182">
+      <c r="A182" s="8"/>
+      <c r="B182" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+        </is>
+      </c>
+      <c r="C182" s="8"/>
+      <c r="D182" s="8"/>
+      <c r="E182" s="8"/>
+      <c r="F182" s="8"/>
+      <c r="G182" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H182" s="8"/>
     </row>
     <row r="183">
-      <c r="A183" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A183" s="8"/>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNITS}</t>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -7074,40 +7098,24 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H183" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B184" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{MVA}</t>
-        </is>
-      </c>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
-      <c r="F184" s="8"/>
-      <c r="G184" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">their MVA</t>
-        </is>
-      </c>
-      <c r="H184" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+        </is>
+      </c>
+      <c r="H183" s="8"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
+        </is>
+      </c>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="7"/>
+      <c r="H184" s="7"/>
     </row>
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
@@ -7117,7 +7125,7 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_MW}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -7126,7 +7134,7 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H185" s="13" t="inlineStr">
@@ -7143,7 +7151,7 @@
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C186" s="8"/>
@@ -7152,7 +7160,7 @@
       <c r="F186" s="8"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H186" s="13" t="inlineStr">
@@ -7169,7 +7177,7 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C187" s="8"/>
@@ -7178,7 +7186,7 @@
       <c r="F187" s="8"/>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H187" s="13" t="inlineStr">
@@ -7195,7 +7203,7 @@
       </c>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C188" s="8"/>
@@ -7204,7 +7212,7 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr">
@@ -7221,7 +7229,7 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C189" s="8"/>
@@ -7230,7 +7238,7 @@
       <c r="F189" s="8"/>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
@@ -7247,7 +7255,7 @@
       </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C190" s="8"/>
@@ -7256,7 +7264,7 @@
       <c r="F190" s="8"/>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H190" s="13" t="inlineStr">
@@ -7273,7 +7281,7 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C191" s="8"/>
@@ -7282,7 +7290,7 @@
       <c r="F191" s="8"/>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H191" s="13" t="inlineStr">
@@ -7299,7 +7307,7 @@
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C192" s="8"/>
@@ -7308,7 +7316,7 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
@@ -7325,7 +7333,7 @@
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C193" s="8"/>
@@ -7334,7 +7342,7 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H193" s="13" t="inlineStr">
@@ -7351,7 +7359,7 @@
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C194" s="8"/>
@@ -7360,7 +7368,7 @@
       <c r="F194" s="8"/>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H194" s="13" t="inlineStr">
@@ -7377,7 +7385,7 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -7386,7 +7394,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
@@ -7403,7 +7411,7 @@
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -7412,7 +7420,7 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
@@ -7429,7 +7437,7 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C197" s="8"/>
@@ -7438,7 +7446,7 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H197" s="13" t="inlineStr">
@@ -7455,7 +7463,7 @@
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C198" s="8"/>
@@ -7464,7 +7472,7 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">frequency (Hz)</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr">
@@ -7481,7 +7489,7 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{P_INV_MW}</t>
         </is>
       </c>
       <c r="C199" s="8"/>
@@ -7490,10 +7498,62 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+        </is>
+      </c>
+      <c r="H199" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B200" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
+        </is>
+      </c>
+      <c r="C200" s="8"/>
+      <c r="D200" s="8"/>
+      <c r="E200" s="8"/>
+      <c r="F200" s="8"/>
+      <c r="G200" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H200" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B201" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C201" s="8"/>
+      <c r="D201" s="8"/>
+      <c r="E201" s="8"/>
+      <c r="F201" s="8"/>
+      <c r="G201" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H199" s="13" t="inlineStr">
+      <c r="H201" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -7506,32 +7566,32 @@
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A116:H116"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A135:H135"/>
-    <mergeCell ref="A138:H138"/>
-    <mergeCell ref="A144:H144"/>
-    <mergeCell ref="A154:H154"/>
-    <mergeCell ref="A158:H158"/>
-    <mergeCell ref="A163:H163"/>
-    <mergeCell ref="A166:H166"/>
-    <mergeCell ref="A170:H170"/>
-    <mergeCell ref="A182:H182"/>
+    <mergeCell ref="A118:H118"/>
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A137:H137"/>
+    <mergeCell ref="A140:H140"/>
+    <mergeCell ref="A146:H146"/>
+    <mergeCell ref="A156:H156"/>
+    <mergeCell ref="A160:H160"/>
+    <mergeCell ref="A165:H165"/>
+    <mergeCell ref="A168:H168"/>
+    <mergeCell ref="A172:H172"/>
+    <mergeCell ref="A184:H184"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
     <hyperlink ref="A51" location="'MPT'!A1" display="MPT"/>
     <hyperlink ref="A79" location="'Generators'!A1" display="Generators"/>
-    <hyperlink ref="A116" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A128" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A135" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A138" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A144" location="'Machines'!A1" display="Machines"/>
-    <hyperlink ref="A154" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A158" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A163" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A166" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A182" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A118" location="'Feeders'!A1" display="Feeders"/>
+    <hyperlink ref="A130" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A137" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A140" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A146" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A156" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A160" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A165" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A168" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A184" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -20544,7 +20604,9 @@
     <col min="33" max="33" width="18" customWidth="1"/>
     <col min="34" max="34" width="16" customWidth="1"/>
     <col min="35" max="35" width="10" customWidth="1"/>
-    <col min="36" max="36" width="10" customWidth="1"/>
+    <col min="36" max="36" width="18" customWidth="1"/>
+    <col min="37" max="37" width="10" customWidth="1"/>
+    <col min="38" max="38" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -20725,6 +20787,16 @@
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD source case</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD component ID</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD inverter at</t>
         </is>
       </c>
@@ -20886,6 +20958,16 @@
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a .pscx or .pslx (or a project open in PSCAD) with one UDM set up as you want it (with PSCAD component ID)</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">that UDM's ID in the source case: copied, with its settings, to every GSU of this generator</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
@@ -20983,7 +21065,9 @@
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">LV</t>
         </is>
@@ -21081,7 +21165,9 @@
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
-      <c r="AJ4" s="3" t="inlineStr">
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">LV</t>
         </is>
@@ -21124,6 +21210,8 @@
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
+      <c r="AK5" s="3"/>
+      <c r="AL5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3"/>
@@ -21162,6 +21250,8 @@
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3"/>
@@ -21200,6 +21290,8 @@
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3"/>
@@ -21238,6 +21330,8 @@
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3"/>
@@ -21276,6 +21370,8 @@
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
@@ -21314,6 +21410,8 @@
       <c r="AH10" s="3"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3"/>
@@ -21352,6 +21450,8 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
@@ -21390,6 +21490,8 @@
       <c r="AH12" s="3"/>
       <c r="AI12" s="3"/>
       <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -21428,6 +21530,8 @@
       <c r="AH13" s="3"/>
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -21466,6 +21570,8 @@
       <c r="AH14" s="3"/>
       <c r="AI14" s="3"/>
       <c r="AJ14" s="3"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -21504,6 +21610,8 @@
       <c r="AH15" s="3"/>
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -21542,6 +21650,8 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -21580,6 +21690,8 @@
       <c r="AH17" s="3"/>
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -21618,6 +21730,8 @@
       <c r="AH18" s="3"/>
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -21656,6 +21770,8 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -21694,6 +21810,8 @@
       <c r="AH20" s="3"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -21732,6 +21850,8 @@
       <c r="AH21" s="3"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
+      <c r="AK21" s="3"/>
+      <c r="AL21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -21770,6 +21890,8 @@
       <c r="AH22" s="3"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -21788,7 +21910,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF3:AF500">
       <formula1>"REEC_A,REEC_C,REEC_D"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AJ3:AJ500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AL3:AL500">
       <formula1>"LV,MV"</formula1>
     </dataValidation>
   </dataValidations>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -717,7 +717,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="56.0" customHeight="1">
+    <row r="44" ht="82.0" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -725,7 +725,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">The collector feeders section by section from the collector bus out: cable, length and the units tapped at the section's far end. A daisy chain needs no From section; a lateral names the section it leaves from (its far end); 0 = straight from the collector bus. Copies: identical feeders. WECC equivalent: Zeq = sum(Zi Wi^2) / W^2, Beq = sum(Bi), Wi = MW of the units downstream of section i.</t>
+          <t xml:space="preserve">The collector feeders section by section from the collector bus out: cable, length and the units tapped at the section's far end. A daisy chain needs no From section; a lateral names the section it leaves from (its far end); 0 = straight from the collector bus. Copies: identical feeders. WECC equivalent: Zeq = sum(Zi Wi^2) / W^2, Beq = sum(Bi), Wi = MW of the units downstream of section i. R ohm, X ohm, B uS: a section's own values (its parallel cables together) in place of Cable x Length -- the GUI's Fill R, X, B from cables shows them to change; Clear R, X, B goes back. A section with R and X needs no cable.</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">The .pscx is built in the same run when PSCAD 5 and its Python library mhi.pscad (pip install mhi.pscad) are on the PC; otherwise run &lt;name&gt;_build_pscad.py where they are. The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and wire your UDM in its place (the report and the build log list every inverter node). Or set one UDM up in a case of its own (a vendor's test case) and give that case and the UDM's component ID (its Properties) in Generators: PSCAD source case, PSCAD component ID -- it is copied, with its settings, to every GSU of that generator (every machine of the DETAILED model), its definition and the case's resources (.lib, .obj) with it; PSCAD_Params rows ({UNITS}, {P_PU} ...) are set on each copy. PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn. It is drawn as a single-line diagram with wires, left to right from the grid; where PSCAD's R, L and C are single-phase, each is drawn three times between breakouts.</t>
+          <t xml:space="preserve">The .pscx is built in the same run when PSCAD 5 and its Python library mhi.pscad (pip install mhi.pscad) are on the PC; otherwise run &lt;name&gt;_build_pscad.py where they are. The case holds the grid (source and Thevenin impedance), the gen-tie, the MPTs, each collector (the WECC equivalent as a pi section, or DETAILED: every feeder section, identical feeder copies lumped), the GSUs and, on each GSU's LV side, the inverter: your UDM (PSCAD library, definition and AC port in Generators) or a stand-in source at the solved voltage -- delete it and wire your UDM in its place (the report and the build log list every inverter node). Or take the UDM from the OEM's PSCAD model: Generators, Pick UDM from OEM model -- the model's definitions are listed (their ports, parameters and the IDs of the ones placed in it); the one picked is added to the case's definitions (with the ones it uses and the model's resources, .lib / .obj) and put at every GSU of that generator (every machine of the DETAILED model), PSCAD_Params rows ({UNITS}, {P_PU} ...) set on each; or, with a component ID, that placed one is copied instead, its settings and all. PSCAD inverter at MV: for a UDM with its GSU inside, the inverter on the GSU's HV side and no GSU drawn. It is drawn as a single-line diagram with wires, left to right from the grid; where PSCAD's R, L and C are single-phase, each is drawn three times between breakouts.</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       <c r="F115" s="8"/>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a .pscx or .pslx (or a project open in PSCAD) with one UDM set up as you want it (with PSCAD component ID)</t>
+          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
@@ -5291,7 +5291,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="17.0" customHeight="1">
+    <row r="116" ht="30.0" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5308,11 +5308,15 @@
         </is>
       </c>
       <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
+        </is>
+      </c>
       <c r="F116" s="8"/>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that UDM's ID in the source case: copied, with its settings, to every GSU of this generator</t>
+          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
@@ -5719,42 +5723,66 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B130" s="7"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
+    <row r="130" ht="17.0" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R ohm</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">r_ohm</t>
+        </is>
+      </c>
+      <c r="D130" s="8"/>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
+      <c r="F130" s="8"/>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
+        </is>
+      </c>
+      <c r="H130" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="17.0" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">X ohm</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">x_ohm</t>
         </is>
       </c>
       <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
       <c r="F131" s="8"/>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable type</t>
+          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
@@ -5766,66 +5794,50 @@
     <row r="132" ht="17.0" customHeight="1">
       <c r="A132" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B uS</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b_us</t>
+        </is>
+      </c>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
+      <c r="F132" s="8"/>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B132" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Length unit</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unit</t>
-        </is>
-      </c>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the values are per</t>
-        </is>
-      </c>
-      <c r="H132" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="17.0" customHeight="1">
-      <c r="A133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B133" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R per length</t>
-        </is>
-      </c>
-      <c r="C133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">r_per</t>
-        </is>
-      </c>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
-        </is>
-      </c>
-      <c r="H133" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="7"/>
+      <c r="H133" s="7"/>
     </row>
     <row r="134" ht="17.0" customHeight="1">
       <c r="A134" s="8" t="inlineStr">
@@ -5835,12 +5847,12 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D134" s="8"/>
@@ -5848,7 +5860,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">cable type</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
@@ -5865,20 +5877,24 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">the values are per</t>
         </is>
       </c>
       <c r="H135" s="13" t="inlineStr">
@@ -5895,12 +5911,12 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D136" s="8"/>
@@ -5908,7 +5924,7 @@
       <c r="F136" s="8"/>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS, instead of C</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -5917,34 +5933,50 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
+    <row r="137" ht="17.0" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X per length</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x_per</t>
+        </is>
+      </c>
+      <c r="D137" s="8"/>
+      <c r="E137" s="8"/>
+      <c r="F137" s="8"/>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="17.0" customHeight="1">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">C per length</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">c_per</t>
         </is>
       </c>
       <c r="D138" s="8"/>
@@ -5952,7 +5984,7 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
+          <t xml:space="preserve">uF</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
@@ -5964,17 +5996,17 @@
     <row r="139" ht="17.0" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">B per length</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">b_per</t>
         </is>
       </c>
       <c r="D139" s="8"/>
@@ -5982,7 +6014,7 @@
       <c r="F139" s="8"/>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
+          <t xml:space="preserve">uS, instead of C</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
@@ -5994,7 +6026,7 @@
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B140" s="7"/>
@@ -6008,29 +6040,25 @@
     <row r="141" ht="17.0" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
-      <c r="F141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
+      <c r="F141" s="8"/>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
+          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
@@ -6042,17 +6070,17 @@
     <row r="142" ht="17.0" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">At bus</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D142" s="8"/>
@@ -6060,7 +6088,7 @@
       <c r="F142" s="8"/>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -6069,35 +6097,19 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="17.0" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B143" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MW</t>
-        </is>
-      </c>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mw</t>
-        </is>
-      </c>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
-        </is>
-      </c>
-      <c r="H143" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B143" s="7"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="7"/>
     </row>
     <row r="144" ht="17.0" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
@@ -6107,20 +6119,24 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
@@ -6137,52 +6153,72 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
-      <c r="G145" s="8"/>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+        </is>
+      </c>
       <c r="H145" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
-    </row>
-    <row r="147" ht="30.0" customHeight="1">
+    <row r="146" ht="17.0" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mw</t>
+        </is>
+      </c>
+      <c r="D146" s="8"/>
+      <c r="E146" s="8"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
+        </is>
+      </c>
+      <c r="H146" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="17.0" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">machine</t>
+          <t xml:space="preserve">mvar</t>
         </is>
       </c>
       <c r="D147" s="8"/>
@@ -6190,7 +6226,7 @@
       <c r="F147" s="8"/>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -6202,97 +6238,65 @@
     <row r="148" ht="17.0" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D148" s="8"/>
+      <c r="E148" s="8"/>
+      <c r="F148" s="8"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B148" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its generator's</t>
-        </is>
-      </c>
-      <c r="F148" s="8"/>
-      <c r="G148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = its generator's</t>
-        </is>
-      </c>
-      <c r="H148" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="30.0" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+    </row>
+    <row r="150" ht="30.0" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B149" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pgen MW</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pgen_mw</t>
-        </is>
-      </c>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
-        </is>
-      </c>
-      <c r="F149" s="8"/>
-      <c r="G149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
-        </is>
-      </c>
-      <c r="H149" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="17.0" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax MW</t>
+          <t xml:space="preserve">Machine</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmax_mw</t>
+          <t xml:space="preserve">machine</t>
         </is>
       </c>
       <c r="D150" s="8"/>
-      <c r="E150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its units x Unit Pmax</t>
-        </is>
-      </c>
+      <c r="E150" s="8"/>
       <c r="F150" s="8"/>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="H150" s="13" t="inlineStr">
@@ -6309,24 +6313,24 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmin MW</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmin_mw</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmin</t>
+          <t xml:space="preserve">its generator's</t>
         </is>
       </c>
       <c r="F151" s="8"/>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -6335,7 +6339,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="17.0" customHeight="1">
+    <row r="152" ht="30.0" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6343,24 +6347,24 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmax MVAr</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmax_mvar</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D152" s="8"/>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmax</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F152" s="8"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -6377,24 +6381,24 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmin MVAr</t>
+          <t xml:space="preserve">Pmax MW</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmin_mvar</t>
+          <t xml:space="preserve">pmax_mw</t>
         </is>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmin</t>
+          <t xml:space="preserve">its units x Unit Pmax</t>
         </is>
       </c>
       <c r="F153" s="8"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
@@ -6403,7 +6407,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="30.0" customHeight="1">
+    <row r="154" ht="17.0" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6411,24 +6415,24 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Pmin MW</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mvar</t>
+          <t xml:space="preserve">pmin_mw</t>
         </is>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as its generator's Q mode</t>
+          <t xml:space="preserve">its units x Unit Pmin</t>
         </is>
       </c>
       <c r="F154" s="8"/>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
         </is>
       </c>
       <c r="H154" s="13" t="inlineStr">
@@ -6445,24 +6449,24 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBASE MVA</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mbase_mva</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit MVA</t>
+          <t xml:space="preserve">its units x Unit Qmax</t>
         </is>
       </c>
       <c r="F155" s="8"/>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit MVA</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
@@ -6471,42 +6475,66 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B156" s="7"/>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
-      <c r="G156" s="7"/>
-      <c r="H156" s="7"/>
-    </row>
-    <row r="157" ht="17.0" customHeight="1">
+    <row r="156" ht="17.0" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qmin MVAr</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">qmin_mvar</t>
+        </is>
+      </c>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Qmin</t>
+        </is>
+      </c>
+      <c r="F156" s="8"/>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+        </is>
+      </c>
+      <c r="H156" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30.0" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bus</t>
+          <t xml:space="preserve">q_mvar</t>
         </is>
       </c>
       <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as its generator's Q mode</t>
+        </is>
+      </c>
       <c r="F157" s="8"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
@@ -6518,29 +6546,29 @@
     <row r="158" ht="17.0" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">MBASE MVA</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">mbase_mva</t>
         </is>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic</t>
+          <t xml:space="preserve">its units x Unit MVA</t>
         </is>
       </c>
       <c r="F158" s="8"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">blank = its units x Unit MVA</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -6549,143 +6577,131 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="30.0" customHeight="1">
-      <c r="A159" s="8" t="inlineStr">
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B159" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
-        </is>
-      </c>
-      <c r="F159" s="8"/>
-      <c r="G159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
-        </is>
-      </c>
-      <c r="H159" s="13" t="inlineStr">
+      <c r="B159" s="7"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
+    </row>
+    <row r="160" ht="17.0" customHeight="1">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bus</t>
+        </is>
+      </c>
+      <c r="D160" s="8"/>
+      <c r="E160" s="8"/>
+      <c r="F160" s="8"/>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+        </is>
+      </c>
+      <c r="H160" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
-    </row>
-    <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B160" s="7"/>
-      <c r="C160" s="7"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
-      <c r="G160" s="7"/>
-      <c r="H160" s="7"/>
     </row>
     <row r="161" ht="17.0" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Number</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic</t>
+        </is>
+      </c>
       <c r="F161" s="8"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+          <t xml:space="preserve">blank = automatic</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="162" ht="30.0" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Model</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">model</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
+      <c r="E162" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
       <c r="F162" s="8"/>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
         </is>
       </c>
       <c r="H162" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="17.0" customHeight="1">
-      <c r="A163" s="8" t="inlineStr">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B163" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parameter</t>
-        </is>
-      </c>
-      <c r="C163" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parameter</t>
-        </is>
-      </c>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
-      <c r="G163" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
-        </is>
-      </c>
-      <c r="H163" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
     </row>
     <row r="164" ht="17.0" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
@@ -6695,64 +6711,80 @@
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
-      <c r="G164" s="8"/>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+        </is>
+      </c>
       <c r="H164" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
+    <row r="165" ht="30.0" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Model</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model</t>
+        </is>
+      </c>
+      <c r="D165" s="8"/>
+      <c r="E165" s="8"/>
+      <c r="F165" s="8"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+        </is>
+      </c>
+      <c r="H165" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="17.0" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D166" s="8"/>
-      <c r="E166" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the plant</t>
-        </is>
-      </c>
+      <c r="E166" s="8"/>
       <c r="F166" s="8"/>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the plant</t>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
         </is>
       </c>
       <c r="H166" s="13" t="inlineStr">
@@ -6764,27 +6796,23 @@
     <row r="167" ht="17.0" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">record</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
-      <c r="G167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
-        </is>
-      </c>
+      <c r="G167" s="8"/>
       <c r="H167" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
@@ -6794,7 +6822,7 @@
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B168" s="7"/>
@@ -6808,7 +6836,7 @@
     <row r="169" ht="17.0" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
@@ -6822,29 +6850,37 @@
         </is>
       </c>
       <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the plant</t>
+        </is>
+      </c>
       <c r="F169" s="8"/>
-      <c r="G169" s="8"/>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = the plant</t>
+        </is>
+      </c>
       <c r="H169" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
     <row r="170" ht="17.0" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Record</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">record</t>
         </is>
       </c>
       <c r="D170" s="8"/>
@@ -6852,118 +6888,134 @@
       <c r="F170" s="8"/>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
+          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
         </is>
       </c>
       <c r="H170" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="7"/>
+      <c r="H171" s="7"/>
+    </row>
+    <row r="172" ht="17.0" customHeight="1">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generator</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator</t>
+        </is>
+      </c>
+      <c r="D172" s="8"/>
+      <c r="E172" s="8"/>
+      <c r="F172" s="8"/>
+      <c r="G172" s="8"/>
+      <c r="H172" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="17.0" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
+    <row r="173" ht="17.0" customHeight="1">
+      <c r="A173" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B171" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
-        </is>
-      </c>
-      <c r="C171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">value</t>
-        </is>
-      </c>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
-      <c r="F171" s="8"/>
-      <c r="G171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
-        </is>
-      </c>
-      <c r="H171" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="18" customHeight="1">
-      <c r="A172" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
-        </is>
-      </c>
-      <c r="B172" s="7"/>
-      <c r="C172" s="7"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
-      <c r="G172" s="7"/>
-      <c r="H172" s="7"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="8"/>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C173" s="8"/>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H173" s="8"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="8"/>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H173" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="17.0" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI</t>
-        </is>
-      </c>
-      <c r="C174" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the point of interconnection</t>
-        </is>
-      </c>
-      <c r="H174" s="8"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="8"/>
-      <c r="B175" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HV</t>
-        </is>
-      </c>
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
-      <c r="F175" s="8"/>
-      <c r="G175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
-        </is>
-      </c>
-      <c r="H175" s="8"/>
+          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+        </is>
+      </c>
+      <c r="H174" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
+        </is>
+      </c>
+      <c r="B175" s="7"/>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
     </row>
     <row r="176">
       <c r="A176" s="8"/>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C176" s="8"/>
@@ -6972,7 +7024,7 @@
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H176" s="8"/>
@@ -6981,7 +7033,7 @@
       <c r="A177" s="8"/>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C177" s="8"/>
@@ -6990,7 +7042,7 @@
       <c r="F177" s="8"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H177" s="8"/>
@@ -6999,7 +7051,7 @@
       <c r="A178" s="8"/>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C178" s="8"/>
@@ -7008,7 +7060,7 @@
       <c r="F178" s="8"/>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
         </is>
       </c>
       <c r="H178" s="8"/>
@@ -7017,7 +7069,7 @@
       <c r="A179" s="8"/>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C179" s="8"/>
@@ -7026,7 +7078,7 @@
       <c r="F179" s="8"/>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
+          <t xml:space="preserve">an MPT's LV winding</t>
         </is>
       </c>
       <c r="H179" s="8"/>
@@ -7035,7 +7087,7 @@
       <c r="A180" s="8"/>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C180" s="8"/>
@@ -7044,7 +7096,7 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
         </is>
       </c>
       <c r="H180" s="8"/>
@@ -7053,7 +7105,7 @@
       <c r="A181" s="8"/>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -7062,7 +7114,7 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
         </is>
       </c>
       <c r="H181" s="8"/>
@@ -7071,7 +7123,7 @@
       <c r="A182" s="8"/>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C182" s="8"/>
@@ -7080,7 +7132,7 @@
       <c r="F182" s="8"/>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H182" s="8"/>
@@ -7089,7 +7141,7 @@
       <c r="A183" s="8"/>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -7098,34 +7150,34 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H183" s="8"/>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
-        </is>
-      </c>
-      <c r="B184" s="7"/>
-      <c r="C184" s="7"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
-      <c r="G184" s="7"/>
-      <c r="H184" s="7"/>
+    <row r="184">
+      <c r="A184" s="8"/>
+      <c r="B184" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+        </is>
+      </c>
+      <c r="C184" s="8"/>
+      <c r="D184" s="8"/>
+      <c r="E184" s="8"/>
+      <c r="F184" s="8"/>
+      <c r="G184" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a generator's terminal</t>
+        </is>
+      </c>
+      <c r="H184" s="8"/>
     </row>
     <row r="185">
-      <c r="A185" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A185" s="8"/>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNITS}</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -7134,24 +7186,16 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H185" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H185" s="8"/>
     </row>
     <row r="186">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A186" s="8"/>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
         </is>
       </c>
       <c r="C186" s="8"/>
@@ -7160,40 +7204,24 @@
       <c r="F186" s="8"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
-        </is>
-      </c>
-      <c r="H186" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B187" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{P_MW}</t>
-        </is>
-      </c>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
-      <c r="F187" s="8"/>
-      <c r="G187" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
-        </is>
-      </c>
-      <c r="H187" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+        </is>
+      </c>
+      <c r="H186" s="8"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
+        </is>
+      </c>
+      <c r="B187" s="7"/>
+      <c r="C187" s="7"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
     </row>
     <row r="188">
       <c r="A188" s="8" t="inlineStr">
@@ -7203,7 +7231,7 @@
       </c>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C188" s="8"/>
@@ -7212,7 +7240,7 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H188" s="13" t="inlineStr">
@@ -7229,7 +7257,7 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C189" s="8"/>
@@ -7238,7 +7266,7 @@
       <c r="F189" s="8"/>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
@@ -7255,7 +7283,7 @@
       </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C190" s="8"/>
@@ -7264,7 +7292,7 @@
       <c r="F190" s="8"/>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H190" s="13" t="inlineStr">
@@ -7281,7 +7309,7 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C191" s="8"/>
@@ -7290,7 +7318,7 @@
       <c r="F191" s="8"/>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H191" s="13" t="inlineStr">
@@ -7307,7 +7335,7 @@
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C192" s="8"/>
@@ -7316,7 +7344,7 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
@@ -7333,7 +7361,7 @@
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C193" s="8"/>
@@ -7342,7 +7370,7 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H193" s="13" t="inlineStr">
@@ -7359,7 +7387,7 @@
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C194" s="8"/>
@@ -7368,7 +7396,7 @@
       <c r="F194" s="8"/>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H194" s="13" t="inlineStr">
@@ -7385,7 +7413,7 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -7394,7 +7422,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
@@ -7411,7 +7439,7 @@
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -7420,7 +7448,7 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
@@ -7437,7 +7465,7 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C197" s="8"/>
@@ -7446,7 +7474,7 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H197" s="13" t="inlineStr">
@@ -7463,7 +7491,7 @@
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C198" s="8"/>
@@ -7472,7 +7500,7 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr">
@@ -7489,7 +7517,7 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C199" s="8"/>
@@ -7498,7 +7526,7 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H199" s="13" t="inlineStr">
@@ -7515,7 +7543,7 @@
       </c>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C200" s="8"/>
@@ -7524,7 +7552,7 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H200" s="13" t="inlineStr">
@@ -7541,7 +7569,7 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C201" s="8"/>
@@ -7550,10 +7578,88 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">frequency (Hz)</t>
+        </is>
+      </c>
+      <c r="H201" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B202" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{P_INV_MW}</t>
+        </is>
+      </c>
+      <c r="C202" s="8"/>
+      <c r="D202" s="8"/>
+      <c r="E202" s="8"/>
+      <c r="F202" s="8"/>
+      <c r="G202" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+        </is>
+      </c>
+      <c r="H202" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B203" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
+        </is>
+      </c>
+      <c r="C203" s="8"/>
+      <c r="D203" s="8"/>
+      <c r="E203" s="8"/>
+      <c r="F203" s="8"/>
+      <c r="G203" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H203" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B204" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C204" s="8"/>
+      <c r="D204" s="8"/>
+      <c r="E204" s="8"/>
+      <c r="F204" s="8"/>
+      <c r="G204" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H201" s="13" t="inlineStr">
+      <c r="H204" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -7567,31 +7673,31 @@
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A79:H79"/>
     <mergeCell ref="A118:H118"/>
-    <mergeCell ref="A130:H130"/>
-    <mergeCell ref="A137:H137"/>
+    <mergeCell ref="A133:H133"/>
     <mergeCell ref="A140:H140"/>
-    <mergeCell ref="A146:H146"/>
-    <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A160:H160"/>
-    <mergeCell ref="A165:H165"/>
+    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A149:H149"/>
+    <mergeCell ref="A159:H159"/>
+    <mergeCell ref="A163:H163"/>
     <mergeCell ref="A168:H168"/>
-    <mergeCell ref="A172:H172"/>
-    <mergeCell ref="A184:H184"/>
+    <mergeCell ref="A171:H171"/>
+    <mergeCell ref="A175:H175"/>
+    <mergeCell ref="A187:H187"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
     <hyperlink ref="A51" location="'MPT'!A1" display="MPT"/>
     <hyperlink ref="A79" location="'Generators'!A1" display="Generators"/>
     <hyperlink ref="A118" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A130" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A137" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A140" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A146" location="'Machines'!A1" display="Machines"/>
-    <hyperlink ref="A156" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A160" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A165" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A168" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A184" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A133" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A140" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A143" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A149" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A159" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A163" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A168" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A171" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A187" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -20959,12 +21065,12 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">a .pscx or .pslx (or a project open in PSCAD) with one UDM set up as you want it (with PSCAD component ID)</t>
+          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">that UDM's ID in the source case: copied, with its settings, to every GSU of this generator</t>
+          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
@@ -21938,6 +22044,9 @@
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -21996,6 +22105,21 @@
           <t xml:space="preserve">Parallel cables</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R ohm</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X ohm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B uS</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="124.0" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -22049,6 +22173,21 @@
           <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -22086,6 +22225,9 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -22123,6 +22265,9 @@
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -22160,6 +22305,9 @@
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -22197,6 +22345,9 @@
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -22234,6 +22385,9 @@
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -22271,6 +22425,9 @@
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -22308,6 +22465,9 @@
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -22345,6 +22505,9 @@
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -22382,6 +22545,9 @@
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -22419,6 +22585,9 @@
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -22456,6 +22625,9 @@
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -22493,6 +22665,9 @@
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -22506,6 +22681,9 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -22519,6 +22697,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -22532,6 +22713,9 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -22545,6 +22729,9 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -22558,6 +22745,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -22571,6 +22761,9 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -22584,6 +22777,9 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -22597,6 +22793,9 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
     </row>
     <row r="23">
       <c r="A23" s="3"/>
@@ -22610,6 +22809,9 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
     </row>
     <row r="24">
       <c r="A24" s="3"/>
@@ -22623,6 +22825,9 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3"/>
@@ -22636,6 +22841,9 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="3"/>
@@ -22649,6 +22857,9 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -2297,58 +2297,66 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gen-tie values per</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_per_unit</t>
+        </is>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Gen-tie length unit</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the length R, X, B, C below are per: km, mi, kft, m, ft (blank = the Gen-tie length unit)</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30.0" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gen-tie R per length</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm</t>
         </is>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one circuit, per length unit</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17.0" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gen-tie X per length</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tie_x_per</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
-      <c r="E24" s="8"/>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a typical overhead line of the POI kV</t>
+        </is>
+      </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit</t>
+          <t xml:space="preserve">one circuit (blank = a typical overhead line of the POI kV)</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -2365,24 +2373,28 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie B per length</t>
+          <t xml:space="preserve">Gen-tie X per length</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_per</t>
+          <t xml:space="preserve">tie_x_per</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
-        </is>
-      </c>
-      <c r="E25" s="8"/>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit (total charging)</t>
+          <t xml:space="preserve">one circuit (blank = typical)</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -2399,24 +2411,28 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie C per length</t>
+          <t xml:space="preserve">Gen-tie B per length</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_c_per</t>
+          <t xml:space="preserve">tie_b_per</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
-        </is>
-      </c>
-      <c r="E26" s="8"/>
+          <t xml:space="preserve">uS</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of B</t>
+          <t xml:space="preserve">one circuit, total charging (blank = typical)</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -2433,24 +2449,24 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie R total</t>
+          <t xml:space="preserve">Gen-tie C per length</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_r_ohm</t>
+          <t xml:space="preserve">tie_c_per</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">uF</t>
         </is>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of per length (one circuit)</t>
+          <t xml:space="preserve">instead of B</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -2467,12 +2483,12 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie X total</t>
+          <t xml:space="preserve">Gen-tie R total</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_ohm</t>
+          <t xml:space="preserve">tie_r_ohm</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2482,7 +2498,11 @@
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instead of per length (one circuit)</t>
+        </is>
+      </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -2497,17 +2517,17 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie B total</t>
+          <t xml:space="preserve">Gen-tie X total</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_us</t>
+          <t xml:space="preserve">tie_x_ohm</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="E29" s="8"/>
@@ -2527,26 +2547,22 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie circuits</t>
+          <t xml:space="preserve">Gen-tie B total</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_parallel</t>
-        </is>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">tie_b_us</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uS</t>
+        </is>
+      </c>
+      <c r="E30" s="8"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">identical circuits in parallel (blank = 1)</t>
-        </is>
-      </c>
+      <c r="G30" s="8"/>
       <c r="H30" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -2561,24 +2577,24 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie rating</t>
+          <t xml:space="preserve">Gen-tie circuits</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_rate_mva</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
-      <c r="E31" s="8"/>
+          <t xml:space="preserve">tie_parallel</t>
+        </is>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F31" s="8"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit</t>
+          <t xml:space="preserve">identical circuits in parallel (blank = 1)</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -2587,7 +2603,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30.0" customHeight="1">
+    <row r="32" ht="17.0" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2595,62 +2611,62 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gen-tie rating</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_rate_mva</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical for the POI kV</t>
+        </is>
+      </c>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one circuit (blank = typical for the POI kV)</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30.0" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Control mode</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">control_mode</t>
         </is>
       </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q | PF | V</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17.0" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI voltage</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v_poi_pu</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.0</t>
-        </is>
-      </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -2667,28 +2683,28 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at POI</t>
+          <t xml:space="preserve">POI voltage</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_poi_mvar</t>
+          <t xml:space="preserve">v_poi_pu</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">pu</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1.0</t>
         </is>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
+          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
@@ -2705,20 +2721,28 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PF at POI</t>
+          <t xml:space="preserve">Q at POI</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pf_poi</t>
-        </is>
-      </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
+          <t xml:space="preserve">q_poi_mvar</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVAr</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
+          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -2735,28 +2759,20 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid voltage</t>
+          <t xml:space="preserve">PF at POI</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">v_grid_pu</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.0</t>
-        </is>
-      </c>
+          <t xml:space="preserve">pf_poi</t>
+        </is>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="8"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
+          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -2765,7 +2781,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="30.0" customHeight="1">
+    <row r="37" ht="17.0" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2773,28 +2789,28 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at POI</t>
+          <t xml:space="preserve">Grid voltage</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">p_poi_mw</t>
+          <t xml:space="preserve">v_grid_pu</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">pu</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each generator at its dispatch</t>
+          <t xml:space="preserve">1.0</t>
         </is>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
+          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -2811,33 +2827,33 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plant controller</t>
+          <t xml:space="preserve">P at POI</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">plant_ctrl</t>
-        </is>
-      </c>
-      <c r="D38" s="8"/>
+          <t xml:space="preserve">p_poi_mw</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REPC_A</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPC_A | REPC_B</t>
-        </is>
-      </c>
+          <t xml:space="preserve">each generator at its dispatch</t>
+        </is>
+      </c>
+      <c r="F38" s="8"/>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
+          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2849,28 +2865,28 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGC_A / REPC_A records</t>
+          <t xml:space="preserve">Plant controller</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">regc_repc</t>
+          <t xml:space="preserve">plant_ctrl</t>
         </is>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard</t>
+          <t xml:space="preserve">REPC_A</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard | USRMDL</t>
+          <t xml:space="preserve">REPC_A | REPC_B</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard: REGCA1 / REPCA1 (PSS/E library) | USRMDL: REGCAU1 / REPCAU1 (the WECC user-model DLL) (blank = standard)</t>
+          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -2887,66 +2903,66 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">REGC_A / REPC_A records</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regc_repc</t>
+        </is>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard | USRMDL</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard: REGCA1 / REPCA1 (PSS/E library) | USRMDL: REGCAU1 / REPCAU1 (the WECC user-model DLL) (blank = standard)</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD time step</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_time_step_us</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">us</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10 (the vendor model's own requirement wins</t>
-        </is>
-      </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 10 (the vendor model's own requirement wins)</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="17.0" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD duration</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_duration_s</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 5</t>
+          <t xml:space="preserve">blank = 10 (the vendor model's own requirement wins)</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -2963,28 +2979,28 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD plot step</t>
+          <t xml:space="preserve">PSCAD duration</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_plot_step_us</t>
+          <t xml:space="preserve">pscad_duration_s</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">us</t>
+          <t xml:space="preserve">s</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 100</t>
+          <t xml:space="preserve">blank = 5</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -3001,62 +3017,62 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD plot step</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_plot_step_us</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">us</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100</t>
+        </is>
+      </c>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = 100</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17.0" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD meter at POI</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_meter</t>
         </is>
       </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
-        </is>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30.0" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD lines as</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_lines</t>
-        </is>
-      </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI | RLC</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -3073,62 +3089,62 @@
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD lines as</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_lines</t>
+        </is>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI | RLC</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30.0" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD fault at POI</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_fault</t>
         </is>
       </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
-        </is>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="17.0" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault time</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_fault_s</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100: none in the run</t>
-        </is>
-      </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -3145,12 +3161,12 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault duration</t>
+          <t xml:space="preserve">PSCAD fault time</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_fault_dur_s</t>
+          <t xml:space="preserve">pscad_fault_s</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3160,89 +3176,89 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
+          <t xml:space="preserve">100: none in the run</t>
         </is>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17.0" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault duration</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_fault_dur_s</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 0.15</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="43.0" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="49" ht="43.0" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault type</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_fault_type</t>
         </is>
       </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="D49" s="8"/>
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="17.0" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault resistance</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_fault_ohm</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.01</t>
-        </is>
-      </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 0.01</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -3259,71 +3275,79 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD libraries</t>
+          <t xml:space="preserve">PSCAD fault resistance</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_libraries</t>
-        </is>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
+          <t xml:space="preserve">pscad_fault_ohm</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.01</t>
+        </is>
+      </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = 0.01</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17.0" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD libraries</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_libraries</t>
+        </is>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
         </is>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-    </row>
-    <row r="52" ht="17.0" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
     </row>
     <row r="53" ht="17.0" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
@@ -3333,18 +3357,22 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV kV</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hv_kv</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
+        </is>
+      </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3359,12 +3387,12 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV kV</t>
+          <t xml:space="preserve">HV kV</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_kv</t>
+          <t xml:space="preserve">hv_kv</t>
         </is>
       </c>
       <c r="D54" s="8"/>
@@ -3385,26 +3413,18 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TV kV</t>
+          <t xml:space="preserve">LV kV</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tv_kv</t>
+          <t xml:space="preserve">lv_kv</t>
         </is>
       </c>
       <c r="D55" s="8"/>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">two windings</t>
-        </is>
-      </c>
+      <c r="E55" s="8"/>
       <c r="F55" s="8"/>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tertiary / 2nd LV winding; blank = two windings</t>
-        </is>
-      </c>
+      <c r="G55" s="8"/>
       <c r="H55" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3419,20 +3439,24 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">TV kV</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mva</t>
+          <t xml:space="preserve">tv_kv</t>
         </is>
       </c>
       <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">two windings</t>
+        </is>
+      </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
+          <t xml:space="preserve">tertiary / 2nd LV winding; blank = two windings</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -3449,12 +3473,12 @@
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV MVA</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_mva</t>
+          <t xml:space="preserve">mva</t>
         </is>
       </c>
       <c r="D57" s="8"/>
@@ -3462,7 +3486,7 @@
       <c r="F57" s="8"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -3479,12 +3503,12 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TV MVA</t>
+          <t xml:space="preserve">LV MVA</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tv_mva</t>
+          <t xml:space="preserve">lv_mva</t>
         </is>
       </c>
       <c r="D58" s="8"/>
@@ -3509,12 +3533,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV %</t>
+          <t xml:space="preserve">TV MVA</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_hl_pct</t>
+          <t xml:space="preserve">tv_mva</t>
         </is>
       </c>
       <c r="D59" s="8"/>
@@ -3522,7 +3546,7 @@
       <c r="F59" s="8"/>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on its base MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -3539,12 +3563,12 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV %</t>
+          <t xml:space="preserve">Z HV-LV %</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_ht_pct</t>
+          <t xml:space="preserve">z_hl_pct</t>
         </is>
       </c>
       <c r="D60" s="8"/>
@@ -3552,7 +3576,7 @@
       <c r="F60" s="8"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">on its base MVA</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -3569,12 +3593,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV %</t>
+          <t xml:space="preserve">Z HV-TV %</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_lt_pct</t>
+          <t xml:space="preserve">z_ht_pct</t>
         </is>
       </c>
       <c r="D61" s="8"/>
@@ -3599,24 +3623,20 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV base MVA</t>
+          <t xml:space="preserve">Z LV-TV %</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_hl_mva</t>
+          <t xml:space="preserve">z_lt_pct</t>
         </is>
       </c>
       <c r="D62" s="8"/>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E62" s="8"/>
       <c r="F62" s="8"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -3633,12 +3653,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-LV base MVA</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_ht_mva</t>
+          <t xml:space="preserve">base_hl_mva</t>
         </is>
       </c>
       <c r="D63" s="8"/>
@@ -3667,12 +3687,12 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-TV base MVA</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_lt_mva</t>
+          <t xml:space="preserve">base_ht_mva</t>
         </is>
       </c>
       <c r="D64" s="8"/>
@@ -3701,20 +3721,24 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X/R</t>
+          <t xml:space="preserve">Z LV-TV base MVA</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_r</t>
+          <t xml:space="preserve">base_lt_mva</t>
         </is>
       </c>
       <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F65" s="8"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each impedance</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -3731,12 +3755,12 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load loss kW</t>
+          <t xml:space="preserve">X/R</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">load_loss_kw</t>
+          <t xml:space="preserve">x_r</t>
         </is>
       </c>
       <c r="D66" s="8"/>
@@ -3744,7 +3768,7 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
+          <t xml:space="preserve">each impedance</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -3761,12 +3785,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector group</t>
+          <t xml:space="preserve">Load loss kW</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vector</t>
+          <t xml:space="preserve">load_loss_kw</t>
         </is>
       </c>
       <c r="D67" s="8"/>
@@ -3774,7 +3798,7 @@
       <c r="F67" s="8"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
+          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -3791,24 +3815,20 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV tap</t>
+          <t xml:space="preserve">Vector group</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tap</t>
+          <t xml:space="preserve">vector</t>
         </is>
       </c>
       <c r="D68" s="8"/>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
+          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -3825,12 +3845,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel units</t>
+          <t xml:space="preserve">HV tap</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">count</t>
+          <t xml:space="preserve">tap</t>
         </is>
       </c>
       <c r="D69" s="8"/>
@@ -3842,7 +3862,7 @@
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical units (blank = 1)</t>
+          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3859,24 +3879,24 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No-load loss %</t>
+          <t xml:space="preserve">Parallel units</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nll_pct</t>
+          <t xml:space="preserve">count</t>
         </is>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">of MVA (blank = 0)</t>
+          <t xml:space="preserve">identical units (blank = 1)</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -3893,12 +3913,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnetising current %</t>
+          <t xml:space="preserve">No-load loss %</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">im_pct</t>
+          <t xml:space="preserve">nll_pct</t>
         </is>
       </c>
       <c r="D71" s="8"/>
@@ -3927,24 +3947,24 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rating MVA</t>
+          <t xml:space="preserve">Magnetising current %</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_mva</t>
+          <t xml:space="preserve">im_pct</t>
         </is>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -3961,24 +3981,24 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length</t>
+          <t xml:space="preserve">Rating MVA</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_length</t>
+          <t xml:space="preserve">rate_mva</t>
         </is>
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -3995,22 +4015,26 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length unit</t>
+          <t xml:space="preserve">Tie length</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_unit</t>
+          <t xml:space="preserve">tie_length</t>
         </is>
       </c>
       <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G74" s="8"/>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+        </is>
+      </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4025,22 +4049,22 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie R per length</t>
+          <t xml:space="preserve">Tie length unit</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_r_per</t>
+          <t xml:space="preserve">tie_unit</t>
         </is>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
+      <c r="G75" s="8"/>
       <c r="H75" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4055,20 +4079,28 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie X per length</t>
+          <t xml:space="preserve">Tie values per</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_per</t>
+          <t xml:space="preserve">tie_per_unit</t>
         </is>
       </c>
       <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tie length unit</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = Tie length unit)</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
@@ -4077,7 +4109,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="17.0" customHeight="1">
+    <row r="77" ht="30.0" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -4085,20 +4117,24 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie B per length</t>
+          <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_per</t>
+          <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
       <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a typical overhead line of the HV kV</t>
+        </is>
+      </c>
       <c r="F77" s="8"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
+          <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -4115,60 +4151,92 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie rating MVA</t>
+          <t xml:space="preserve">Tie X per length</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_rate_mva</t>
+          <t xml:space="preserve">tie_x_per</t>
         </is>
       </c>
       <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
       <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm (blank = typical)</t>
+        </is>
+      </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
+    <row r="79" ht="17.0" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tie B per length</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_b_per</t>
+        </is>
+      </c>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uS (blank = typical)</t>
+        </is>
+      </c>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17.0" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generators</t>
+          <t xml:space="preserve">MPT</t>
         </is>
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Tie rating MVA</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">tie_rate_mva</t>
         </is>
       </c>
       <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
       <c r="F80" s="8"/>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
+          <t xml:space="preserve">blank = typical</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -4177,39 +4245,19 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="30.0" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
-        </is>
-      </c>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
-        </is>
-      </c>
-      <c r="H81" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
     </row>
     <row r="82" ht="17.0" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
@@ -4219,24 +4267,20 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine ID</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D82" s="8"/>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E82" s="8"/>
       <c r="F82" s="8"/>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
@@ -4245,7 +4289,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="17.0" customHeight="1">
+    <row r="83" ht="30.0" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4253,20 +4297,24 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Type</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
+          <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -4283,20 +4331,24 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F84" s="8"/>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number of units</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -4313,24 +4365,20 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit MVA</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_mva</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D85" s="8"/>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from P and Q</t>
-        </is>
-      </c>
+      <c r="E85" s="8"/>
       <c r="F85" s="8"/>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4347,18 +4395,22 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmax MW</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmax_mw</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number of units</t>
+        </is>
+      </c>
       <c r="H86" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4373,24 +4425,24 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmin MW</t>
+          <t xml:space="preserve">Unit MVA</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmin_mw</t>
+          <t xml:space="preserve">unit_mva</t>
         </is>
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">from P and Q</t>
         </is>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
+          <t xml:space="preserve">one unit (blank = from P and Q)</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4407,26 +4459,18 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmax MVAr</t>
+          <t xml:space="preserve">Unit Pmax MW</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmax_mvar</t>
+          <t xml:space="preserve">unit_pmax_mw</t>
         </is>
       </c>
       <c r="D88" s="8"/>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from Unit PF</t>
-        </is>
-      </c>
+      <c r="E88" s="8"/>
       <c r="F88" s="8"/>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = from Unit PF</t>
-        </is>
-      </c>
+      <c r="G88" s="8"/>
       <c r="H88" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4441,24 +4485,24 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmin MVAr</t>
+          <t xml:space="preserve">Unit Pmin MW</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmin_mvar</t>
+          <t xml:space="preserve">unit_pmin_mw</t>
         </is>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Qmax</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = -Qmax</t>
+          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
@@ -4475,24 +4519,24 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit PF</t>
+          <t xml:space="preserve">Unit Qmax MVAr</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pf</t>
+          <t xml:space="preserve">unit_qmax_mvar</t>
         </is>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95</t>
+          <t xml:space="preserve">from Unit PF</t>
         </is>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
+          <t xml:space="preserve">blank = from Unit PF</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4509,24 +4553,24 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminal kV</t>
+          <t xml:space="preserve">Unit Qmin MVAr</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kv</t>
+          <t xml:space="preserve">unit_qmin_mvar</t>
         </is>
       </c>
       <c r="D91" s="8"/>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">-Qmax</t>
         </is>
       </c>
       <c r="F91" s="8"/>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = GSU LV kV</t>
+          <t xml:space="preserve">blank = -Qmax</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -4535,7 +4579,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="30.0" customHeight="1">
+    <row r="92" ht="17.0" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4543,24 +4587,24 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispatch MW</t>
+          <t xml:space="preserve">Unit PF</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dispatch_mw</t>
+          <t xml:space="preserve">unit_pf</t>
         </is>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+          <t xml:space="preserve">0.95</t>
         </is>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
+          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
@@ -4577,24 +4621,24 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode</t>
+          <t xml:space="preserve">Terminal kV</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mode</t>
+          <t xml:space="preserve">kv</t>
         </is>
       </c>
       <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share | fixed</t>
-        </is>
-      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSU LV kV</t>
+        </is>
+      </c>
+      <c r="F93" s="8"/>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
+          <t xml:space="preserve">blank = GSU LV kV</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
@@ -4603,7 +4647,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="17.0" customHeight="1">
+    <row r="94" ht="30.0" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4611,24 +4655,24 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Dispatch MW</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_q_mvar</t>
+          <t xml:space="preserve">dispatch_mw</t>
         </is>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Pmax (BESS charging: negative</t>
         </is>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
+          <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
@@ -4645,20 +4689,24 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed PF</t>
+          <t xml:space="preserve">Q mode</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_pf</t>
+          <t xml:space="preserve">q_mode</t>
         </is>
       </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">share | fixed</t>
+        </is>
+      </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
+          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
@@ -4675,24 +4723,24 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU count</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_count</t>
+          <t xml:space="preserve">fixed_q_mvar</t>
         </is>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = Units</t>
+          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
         </is>
       </c>
       <c r="H96" s="13" t="inlineStr">
@@ -4701,7 +4749,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="30.0" customHeight="1">
+    <row r="97" ht="17.0" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4709,24 +4757,20 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU MVA</t>
+          <t xml:space="preserve">Fixed PF</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_mva</t>
+          <t xml:space="preserve">fixed_pf</t>
         </is>
       </c>
       <c r="D97" s="8"/>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no GSU (units on the MV bus</t>
-        </is>
-      </c>
+      <c r="E97" s="8"/>
       <c r="F97" s="8"/>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
+          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
@@ -4743,25 +4787,33 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV kV</t>
+          <t xml:space="preserve">GSU count</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_hv_kv</t>
+          <t xml:space="preserve">gsu_count</t>
         </is>
       </c>
       <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units</t>
+        </is>
+      </c>
       <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = Units</t>
+        </is>
+      </c>
       <c r="H98" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="17.0" customHeight="1">
+    <row r="99" ht="30.0" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4769,18 +4821,26 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">GSU MVA</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_lv_kv</t>
+          <t xml:space="preserve">gsu_mva</t>
         </is>
       </c>
       <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no GSU (units on the MV bus</t>
+        </is>
+      </c>
       <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
+        </is>
+      </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4795,22 +4855,18 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU Z %</t>
+          <t xml:space="preserve">GSU HV kV</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_z_pct</t>
+          <t xml:space="preserve">gsu_hv_kv</t>
         </is>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">on GSU MVA</t>
-        </is>
-      </c>
+      <c r="G100" s="8"/>
       <c r="H100" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4825,12 +4881,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU X/R</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_x_r</t>
+          <t xml:space="preserve">gsu_lv_kv</t>
         </is>
       </c>
       <c r="D101" s="8"/>
@@ -4851,18 +4907,22 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU vector group</t>
+          <t xml:space="preserve">GSU Z %</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_vector</t>
+          <t xml:space="preserve">gsu_z_pct</t>
         </is>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
-      <c r="G102" s="8"/>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on GSU MVA</t>
+        </is>
+      </c>
       <c r="H102" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4877,26 +4937,18 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV tap</t>
+          <t xml:space="preserve">GSU X/R</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_tap</t>
+          <t xml:space="preserve">gsu_x_r</t>
         </is>
       </c>
       <c r="D103" s="8"/>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E103" s="8"/>
       <c r="F103" s="8"/>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 1</t>
-        </is>
-      </c>
+      <c r="G103" s="8"/>
       <c r="H103" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4911,26 +4963,18 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">GSU vector group</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">gsu_vector</t>
         </is>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
-        </is>
-      </c>
-      <c r="G104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
-        </is>
-      </c>
+      <c r="F104" s="8"/>
+      <c r="G104" s="8"/>
       <c r="H104" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4945,20 +4989,24 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector R</t>
+          <t xml:space="preserve">GSU HV tap</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_r</t>
+          <t xml:space="preserve">gsu_tap</t>
         </is>
       </c>
       <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F105" s="8"/>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H105" s="13" t="inlineStr">
@@ -4975,20 +5023,24 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector X</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_x</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
+        </is>
+      </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT</t>
+          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
         </is>
       </c>
       <c r="H106" s="13" t="inlineStr">
@@ -5005,12 +5057,12 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector B</t>
+          <t xml:space="preserve">Collector R</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_b</t>
+          <t xml:space="preserve">coll_r</t>
         </is>
       </c>
       <c r="D107" s="8"/>
@@ -5018,7 +5070,7 @@
       <c r="F107" s="8"/>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT, total charging</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H107" s="13" t="inlineStr">
@@ -5035,24 +5087,20 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector units</t>
+          <t xml:space="preserve">Collector X</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_units</t>
+          <t xml:space="preserve">coll_x</t>
         </is>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu | ohm</t>
-        </is>
-      </c>
+      <c r="F108" s="8"/>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H108" s="13" t="inlineStr">
@@ -5069,12 +5117,12 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZSORCE X pu</t>
+          <t xml:space="preserve">Collector B</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zsorce_x</t>
+          <t xml:space="preserve">coll_b</t>
         </is>
       </c>
       <c r="D109" s="8"/>
@@ -5082,12 +5130,12 @@
       <c r="F109" s="8"/>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+          <t xml:space="preserve">EQUIVALENT, total charging</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5099,29 +5147,33 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WMOD</t>
+          <t xml:space="preserve">Collector units</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wmod</t>
+          <t xml:space="preserve">coll_units</t>
         </is>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu | ohm</t>
+        </is>
+      </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
+          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
         </is>
       </c>
       <c r="H110" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="17.0" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5129,28 +5181,20 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical control</t>
+          <t xml:space="preserve">ZSORCE X pu</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">reec</t>
+          <t xml:space="preserve">zsorce_x</t>
         </is>
       </c>
       <c r="D111" s="8"/>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
-        </is>
-      </c>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8"/>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
+          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
@@ -5167,33 +5211,29 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD library</t>
+          <t xml:space="preserve">WMOD</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_library</t>
+          <t xml:space="preserve">wmod</t>
         </is>
       </c>
       <c r="D112" s="8"/>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
+      <c r="E112" s="8"/>
       <c r="F112" s="8"/>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
+          <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30.0" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5201,29 +5241,33 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD definition</t>
+          <t xml:space="preserve">Electrical control</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_definition</t>
+          <t xml:space="preserve">reec</t>
         </is>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a source: network check</t>
-        </is>
-      </c>
-      <c r="F113" s="8"/>
+          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
+        </is>
+      </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
+          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
@@ -5235,24 +5279,24 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD AC port</t>
+          <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_ac_port</t>
+          <t xml:space="preserve">pscad_library</t>
         </is>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its 3-phase port</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F114" s="8"/>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
       <c r="H114" s="13" t="inlineStr">
@@ -5261,7 +5305,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="30.0" customHeight="1">
+    <row r="115" ht="17.0" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5269,20 +5313,24 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD source case</t>
+          <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_source</t>
+          <t xml:space="preserve">pscad_definition</t>
         </is>
       </c>
       <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a source: network check</t>
+        </is>
+      </c>
       <c r="F115" s="8"/>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
+          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
@@ -5291,7 +5339,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="30.0" customHeight="1">
+    <row r="116" ht="17.0" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5299,24 +5347,24 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD component ID</t>
+          <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_component_id</t>
+          <t xml:space="preserve">pscad_ac_port</t>
         </is>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
+          <t xml:space="preserve">its 3-phase port</t>
         </is>
       </c>
       <c r="F116" s="8"/>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
+          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
@@ -5333,109 +5381,113 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD source case</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_source</t>
+        </is>
+      </c>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
+        </is>
+      </c>
+      <c r="H117" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="30.0" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD component ID</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_component_id</t>
+        </is>
+      </c>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
+        </is>
+      </c>
+      <c r="H118" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30.0" customHeight="1">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD inverter at</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_inv_at</t>
         </is>
       </c>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8" t="inlineStr">
+      <c r="D119" s="8"/>
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV</t>
         </is>
       </c>
-      <c r="F117" s="8" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV | MV</t>
         </is>
       </c>
-      <c r="G117" s="8" t="inlineStr">
+      <c r="G119" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
       </c>
-      <c r="H117" s="13" t="inlineStr">
+      <c r="H119" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B118" s="7"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-    </row>
-    <row r="119" ht="17.0" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B119" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collector</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collector</t>
-        </is>
-      </c>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
-        </is>
-      </c>
-      <c r="H119" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="17.0" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B120" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeder</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feeder</t>
-        </is>
-      </c>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
-      <c r="G120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feeder name</t>
-        </is>
-      </c>
-      <c r="H120" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
     </row>
     <row r="121" ht="17.0" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
@@ -5445,24 +5497,20 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copies</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">copies</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D121" s="8"/>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E121" s="8"/>
       <c r="F121" s="8"/>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
+          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
@@ -5479,12 +5527,12 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section</t>
+          <t xml:space="preserve">Feeder</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">section</t>
+          <t xml:space="preserve">feeder</t>
         </is>
       </c>
       <c r="D122" s="8"/>
@@ -5492,7 +5540,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+          <t xml:space="preserve">feeder name</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
@@ -5501,7 +5549,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="30.0" customHeight="1">
+    <row r="123" ht="17.0" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5509,24 +5557,24 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">From section</t>
+          <t xml:space="preserve">Copies</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_section</t>
+          <t xml:space="preserve">copies</t>
         </is>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the one before (daisy chain</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123" s="8"/>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+          <t xml:space="preserve">identical feeders (blank = 1)</t>
         </is>
       </c>
       <c r="H123" s="13" t="inlineStr">
@@ -5543,12 +5591,12 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">Section</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">section</t>
         </is>
       </c>
       <c r="D124" s="8"/>
@@ -5556,7 +5604,7 @@
       <c r="F124" s="8"/>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Cables</t>
+          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
@@ -5565,7 +5613,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="17.0" customHeight="1">
+    <row r="125" ht="30.0" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5573,18 +5621,26 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length</t>
+          <t xml:space="preserve">From section</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">length</t>
+          <t xml:space="preserve">from_section</t>
         </is>
       </c>
       <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the one before (daisy chain</t>
+        </is>
+      </c>
       <c r="F125" s="8"/>
-      <c r="G125" s="8"/>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+        </is>
+      </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5599,28 +5655,20 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D126" s="8"/>
-      <c r="E126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+      <c r="E126" s="8"/>
+      <c r="F126" s="8"/>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = km</t>
+          <t xml:space="preserve">from Cables</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
@@ -5637,22 +5685,18 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units at end</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">length</t>
         </is>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">units tapped at the far end</t>
-        </is>
-      </c>
+      <c r="G127" s="8"/>
       <c r="H127" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5667,20 +5711,28 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units of</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units_of</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
+          <t xml:space="preserve">blank = km</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
@@ -5697,24 +5749,20 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel cables</t>
+          <t xml:space="preserve">Units at end</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parallel</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D129" s="8"/>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E129" s="8"/>
       <c r="F129" s="8"/>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">units tapped at the far end</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -5731,24 +5779,20 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R ohm</t>
+          <t xml:space="preserve">Units of</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_ohm</t>
+          <t xml:space="preserve">units_of</t>
         </is>
       </c>
       <c r="D130" s="8"/>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable x Length</t>
-        </is>
-      </c>
+      <c r="E130" s="8"/>
       <c r="F130" s="8"/>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
+          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
@@ -5765,24 +5809,24 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X ohm</t>
+          <t xml:space="preserve">Parallel cables</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_ohm</t>
+          <t xml:space="preserve">parallel</t>
         </is>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable x Length</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F131" s="8"/>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
@@ -5799,12 +5843,12 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B uS</t>
+          <t xml:space="preserve">R ohm</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_us</t>
+          <t xml:space="preserve">r_ohm</t>
         </is>
       </c>
       <c r="D132" s="8"/>
@@ -5816,7 +5860,7 @@
       <c r="F132" s="8"/>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
+          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H132" s="13" t="inlineStr">
@@ -5825,42 +5869,66 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B133" s="7"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
+    <row r="133" ht="17.0" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X ohm</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x_ohm</t>
+        </is>
+      </c>
+      <c r="D133" s="8"/>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
+      <c r="F133" s="8"/>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="17.0" customHeight="1">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">B uS</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">b_us</t>
         </is>
       </c>
       <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
       <c r="F134" s="8"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable type</t>
+          <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
@@ -5869,39 +5937,19 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="17.0" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B135" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Length unit</t>
-        </is>
-      </c>
-      <c r="C135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unit</t>
-        </is>
-      </c>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the values are per</t>
-        </is>
-      </c>
-      <c r="H135" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B135" s="7"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
     </row>
     <row r="136" ht="17.0" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
@@ -5911,12 +5959,12 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R per length</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_per</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D136" s="8"/>
@@ -5924,7 +5972,7 @@
       <c r="F136" s="8"/>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
+          <t xml:space="preserve">cable type</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -5941,20 +5989,24 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">the values are per</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
@@ -5971,12 +6023,12 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D138" s="8"/>
@@ -5984,7 +6036,7 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
@@ -6001,12 +6053,12 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">X per length</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">x_per</t>
         </is>
       </c>
       <c r="D139" s="8"/>
@@ -6014,7 +6066,7 @@
       <c r="F139" s="8"/>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS, instead of C</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
@@ -6023,34 +6075,50 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
+    <row r="140" ht="17.0" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C per length</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c_per</t>
+        </is>
+      </c>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uF</t>
+        </is>
+      </c>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="17.0" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">B per length</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">b_per</t>
         </is>
       </c>
       <c r="D141" s="8"/>
@@ -6058,85 +6126,81 @@
       <c r="F141" s="8"/>
       <c r="G141" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">uS, instead of C</t>
+        </is>
+      </c>
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collectors</t>
+        </is>
+      </c>
+      <c r="B142" s="7"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="7"/>
+    </row>
+    <row r="143" ht="17.0" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collectors</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D143" s="8"/>
+      <c r="E143" s="8"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">shared collector: its far-end bus has this name</t>
         </is>
       </c>
-      <c r="H141" s="13" t="inlineStr">
+      <c r="H143" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
-    </row>
-    <row r="142" ht="17.0" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B142" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connect to</t>
-        </is>
-      </c>
-      <c r="C142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">connect</t>
-        </is>
-      </c>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
-        </is>
-      </c>
-      <c r="H142" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loads_Shunts</t>
-        </is>
-      </c>
-      <c r="B143" s="7"/>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7"/>
-      <c r="G143" s="7"/>
-      <c r="H143" s="7"/>
     </row>
     <row r="144" ht="17.0" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
-      <c r="F144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
+      <c r="F144" s="8"/>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
+          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
@@ -6145,35 +6209,19 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="17.0" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B145" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">At bus</t>
-        </is>
-      </c>
-      <c r="C145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">at</t>
-        </is>
-      </c>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
-        </is>
-      </c>
-      <c r="H145" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
     </row>
     <row r="146" ht="17.0" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
@@ -6183,20 +6231,24 @@
       </c>
       <c r="B146" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mw</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
         </is>
       </c>
       <c r="H146" s="13" t="inlineStr">
@@ -6213,12 +6265,12 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D147" s="8"/>
@@ -6226,7 +6278,7 @@
       <c r="F147" s="8"/>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -6243,101 +6295,97 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">MW</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">mw</t>
         </is>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
-      <c r="G148" s="8"/>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
+        </is>
+      </c>
       <c r="H148" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B149" s="7"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="7"/>
-    </row>
-    <row r="150" ht="30.0" customHeight="1">
+    <row r="149" ht="17.0" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVAr</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mvar</t>
+        </is>
+      </c>
+      <c r="D149" s="8"/>
+      <c r="E149" s="8"/>
+      <c r="F149" s="8"/>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+        </is>
+      </c>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="17.0" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">machine</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
-      <c r="G150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
-        </is>
-      </c>
+      <c r="G150" s="8"/>
       <c r="H150" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="17.0" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B151" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its generator's</t>
-        </is>
-      </c>
-      <c r="F151" s="8"/>
-      <c r="G151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = its generator's</t>
-        </is>
-      </c>
-      <c r="H151" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B151" s="7"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
     </row>
     <row r="152" ht="30.0" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
@@ -6347,24 +6395,20 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pgen MW</t>
+          <t xml:space="preserve">Machine</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pgen_mw</t>
+          <t xml:space="preserve">machine</t>
         </is>
       </c>
       <c r="D152" s="8"/>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
-        </is>
-      </c>
+      <c r="E152" s="8"/>
       <c r="F152" s="8"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -6381,24 +6425,24 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax MW</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmax_mw</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D153" s="8"/>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmax</t>
+          <t xml:space="preserve">its generator's</t>
         </is>
       </c>
       <c r="F153" s="8"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
@@ -6407,7 +6451,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="17.0" customHeight="1">
+    <row r="154" ht="30.0" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6415,24 +6459,24 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmin MW</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmin_mw</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmin</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F154" s="8"/>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H154" s="13" t="inlineStr">
@@ -6449,24 +6493,24 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmax MVAr</t>
+          <t xml:space="preserve">Pmax MW</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmax_mvar</t>
+          <t xml:space="preserve">pmax_mw</t>
         </is>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmax</t>
+          <t xml:space="preserve">its units x Unit Pmax</t>
         </is>
       </c>
       <c r="F155" s="8"/>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
@@ -6483,24 +6527,24 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmin MVAr</t>
+          <t xml:space="preserve">Pmin MW</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmin_mvar</t>
+          <t xml:space="preserve">pmin_mw</t>
         </is>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmin</t>
+          <t xml:space="preserve">its units x Unit Pmin</t>
         </is>
       </c>
       <c r="F156" s="8"/>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
         </is>
       </c>
       <c r="H156" s="13" t="inlineStr">
@@ -6509,7 +6553,7 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="30.0" customHeight="1">
+    <row r="157" ht="17.0" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6517,24 +6561,24 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mvar</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as its generator's Q mode</t>
+          <t xml:space="preserve">its units x Unit Qmax</t>
         </is>
       </c>
       <c r="F157" s="8"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
@@ -6551,24 +6595,24 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBASE MVA</t>
+          <t xml:space="preserve">Qmin MVAr</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mbase_mva</t>
+          <t xml:space="preserve">qmin_mvar</t>
         </is>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit MVA</t>
+          <t xml:space="preserve">its units x Unit Qmin</t>
         </is>
       </c>
       <c r="F158" s="8"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit MVA</t>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -6577,42 +6621,66 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B159" s="7"/>
-      <c r="C159" s="7"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7"/>
-      <c r="G159" s="7"/>
-      <c r="H159" s="7"/>
+    <row r="159" ht="30.0" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixed Q MVAr</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q_mvar</t>
+        </is>
+      </c>
+      <c r="D159" s="8"/>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as its generator's Q mode</t>
+        </is>
+      </c>
+      <c r="F159" s="8"/>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+        </is>
+      </c>
+      <c r="H159" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="17.0" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus</t>
+          <t xml:space="preserve">MBASE MVA</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bus</t>
+          <t xml:space="preserve">mbase_mva</t>
         </is>
       </c>
       <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit MVA</t>
+        </is>
+      </c>
       <c r="F160" s="8"/>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+          <t xml:space="preserve">blank = its units x Unit MVA</t>
         </is>
       </c>
       <c r="H160" s="13" t="inlineStr">
@@ -6621,41 +6689,21 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="17.0" customHeight="1">
-      <c r="A161" s="8" t="inlineStr">
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B161" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number</t>
-        </is>
-      </c>
-      <c r="C161" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic</t>
-        </is>
-      </c>
-      <c r="F161" s="8"/>
-      <c r="G161" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = automatic</t>
-        </is>
-      </c>
-      <c r="H161" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="30.0" customHeight="1">
+      <c r="B161" s="7"/>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
+      <c r="G161" s="7"/>
+      <c r="H161" s="7"/>
+    </row>
+    <row r="162" ht="17.0" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
@@ -6663,24 +6711,20 @@
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Bus</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">bus</t>
         </is>
       </c>
       <c r="D162" s="8"/>
-      <c r="E162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
-        </is>
-      </c>
+      <c r="E162" s="8"/>
       <c r="F162" s="8"/>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
         </is>
       </c>
       <c r="H162" s="13" t="inlineStr">
@@ -6689,79 +6733,87 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B163" s="7"/>
-      <c r="C163" s="7"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
-      <c r="G163" s="7"/>
-      <c r="H163" s="7"/>
-    </row>
-    <row r="164" ht="17.0" customHeight="1">
+    <row r="163" ht="17.0" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D163" s="8"/>
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic</t>
+        </is>
+      </c>
+      <c r="F163" s="8"/>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = automatic</t>
+        </is>
+      </c>
+      <c r="H163" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="30.0" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
       <c r="F164" s="8"/>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
         </is>
       </c>
       <c r="H164" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="30.0" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B165" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Model</t>
-        </is>
-      </c>
-      <c r="C165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">model</t>
-        </is>
-      </c>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
-        </is>
-      </c>
-      <c r="H165" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
+      <c r="H165" s="7"/>
     </row>
     <row r="166" ht="17.0" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
@@ -6771,12 +6823,12 @@
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D166" s="8"/>
@@ -6784,7 +6836,7 @@
       <c r="F166" s="8"/>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
         </is>
       </c>
       <c r="H166" s="13" t="inlineStr">
@@ -6793,7 +6845,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="17.0" customHeight="1">
+    <row r="167" ht="30.0" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
@@ -6801,171 +6853,175 @@
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Model</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
-      <c r="G167" s="8"/>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+        </is>
+      </c>
       <c r="H167" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B168" s="7"/>
-      <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
-      <c r="G168" s="7"/>
-      <c r="H168" s="7"/>
+    <row r="168" ht="17.0" customHeight="1">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
+      <c r="D168" s="8"/>
+      <c r="E168" s="8"/>
+      <c r="F168" s="8"/>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="17.0" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D169" s="8"/>
+      <c r="E169" s="8"/>
+      <c r="F169" s="8"/>
+      <c r="G169" s="8"/>
+      <c r="H169" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
-      <c r="B169" s="12" t="inlineStr">
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="7"/>
+      <c r="H170" s="7"/>
+    </row>
+    <row r="171" ht="17.0" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Generator</t>
         </is>
       </c>
-      <c r="C169" s="8" t="inlineStr">
+      <c r="C171" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">generator</t>
         </is>
       </c>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8" t="inlineStr">
+      <c r="D171" s="8"/>
+      <c r="E171" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">the plant</t>
         </is>
       </c>
-      <c r="F169" s="8"/>
-      <c r="G169" s="8" t="inlineStr">
+      <c r="F171" s="8"/>
+      <c r="G171" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = the plant</t>
         </is>
       </c>
-      <c r="H169" s="13" t="inlineStr">
+      <c r="H171" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
-    </row>
-    <row r="170" ht="17.0" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B170" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Record</t>
-        </is>
-      </c>
-      <c r="C170" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">record</t>
-        </is>
-      </c>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
-      <c r="F170" s="8"/>
-      <c r="G170" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
-        </is>
-      </c>
-      <c r="H170" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B171" s="7"/>
-      <c r="C171" s="7"/>
-      <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
-      <c r="G171" s="7"/>
-      <c r="H171" s="7"/>
     </row>
     <row r="172" ht="17.0" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Record</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">record</t>
         </is>
       </c>
       <c r="D172" s="8"/>
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
-      <c r="G172" s="8"/>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
+        </is>
+      </c>
       <c r="H172" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="17.0" customHeight="1">
-      <c r="A173" s="8" t="inlineStr">
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B173" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parameter</t>
-        </is>
-      </c>
-      <c r="C173" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parameter</t>
-        </is>
-      </c>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
-      <c r="F173" s="8"/>
-      <c r="G173" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
-        </is>
-      </c>
-      <c r="H173" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+      <c r="B173" s="7"/>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
     </row>
     <row r="174" ht="17.0" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
@@ -6975,83 +7031,103 @@
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
-      <c r="G174" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
-        </is>
-      </c>
+      <c r="G174" s="8"/>
       <c r="H174" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
-        </is>
-      </c>
-      <c r="B175" s="7"/>
-      <c r="C175" s="7"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
-      <c r="G175" s="7"/>
-      <c r="H175" s="7"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="8"/>
+    <row r="175" ht="17.0" customHeight="1">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
+      <c r="D175" s="8"/>
+      <c r="E175" s="8"/>
+      <c r="F175" s="8"/>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H175" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="17.0" customHeight="1">
+      <c r="A176" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C176" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D176" s="8"/>
       <c r="E176" s="8"/>
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H176" s="8"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="8"/>
-      <c r="B177" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI</t>
-        </is>
-      </c>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the point of interconnection</t>
-        </is>
-      </c>
-      <c r="H177" s="8"/>
+          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+        </is>
+      </c>
+      <c r="H176" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
+        </is>
+      </c>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="7"/>
+      <c r="H177" s="7"/>
     </row>
     <row r="178">
       <c r="A178" s="8"/>
       <c r="B178" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C178" s="8"/>
@@ -7060,7 +7136,7 @@
       <c r="F178" s="8"/>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H178" s="8"/>
@@ -7069,7 +7145,7 @@
       <c r="A179" s="8"/>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C179" s="8"/>
@@ -7078,7 +7154,7 @@
       <c r="F179" s="8"/>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H179" s="8"/>
@@ -7087,7 +7163,7 @@
       <c r="A180" s="8"/>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C180" s="8"/>
@@ -7096,7 +7172,7 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
         </is>
       </c>
       <c r="H180" s="8"/>
@@ -7105,7 +7181,7 @@
       <c r="A181" s="8"/>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -7114,7 +7190,7 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+          <t xml:space="preserve">an MPT's LV winding</t>
         </is>
       </c>
       <c r="H181" s="8"/>
@@ -7123,7 +7199,7 @@
       <c r="A182" s="8"/>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C182" s="8"/>
@@ -7132,7 +7208,7 @@
       <c r="F182" s="8"/>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
         </is>
       </c>
       <c r="H182" s="8"/>
@@ -7141,7 +7217,7 @@
       <c r="A183" s="8"/>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -7150,7 +7226,7 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
         </is>
       </c>
       <c r="H183" s="8"/>
@@ -7159,7 +7235,7 @@
       <c r="A184" s="8"/>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C184" s="8"/>
@@ -7168,7 +7244,7 @@
       <c r="F184" s="8"/>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H184" s="8"/>
@@ -7177,7 +7253,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -7186,7 +7262,7 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H185" s="8"/>
@@ -7195,7 +7271,7 @@
       <c r="A186" s="8"/>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
         </is>
       </c>
       <c r="C186" s="8"/>
@@ -7204,34 +7280,34 @@
       <c r="F186" s="8"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+          <t xml:space="preserve">a generator's terminal</t>
         </is>
       </c>
       <c r="H186" s="8"/>
     </row>
-    <row r="187" ht="18" customHeight="1">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
-        </is>
-      </c>
-      <c r="B187" s="7"/>
-      <c r="C187" s="7"/>
-      <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7"/>
-      <c r="G187" s="7"/>
-      <c r="H187" s="7"/>
+    <row r="187">
+      <c r="A187" s="8"/>
+      <c r="B187" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+        </is>
+      </c>
+      <c r="C187" s="8"/>
+      <c r="D187" s="8"/>
+      <c r="E187" s="8"/>
+      <c r="F187" s="8"/>
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H187" s="8"/>
     </row>
     <row r="188">
-      <c r="A188" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A188" s="8"/>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNITS}</t>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
         </is>
       </c>
       <c r="C188" s="8"/>
@@ -7240,40 +7316,24 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H188" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B189" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{MVA}</t>
-        </is>
-      </c>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
-      <c r="F189" s="8"/>
-      <c r="G189" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">their MVA</t>
-        </is>
-      </c>
-      <c r="H189" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+        </is>
+      </c>
+      <c r="H188" s="8"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
+        </is>
+      </c>
+      <c r="B189" s="7"/>
+      <c r="C189" s="7"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
     </row>
     <row r="190">
       <c r="A190" s="8" t="inlineStr">
@@ -7283,7 +7343,7 @@
       </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_MW}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C190" s="8"/>
@@ -7292,7 +7352,7 @@
       <c r="F190" s="8"/>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H190" s="13" t="inlineStr">
@@ -7309,7 +7369,7 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C191" s="8"/>
@@ -7318,7 +7378,7 @@
       <c r="F191" s="8"/>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H191" s="13" t="inlineStr">
@@ -7335,7 +7395,7 @@
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C192" s="8"/>
@@ -7344,7 +7404,7 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
@@ -7361,7 +7421,7 @@
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C193" s="8"/>
@@ -7370,7 +7430,7 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H193" s="13" t="inlineStr">
@@ -7387,7 +7447,7 @@
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C194" s="8"/>
@@ -7396,7 +7456,7 @@
       <c r="F194" s="8"/>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H194" s="13" t="inlineStr">
@@ -7413,7 +7473,7 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -7422,7 +7482,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
@@ -7439,7 +7499,7 @@
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -7448,7 +7508,7 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
@@ -7465,7 +7525,7 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C197" s="8"/>
@@ -7474,7 +7534,7 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H197" s="13" t="inlineStr">
@@ -7491,7 +7551,7 @@
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C198" s="8"/>
@@ -7500,7 +7560,7 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr">
@@ -7517,7 +7577,7 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C199" s="8"/>
@@ -7526,7 +7586,7 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H199" s="13" t="inlineStr">
@@ -7543,7 +7603,7 @@
       </c>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C200" s="8"/>
@@ -7552,7 +7612,7 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H200" s="13" t="inlineStr">
@@ -7569,7 +7629,7 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C201" s="8"/>
@@ -7578,7 +7638,7 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H201" s="13" t="inlineStr">
@@ -7595,7 +7655,7 @@
       </c>
       <c r="B202" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C202" s="8"/>
@@ -7604,7 +7664,7 @@
       <c r="F202" s="8"/>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H202" s="13" t="inlineStr">
@@ -7621,7 +7681,7 @@
       </c>
       <c r="B203" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C203" s="8"/>
@@ -7630,7 +7690,7 @@
       <c r="F203" s="8"/>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">frequency (Hz)</t>
         </is>
       </c>
       <c r="H203" s="13" t="inlineStr">
@@ -7647,7 +7707,7 @@
       </c>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{P_INV_MW}</t>
         </is>
       </c>
       <c r="C204" s="8"/>
@@ -7656,10 +7716,62 @@
       <c r="F204" s="8"/>
       <c r="G204" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+        </is>
+      </c>
+      <c r="H204" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B205" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
+        </is>
+      </c>
+      <c r="C205" s="8"/>
+      <c r="D205" s="8"/>
+      <c r="E205" s="8"/>
+      <c r="F205" s="8"/>
+      <c r="G205" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H205" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B206" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C206" s="8"/>
+      <c r="D206" s="8"/>
+      <c r="E206" s="8"/>
+      <c r="F206" s="8"/>
+      <c r="G206" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H204" s="13" t="inlineStr">
+      <c r="H206" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -7670,34 +7782,34 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A118:H118"/>
-    <mergeCell ref="A133:H133"/>
-    <mergeCell ref="A140:H140"/>
-    <mergeCell ref="A143:H143"/>
-    <mergeCell ref="A149:H149"/>
-    <mergeCell ref="A159:H159"/>
-    <mergeCell ref="A163:H163"/>
-    <mergeCell ref="A168:H168"/>
-    <mergeCell ref="A171:H171"/>
-    <mergeCell ref="A175:H175"/>
-    <mergeCell ref="A187:H187"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A135:H135"/>
+    <mergeCell ref="A142:H142"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A151:H151"/>
+    <mergeCell ref="A161:H161"/>
+    <mergeCell ref="A165:H165"/>
+    <mergeCell ref="A170:H170"/>
+    <mergeCell ref="A173:H173"/>
+    <mergeCell ref="A177:H177"/>
+    <mergeCell ref="A189:H189"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
-    <hyperlink ref="A51" location="'MPT'!A1" display="MPT"/>
-    <hyperlink ref="A79" location="'Generators'!A1" display="Generators"/>
-    <hyperlink ref="A118" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A133" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A140" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A143" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A149" location="'Machines'!A1" display="Machines"/>
-    <hyperlink ref="A159" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A163" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A168" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A171" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A187" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A52" location="'MPT'!A1" display="MPT"/>
+    <hyperlink ref="A81" location="'Generators'!A1" display="Generators"/>
+    <hyperlink ref="A120" location="'Feeders'!A1" display="Feeders"/>
+    <hyperlink ref="A135" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A142" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A145" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A151" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A161" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A165" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A170" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A173" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A189" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -18844,52 +18956,62 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="17.0" customHeight="1">
+    <row r="23" ht="30.0" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gen-tie values per</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Gen-tie length unit</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the length R, X, B, C below are per: km, mi, kft, m, ft (blank = the Gen-tie length unit)</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30.0" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gen-tie R per length</t>
         </is>
       </c>
-      <c r="B23" s="3">
+      <c r="B24" s="3">
         <v>0.072</v>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm</t>
         </is>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one circuit, per length unit</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17.0" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gen-tie X per length</t>
-        </is>
-      </c>
-      <c r="B24" s="3">
-        <v>0.495</v>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
-      <c r="D24" s="8"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a typical overhead line of the POI kV</t>
+        </is>
+      </c>
       <c r="E24" s="8"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit</t>
+          <t xml:space="preserve">one circuit (blank = a typical overhead line of the POI kV)</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -18901,22 +19023,26 @@
     <row r="25" ht="17.0" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie B per length</t>
+          <t xml:space="preserve">Gen-tie X per length</t>
         </is>
       </c>
       <c r="B25" s="3">
-        <v>3.35</v>
+        <v>0.495</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
-        </is>
-      </c>
-      <c r="D25" s="8"/>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
       <c r="E25" s="8"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit, per length unit (total charging)</t>
+          <t xml:space="preserve">one circuit (blank = typical)</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -18928,20 +19054,26 @@
     <row r="26" ht="17.0" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie C per length</t>
-        </is>
-      </c>
-      <c r="B26" s="3"/>
+          <t xml:space="preserve">Gen-tie B per length</t>
+        </is>
+      </c>
+      <c r="B26" s="3">
+        <v>3.35</v>
+      </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
-        </is>
-      </c>
-      <c r="D26" s="8"/>
+          <t xml:space="preserve">uS</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
       <c r="E26" s="8"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of B</t>
+          <t xml:space="preserve">one circuit, total charging (blank = typical)</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
@@ -18953,20 +19085,20 @@
     <row r="27" ht="17.0" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie R total</t>
+          <t xml:space="preserve">Gen-tie C per length</t>
         </is>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">uF</t>
         </is>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of per length (one circuit)</t>
+          <t xml:space="preserve">instead of B</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -18978,7 +19110,7 @@
     <row r="28" ht="17.0" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie X total</t>
+          <t xml:space="preserve">Gen-tie R total</t>
         </is>
       </c>
       <c r="B28" s="3"/>
@@ -18989,7 +19121,11 @@
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="2"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instead of per length (one circuit)</t>
+        </is>
+      </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -18999,13 +19135,13 @@
     <row r="29" ht="17.0" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie B total</t>
+          <t xml:space="preserve">Gen-tie X total</t>
         </is>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="D29" s="8"/>
@@ -19020,24 +19156,18 @@
     <row r="30" ht="17.0" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie circuits</t>
-        </is>
-      </c>
-      <c r="B30" s="3">
-        <v>1</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Gen-tie B total</t>
+        </is>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uS</t>
+        </is>
+      </c>
+      <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">identical circuits in parallel (blank = 1)</t>
-        </is>
-      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -19047,22 +19177,22 @@
     <row r="31" ht="17.0" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gen-tie rating</t>
+          <t xml:space="preserve">Gen-tie circuits</t>
         </is>
       </c>
       <c r="B31" s="3">
-        <v>400.0</v>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
-      <c r="D31" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="E31" s="8"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">one circuit</t>
+          <t xml:space="preserve">identical circuits in parallel (blank = 1)</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -19071,71 +19201,71 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="32" ht="30.0" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gen-tie rating</t>
+        </is>
+      </c>
+      <c r="B32" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical for the POI kV</t>
+        </is>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one circuit (blank = typical for the POI kV)</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">OPERATING POINT (the load flow's targets at the POI)</t>
         </is>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" ht="30.0" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" ht="30.0" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Control mode</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Q</t>
         </is>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q | PF | V</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage</t>
-        </is>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="17.0" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI voltage</t>
-        </is>
-      </c>
-      <c r="B34" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.0</t>
-        </is>
-      </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
@@ -19147,26 +19277,26 @@
     <row r="35" ht="17.0" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at POI</t>
+          <t xml:space="preserve">POI voltage</t>
         </is>
       </c>
       <c r="B35" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">pu</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1.0</t>
         </is>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
+          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -19178,18 +19308,26 @@
     <row r="36" ht="17.0" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PF at POI</t>
+          <t xml:space="preserve">Q at POI</t>
         </is>
       </c>
       <c r="B36" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
+        <v>0.0</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVAr</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
       <c r="E36" s="8"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
+          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
@@ -19201,26 +19339,18 @@
     <row r="37" ht="17.0" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid voltage</t>
+          <t xml:space="preserve">PF at POI</t>
         </is>
       </c>
       <c r="B37" s="3">
         <v>1.0</v>
       </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.0</t>
-        </is>
-      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
+          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
@@ -19229,181 +19359,181 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="30.0" customHeight="1">
+    <row r="38" ht="17.0" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at POI</t>
-        </is>
-      </c>
-      <c r="B38" s="3"/>
+          <t xml:space="preserve">Grid voltage</t>
+        </is>
+      </c>
+      <c r="B38" s="3">
+        <v>1.0</v>
+      </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">pu</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each generator at its dispatch</t>
+          <t xml:space="preserve">1.0</t>
         </is>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30.0" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P at POI</t>
+        </is>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">each generator at its dispatch</t>
+        </is>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PLANT CONTROLLER (PSS/E .dyr)</t>
         </is>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-    </row>
-    <row r="40" ht="30.0" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant controller</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPC_B</t>
-        </is>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPC_A</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REPC_A | REPC_B</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
     </row>
     <row r="41" ht="30.0" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGC_A / REPC_A records</t>
+          <t xml:space="preserve">Plant controller</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard</t>
+          <t xml:space="preserve">REPC_B</t>
         </is>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">REPC_A</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REPC_A | REPC_B</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr -- REPC_A: a REPCA1 on each generator | REPC_B: one for the plant, PLNTBU1 at the POI and a REAX4BU1 on each generator (hybrid plants) (blank = REPC_A)</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30.0" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGC_A / REPC_A records</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">standard</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="C42" s="8"/>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">standard | USRMDL</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">standard: REGCA1 / REPCA1 (PSS/E library) | USRMDL: REGCAU1 / REPCAU1 (the WECC user-model DLL) (blank = standard)</t>
         </is>
       </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD RUN</t>
         </is>
       </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-    </row>
-    <row r="43" ht="43.0" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+    </row>
+    <row r="44" ht="43.0" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD time step</t>
         </is>
       </c>
-      <c r="B43" s="3">
+      <c r="B44" s="3">
         <v>10.0</v>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">us</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10 (the vendor model's own requirement wins</t>
-        </is>
-      </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 10 (the vendor model's own requirement wins)</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="17.0" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD duration</t>
-        </is>
-      </c>
-      <c r="B44" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 5</t>
+          <t xml:space="preserve">blank = 10 (the vendor model's own requirement wins)</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -19415,26 +19545,26 @@
     <row r="45" ht="17.0" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD plot step</t>
+          <t xml:space="preserve">PSCAD duration</t>
         </is>
       </c>
       <c r="B45" s="3">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">us</t>
+          <t xml:space="preserve">s</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 100</t>
+          <t xml:space="preserve">blank = 5</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
@@ -19446,128 +19576,130 @@
     <row r="46" ht="17.0" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD plot step</t>
+        </is>
+      </c>
+      <c r="B46" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">us</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100</t>
+        </is>
+      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = 100</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17.0" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD meter at POI</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">YES</t>
         </is>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
         </is>
       </c>
-      <c r="G46" s="13" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="43.0" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="48" ht="43.0" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD lines as</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">PI</t>
         </is>
       </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="C48" s="8"/>
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PI</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PI | RLC</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
         </is>
       </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD FAULT AT THE POI</t>
         </is>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-    </row>
-    <row r="49" ht="30.0" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+    </row>
+    <row r="50" ht="30.0" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault at POI</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">YES</t>
         </is>
       </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="17.0" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault time</t>
-        </is>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100: none in the run</t>
-        </is>
-      </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
@@ -19579,12 +19711,10 @@
     <row r="51" ht="17.0" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault duration</t>
-        </is>
-      </c>
-      <c r="B51" s="3">
-        <v>0.15</v>
-      </c>
+          <t xml:space="preserve">PSCAD fault time</t>
+        </is>
+      </c>
+      <c r="B51" s="3"/>
       <c r="C51" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">s</t>
@@ -19592,114 +19722,145 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
+          <t xml:space="preserve">100: none in the run</t>
         </is>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="17.0" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault duration</t>
+        </is>
+      </c>
+      <c r="B52" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
+      <c r="E52" s="8"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 0.15</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="43.0" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+    <row r="53" ht="43.0" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault type</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="C53" s="8"/>
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="17.0" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
+    <row r="54" ht="17.0" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault resistance</t>
         </is>
       </c>
-      <c r="B53" s="3">
+      <c r="B54" s="3">
         <v>0.01</v>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">0.01</t>
         </is>
       </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="E54" s="8"/>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 0.01</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD LIBRARIES</t>
         </is>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-    </row>
-    <row r="55" ht="17.0" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+    </row>
+    <row r="56" ht="17.0" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD libraries</t>
         </is>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="B56" s="3"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -19710,13 +19871,13 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A55:G55"/>
   </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="13">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4">
       <formula1>"SMIB,DETAILED"</formula1>
     </dataValidation>
@@ -19732,25 +19893,28 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B22">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B33">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B23">
+      <formula1>"km,mi,kft,m,ft"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B34">
       <formula1>"Q,PF,V"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B40">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B41">
       <formula1>"REPC_A,REPC_B"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B41">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B42">
       <formula1>"standard,USRMDL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B46">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B47">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B47">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B48">
       <formula1>"PI,RLC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B49">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B50">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B52">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B53">
       <formula1>"ABCG,ABC,AG,BG,CG,ABG,BCG,ACG,AB,BC,AC"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19793,6 +19957,7 @@
     <col min="25" max="25" width="10" customWidth="1"/>
     <col min="26" max="26" width="10" customWidth="1"/>
     <col min="27" max="27" width="10" customWidth="1"/>
+    <col min="28" max="28" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -19913,20 +20078,25 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tie values per</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie X per length</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie B per length</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie rating MVA</t>
         </is>
@@ -20038,20 +20208,29 @@
       <c r="W2" s="2"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = Tie length unit)</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS</t>
-        </is>
-      </c>
-      <c r="AA2" s="2"/>
+          <t xml:space="preserve">ohm (blank = typical)</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uS (blank = typical)</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = typical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -20105,6 +20284,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3"/>
@@ -20134,6 +20314,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
@@ -20163,6 +20344,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3"/>
@@ -20192,6 +20374,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3"/>
@@ -20221,6 +20404,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3"/>
@@ -20250,6 +20434,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3"/>
@@ -20279,6 +20464,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
@@ -20308,6 +20494,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3"/>
@@ -20337,6 +20524,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
@@ -20366,6 +20554,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -20395,6 +20584,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -20424,6 +20614,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -20453,6 +20644,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -20482,6 +20674,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -20511,6 +20704,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -20540,6 +20734,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -20569,6 +20764,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -20598,6 +20794,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -20627,6 +20824,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -20656,10 +20854,14 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W3:W500">
+      <formula1>"km,mi,kft,m,ft"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X3:X500">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
   </dataValidations>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -3379,7 +3379,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="17.0" customHeight="1">
+    <row r="54" ht="30.0" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -3387,18 +3387,30 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV kV</t>
+          <t xml:space="preserve">Windings</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hv_kv</t>
+          <t xml:space="preserve">windings</t>
         </is>
       </c>
       <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 when TV kV is given, else 2</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 | 3</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 or 3 (blank = 3 when TV kV is given, else 2)</t>
+        </is>
+      </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -3413,12 +3425,12 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV kV</t>
+          <t xml:space="preserve">HV kV</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_kv</t>
+          <t xml:space="preserve">hv_kv</t>
         </is>
       </c>
       <c r="D55" s="8"/>
@@ -3439,54 +3451,50 @@
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">LV kV</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lv_kv</t>
+        </is>
+      </c>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30.0" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">TV kV</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">tv_kv</t>
         </is>
       </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">two windings</t>
-        </is>
-      </c>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tertiary / 2nd LV winding; blank = two windings</t>
-        </is>
-      </c>
-      <c r="H56" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="17.0" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mva</t>
-        </is>
-      </c>
       <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the LV kV, a split LV winding</t>
+        </is>
+      </c>
       <c r="F57" s="8"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
+          <t xml:space="preserve">tertiary / 2nd LV winding (Windings 3; blank = the LV kV, a split LV winding)</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -3503,12 +3511,12 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV MVA</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_mva</t>
+          <t xml:space="preserve">mva</t>
         </is>
       </c>
       <c r="D58" s="8"/>
@@ -3516,7 +3524,7 @@
       <c r="F58" s="8"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -3533,12 +3541,12 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TV MVA</t>
+          <t xml:space="preserve">LV MVA</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tv_mva</t>
+          <t xml:space="preserve">lv_mva</t>
         </is>
       </c>
       <c r="D59" s="8"/>
@@ -3563,12 +3571,12 @@
       </c>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV %</t>
+          <t xml:space="preserve">TV MVA</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_hl_pct</t>
+          <t xml:space="preserve">tv_mva</t>
         </is>
       </c>
       <c r="D60" s="8"/>
@@ -3576,7 +3584,7 @@
       <c r="F60" s="8"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on its base MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -3593,12 +3601,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV %</t>
+          <t xml:space="preserve">Z HV-LV %</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_ht_pct</t>
+          <t xml:space="preserve">z_hl_pct</t>
         </is>
       </c>
       <c r="D61" s="8"/>
@@ -3606,7 +3614,7 @@
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">on its base MVA</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -3623,12 +3631,12 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV %</t>
+          <t xml:space="preserve">Z HV-TV %</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_lt_pct</t>
+          <t xml:space="preserve">z_ht_pct</t>
         </is>
       </c>
       <c r="D62" s="8"/>
@@ -3653,24 +3661,20 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV base MVA</t>
+          <t xml:space="preserve">Z LV-TV %</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_hl_mva</t>
+          <t xml:space="preserve">z_lt_pct</t>
         </is>
       </c>
       <c r="D63" s="8"/>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E63" s="8"/>
       <c r="F63" s="8"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -3687,12 +3691,12 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-LV base MVA</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_ht_mva</t>
+          <t xml:space="preserve">base_hl_mva</t>
         </is>
       </c>
       <c r="D64" s="8"/>
@@ -3721,12 +3725,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-TV base MVA</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_lt_mva</t>
+          <t xml:space="preserve">base_ht_mva</t>
         </is>
       </c>
       <c r="D65" s="8"/>
@@ -3755,20 +3759,24 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X/R</t>
+          <t xml:space="preserve">Z LV-TV base MVA</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_r</t>
+          <t xml:space="preserve">base_lt_mva</t>
         </is>
       </c>
       <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each impedance</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -3785,12 +3793,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load loss kW</t>
+          <t xml:space="preserve">X/R</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">load_loss_kw</t>
+          <t xml:space="preserve">x_r</t>
         </is>
       </c>
       <c r="D67" s="8"/>
@@ -3798,7 +3806,7 @@
       <c r="F67" s="8"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
+          <t xml:space="preserve">each impedance</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -3815,12 +3823,12 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector group</t>
+          <t xml:space="preserve">Load loss kW</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vector</t>
+          <t xml:space="preserve">load_loss_kw</t>
         </is>
       </c>
       <c r="D68" s="8"/>
@@ -3828,7 +3836,7 @@
       <c r="F68" s="8"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
+          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -3845,24 +3853,20 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV tap</t>
+          <t xml:space="preserve">Vector group</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tap</t>
+          <t xml:space="preserve">vector</t>
         </is>
       </c>
       <c r="D69" s="8"/>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
+          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3879,12 +3883,12 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel units</t>
+          <t xml:space="preserve">HV tap</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">count</t>
+          <t xml:space="preserve">tap</t>
         </is>
       </c>
       <c r="D70" s="8"/>
@@ -3896,7 +3900,7 @@
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical units (blank = 1)</t>
+          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -3913,24 +3917,24 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No-load loss %</t>
+          <t xml:space="preserve">Parallel units</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nll_pct</t>
+          <t xml:space="preserve">count</t>
         </is>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">of MVA (blank = 0)</t>
+          <t xml:space="preserve">identical units (blank = 1)</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -3947,12 +3951,12 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnetising current %</t>
+          <t xml:space="preserve">No-load loss %</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">im_pct</t>
+          <t xml:space="preserve">nll_pct</t>
         </is>
       </c>
       <c r="D72" s="8"/>
@@ -3981,24 +3985,24 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rating MVA</t>
+          <t xml:space="preserve">Magnetising current %</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_mva</t>
+          <t xml:space="preserve">im_pct</t>
         </is>
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -4015,24 +4019,24 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length</t>
+          <t xml:space="preserve">Rating MVA</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_length</t>
+          <t xml:space="preserve">rate_mva</t>
         </is>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -4049,22 +4053,26 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length unit</t>
+          <t xml:space="preserve">Tie length</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_unit</t>
+          <t xml:space="preserve">tie_length</t>
         </is>
       </c>
       <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G75" s="8"/>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+        </is>
+      </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4079,62 +4087,58 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tie length unit</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_unit</t>
+        </is>
+      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
+      <c r="G76" s="8"/>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="17.0" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tie values per</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">tie_per_unit</t>
-        </is>
-      </c>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tie length unit</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the length R, X, B are per (blank = Tie length unit)</t>
-        </is>
-      </c>
-      <c r="H76" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30.0" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tie R per length</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a typical overhead line of the HV kV</t>
-        </is>
-      </c>
-      <c r="F77" s="8"/>
+          <t xml:space="preserve">Tie length unit</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = Tie length unit)</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -4143,7 +4147,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="17.0" customHeight="1">
+    <row r="78" ht="30.0" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -4151,24 +4155,24 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie X per length</t>
+          <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_per</t>
+          <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">typical</t>
+          <t xml:space="preserve">a typical overhead line of the HV kV</t>
         </is>
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm (blank = typical)</t>
+          <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -4185,12 +4189,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie B per length</t>
+          <t xml:space="preserve">Tie X per length</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_per</t>
+          <t xml:space="preserve">tie_x_per</t>
         </is>
       </c>
       <c r="D79" s="8"/>
@@ -4202,7 +4206,7 @@
       <c r="F79" s="8"/>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS (blank = typical)</t>
+          <t xml:space="preserve">ohm (blank = typical)</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
@@ -4219,12 +4223,12 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie rating MVA</t>
+          <t xml:space="preserve">Tie B per length</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_rate_mva</t>
+          <t xml:space="preserve">tie_b_per</t>
         </is>
       </c>
       <c r="D80" s="8"/>
@@ -4236,119 +4240,119 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">uS (blank = typical)</t>
+        </is>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="17.0" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tie rating MVA</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_rate_mva</t>
+        </is>
+      </c>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = typical</t>
         </is>
       </c>
-      <c r="H80" s="13" t="inlineStr">
+      <c r="H81" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-    </row>
-    <row r="82" ht="17.0" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+    </row>
+    <row r="83" ht="17.0" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
-        </is>
-      </c>
-      <c r="H82" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="30.0" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F83" s="8"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
+        </is>
+      </c>
+      <c r="H83" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30.0" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
         </is>
       </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
-        </is>
-      </c>
-      <c r="H83" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="17.0" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -4365,20 +4369,24 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F85" s="8"/>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4395,12 +4403,12 @@
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D86" s="8"/>
@@ -4408,7 +4416,7 @@
       <c r="F86" s="8"/>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number of units</t>
+          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
@@ -4425,24 +4433,20 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit MVA</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_mva</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D87" s="8"/>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from P and Q</t>
-        </is>
-      </c>
+      <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+          <t xml:space="preserve">number of units</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4459,18 +4463,26 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmax MW</t>
+          <t xml:space="preserve">Unit MVA</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmax_mw</t>
+          <t xml:space="preserve">unit_mva</t>
         </is>
       </c>
       <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from P and Q</t>
+        </is>
+      </c>
       <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+        </is>
+      </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4485,26 +4497,18 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmin MW</t>
+          <t xml:space="preserve">Unit Pmax MW</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmin_mw</t>
+          <t xml:space="preserve">unit_pmax_mw</t>
         </is>
       </c>
       <c r="D89" s="8"/>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
+      <c r="E89" s="8"/>
       <c r="F89" s="8"/>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
-        </is>
-      </c>
+      <c r="G89" s="8"/>
       <c r="H89" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4519,24 +4523,24 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmax MVAr</t>
+          <t xml:space="preserve">Unit Pmin MW</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmax_mvar</t>
+          <t xml:space="preserve">unit_pmin_mw</t>
         </is>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Unit PF</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = from Unit PF</t>
+          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4553,24 +4557,24 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmin MVAr</t>
+          <t xml:space="preserve">Unit Qmax MVAr</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmin_mvar</t>
+          <t xml:space="preserve">unit_qmax_mvar</t>
         </is>
       </c>
       <c r="D91" s="8"/>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Qmax</t>
+          <t xml:space="preserve">from Unit PF</t>
         </is>
       </c>
       <c r="F91" s="8"/>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = -Qmax</t>
+          <t xml:space="preserve">blank = from Unit PF</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -4587,24 +4591,24 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit PF</t>
+          <t xml:space="preserve">Unit Qmin MVAr</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pf</t>
+          <t xml:space="preserve">unit_qmin_mvar</t>
         </is>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95</t>
+          <t xml:space="preserve">-Qmax</t>
         </is>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
+          <t xml:space="preserve">blank = -Qmax</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
@@ -4621,24 +4625,24 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminal kV</t>
+          <t xml:space="preserve">Unit PF</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kv</t>
+          <t xml:space="preserve">unit_pf</t>
         </is>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">0.95</t>
         </is>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = GSU LV kV</t>
+          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
@@ -4647,7 +4651,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="30.0" customHeight="1">
+    <row r="94" ht="17.0" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4655,58 +4659,58 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispatch MW</t>
+          <t xml:space="preserve">Terminal kV</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dispatch_mw</t>
+          <t xml:space="preserve">kv</t>
         </is>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = GSU LV kV</t>
+        </is>
+      </c>
+      <c r="H94" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30.0" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dispatch MW</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dispatch_mw</t>
+        </is>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+        </is>
+      </c>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
-        </is>
-      </c>
-      <c r="H94" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="17.0" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q mode</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">q_mode</t>
-        </is>
-      </c>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share | fixed</t>
-        </is>
-      </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
@@ -4723,24 +4727,24 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Q mode</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_q_mvar</t>
+          <t xml:space="preserve">q_mode</t>
         </is>
       </c>
       <c r="D96" s="8"/>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">share | fixed</t>
+        </is>
+      </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
+          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
         </is>
       </c>
       <c r="H96" s="13" t="inlineStr">
@@ -4757,20 +4761,24 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed PF</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_pf</t>
+          <t xml:space="preserve">fixed_q_mvar</t>
         </is>
       </c>
       <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
       <c r="F97" s="8"/>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
+          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
@@ -4787,24 +4795,20 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU count</t>
+          <t xml:space="preserve">Fixed PF</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_count</t>
+          <t xml:space="preserve">fixed_pf</t>
         </is>
       </c>
       <c r="D98" s="8"/>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Units</t>
-        </is>
-      </c>
+      <c r="E98" s="8"/>
       <c r="F98" s="8"/>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = Units</t>
+          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
         </is>
       </c>
       <c r="H98" s="13" t="inlineStr">
@@ -4813,7 +4817,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="30.0" customHeight="1">
+    <row r="99" ht="17.0" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4821,52 +4825,60 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU MVA</t>
+          <t xml:space="preserve">GSU count</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_mva</t>
+          <t xml:space="preserve">gsu_count</t>
         </is>
       </c>
       <c r="D99" s="8"/>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">no GSU (units on the MV bus</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="F99" s="8"/>
       <c r="G99" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = Units</t>
+        </is>
+      </c>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30.0" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSU MVA</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gsu_mva</t>
+        </is>
+      </c>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no GSU (units on the MV bus</t>
+        </is>
+      </c>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
         </is>
       </c>
-      <c r="H99" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="17.0" customHeight="1">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GSU HV kV</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gsu_hv_kv</t>
-        </is>
-      </c>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
       <c r="H100" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4881,12 +4893,12 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">GSU HV kV</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_lv_kv</t>
+          <t xml:space="preserve">gsu_hv_kv</t>
         </is>
       </c>
       <c r="D101" s="8"/>
@@ -4907,22 +4919,18 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU Z %</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_z_pct</t>
+          <t xml:space="preserve">gsu_lv_kv</t>
         </is>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">on GSU MVA</t>
-        </is>
-      </c>
+      <c r="G102" s="8"/>
       <c r="H102" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4937,18 +4945,22 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU X/R</t>
+          <t xml:space="preserve">GSU Z %</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_x_r</t>
+          <t xml:space="preserve">gsu_z_pct</t>
         </is>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on GSU MVA</t>
+        </is>
+      </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -4963,12 +4975,12 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU vector group</t>
+          <t xml:space="preserve">GSU X/R</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_vector</t>
+          <t xml:space="preserve">gsu_x_r</t>
         </is>
       </c>
       <c r="D104" s="8"/>
@@ -4989,26 +5001,18 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV tap</t>
+          <t xml:space="preserve">GSU vector group</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_tap</t>
+          <t xml:space="preserve">gsu_vector</t>
         </is>
       </c>
       <c r="D105" s="8"/>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E105" s="8"/>
       <c r="F105" s="8"/>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 1</t>
-        </is>
-      </c>
+      <c r="G105" s="8"/>
       <c r="H105" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5023,24 +5027,24 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">GSU HV tap</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">gsu_tap</t>
         </is>
       </c>
       <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
-        </is>
-      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F106" s="8"/>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H106" s="13" t="inlineStr">
@@ -5057,20 +5061,24 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector R</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_r</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
+        </is>
+      </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT</t>
+          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
         </is>
       </c>
       <c r="H107" s="13" t="inlineStr">
@@ -5087,12 +5095,12 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector X</t>
+          <t xml:space="preserve">Collector R</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_x</t>
+          <t xml:space="preserve">coll_r</t>
         </is>
       </c>
       <c r="D108" s="8"/>
@@ -5117,12 +5125,12 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector B</t>
+          <t xml:space="preserve">Collector X</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_b</t>
+          <t xml:space="preserve">coll_x</t>
         </is>
       </c>
       <c r="D109" s="8"/>
@@ -5130,7 +5138,7 @@
       <c r="F109" s="8"/>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT, total charging</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
@@ -5147,24 +5155,20 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector units</t>
+          <t xml:space="preserve">Collector B</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_units</t>
+          <t xml:space="preserve">coll_b</t>
         </is>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu | ohm</t>
-        </is>
-      </c>
+      <c r="F110" s="8"/>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
+          <t xml:space="preserve">EQUIVALENT, total charging</t>
         </is>
       </c>
       <c r="H110" s="13" t="inlineStr">
@@ -5181,25 +5185,29 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZSORCE X pu</t>
+          <t xml:space="preserve">Collector units</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zsorce_x</t>
+          <t xml:space="preserve">coll_units</t>
         </is>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu | ohm</t>
+        </is>
+      </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5219,12 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WMOD</t>
+          <t xml:space="preserve">ZSORCE X pu</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wmod</t>
+          <t xml:space="preserve">zsorce_x</t>
         </is>
       </c>
       <c r="D112" s="8"/>
@@ -5224,84 +5232,80 @@
       <c r="F112" s="8"/>
       <c r="G112" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+        </is>
+      </c>
+      <c r="H112" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="17.0" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WMOD</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wmod</t>
+        </is>
+      </c>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
         </is>
       </c>
-      <c r="H112" s="13" t="inlineStr">
+      <c r="H113" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="30.0" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+    <row r="114" ht="30.0" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
+      <c r="B114" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Electrical control</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">reec</t>
-        </is>
-      </c>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
-        </is>
-      </c>
-      <c r="H113" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="17.0" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD library</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_library</t>
         </is>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
-      <c r="F114" s="8"/>
+          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
+        </is>
+      </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
+          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
@@ -5313,24 +5317,24 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD definition</t>
+          <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_definition</t>
+          <t xml:space="preserve">pscad_library</t>
         </is>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a source: network check</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F115" s="8"/>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
+          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
@@ -5347,24 +5351,24 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD AC port</t>
+          <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_ac_port</t>
+          <t xml:space="preserve">pscad_definition</t>
         </is>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its 3-phase port</t>
+          <t xml:space="preserve">a source: network check</t>
         </is>
       </c>
       <c r="F116" s="8"/>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
@@ -5373,7 +5377,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="30.0" customHeight="1">
+    <row r="117" ht="17.0" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5381,20 +5385,24 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD source case</t>
+          <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_source</t>
+          <t xml:space="preserve">pscad_ac_port</t>
         </is>
       </c>
       <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its 3-phase port</t>
+        </is>
+      </c>
       <c r="F117" s="8"/>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
+          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
@@ -5411,24 +5419,20 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD component ID</t>
+          <t xml:space="preserve">PSCAD source case</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_component_id</t>
+          <t xml:space="preserve">pscad_source</t>
         </is>
       </c>
       <c r="D118" s="8"/>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="E118" s="8"/>
       <c r="F118" s="8"/>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
+          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
@@ -5445,79 +5449,83 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD inverter at</t>
+          <t xml:space="preserve">PSCAD component ID</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_inv_at</t>
+          <t xml:space="preserve">pscad_component_id</t>
         </is>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="F119" s="8"/>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
+        </is>
+      </c>
+      <c r="H119" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="30.0" customHeight="1">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD inverter at</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_inv_at</t>
+        </is>
+      </c>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">LV</t>
         </is>
       </c>
-      <c r="F119" s="8" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV | MV</t>
         </is>
       </c>
-      <c r="G119" s="8" t="inlineStr">
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
       </c>
-      <c r="H119" s="13" t="inlineStr">
+      <c r="H120" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-    </row>
-    <row r="121" ht="17.0" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B121" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collector</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collector</t>
-        </is>
-      </c>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
-      <c r="G121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
-        </is>
-      </c>
-      <c r="H121" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
     </row>
     <row r="122" ht="17.0" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
@@ -5527,12 +5535,12 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeder</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">feeder</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D122" s="8"/>
@@ -5540,7 +5548,7 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">feeder name</t>
+          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
@@ -5557,24 +5565,20 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copies</t>
+          <t xml:space="preserve">Feeder</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">copies</t>
+          <t xml:space="preserve">feeder</t>
         </is>
       </c>
       <c r="D123" s="8"/>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E123" s="8"/>
       <c r="F123" s="8"/>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
+          <t xml:space="preserve">feeder name</t>
         </is>
       </c>
       <c r="H123" s="13" t="inlineStr">
@@ -5591,20 +5595,24 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section</t>
+          <t xml:space="preserve">Copies</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">section</t>
+          <t xml:space="preserve">copies</t>
         </is>
       </c>
       <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F124" s="8"/>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+          <t xml:space="preserve">identical feeders (blank = 1)</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
@@ -5613,7 +5621,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="30.0" customHeight="1">
+    <row r="125" ht="17.0" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5621,24 +5629,20 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">From section</t>
+          <t xml:space="preserve">Section</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_section</t>
+          <t xml:space="preserve">section</t>
         </is>
       </c>
       <c r="D125" s="8"/>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the one before (daisy chain</t>
-        </is>
-      </c>
+      <c r="E125" s="8"/>
       <c r="F125" s="8"/>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
         </is>
       </c>
       <c r="H125" s="13" t="inlineStr">
@@ -5647,7 +5651,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="17.0" customHeight="1">
+    <row r="126" ht="30.0" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5655,20 +5659,24 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">From section</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">from_section</t>
         </is>
       </c>
       <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the one before (daisy chain</t>
+        </is>
+      </c>
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Cables</t>
+          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
@@ -5685,18 +5693,22 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">length</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from Cables</t>
+        </is>
+      </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5711,30 +5723,18 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">length</t>
         </is>
       </c>
       <c r="D128" s="8"/>
-      <c r="E128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = km</t>
-        </is>
-      </c>
+      <c r="E128" s="8"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8"/>
       <c r="H128" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
@@ -5749,20 +5749,28 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units at end</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units tapped at the far end</t>
+          <t xml:space="preserve">blank = km</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -5779,12 +5787,12 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units of</t>
+          <t xml:space="preserve">Units at end</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units_of</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D130" s="8"/>
@@ -5792,7 +5800,7 @@
       <c r="F130" s="8"/>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
+          <t xml:space="preserve">units tapped at the far end</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
@@ -5809,24 +5817,20 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel cables</t>
+          <t xml:space="preserve">Units of</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parallel</t>
+          <t xml:space="preserve">units_of</t>
         </is>
       </c>
       <c r="D131" s="8"/>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E131" s="8"/>
       <c r="F131" s="8"/>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
@@ -5843,24 +5847,24 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R ohm</t>
+          <t xml:space="preserve">Parallel cables</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_ohm</t>
+          <t xml:space="preserve">parallel</t>
         </is>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable x Length</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F132" s="8"/>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H132" s="13" t="inlineStr">
@@ -5877,12 +5881,12 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X ohm</t>
+          <t xml:space="preserve">R ohm</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_ohm</t>
+          <t xml:space="preserve">r_ohm</t>
         </is>
       </c>
       <c r="D133" s="8"/>
@@ -5894,7 +5898,7 @@
       <c r="F133" s="8"/>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
+          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
@@ -5911,12 +5915,12 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B uS</t>
+          <t xml:space="preserve">X ohm</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_us</t>
+          <t xml:space="preserve">x_ohm</t>
         </is>
       </c>
       <c r="D134" s="8"/>
@@ -5928,58 +5932,62 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="17.0" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B uS</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b_us</t>
+        </is>
+      </c>
+      <c r="D135" s="8"/>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
+      <c r="F135" s="8"/>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
         </is>
       </c>
-      <c r="H134" s="13" t="inlineStr">
+      <c r="H135" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
-    </row>
-    <row r="136" ht="17.0" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B136" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable</t>
-        </is>
-      </c>
-      <c r="C136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cable</t>
-        </is>
-      </c>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
-      <c r="G136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cable type</t>
-        </is>
-      </c>
-      <c r="H136" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B136" s="7"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
     </row>
     <row r="137" ht="17.0" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
@@ -5989,24 +5997,20 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+      <c r="F137" s="8"/>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per</t>
+          <t xml:space="preserve">cable type</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
@@ -6023,20 +6027,24 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R per length</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_per</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
+      <c r="F138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
+          <t xml:space="preserve">the values are per</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
@@ -6053,12 +6061,12 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D139" s="8"/>
@@ -6066,7 +6074,7 @@
       <c r="F139" s="8"/>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
@@ -6083,12 +6091,12 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">X per length</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">x_per</t>
         </is>
       </c>
       <c r="D140" s="8"/>
@@ -6096,7 +6104,7 @@
       <c r="F140" s="8"/>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="H140" s="13" t="inlineStr">
@@ -6113,12 +6121,12 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">C per length</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">c_per</t>
         </is>
       </c>
       <c r="D141" s="8"/>
@@ -6126,58 +6134,58 @@
       <c r="F141" s="8"/>
       <c r="G141" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">uF</t>
+        </is>
+      </c>
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="17.0" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B per length</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b_per</t>
+        </is>
+      </c>
+      <c r="D142" s="8"/>
+      <c r="E142" s="8"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">uS, instead of C</t>
         </is>
       </c>
-      <c r="H141" s="13" t="inlineStr">
+      <c r="H142" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Collectors</t>
         </is>
       </c>
-      <c r="B142" s="7"/>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="7"/>
-    </row>
-    <row r="143" ht="17.0" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B143" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
-        </is>
-      </c>
-      <c r="H143" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B143" s="7"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="7"/>
     </row>
     <row r="144" ht="17.0" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
@@ -6187,12 +6195,12 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D144" s="8"/>
@@ -6200,62 +6208,58 @@
       <c r="F144" s="8"/>
       <c r="G144" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
+        </is>
+      </c>
+      <c r="H144" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="17.0" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collectors</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connect to</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">connect</t>
+        </is>
+      </c>
+      <c r="D145" s="8"/>
+      <c r="E145" s="8"/>
+      <c r="F145" s="8"/>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
-      <c r="H144" s="13" t="inlineStr">
+      <c r="H145" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B145" s="7"/>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7"/>
-      <c r="G145" s="7"/>
-      <c r="H145" s="7"/>
-    </row>
-    <row r="146" ht="17.0" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loads_Shunts</t>
-        </is>
-      </c>
-      <c r="B146" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kind</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
-      <c r="G146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
-        </is>
-      </c>
-      <c r="H146" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
     </row>
     <row r="147" ht="17.0" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
@@ -6265,20 +6269,24 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">At bus</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -6295,12 +6303,12 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mw</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D148" s="8"/>
@@ -6308,7 +6316,7 @@
       <c r="F148" s="8"/>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
@@ -6325,12 +6333,12 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">MW</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">mw</t>
         </is>
       </c>
       <c r="D149" s="8"/>
@@ -6338,7 +6346,7 @@
       <c r="F149" s="8"/>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
         </is>
       </c>
       <c r="H149" s="13" t="inlineStr">
@@ -6355,94 +6363,90 @@
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">mvar</t>
         </is>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
-      <c r="G150" s="8"/>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+        </is>
+      </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="7" t="inlineStr">
+    <row r="151" ht="17.0" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D151" s="8"/>
+      <c r="E151" s="8"/>
+      <c r="F151" s="8"/>
+      <c r="G151" s="8"/>
+      <c r="H151" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B151" s="7"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
-      <c r="H151" s="7"/>
-    </row>
-    <row r="152" ht="30.0" customHeight="1">
-      <c r="A152" s="8" t="inlineStr">
+      <c r="B152" s="7"/>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+    </row>
+    <row r="153" ht="30.0" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B152" s="12" t="inlineStr">
+      <c r="B153" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Machine</t>
         </is>
       </c>
-      <c r="C152" s="8" t="inlineStr">
+      <c r="C153" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">machine</t>
         </is>
       </c>
-      <c r="D152" s="8"/>
-      <c r="E152" s="8"/>
-      <c r="F152" s="8"/>
-      <c r="G152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
-        </is>
-      </c>
-      <c r="H152" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="17.0" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B153" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="D153" s="8"/>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its generator's</t>
-        </is>
-      </c>
+      <c r="E153" s="8"/>
       <c r="F153" s="8"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its generator's</t>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
@@ -6451,7 +6455,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="30.0" customHeight="1">
+    <row r="154" ht="17.0" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6459,24 +6463,24 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pgen MW</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pgen_mw</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
+          <t xml:space="preserve">its generator's</t>
         </is>
       </c>
       <c r="F154" s="8"/>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H154" s="13" t="inlineStr">
@@ -6485,7 +6489,7 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="17.0" customHeight="1">
+    <row r="155" ht="30.0" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6493,24 +6497,24 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax MW</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmax_mw</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmax</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F155" s="8"/>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
@@ -6527,24 +6531,24 @@
       </c>
       <c r="B156" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmin MW</t>
+          <t xml:space="preserve">Pmax MW</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmin_mw</t>
+          <t xml:space="preserve">pmax_mw</t>
         </is>
       </c>
       <c r="D156" s="8"/>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmin</t>
+          <t xml:space="preserve">its units x Unit Pmax</t>
         </is>
       </c>
       <c r="F156" s="8"/>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
         </is>
       </c>
       <c r="H156" s="13" t="inlineStr">
@@ -6561,24 +6565,24 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmax MVAr</t>
+          <t xml:space="preserve">Pmin MW</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmax_mvar</t>
+          <t xml:space="preserve">pmin_mw</t>
         </is>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmax</t>
+          <t xml:space="preserve">its units x Unit Pmin</t>
         </is>
       </c>
       <c r="F157" s="8"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
@@ -6595,24 +6599,24 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmin MVAr</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmin_mvar</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmin</t>
+          <t xml:space="preserve">its units x Unit Qmax</t>
         </is>
       </c>
       <c r="F158" s="8"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -6621,7 +6625,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="30.0" customHeight="1">
+    <row r="159" ht="17.0" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6629,24 +6633,24 @@
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Qmin MVAr</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mvar</t>
+          <t xml:space="preserve">qmin_mvar</t>
         </is>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as its generator's Q mode</t>
+          <t xml:space="preserve">its units x Unit Qmin</t>
         </is>
       </c>
       <c r="F159" s="8"/>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
         </is>
       </c>
       <c r="H159" s="13" t="inlineStr">
@@ -6655,7 +6659,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="17.0" customHeight="1">
+    <row r="160" ht="30.0" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6663,75 +6667,79 @@
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBASE MVA</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mbase_mva</t>
+          <t xml:space="preserve">q_mvar</t>
         </is>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit MVA</t>
+          <t xml:space="preserve">as its generator's Q mode</t>
         </is>
       </c>
       <c r="F160" s="8"/>
       <c r="G160" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+        </is>
+      </c>
+      <c r="H160" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="17.0" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBASE MVA</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mbase_mva</t>
+        </is>
+      </c>
+      <c r="D161" s="8"/>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit MVA</t>
+        </is>
+      </c>
+      <c r="F161" s="8"/>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = its units x Unit MVA</t>
         </is>
       </c>
-      <c r="H160" s="13" t="inlineStr">
+      <c r="H161" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="7" t="inlineStr">
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B161" s="7"/>
-      <c r="C161" s="7"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7"/>
-      <c r="G161" s="7"/>
-      <c r="H161" s="7"/>
-    </row>
-    <row r="162" ht="17.0" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B162" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus</t>
-        </is>
-      </c>
-      <c r="C162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bus</t>
-        </is>
-      </c>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
-      <c r="F162" s="8"/>
-      <c r="G162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
-        </is>
-      </c>
-      <c r="H162" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
-        </is>
-      </c>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
     </row>
     <row r="163" ht="17.0" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
@@ -6741,24 +6749,20 @@
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">Bus</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">bus</t>
         </is>
       </c>
       <c r="D163" s="8"/>
-      <c r="E163" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic</t>
-        </is>
-      </c>
+      <c r="E163" s="8"/>
       <c r="F163" s="8"/>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
         </is>
       </c>
       <c r="H163" s="13" t="inlineStr">
@@ -6767,7 +6771,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="30.0" customHeight="1">
+    <row r="164" ht="17.0" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
@@ -6775,90 +6779,94 @@
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Number</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
+          <t xml:space="preserve">automatic</t>
         </is>
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = automatic</t>
+        </is>
+      </c>
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30.0" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D165" s="8"/>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
+      <c r="F165" s="8"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = automatic (12 characters at most)</t>
         </is>
       </c>
-      <c r="H164" s="13" t="inlineStr">
+      <c r="H165" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
-    </row>
-    <row r="166" ht="17.0" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+    </row>
+    <row r="167" ht="17.0" customHeight="1">
+      <c r="A167" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B166" s="12" t="inlineStr">
+      <c r="B167" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Generator</t>
         </is>
       </c>
-      <c r="C166" s="8" t="inlineStr">
+      <c r="C167" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
-      <c r="G166" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
-        </is>
-      </c>
-      <c r="H166" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="30.0" customHeight="1">
-      <c r="A167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B167" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Model</t>
-        </is>
-      </c>
-      <c r="C167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D167" s="8"/>
@@ -6866,7 +6874,7 @@
       <c r="F167" s="8"/>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
         </is>
       </c>
       <c r="H167" s="13" t="inlineStr">
@@ -6875,7 +6883,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="17.0" customHeight="1">
+    <row r="168" ht="30.0" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
@@ -6883,12 +6891,12 @@
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Model</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D168" s="8"/>
@@ -6896,7 +6904,7 @@
       <c r="F168" s="8"/>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
         </is>
       </c>
       <c r="H168" s="13" t="inlineStr">
@@ -6913,71 +6921,67 @@
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
-      <c r="G169" s="8"/>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+        </is>
+      </c>
       <c r="H169" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
+    <row r="170" ht="17.0" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D170" s="8"/>
+      <c r="E170" s="8"/>
+      <c r="F170" s="8"/>
+      <c r="G170" s="8"/>
+      <c r="H170" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
-      <c r="B170" s="7"/>
-      <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
-      <c r="G170" s="7"/>
-      <c r="H170" s="7"/>
-    </row>
-    <row r="171" ht="17.0" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B171" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generator</t>
-        </is>
-      </c>
-      <c r="C171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the plant</t>
-        </is>
-      </c>
-      <c r="F171" s="8"/>
-      <c r="G171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = the plant</t>
-        </is>
-      </c>
-      <c r="H171" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="7"/>
+      <c r="H171" s="7"/>
     </row>
     <row r="172" ht="17.0" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
@@ -6987,67 +6991,75 @@
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">record</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the plant</t>
+        </is>
+      </c>
       <c r="F172" s="8"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = the plant</t>
+        </is>
+      </c>
+      <c r="H172" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E .dyr</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="17.0" customHeight="1">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Record</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">record</t>
+        </is>
+      </c>
+      <c r="D173" s="8"/>
+      <c r="E173" s="8"/>
+      <c r="F173" s="8"/>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
         </is>
       </c>
-      <c r="H172" s="13" t="inlineStr">
+      <c r="H173" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E .dyr</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B173" s="7"/>
-      <c r="C173" s="7"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7"/>
-      <c r="G173" s="7"/>
-      <c r="H173" s="7"/>
-    </row>
-    <row r="174" ht="17.0" customHeight="1">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B174" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generator</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
-      <c r="F174" s="8"/>
-      <c r="G174" s="8"/>
-      <c r="H174" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+      <c r="B174" s="7"/>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
     </row>
     <row r="175" ht="17.0" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
@@ -7057,22 +7069,18 @@
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D175" s="8"/>
       <c r="E175" s="8"/>
       <c r="F175" s="8"/>
-      <c r="G175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
-        </is>
-      </c>
+      <c r="G175" s="8"/>
       <c r="H175" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
@@ -7087,12 +7095,12 @@
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D176" s="8"/>
@@ -7100,52 +7108,64 @@
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H176" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="17.0" customHeight="1">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D177" s="8"/>
+      <c r="E177" s="8"/>
+      <c r="F177" s="8"/>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
         </is>
       </c>
-      <c r="H176" s="13" t="inlineStr">
+      <c r="H177" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="7" t="inlineStr">
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
         </is>
       </c>
-      <c r="B177" s="7"/>
-      <c r="C177" s="7"/>
-      <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
-      <c r="G177" s="7"/>
-      <c r="H177" s="7"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="8"/>
-      <c r="B178" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H178" s="8"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="7"/>
     </row>
     <row r="179">
       <c r="A179" s="8"/>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C179" s="8"/>
@@ -7154,7 +7174,7 @@
       <c r="F179" s="8"/>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the point of interconnection</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H179" s="8"/>
@@ -7163,7 +7183,7 @@
       <c r="A180" s="8"/>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C180" s="8"/>
@@ -7172,7 +7192,7 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H180" s="8"/>
@@ -7181,7 +7201,7 @@
       <c r="A181" s="8"/>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -7190,7 +7210,7 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
         </is>
       </c>
       <c r="H181" s="8"/>
@@ -7199,7 +7219,7 @@
       <c r="A182" s="8"/>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C182" s="8"/>
@@ -7208,7 +7228,7 @@
       <c r="F182" s="8"/>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+          <t xml:space="preserve">an MPT's LV winding</t>
         </is>
       </c>
       <c r="H182" s="8"/>
@@ -7217,7 +7237,7 @@
       <c r="A183" s="8"/>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -7226,7 +7246,7 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
         </is>
       </c>
       <c r="H183" s="8"/>
@@ -7235,7 +7255,7 @@
       <c r="A184" s="8"/>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C184" s="8"/>
@@ -7244,7 +7264,7 @@
       <c r="F184" s="8"/>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
         </is>
       </c>
       <c r="H184" s="8"/>
@@ -7253,7 +7273,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -7262,7 +7282,7 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H185" s="8"/>
@@ -7271,7 +7291,7 @@
       <c r="A186" s="8"/>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C186" s="8"/>
@@ -7280,7 +7300,7 @@
       <c r="F186" s="8"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H186" s="8"/>
@@ -7289,7 +7309,7 @@
       <c r="A187" s="8"/>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
         </is>
       </c>
       <c r="C187" s="8"/>
@@ -7298,7 +7318,7 @@
       <c r="F187" s="8"/>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">a generator's terminal</t>
         </is>
       </c>
       <c r="H187" s="8"/>
@@ -7307,7 +7327,7 @@
       <c r="A188" s="8"/>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C188" s="8"/>
@@ -7316,50 +7336,42 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H188" s="8"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="8"/>
+      <c r="B189" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+        </is>
+      </c>
+      <c r="C189" s="8"/>
+      <c r="D189" s="8"/>
+      <c r="E189" s="8"/>
+      <c r="F189" s="8"/>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
         </is>
       </c>
-      <c r="H188" s="8"/>
-    </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="A189" s="7" t="inlineStr">
+      <c r="H189" s="8"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
         </is>
       </c>
-      <c r="B189" s="7"/>
-      <c r="C189" s="7"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
-      <c r="G189" s="7"/>
-      <c r="H189" s="7"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B190" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{UNITS}</t>
-        </is>
-      </c>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
-      <c r="F190" s="8"/>
-      <c r="G190" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H190" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+      <c r="B190" s="7"/>
+      <c r="C190" s="7"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
     </row>
     <row r="191">
       <c r="A191" s="8" t="inlineStr">
@@ -7369,7 +7381,7 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C191" s="8"/>
@@ -7378,7 +7390,7 @@
       <c r="F191" s="8"/>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H191" s="13" t="inlineStr">
@@ -7395,7 +7407,7 @@
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_MW}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C192" s="8"/>
@@ -7404,7 +7416,7 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H192" s="13" t="inlineStr">
@@ -7421,7 +7433,7 @@
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C193" s="8"/>
@@ -7430,7 +7442,7 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H193" s="13" t="inlineStr">
@@ -7447,7 +7459,7 @@
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C194" s="8"/>
@@ -7456,7 +7468,7 @@
       <c r="F194" s="8"/>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H194" s="13" t="inlineStr">
@@ -7473,7 +7485,7 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -7482,7 +7494,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
@@ -7499,7 +7511,7 @@
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -7508,7 +7520,7 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
@@ -7525,7 +7537,7 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C197" s="8"/>
@@ -7534,7 +7546,7 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H197" s="13" t="inlineStr">
@@ -7551,7 +7563,7 @@
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C198" s="8"/>
@@ -7560,7 +7572,7 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr">
@@ -7577,7 +7589,7 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C199" s="8"/>
@@ -7586,7 +7598,7 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H199" s="13" t="inlineStr">
@@ -7603,7 +7615,7 @@
       </c>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C200" s="8"/>
@@ -7612,7 +7624,7 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H200" s="13" t="inlineStr">
@@ -7629,7 +7641,7 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C201" s="8"/>
@@ -7638,7 +7650,7 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H201" s="13" t="inlineStr">
@@ -7655,7 +7667,7 @@
       </c>
       <c r="B202" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C202" s="8"/>
@@ -7664,7 +7676,7 @@
       <c r="F202" s="8"/>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H202" s="13" t="inlineStr">
@@ -7681,7 +7693,7 @@
       </c>
       <c r="B203" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C203" s="8"/>
@@ -7690,7 +7702,7 @@
       <c r="F203" s="8"/>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H203" s="13" t="inlineStr">
@@ -7707,7 +7719,7 @@
       </c>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C204" s="8"/>
@@ -7716,7 +7728,7 @@
       <c r="F204" s="8"/>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">frequency (Hz)</t>
         </is>
       </c>
       <c r="H204" s="13" t="inlineStr">
@@ -7733,7 +7745,7 @@
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{P_INV_MW}</t>
         </is>
       </c>
       <c r="C205" s="8"/>
@@ -7742,7 +7754,7 @@
       <c r="F205" s="8"/>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
         </is>
       </c>
       <c r="H205" s="13" t="inlineStr">
@@ -7759,7 +7771,7 @@
       </c>
       <c r="B206" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
         </is>
       </c>
       <c r="C206" s="8"/>
@@ -7768,10 +7780,36 @@
       <c r="F206" s="8"/>
       <c r="G206" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H206" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B207" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C207" s="8"/>
+      <c r="D207" s="8"/>
+      <c r="E207" s="8"/>
+      <c r="F207" s="8"/>
+      <c r="G207" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H206" s="13" t="inlineStr">
+      <c r="H207" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -7783,33 +7821,33 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A120:H120"/>
-    <mergeCell ref="A135:H135"/>
-    <mergeCell ref="A142:H142"/>
-    <mergeCell ref="A145:H145"/>
-    <mergeCell ref="A151:H151"/>
-    <mergeCell ref="A161:H161"/>
-    <mergeCell ref="A165:H165"/>
-    <mergeCell ref="A170:H170"/>
-    <mergeCell ref="A173:H173"/>
-    <mergeCell ref="A177:H177"/>
-    <mergeCell ref="A189:H189"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A136:H136"/>
+    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A146:H146"/>
+    <mergeCell ref="A152:H152"/>
+    <mergeCell ref="A162:H162"/>
+    <mergeCell ref="A166:H166"/>
+    <mergeCell ref="A171:H171"/>
+    <mergeCell ref="A174:H174"/>
+    <mergeCell ref="A178:H178"/>
+    <mergeCell ref="A190:H190"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
     <hyperlink ref="A52" location="'MPT'!A1" display="MPT"/>
-    <hyperlink ref="A81" location="'Generators'!A1" display="Generators"/>
-    <hyperlink ref="A120" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A135" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A142" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A145" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A151" location="'Machines'!A1" display="Machines"/>
-    <hyperlink ref="A161" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A165" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A170" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A173" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A189" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A82" location="'Generators'!A1" display="Generators"/>
+    <hyperlink ref="A121" location="'Feeders'!A1" display="Feeders"/>
+    <hyperlink ref="A136" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A143" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A146" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A152" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A162" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A166" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A171" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A174" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A190" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -19958,6 +19996,7 @@
     <col min="26" max="26" width="10" customWidth="1"/>
     <col min="27" max="27" width="10" customWidth="1"/>
     <col min="28" max="28" width="10" customWidth="1"/>
+    <col min="29" max="29" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -19968,135 +20007,140 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Windings</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">HV kV</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">LV kV</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">TV kV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">MVA</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">LV MVA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">TV MVA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z HV-LV %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z HV-TV %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z LV-TV %</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z HV-LV base MVA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z HV-TV base MVA</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z LV-TV base MVA</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">X/R</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Load loss kW</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Vector group</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">HV tap</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Parallel units</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No-load loss %</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Magnetising current %</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Rating MVA</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie length</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie length unit</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie values per</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie X per length</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie B per length</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie rating MVA</t>
         </is>
@@ -20108,125 +20152,130 @@
           <t xml:space="preserve"># MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
         </is>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 or 3 (blank = 3 when TV kV is given, else 2)</t>
+        </is>
+      </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tertiary / 2nd LV winding; blank = two windings</t>
-        </is>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">tertiary / 2nd LV winding (Windings 3; blank = the LV kV, a split LV winding)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">the rating (3 windings: HV winding)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3 windings</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3 windings</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">on its base MVA</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3 windings</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3 windings</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">each impedance</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">identical units (blank = 1)</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
         </is>
       </c>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">the length R, X, B are per (blank = Tie length unit)</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm (blank = typical)</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">uS (blank = typical)</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = typical</t>
         </is>
@@ -20238,53 +20287,58 @@
           <t xml:space="preserve">MPT1</t>
         </is>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C3" s="3">
         <v>230.0</v>
       </c>
-      <c r="C3" s="3">
+      <c r="D3" s="3">
         <v>34.5</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
         <v>225.0</v>
       </c>
-      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3">
         <v>10.0</v>
       </c>
-      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3">
+      <c r="N3" s="3"/>
+      <c r="O3" s="3">
         <v>45.0</v>
       </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">YNd1</t>
         </is>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="3">
         <v>1.0</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <v>1</v>
       </c>
-      <c r="S3" s="3"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="3">
+      <c r="U3" s="3"/>
+      <c r="V3" s="3">
         <v>225.0</v>
       </c>
-      <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3"/>
@@ -20315,6 +20369,7 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
@@ -20345,6 +20400,7 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3"/>
@@ -20375,6 +20431,7 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3"/>
@@ -20405,6 +20462,7 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3"/>
@@ -20435,6 +20493,7 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3"/>
@@ -20465,6 +20524,7 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
@@ -20495,6 +20555,7 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3"/>
@@ -20525,6 +20586,7 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
@@ -20555,6 +20617,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -20585,6 +20648,7 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -20615,6 +20679,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -20645,6 +20710,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -20675,6 +20741,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -20705,6 +20772,7 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -20735,6 +20803,7 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -20765,6 +20834,7 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -20795,6 +20865,7 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -20825,6 +20896,7 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -20855,13 +20927,17 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W3:W500">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B500">
+      <formula1>"2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X3:X500">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X3:X500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y3:Y500">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
   </dataValidations>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -2365,7 +2365,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="17.0" customHeight="1">
+    <row r="25" ht="43.0" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2384,7 +2384,7 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Gen-tie length unit</t>
+          <t xml:space="preserve">km or mi, whichever matches a line of the POI kV</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the length R, X, B, C below are per: km, mi, kft, m, ft (blank = the Gen-tie length unit)</t>
+          <t xml:space="preserve">the length R, X, B, C below are per: km, mi, kft, m, ft (blank = km or mi, whichever matches a line of the POI kV)</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="17.0" customHeight="1">
+    <row r="79" ht="30.0" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -4204,7 +4204,7 @@
       <c r="D79" s="8"/>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length unit</t>
+          <t xml:space="preserve">km or mi, whichever matches a line of its kV</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the length R, X, B are per (blank = Tie length unit)</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
@@ -20407,7 +20407,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30.0" customHeight="1">
+    <row r="25" ht="43.0" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Gen-tie values per</t>
@@ -20421,7 +20421,7 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Gen-tie length unit</t>
+          <t xml:space="preserve">km or mi, whichever matches a line of the POI kV</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the length R, X, B, C below are per: km, mi, kft, m, ft (blank = the Gen-tie length unit)</t>
+          <t xml:space="preserve">the length R, X, B, C below are per: km, mi, kft, m, ft (blank = km or mi, whichever matches a line of the POI kV)</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -21565,7 +21565,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="88.0" customHeight="1">
+    <row r="2" ht="100.0" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"># MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
@@ -21676,7 +21676,7 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the length R, X, B are per (blank = Tie length unit)</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -594,7 +594,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSLF</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSLF</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       <c r="G58" s="8"/>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="H71" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       <c r="G78" s="8"/>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="H80" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="H86" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="H90" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       <c r="G91" s="8"/>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="H92" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="H94" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="H96" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="H98" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="H100" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="H101" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H102" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       <c r="G104" s="8"/>
       <c r="H104" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="H105" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5065,7 @@
       <c r="G106" s="8"/>
       <c r="H106" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       <c r="G107" s="8"/>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="H108" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="H109" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H110" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="H112" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -5343,11 +5343,11 @@
       </c>
       <c r="H115" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="43.0" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5376,12 +5376,12 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REGC_A: a current source (REGCA1) | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (REGCBU1; ZSORCE X its Xe) -- PV, BESS, WT4 (blank = REGC_A)</t>
+          <t xml:space="preserve">REGC_A: a current source, the standard | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (ZSORCE X its Xe) -- PV, BESS, WT4; .dyr REGCA1 / REGCBU1, .dyd regc_a / regc_b (blank = REGC_A)</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
+          <t xml:space="preserve">REEC_A: PV, WT | REEC_C: BESS (state of charge) | REEC_D: PV, BESS, WT4, the newest (voltage-dependent limits, momentary cessation) -- .dyr and .dyd alike (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="H126" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="H128" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="H130" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       <c r="G131" s="8"/>
       <c r="H131" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="H132" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="H133" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="H134" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H135" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="H136" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H137" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="H138" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="H140" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="H141" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="H142" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H143" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="H144" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H145" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="H148" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="H151" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="H152" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="H153" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       <c r="G154" s="8"/>
       <c r="H154" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="H158" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="H159" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="H160" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="H161" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="H162" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="H163" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="H164" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="H166" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H167" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="H168" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="H170" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="H171" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="H172" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       <c r="G173" s="8"/>
       <c r="H173" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="H175" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="H176" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E</t>
         </is>
       </c>
     </row>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -19896,7 +19896,7 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSLF</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSLF</t>
         </is>
       </c>
     </row>
@@ -20092,7 +20092,7 @@
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20155,7 +20155,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20180,7 +20180,7 @@
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20226,7 +20226,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20280,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20330,7 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20436,7 +20436,7 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20467,7 @@
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20498,7 +20498,7 @@
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20554,7 +20554,7 @@
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20600,7 +20600,7 @@
       <c r="F31" s="2"/>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20621,7 +20621,7 @@
       <c r="F32" s="2"/>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20648,7 +20648,7 @@
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20679,7 +20679,7 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20721,7 +20721,7 @@
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20783,7 +20783,7 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20806,7 +20806,7 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20837,7 +20837,7 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -20912,7 +20912,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -20945,7 +20945,7 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr</t>
+          <t xml:space="preserve">PSS/E</t>
         </is>
       </c>
     </row>
@@ -22748,12 +22748,12 @@
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REGC_A: a current source (REGCA1) | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (REGCBU1; ZSORCE X its Xe) -- PV, BESS, WT4 (blank = REGC_A)</t>
+          <t xml:space="preserve">REGC_A: a current source, the standard | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (ZSORCE X its Xe) -- PV, BESS, WT4; .dyr REGCA1 / REGCBU1, .dyd regc_a / regc_b (blank = REGC_A)</t>
         </is>
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E .dyr -- REEC_A: PV, WT | REEC_C: BESS | REEC_D: PV, BESS, WT4 (blank = REEC_A, BESS REEC_C)</t>
+          <t xml:space="preserve">REEC_A: PV, WT | REEC_C: BESS (state of charge) | REEC_D: PV, BESS, WT4, the newest (voltage-dependent limits, momentary cessation) -- .dyr and .dyd alike (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -3165,28 +3165,28 @@
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD lines as</t>
+          <t xml:space="preserve">PSCAD meter at each inverter</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_lines</t>
+          <t xml:space="preserve">pscad_inv_meter</t>
         </is>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI | RLC</t>
+          <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
+          <t xml:space="preserve">YES = a multimeter between each inverter and its GSU: P_, Q_, V_&lt;unit&gt; in MW, MVAr, kV (blank = YES)</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -3203,62 +3203,62 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSCAD lines as</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_lines</t>
+        </is>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI | RLC</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30.0" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD fault at POI</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_fault</t>
         </is>
       </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="17.0" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault time</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_fault_s</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100: none in the run</t>
-        </is>
-      </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault duration</t>
+          <t xml:space="preserve">PSCAD fault time</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_fault_dur_s</t>
+          <t xml:space="preserve">pscad_fault_s</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3290,89 +3290,89 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
+          <t xml:space="preserve">100: none in the run</t>
         </is>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17.0" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault duration</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_fault_dur_s</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 0.15</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="43.0" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="52" ht="43.0" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault type</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pscad_fault_type</t>
         </is>
       </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="D52" s="8"/>
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="17.0" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plant</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault resistance</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pscad_fault_ohm</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.01</t>
-        </is>
-      </c>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 0.01</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -3389,130 +3389,142 @@
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD libraries</t>
+          <t xml:space="preserve">PSCAD fault resistance</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_libraries</t>
-        </is>
-      </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
+          <t xml:space="preserve">pscad_fault_ohm</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.01</t>
+        </is>
+      </c>
       <c r="F53" s="8"/>
       <c r="G53" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = 0.01</t>
+        </is>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17.0" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plant</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD libraries</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_libraries</t>
+        </is>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
-      <c r="H53" s="13" t="inlineStr">
+      <c r="H54" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
         </is>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-    </row>
-    <row r="55" ht="17.0" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+    </row>
+    <row r="56" ht="17.0" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">name</t>
         </is>
       </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
         </is>
       </c>
-      <c r="H55" s="13" t="inlineStr">
+      <c r="H56" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30.0" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="57" ht="30.0" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Windings</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">windings</t>
         </is>
       </c>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="D57" s="8"/>
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3 when TV kV is given, else 2</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2 | 3</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2 or 3 (blank = 3 when TV kV is given, else 2)</t>
         </is>
       </c>
-      <c r="H56" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="17.0" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HV kV</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hv_kv</t>
-        </is>
-      </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
       <c r="H57" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -3527,12 +3539,12 @@
       </c>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV kV</t>
+          <t xml:space="preserve">HV kV</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_kv</t>
+          <t xml:space="preserve">hv_kv</t>
         </is>
       </c>
       <c r="D58" s="8"/>
@@ -3545,7 +3557,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="30.0" customHeight="1">
+    <row r="59" ht="17.0" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -3553,54 +3565,50 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">LV kV</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lv_kv</t>
+        </is>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30.0" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">TV kV</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">tv_kv</t>
         </is>
       </c>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="D60" s="8"/>
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">the LV kV, a split LV winding</t>
         </is>
       </c>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tertiary / 2nd LV winding (Windings 3; blank = the LV kV, a split LV winding)</t>
-        </is>
-      </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="17.0" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mva</t>
-        </is>
-      </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
       <c r="F60" s="8"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
+          <t xml:space="preserve">tertiary / 2nd LV winding (Windings 3; blank = the LV kV, a split LV winding)</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -3617,12 +3625,12 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV MVA</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">lv_mva</t>
+          <t xml:space="preserve">mva</t>
         </is>
       </c>
       <c r="D61" s="8"/>
@@ -3630,7 +3638,7 @@
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -3647,12 +3655,12 @@
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TV MVA</t>
+          <t xml:space="preserve">LV MVA</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tv_mva</t>
+          <t xml:space="preserve">lv_mva</t>
         </is>
       </c>
       <c r="D62" s="8"/>
@@ -3677,12 +3685,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV %</t>
+          <t xml:space="preserve">TV MVA</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_hl_pct</t>
+          <t xml:space="preserve">tv_mva</t>
         </is>
       </c>
       <c r="D63" s="8"/>
@@ -3690,7 +3698,7 @@
       <c r="F63" s="8"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on its base MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -3707,12 +3715,12 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV %</t>
+          <t xml:space="preserve">Z HV-LV %</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_ht_pct</t>
+          <t xml:space="preserve">z_hl_pct</t>
         </is>
       </c>
       <c r="D64" s="8"/>
@@ -3720,7 +3728,7 @@
       <c r="F64" s="8"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">on its base MVA</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -3737,12 +3745,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV %</t>
+          <t xml:space="preserve">Z HV-TV %</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_lt_pct</t>
+          <t xml:space="preserve">z_ht_pct</t>
         </is>
       </c>
       <c r="D65" s="8"/>
@@ -3767,24 +3775,20 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV base MVA</t>
+          <t xml:space="preserve">Z LV-TV %</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_hl_mva</t>
+          <t xml:space="preserve">z_lt_pct</t>
         </is>
       </c>
       <c r="D66" s="8"/>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E66" s="8"/>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -3801,12 +3805,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-LV base MVA</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_ht_mva</t>
+          <t xml:space="preserve">base_hl_mva</t>
         </is>
       </c>
       <c r="D67" s="8"/>
@@ -3835,12 +3839,12 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-TV base MVA</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_lt_mva</t>
+          <t xml:space="preserve">base_ht_mva</t>
         </is>
       </c>
       <c r="D68" s="8"/>
@@ -3869,20 +3873,24 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X/R</t>
+          <t xml:space="preserve">Z LV-TV base MVA</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_r</t>
+          <t xml:space="preserve">base_lt_mva</t>
         </is>
       </c>
       <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each impedance</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3899,12 +3907,12 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load loss kW</t>
+          <t xml:space="preserve">X/R</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">load_loss_kw</t>
+          <t xml:space="preserve">x_r</t>
         </is>
       </c>
       <c r="D70" s="8"/>
@@ -3912,7 +3920,7 @@
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
+          <t xml:space="preserve">each impedance</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -3929,12 +3937,12 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector group</t>
+          <t xml:space="preserve">Load loss kW</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vector</t>
+          <t xml:space="preserve">load_loss_kw</t>
         </is>
       </c>
       <c r="D71" s="8"/>
@@ -3942,7 +3950,7 @@
       <c r="F71" s="8"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
+          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -3959,24 +3967,20 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV tap</t>
+          <t xml:space="preserve">Vector group</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tap</t>
+          <t xml:space="preserve">vector</t>
         </is>
       </c>
       <c r="D72" s="8"/>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
+          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -3993,12 +3997,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel units</t>
+          <t xml:space="preserve">HV tap</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">count</t>
+          <t xml:space="preserve">tap</t>
         </is>
       </c>
       <c r="D73" s="8"/>
@@ -4010,7 +4014,7 @@
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical units (blank = 1)</t>
+          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -4027,24 +4031,24 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No-load loss %</t>
+          <t xml:space="preserve">Parallel units</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nll_pct</t>
+          <t xml:space="preserve">count</t>
         </is>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">of MVA (blank = 0)</t>
+          <t xml:space="preserve">identical units (blank = 1)</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -4061,12 +4065,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnetising current %</t>
+          <t xml:space="preserve">No-load loss %</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">im_pct</t>
+          <t xml:space="preserve">nll_pct</t>
         </is>
       </c>
       <c r="D75" s="8"/>
@@ -4095,24 +4099,24 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rating MVA</t>
+          <t xml:space="preserve">Magnetising current %</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_mva</t>
+          <t xml:space="preserve">im_pct</t>
         </is>
       </c>
       <c r="D76" s="8"/>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
@@ -4129,24 +4133,24 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length</t>
+          <t xml:space="preserve">Rating MVA</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_length</t>
+          <t xml:space="preserve">rate_mva</t>
         </is>
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">MVA</t>
         </is>
       </c>
       <c r="F77" s="8"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -4163,60 +4167,56 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tie length</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_length</t>
+        </is>
+      </c>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+        </is>
+      </c>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="17.0" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tie length unit</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">tie_unit</t>
         </is>
       </c>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">km | mi | kft | m | ft</t>
         </is>
       </c>
-      <c r="G78" s="8"/>
-      <c r="H78" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30.0" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tie values per</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tie_per_unit</t>
-        </is>
-      </c>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km or mi, whichever matches a line of its kV</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
-        </is>
-      </c>
+      <c r="G79" s="8"/>
       <c r="H79" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -4231,24 +4231,28 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie R per length</t>
+          <t xml:space="preserve">Tie values per</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_r_per</t>
+          <t xml:space="preserve">tie_per_unit</t>
         </is>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a typical overhead line of the HV kV</t>
-        </is>
-      </c>
-      <c r="F80" s="8"/>
+          <t xml:space="preserve">km or mi, whichever matches a line of its kV</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -4257,7 +4261,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="17.0" customHeight="1">
+    <row r="81" ht="30.0" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -4265,24 +4269,24 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie X per length</t>
+          <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_per</t>
+          <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">typical</t>
+          <t xml:space="preserve">a typical overhead line of the HV kV</t>
         </is>
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm (blank = typical)</t>
+          <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -4299,12 +4303,12 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie B per length</t>
+          <t xml:space="preserve">Tie X per length</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_per</t>
+          <t xml:space="preserve">tie_x_per</t>
         </is>
       </c>
       <c r="D82" s="8"/>
@@ -4316,7 +4320,7 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS (blank = typical)</t>
+          <t xml:space="preserve">ohm (blank = typical)</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
@@ -4333,12 +4337,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie rating MVA</t>
+          <t xml:space="preserve">Tie B per length</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_rate_mva</t>
+          <t xml:space="preserve">tie_b_per</t>
         </is>
       </c>
       <c r="D83" s="8"/>
@@ -4350,119 +4354,119 @@
       <c r="F83" s="8"/>
       <c r="G83" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">uS (blank = typical)</t>
+        </is>
+      </c>
+      <c r="H83" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="17.0" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tie rating MVA</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_rate_mva</t>
+        </is>
+      </c>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = typical</t>
         </is>
       </c>
-      <c r="H83" s="13" t="inlineStr">
+      <c r="H84" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-    </row>
-    <row r="85" ht="17.0" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+    </row>
+    <row r="86" ht="17.0" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
-        </is>
-      </c>
-      <c r="H85" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="30.0" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="F86" s="8"/>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
+        </is>
+      </c>
+      <c r="H86" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30.0" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
-        </is>
-      </c>
-      <c r="H86" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="17.0" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4479,20 +4483,24 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F88" s="8"/>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
@@ -4509,12 +4517,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D89" s="8"/>
@@ -4522,7 +4530,7 @@
       <c r="F89" s="8"/>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number of units</t>
+          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
@@ -4539,24 +4547,20 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit MVA</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_mva</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D90" s="8"/>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from P and Q</t>
-        </is>
-      </c>
+      <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+          <t xml:space="preserve">number of units</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4573,18 +4577,26 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmax MW</t>
+          <t xml:space="preserve">Unit MVA</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmax_mw</t>
+          <t xml:space="preserve">unit_mva</t>
         </is>
       </c>
       <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from P and Q</t>
+        </is>
+      </c>
       <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+        </is>
+      </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -4599,26 +4611,18 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmin MW</t>
+          <t xml:space="preserve">Unit Pmax MW</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmin_mw</t>
+          <t xml:space="preserve">unit_pmax_mw</t>
         </is>
       </c>
       <c r="D92" s="8"/>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
+      <c r="E92" s="8"/>
       <c r="F92" s="8"/>
-      <c r="G92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
-        </is>
-      </c>
+      <c r="G92" s="8"/>
       <c r="H92" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -4633,24 +4637,24 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmax MVAr</t>
+          <t xml:space="preserve">Unit Pmin MW</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmax_mvar</t>
+          <t xml:space="preserve">unit_pmin_mw</t>
         </is>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Unit PF</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = from Unit PF</t>
+          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
@@ -4667,24 +4671,24 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmin MVAr</t>
+          <t xml:space="preserve">Unit Qmax MVAr</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmin_mvar</t>
+          <t xml:space="preserve">unit_qmax_mvar</t>
         </is>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Qmax</t>
+          <t xml:space="preserve">from Unit PF</t>
         </is>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = -Qmax</t>
+          <t xml:space="preserve">blank = from Unit PF</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
@@ -4701,24 +4705,24 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit PF</t>
+          <t xml:space="preserve">Unit Qmin MVAr</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pf</t>
+          <t xml:space="preserve">unit_qmin_mvar</t>
         </is>
       </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95</t>
+          <t xml:space="preserve">-Qmax</t>
         </is>
       </c>
       <c r="F95" s="8"/>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
+          <t xml:space="preserve">blank = -Qmax</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
@@ -4735,24 +4739,24 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminal kV</t>
+          <t xml:space="preserve">Unit PF</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kv</t>
+          <t xml:space="preserve">unit_pf</t>
         </is>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">0.95</t>
         </is>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = GSU LV kV</t>
+          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
         </is>
       </c>
       <c r="H96" s="13" t="inlineStr">
@@ -4761,7 +4765,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="30.0" customHeight="1">
+    <row r="97" ht="17.0" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4769,58 +4773,58 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispatch MW</t>
+          <t xml:space="preserve">Terminal kV</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dispatch_mw</t>
+          <t xml:space="preserve">kv</t>
         </is>
       </c>
       <c r="D97" s="8"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="F97" s="8"/>
       <c r="G97" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = GSU LV kV</t>
+        </is>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30.0" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dispatch MW</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dispatch_mw</t>
+        </is>
+      </c>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+        </is>
+      </c>
+      <c r="F98" s="8"/>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
-        </is>
-      </c>
-      <c r="H97" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="17.0" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q mode</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">q_mode</t>
-        </is>
-      </c>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share | fixed</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
         </is>
       </c>
       <c r="H98" s="13" t="inlineStr">
@@ -4837,24 +4841,24 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Q mode</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_q_mvar</t>
+          <t xml:space="preserve">q_mode</t>
         </is>
       </c>
       <c r="D99" s="8"/>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">share | fixed</t>
+        </is>
+      </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
+          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
         </is>
       </c>
       <c r="H99" s="13" t="inlineStr">
@@ -4871,20 +4875,24 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed PF</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_pf</t>
+          <t xml:space="preserve">fixed_q_mvar</t>
         </is>
       </c>
       <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
       <c r="F100" s="8"/>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
+          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
         </is>
       </c>
       <c r="H100" s="13" t="inlineStr">
@@ -4901,24 +4909,20 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU count</t>
+          <t xml:space="preserve">Fixed PF</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_count</t>
+          <t xml:space="preserve">fixed_pf</t>
         </is>
       </c>
       <c r="D101" s="8"/>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Units</t>
-        </is>
-      </c>
+      <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = Units</t>
+          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
@@ -4927,7 +4931,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="30.0" customHeight="1">
+    <row r="102" ht="17.0" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4935,52 +4939,60 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU MVA</t>
+          <t xml:space="preserve">GSU count</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_mva</t>
+          <t xml:space="preserve">gsu_count</t>
         </is>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">no GSU (units on the MV bus</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = Units</t>
+        </is>
+      </c>
+      <c r="H102" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="30.0" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSU MVA</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gsu_mva</t>
+        </is>
+      </c>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no GSU (units on the MV bus</t>
+        </is>
+      </c>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
         </is>
       </c>
-      <c r="H102" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="17.0" customHeight="1">
-      <c r="A103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GSU HV kV</t>
-        </is>
-      </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gsu_hv_kv</t>
-        </is>
-      </c>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
       <c r="H103" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -4995,12 +5007,12 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">GSU HV kV</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_lv_kv</t>
+          <t xml:space="preserve">gsu_hv_kv</t>
         </is>
       </c>
       <c r="D104" s="8"/>
@@ -5021,22 +5033,18 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU Z %</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_z_pct</t>
+          <t xml:space="preserve">gsu_lv_kv</t>
         </is>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">on GSU MVA</t>
-        </is>
-      </c>
+      <c r="G105" s="8"/>
       <c r="H105" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5051,18 +5059,22 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU X/R</t>
+          <t xml:space="preserve">GSU Z %</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_x_r</t>
+          <t xml:space="preserve">gsu_z_pct</t>
         </is>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">on GSU MVA</t>
+        </is>
+      </c>
       <c r="H106" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5077,12 +5089,12 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU vector group</t>
+          <t xml:space="preserve">GSU X/R</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_vector</t>
+          <t xml:space="preserve">gsu_x_r</t>
         </is>
       </c>
       <c r="D107" s="8"/>
@@ -5103,26 +5115,18 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV tap</t>
+          <t xml:space="preserve">GSU vector group</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_tap</t>
+          <t xml:space="preserve">gsu_vector</t>
         </is>
       </c>
       <c r="D108" s="8"/>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E108" s="8"/>
       <c r="F108" s="8"/>
-      <c r="G108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = 1</t>
-        </is>
-      </c>
+      <c r="G108" s="8"/>
       <c r="H108" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5137,24 +5141,24 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">GSU HV tap</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">gsu_tap</t>
         </is>
       </c>
       <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
-        </is>
-      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F109" s="8"/>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
@@ -5171,20 +5175,24 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector R</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_r</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
+        </is>
+      </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT</t>
+          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
         </is>
       </c>
       <c r="H110" s="13" t="inlineStr">
@@ -5201,12 +5209,12 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector X</t>
+          <t xml:space="preserve">Collector R</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_x</t>
+          <t xml:space="preserve">coll_r</t>
         </is>
       </c>
       <c r="D111" s="8"/>
@@ -5231,12 +5239,12 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector B</t>
+          <t xml:space="preserve">Collector X</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_b</t>
+          <t xml:space="preserve">coll_x</t>
         </is>
       </c>
       <c r="D112" s="8"/>
@@ -5244,7 +5252,7 @@
       <c r="F112" s="8"/>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT, total charging</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
@@ -5261,24 +5269,20 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector units</t>
+          <t xml:space="preserve">Collector B</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_units</t>
+          <t xml:space="preserve">coll_b</t>
         </is>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu | ohm</t>
-        </is>
-      </c>
+      <c r="F113" s="8"/>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
+          <t xml:space="preserve">EQUIVALENT, total charging</t>
         </is>
       </c>
       <c r="H113" s="13" t="inlineStr">
@@ -5295,25 +5299,29 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZSORCE X pu</t>
+          <t xml:space="preserve">Collector units</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zsorce_x</t>
+          <t xml:space="preserve">coll_units</t>
         </is>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu | ohm</t>
+        </is>
+      </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
         </is>
       </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5333,12 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WMOD</t>
+          <t xml:space="preserve">ZSORCE X pu</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wmod</t>
+          <t xml:space="preserve">zsorce_x</t>
         </is>
       </c>
       <c r="D115" s="8"/>
@@ -5338,83 +5346,75 @@
       <c r="F115" s="8"/>
       <c r="G115" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="17.0" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WMOD</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wmod</t>
+        </is>
+      </c>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="8"/>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
         </is>
       </c>
-      <c r="H115" s="13" t="inlineStr">
+      <c r="H116" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="43.0" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
+    <row r="117" ht="43.0" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B116" s="12" t="inlineStr">
+      <c r="B117" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Converter model</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">regc</t>
-        </is>
-      </c>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REGC_A</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REGC_A | REGC_B</t>
-        </is>
-      </c>
-      <c r="G116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REGC_A: a current source, the standard | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (ZSORCE X its Xe) -- PV, BESS, WT4; .dyr REGCA1 / REGCBU1, .dyd regc_a / regc_b (blank = REGC_A)</t>
-        </is>
-      </c>
-      <c r="H116" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="30.0" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B117" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrical control</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reec</t>
         </is>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
+          <t xml:space="preserve">REGC_A</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
+          <t xml:space="preserve">REGC_A | REGC_B</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REEC_A: PV, WT | REEC_C: BESS (state of charge) | REEC_D: PV, BESS, WT4, the newest (voltage-dependent limits, momentary cessation) -- .dyr and .dyd alike (blank = REEC_A, BESS REEC_C)</t>
+          <t xml:space="preserve">REGC_A: a current source, the standard | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (ZSORCE X its Xe) -- PV, BESS, WT4; .dyr REGCA1 / REGCBU1, .dyd regc_a / regc_b (blank = REGC_A)</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="17.0" customHeight="1">
+    <row r="118" ht="30.0" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5431,29 +5431,33 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD library</t>
+          <t xml:space="preserve">Electrical control</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_library</t>
+          <t xml:space="preserve">reec</t>
         </is>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
-      <c r="F118" s="8"/>
+          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
+        </is>
+      </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
+          <t xml:space="preserve">REEC_A: PV, WT | REEC_C: BESS (state of charge) | REEC_D: PV, BESS, WT4, the newest (voltage-dependent limits, momentary cessation) -- .dyr and .dyd alike (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -5465,24 +5469,24 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD definition</t>
+          <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_definition</t>
+          <t xml:space="preserve">pscad_library</t>
         </is>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a source: network check</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="F119" s="8"/>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
+          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
@@ -5499,24 +5503,24 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD AC port</t>
+          <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_ac_port</t>
+          <t xml:space="preserve">pscad_definition</t>
         </is>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its 3-phase port</t>
+          <t xml:space="preserve">a source: network check</t>
         </is>
       </c>
       <c r="F120" s="8"/>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
       <c r="H120" s="13" t="inlineStr">
@@ -5525,7 +5529,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="30.0" customHeight="1">
+    <row r="121" ht="17.0" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5533,20 +5537,24 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD source case</t>
+          <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_source</t>
+          <t xml:space="preserve">pscad_ac_port</t>
         </is>
       </c>
       <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its 3-phase port</t>
+        </is>
+      </c>
       <c r="F121" s="8"/>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
+          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
@@ -5563,24 +5571,20 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD component ID</t>
+          <t xml:space="preserve">PSCAD source case</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_component_id</t>
+          <t xml:space="preserve">pscad_source</t>
         </is>
       </c>
       <c r="D122" s="8"/>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="E122" s="8"/>
       <c r="F122" s="8"/>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
+          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
@@ -5597,79 +5601,83 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD inverter at</t>
+          <t xml:space="preserve">PSCAD component ID</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_inv_at</t>
+          <t xml:space="preserve">pscad_component_id</t>
         </is>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="F123" s="8"/>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="30.0" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD inverter at</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_inv_at</t>
+        </is>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">LV</t>
         </is>
       </c>
-      <c r="F123" s="8" t="inlineStr">
+      <c r="F124" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV | MV</t>
         </is>
       </c>
-      <c r="G123" s="8" t="inlineStr">
+      <c r="G124" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
       </c>
-      <c r="H123" s="13" t="inlineStr">
+      <c r="H124" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-    </row>
-    <row r="125" ht="17.0" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collector</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collector</t>
-        </is>
-      </c>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
-        </is>
-      </c>
-      <c r="H125" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
     </row>
     <row r="126" ht="17.0" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
@@ -5679,12 +5687,12 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeder</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">feeder</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D126" s="8"/>
@@ -5692,7 +5700,7 @@
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">feeder name</t>
+          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
@@ -5709,24 +5717,20 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copies</t>
+          <t xml:space="preserve">Feeder</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">copies</t>
+          <t xml:space="preserve">feeder</t>
         </is>
       </c>
       <c r="D127" s="8"/>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E127" s="8"/>
       <c r="F127" s="8"/>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
+          <t xml:space="preserve">feeder name</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
@@ -5743,20 +5747,24 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section</t>
+          <t xml:space="preserve">Copies</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">section</t>
+          <t xml:space="preserve">copies</t>
         </is>
       </c>
       <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F128" s="8"/>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+          <t xml:space="preserve">identical feeders (blank = 1)</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
@@ -5765,7 +5773,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="30.0" customHeight="1">
+    <row r="129" ht="17.0" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5773,24 +5781,20 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">From section</t>
+          <t xml:space="preserve">Section</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_section</t>
+          <t xml:space="preserve">section</t>
         </is>
       </c>
       <c r="D129" s="8"/>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the one before (daisy chain</t>
-        </is>
-      </c>
+      <c r="E129" s="8"/>
       <c r="F129" s="8"/>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -5799,7 +5803,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="17.0" customHeight="1">
+    <row r="130" ht="30.0" customHeight="1">
       <c r="A130" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -5807,20 +5811,24 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">From section</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">from_section</t>
         </is>
       </c>
       <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the one before (daisy chain</t>
+        </is>
+      </c>
       <c r="F130" s="8"/>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Cables</t>
+          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
@@ -5837,18 +5845,22 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">length</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from Cables</t>
+        </is>
+      </c>
       <c r="H131" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5863,30 +5875,18 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">length</t>
         </is>
       </c>
       <c r="D132" s="8"/>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = km</t>
-        </is>
-      </c>
+      <c r="E132" s="8"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="8"/>
       <c r="H132" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5901,20 +5901,28 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units at end</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units tapped at the far end</t>
+          <t xml:space="preserve">blank = km</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
@@ -5931,12 +5939,12 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units of</t>
+          <t xml:space="preserve">Units at end</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units_of</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D134" s="8"/>
@@ -5944,7 +5952,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
+          <t xml:space="preserve">units tapped at the far end</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
@@ -5961,24 +5969,20 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel cables</t>
+          <t xml:space="preserve">Units of</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parallel</t>
+          <t xml:space="preserve">units_of</t>
         </is>
       </c>
       <c r="D135" s="8"/>
-      <c r="E135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E135" s="8"/>
       <c r="F135" s="8"/>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
         </is>
       </c>
       <c r="H135" s="13" t="inlineStr">
@@ -5995,24 +5999,24 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R ohm</t>
+          <t xml:space="preserve">Parallel cables</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_ohm</t>
+          <t xml:space="preserve">parallel</t>
         </is>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable x Length</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F136" s="8"/>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6029,12 +6033,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X ohm</t>
+          <t xml:space="preserve">R ohm</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_ohm</t>
+          <t xml:space="preserve">r_ohm</t>
         </is>
       </c>
       <c r="D137" s="8"/>
@@ -6046,7 +6050,7 @@
       <c r="F137" s="8"/>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
+          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
@@ -6063,12 +6067,12 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B uS</t>
+          <t xml:space="preserve">X ohm</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_us</t>
+          <t xml:space="preserve">x_ohm</t>
         </is>
       </c>
       <c r="D138" s="8"/>
@@ -6080,58 +6084,62 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
+        </is>
+      </c>
+      <c r="H138" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="17.0" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B uS</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b_us</t>
+        </is>
+      </c>
+      <c r="D139" s="8"/>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
+      <c r="F139" s="8"/>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
         </is>
       </c>
-      <c r="H138" s="13" t="inlineStr">
+      <c r="H139" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B139" s="7"/>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="7"/>
-    </row>
-    <row r="140" ht="17.0" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cable</t>
-        </is>
-      </c>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
-      <c r="G140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cable type</t>
-        </is>
-      </c>
-      <c r="H140" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B140" s="7"/>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
     </row>
     <row r="141" ht="17.0" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
@@ -6141,24 +6149,20 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
-      <c r="F141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+      <c r="F141" s="8"/>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per</t>
+          <t xml:space="preserve">cable type</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
@@ -6175,20 +6179,24 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R per length</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_per</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
+          <t xml:space="preserve">the values are per</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -6205,12 +6213,12 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D143" s="8"/>
@@ -6218,7 +6226,7 @@
       <c r="F143" s="8"/>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr">
@@ -6235,12 +6243,12 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">X per length</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">x_per</t>
         </is>
       </c>
       <c r="D144" s="8"/>
@@ -6248,7 +6256,7 @@
       <c r="F144" s="8"/>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
@@ -6265,12 +6273,12 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">C per length</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">c_per</t>
         </is>
       </c>
       <c r="D145" s="8"/>
@@ -6278,58 +6286,58 @@
       <c r="F145" s="8"/>
       <c r="G145" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">uF</t>
+        </is>
+      </c>
+      <c r="H145" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="17.0" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B per length</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b_per</t>
+        </is>
+      </c>
+      <c r="D146" s="8"/>
+      <c r="E146" s="8"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">uS, instead of C</t>
         </is>
       </c>
-      <c r="H145" s="13" t="inlineStr">
+      <c r="H146" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Collectors</t>
         </is>
       </c>
-      <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
-    </row>
-    <row r="147" ht="17.0" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B147" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="C147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
-      <c r="G147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
-        </is>
-      </c>
-      <c r="H147" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B147" s="7"/>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
     </row>
     <row r="148" ht="17.0" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
@@ -6339,12 +6347,12 @@
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D148" s="8"/>
@@ -6352,62 +6360,58 @@
       <c r="F148" s="8"/>
       <c r="G148" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="17.0" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collectors</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connect to</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">connect</t>
+        </is>
+      </c>
+      <c r="D149" s="8"/>
+      <c r="E149" s="8"/>
+      <c r="F149" s="8"/>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
-      <c r="H148" s="13" t="inlineStr">
+      <c r="H149" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B149" s="7"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7"/>
-      <c r="G149" s="7"/>
-      <c r="H149" s="7"/>
-    </row>
-    <row r="150" ht="17.0" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loads_Shunts</t>
-        </is>
-      </c>
-      <c r="B150" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kind</t>
-        </is>
-      </c>
-      <c r="C150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8"/>
-      <c r="F150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
-      <c r="G150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
-        </is>
-      </c>
-      <c r="H150" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B150" s="7"/>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
     </row>
     <row r="151" ht="17.0" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
@@ -6417,20 +6421,24 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">At bus</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
-      <c r="F151" s="8"/>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -6447,12 +6455,12 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mw</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D152" s="8"/>
@@ -6460,7 +6468,7 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -6477,12 +6485,12 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">MW</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">mw</t>
         </is>
       </c>
       <c r="D153" s="8"/>
@@ -6490,7 +6498,7 @@
       <c r="F153" s="8"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
@@ -6507,94 +6515,90 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">mvar</t>
         </is>
       </c>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
-      <c r="G154" s="8"/>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+        </is>
+      </c>
       <c r="H154" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
+    <row r="155" ht="17.0" customHeight="1">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D155" s="8"/>
+      <c r="E155" s="8"/>
+      <c r="F155" s="8"/>
+      <c r="G155" s="8"/>
+      <c r="H155" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B155" s="7"/>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
-      <c r="H155" s="7"/>
-    </row>
-    <row r="156" ht="30.0" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+      <c r="B156" s="7"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+    </row>
+    <row r="157" ht="30.0" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B156" s="12" t="inlineStr">
+      <c r="B157" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Machine</t>
         </is>
       </c>
-      <c r="C156" s="8" t="inlineStr">
+      <c r="C157" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">machine</t>
         </is>
       </c>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
-      <c r="F156" s="8"/>
-      <c r="G156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
-        </is>
-      </c>
-      <c r="H156" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="17.0" customHeight="1">
-      <c r="A157" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B157" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C157" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="D157" s="8"/>
-      <c r="E157" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its generator's</t>
-        </is>
-      </c>
+      <c r="E157" s="8"/>
       <c r="F157" s="8"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its generator's</t>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
@@ -6603,7 +6607,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="30.0" customHeight="1">
+    <row r="158" ht="17.0" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6611,24 +6615,24 @@
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pgen MW</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pgen_mw</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
+          <t xml:space="preserve">its generator's</t>
         </is>
       </c>
       <c r="F158" s="8"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -6637,7 +6641,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="17.0" customHeight="1">
+    <row r="159" ht="30.0" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6645,24 +6649,24 @@
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax MW</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmax_mw</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmax</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F159" s="8"/>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H159" s="13" t="inlineStr">
@@ -6679,24 +6683,24 @@
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmin MW</t>
+          <t xml:space="preserve">Pmax MW</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmin_mw</t>
+          <t xml:space="preserve">pmax_mw</t>
         </is>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmin</t>
+          <t xml:space="preserve">its units x Unit Pmax</t>
         </is>
       </c>
       <c r="F160" s="8"/>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
         </is>
       </c>
       <c r="H160" s="13" t="inlineStr">
@@ -6713,24 +6717,24 @@
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmax MVAr</t>
+          <t xml:space="preserve">Pmin MW</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmax_mvar</t>
+          <t xml:space="preserve">pmin_mw</t>
         </is>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmax</t>
+          <t xml:space="preserve">its units x Unit Pmin</t>
         </is>
       </c>
       <c r="F161" s="8"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
@@ -6747,24 +6751,24 @@
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmin MVAr</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmin_mvar</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmin</t>
+          <t xml:space="preserve">its units x Unit Qmax</t>
         </is>
       </c>
       <c r="F162" s="8"/>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H162" s="13" t="inlineStr">
@@ -6773,7 +6777,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="30.0" customHeight="1">
+    <row r="163" ht="17.0" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6781,24 +6785,24 @@
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Qmin MVAr</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mvar</t>
+          <t xml:space="preserve">qmin_mvar</t>
         </is>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as its generator's Q mode</t>
+          <t xml:space="preserve">its units x Unit Qmin</t>
         </is>
       </c>
       <c r="F163" s="8"/>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
         </is>
       </c>
       <c r="H163" s="13" t="inlineStr">
@@ -6807,7 +6811,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="17.0" customHeight="1">
+    <row r="164" ht="30.0" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -6815,75 +6819,79 @@
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBASE MVA</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mbase_mva</t>
+          <t xml:space="preserve">q_mvar</t>
         </is>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit MVA</t>
+          <t xml:space="preserve">as its generator's Q mode</t>
         </is>
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+        </is>
+      </c>
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="17.0" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBASE MVA</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mbase_mva</t>
+        </is>
+      </c>
+      <c r="D165" s="8"/>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit MVA</t>
+        </is>
+      </c>
+      <c r="F165" s="8"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = its units x Unit MVA</t>
         </is>
       </c>
-      <c r="H164" s="13" t="inlineStr">
+      <c r="H165" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
-    </row>
-    <row r="166" ht="17.0" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B166" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bus</t>
-        </is>
-      </c>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
-      <c r="G166" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
-        </is>
-      </c>
-      <c r="H166" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
     </row>
     <row r="167" ht="17.0" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
@@ -6893,24 +6901,20 @@
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">Bus</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">bus</t>
         </is>
       </c>
       <c r="D167" s="8"/>
-      <c r="E167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic</t>
-        </is>
-      </c>
+      <c r="E167" s="8"/>
       <c r="F167" s="8"/>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
         </is>
       </c>
       <c r="H167" s="13" t="inlineStr">
@@ -6919,7 +6923,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="30.0" customHeight="1">
+    <row r="168" ht="17.0" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
@@ -6927,90 +6931,94 @@
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Number</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
+          <t xml:space="preserve">automatic</t>
         </is>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = automatic</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="30.0" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B169" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D169" s="8"/>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
+      <c r="F169" s="8"/>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = automatic (12 characters at most)</t>
         </is>
       </c>
-      <c r="H168" s="13" t="inlineStr">
+      <c r="H169" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
-      <c r="G169" s="7"/>
-      <c r="H169" s="7"/>
-    </row>
-    <row r="170" ht="17.0" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="7"/>
+      <c r="H170" s="7"/>
+    </row>
+    <row r="171" ht="17.0" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B170" s="12" t="inlineStr">
+      <c r="B171" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Generator</t>
         </is>
       </c>
-      <c r="C170" s="8" t="inlineStr">
+      <c r="C171" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
-      <c r="F170" s="8"/>
-      <c r="G170" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
-        </is>
-      </c>
-      <c r="H170" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="30.0" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B171" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Model</t>
-        </is>
-      </c>
-      <c r="C171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D171" s="8"/>
@@ -7018,7 +7026,7 @@
       <c r="F171" s="8"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
@@ -7027,7 +7035,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="17.0" customHeight="1">
+    <row r="172" ht="30.0" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
@@ -7035,12 +7043,12 @@
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Model</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D172" s="8"/>
@@ -7048,7 +7056,7 @@
       <c r="F172" s="8"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
@@ -7065,71 +7073,67 @@
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
-      <c r="G173" s="8"/>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+        </is>
+      </c>
       <c r="H173" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="7" t="inlineStr">
+    <row r="174" ht="17.0" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D174" s="8"/>
+      <c r="E174" s="8"/>
+      <c r="F174" s="8"/>
+      <c r="G174" s="8"/>
+      <c r="H174" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
-      <c r="B174" s="7"/>
-      <c r="C174" s="7"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
-      <c r="G174" s="7"/>
-      <c r="H174" s="7"/>
-    </row>
-    <row r="175" ht="17.0" customHeight="1">
-      <c r="A175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B175" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generator</t>
-        </is>
-      </c>
-      <c r="C175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the plant</t>
-        </is>
-      </c>
-      <c r="F175" s="8"/>
-      <c r="G175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = the plant</t>
-        </is>
-      </c>
-      <c r="H175" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E</t>
-        </is>
-      </c>
+      <c r="B175" s="7"/>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
     </row>
     <row r="176" ht="17.0" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
@@ -7139,67 +7143,75 @@
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">record</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the plant</t>
+        </is>
+      </c>
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = the plant</t>
+        </is>
+      </c>
+      <c r="H176" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="17.0" customHeight="1">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
+      <c r="B177" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Record</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">record</t>
+        </is>
+      </c>
+      <c r="D177" s="8"/>
+      <c r="E177" s="8"/>
+      <c r="F177" s="8"/>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
         </is>
       </c>
-      <c r="H176" s="13" t="inlineStr">
+      <c r="H177" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="7" t="inlineStr">
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B177" s="7"/>
-      <c r="C177" s="7"/>
-      <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
-      <c r="G177" s="7"/>
-      <c r="H177" s="7"/>
-    </row>
-    <row r="178" ht="17.0" customHeight="1">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B178" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generator</t>
-        </is>
-      </c>
-      <c r="C178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="8"/>
-      <c r="H178" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="7"/>
     </row>
     <row r="179" ht="17.0" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
@@ -7209,22 +7221,18 @@
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D179" s="8"/>
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
-      <c r="G179" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
-        </is>
-      </c>
+      <c r="G179" s="8"/>
       <c r="H179" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
@@ -7239,12 +7247,12 @@
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D180" s="8"/>
@@ -7252,52 +7260,64 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H180" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="17.0" customHeight="1">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B181" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="D181" s="8"/>
+      <c r="E181" s="8"/>
+      <c r="F181" s="8"/>
+      <c r="G181" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
         </is>
       </c>
-      <c r="H180" s="13" t="inlineStr">
+      <c r="H181" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="7" t="inlineStr">
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
         </is>
       </c>
-      <c r="B181" s="7"/>
-      <c r="C181" s="7"/>
-      <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7"/>
-      <c r="G181" s="7"/>
-      <c r="H181" s="7"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="8"/>
-      <c r="B182" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
-      <c r="F182" s="8"/>
-      <c r="G182" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H182" s="8"/>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
+      <c r="G182" s="7"/>
+      <c r="H182" s="7"/>
     </row>
     <row r="183">
       <c r="A183" s="8"/>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -7306,7 +7326,7 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the point of interconnection</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H183" s="8"/>
@@ -7315,7 +7335,7 @@
       <c r="A184" s="8"/>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C184" s="8"/>
@@ -7324,7 +7344,7 @@
       <c r="F184" s="8"/>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H184" s="8"/>
@@ -7333,7 +7353,7 @@
       <c r="A185" s="8"/>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C185" s="8"/>
@@ -7342,7 +7362,7 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
         </is>
       </c>
       <c r="H185" s="8"/>
@@ -7351,7 +7371,7 @@
       <c r="A186" s="8"/>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C186" s="8"/>
@@ -7360,7 +7380,7 @@
       <c r="F186" s="8"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+          <t xml:space="preserve">an MPT's LV winding</t>
         </is>
       </c>
       <c r="H186" s="8"/>
@@ -7369,7 +7389,7 @@
       <c r="A187" s="8"/>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C187" s="8"/>
@@ -7378,7 +7398,7 @@
       <c r="F187" s="8"/>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
         </is>
       </c>
       <c r="H187" s="8"/>
@@ -7387,7 +7407,7 @@
       <c r="A188" s="8"/>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C188" s="8"/>
@@ -7396,7 +7416,7 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
         </is>
       </c>
       <c r="H188" s="8"/>
@@ -7405,7 +7425,7 @@
       <c r="A189" s="8"/>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C189" s="8"/>
@@ -7414,7 +7434,7 @@
       <c r="F189" s="8"/>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H189" s="8"/>
@@ -7423,7 +7443,7 @@
       <c r="A190" s="8"/>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C190" s="8"/>
@@ -7432,7 +7452,7 @@
       <c r="F190" s="8"/>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H190" s="8"/>
@@ -7441,7 +7461,7 @@
       <c r="A191" s="8"/>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
         </is>
       </c>
       <c r="C191" s="8"/>
@@ -7450,7 +7470,7 @@
       <c r="F191" s="8"/>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">a generator's terminal</t>
         </is>
       </c>
       <c r="H191" s="8"/>
@@ -7459,7 +7479,7 @@
       <c r="A192" s="8"/>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C192" s="8"/>
@@ -7468,50 +7488,42 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H192" s="8"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="8"/>
+      <c r="B193" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+        </is>
+      </c>
+      <c r="C193" s="8"/>
+      <c r="D193" s="8"/>
+      <c r="E193" s="8"/>
+      <c r="F193" s="8"/>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
         </is>
       </c>
-      <c r="H192" s="8"/>
-    </row>
-    <row r="193" ht="18" customHeight="1">
-      <c r="A193" s="7" t="inlineStr">
+      <c r="H193" s="8"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
         </is>
       </c>
-      <c r="B193" s="7"/>
-      <c r="C193" s="7"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
-      <c r="H193" s="7"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B194" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{UNITS}</t>
-        </is>
-      </c>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
-      <c r="F194" s="8"/>
-      <c r="G194" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H194" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+      <c r="B194" s="7"/>
+      <c r="C194" s="7"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
+      <c r="G194" s="7"/>
+      <c r="H194" s="7"/>
     </row>
     <row r="195">
       <c r="A195" s="8" t="inlineStr">
@@ -7521,7 +7533,7 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -7530,7 +7542,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H195" s="13" t="inlineStr">
@@ -7547,7 +7559,7 @@
       </c>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_MW}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -7556,7 +7568,7 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H196" s="13" t="inlineStr">
@@ -7573,7 +7585,7 @@
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C197" s="8"/>
@@ -7582,7 +7594,7 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H197" s="13" t="inlineStr">
@@ -7599,7 +7611,7 @@
       </c>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C198" s="8"/>
@@ -7608,7 +7620,7 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H198" s="13" t="inlineStr">
@@ -7625,7 +7637,7 @@
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C199" s="8"/>
@@ -7634,7 +7646,7 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H199" s="13" t="inlineStr">
@@ -7651,7 +7663,7 @@
       </c>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C200" s="8"/>
@@ -7660,7 +7672,7 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H200" s="13" t="inlineStr">
@@ -7677,7 +7689,7 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C201" s="8"/>
@@ -7686,7 +7698,7 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H201" s="13" t="inlineStr">
@@ -7703,7 +7715,7 @@
       </c>
       <c r="B202" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C202" s="8"/>
@@ -7712,7 +7724,7 @@
       <c r="F202" s="8"/>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H202" s="13" t="inlineStr">
@@ -7729,7 +7741,7 @@
       </c>
       <c r="B203" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C203" s="8"/>
@@ -7738,7 +7750,7 @@
       <c r="F203" s="8"/>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H203" s="13" t="inlineStr">
@@ -7755,7 +7767,7 @@
       </c>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C204" s="8"/>
@@ -7764,7 +7776,7 @@
       <c r="F204" s="8"/>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H204" s="13" t="inlineStr">
@@ -7781,7 +7793,7 @@
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C205" s="8"/>
@@ -7790,7 +7802,7 @@
       <c r="F205" s="8"/>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H205" s="13" t="inlineStr">
@@ -7807,7 +7819,7 @@
       </c>
       <c r="B206" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C206" s="8"/>
@@ -7816,7 +7828,7 @@
       <c r="F206" s="8"/>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H206" s="13" t="inlineStr">
@@ -7833,7 +7845,7 @@
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C207" s="8"/>
@@ -7842,7 +7854,7 @@
       <c r="F207" s="8"/>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H207" s="13" t="inlineStr">
@@ -7859,7 +7871,7 @@
       </c>
       <c r="B208" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C208" s="8"/>
@@ -7868,7 +7880,7 @@
       <c r="F208" s="8"/>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">frequency (Hz)</t>
         </is>
       </c>
       <c r="H208" s="13" t="inlineStr">
@@ -7885,7 +7897,7 @@
       </c>
       <c r="B209" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{P_INV_MW}</t>
         </is>
       </c>
       <c r="C209" s="8"/>
@@ -7894,7 +7906,7 @@
       <c r="F209" s="8"/>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
         </is>
       </c>
       <c r="H209" s="13" t="inlineStr">
@@ -7911,7 +7923,7 @@
       </c>
       <c r="B210" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
         </is>
       </c>
       <c r="C210" s="8"/>
@@ -7920,10 +7932,36 @@
       <c r="F210" s="8"/>
       <c r="G210" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H210" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B211" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C211" s="8"/>
+      <c r="D211" s="8"/>
+      <c r="E211" s="8"/>
+      <c r="F211" s="8"/>
+      <c r="G211" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H210" s="13" t="inlineStr">
+      <c r="H211" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -7934,34 +7972,34 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A84:H84"/>
-    <mergeCell ref="A124:H124"/>
-    <mergeCell ref="A139:H139"/>
-    <mergeCell ref="A146:H146"/>
-    <mergeCell ref="A149:H149"/>
-    <mergeCell ref="A155:H155"/>
-    <mergeCell ref="A165:H165"/>
-    <mergeCell ref="A169:H169"/>
-    <mergeCell ref="A174:H174"/>
-    <mergeCell ref="A177:H177"/>
-    <mergeCell ref="A181:H181"/>
-    <mergeCell ref="A193:H193"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A125:H125"/>
+    <mergeCell ref="A140:H140"/>
+    <mergeCell ref="A147:H147"/>
+    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A156:H156"/>
+    <mergeCell ref="A166:H166"/>
+    <mergeCell ref="A170:H170"/>
+    <mergeCell ref="A175:H175"/>
+    <mergeCell ref="A178:H178"/>
+    <mergeCell ref="A182:H182"/>
+    <mergeCell ref="A194:H194"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
-    <hyperlink ref="A54" location="'MPT'!A1" display="MPT"/>
-    <hyperlink ref="A84" location="'Generators'!A1" display="Generators"/>
-    <hyperlink ref="A124" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A139" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A146" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A149" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A155" location="'Machines'!A1" display="Machines"/>
-    <hyperlink ref="A165" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A169" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A174" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A177" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A193" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A55" location="'MPT'!A1" display="MPT"/>
+    <hyperlink ref="A85" location="'Generators'!A1" display="Generators"/>
+    <hyperlink ref="A125" location="'Feeders'!A1" display="Feeders"/>
+    <hyperlink ref="A140" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A147" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A150" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A156" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A166" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A170" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A175" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A178" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A194" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -21084,102 +21122,102 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="43.0" customHeight="1">
+    <row r="50" ht="30.0" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD lines as</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PI</t>
-        </is>
-      </c>
+          <t xml:space="preserve">PSCAD meter at each inverter</t>
+        </is>
+      </c>
+      <c r="B50" s="3"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES | NO</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES = a multimeter between each inverter and its GSU: P_, Q_, V_&lt;unit&gt; in MW, MVAr, kV (blank = YES)</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="43.0" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD lines as</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">PI</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="C51" s="8"/>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PI | RLC</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PI = the gen-tie, each collector and each feeder section one Coupled PI Section (R, X, B in pu, its charging inside); RLC = an R and an L, the charging a C at each end (blank = PI)</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD FAULT AT THE POI</t>
         </is>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-    </row>
-    <row r="52" ht="30.0" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+    </row>
+    <row r="53" ht="30.0" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault at POI</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">YES</t>
         </is>
       </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="17.0" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD fault time</t>
-        </is>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100: none in the run</t>
-        </is>
-      </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -21191,12 +21229,10 @@
     <row r="54" ht="17.0" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD fault duration</t>
-        </is>
-      </c>
-      <c r="B54" s="3">
-        <v>0.15</v>
-      </c>
+          <t xml:space="preserve">PSCAD fault time</t>
+        </is>
+      </c>
+      <c r="B54" s="3"/>
       <c r="C54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">s</t>
@@ -21204,114 +21240,145 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.15</t>
+          <t xml:space="preserve">100: none in the run</t>
         </is>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">when the fault starts (blank = 100: none in the run)</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="17.0" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD fault duration</t>
+        </is>
+      </c>
+      <c r="B55" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.15</t>
+        </is>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">blank = 0.15</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="43.0" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
+    <row r="56" ht="43.0" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault type</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="C56" s="8"/>
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ABCG | ABC | AG | BG | CG | ABG | BCG | ACG | AB | BC | AC</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">the phases faulted, G = to ground (blank = ABCG)</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="17.0" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
+    <row r="57" ht="17.0" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD fault resistance</t>
         </is>
       </c>
-      <c r="B56" s="3">
+      <c r="B57" s="3">
         <v>0.01</v>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">0.01</t>
         </is>
       </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="E57" s="8"/>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 0.01</t>
         </is>
       </c>
-      <c r="G56" s="13" t="inlineStr">
+      <c r="G57" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD LIBRARIES</t>
         </is>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-    </row>
-    <row r="58" ht="17.0" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+    </row>
+    <row r="59" ht="17.0" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD libraries</t>
         </is>
       </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="B59" s="3"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">user-model libraries (.pslx) to load, separated by ;</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -21325,10 +21392,10 @@
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A58:G58"/>
   </mergeCells>
-  <dataValidations count="15">
+  <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4">
       <formula1>"SMIB,DETAILED"</formula1>
     </dataValidation>
@@ -21366,12 +21433,15 @@
       <formula1>"YES,NO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B50">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B51">
       <formula1>"PI,RLC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B52">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B53">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B55">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B56">
       <formula1>"ABCG,ABC,AG,BG,CG,ABG,BCG,ACG,AB,BC,AC"</formula1>
     </dataValidation>
   </dataValidations>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -225,7 +225,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E (.raw, .dyr) and PSCAD (.pscx) models of a plant from one workbook -- smib_build.py, 2026-10-15</t>
+          <t xml:space="preserve">PSS/E (.raw, .dyr) and PSCAD (.pscx) models of a plant from one workbook -- smib_build.py, 2026-10-16</t>
         </is>
       </c>
       <c r="B2" s="10"/>
@@ -813,7 +813,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="69.0" customHeight="1">
+    <row r="52" ht="95.0" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
@@ -821,7 +821,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameters of each generator's vendor PSCAD model (UDM), as PSCAD takes them. Filled in for each inverter it stands for (DETAILED: each node): {UNITS} units, {MVA} their MVA, {P_MW} {Q_MVAR} their P and Q where it connects, {P_PU} {Q_PU} on {MVA}, {UNIT_MVA} {UNIT_P_MW} {UNIT_Q_MVAR} one unit's, {V_PU} {V_KV} {KV} {ANGLE} the voltage there, its base and PSCAD angle, {P_INV_MW} {Q_INV_MVAR} {V_INV_PU} at the inverters' own terminals (a UDM on the MV side), {FREQ} -- e.g. Ninv = {UNITS}, Vt0 = {V_PU}.</t>
+          <t xml:space="preserve">Parameters of each generator's vendor PSCAD model (UDM), as PSCAD takes them. Filled in for each inverter it stands for (DETAILED: each node): {UNITS} units, {MVA} their MVA, {P_MW} {Q_MVAR} their P and Q where it connects, {P_PU} {Q_PU} on {MVA}, {UNIT_MVA} {UNIT_P_MW} {UNIT_Q_MVAR} one unit's, {V_PU} {V_KV} {KV} {ANGLE} the voltage there, its base and PSCAD angle, {P_INV_MW} {Q_INV_MVAR} {V_INV_PU} at the inverters' own terminals (a UDM on the MV side), {FREQ} -- e.g. Ninv = {UNITS}, Vt0 = {V_PU}. In the GUI, the PSCAD_Params tab shows each vendor model's parameters, read from its definition in its file, a column per generator: double-click one to change it (a choice from its list), clear it to go back to the model's own.</t>
         </is>
       </c>
     </row>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -813,7 +813,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="95.0" customHeight="1">
+    <row r="52" ht="134.0" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
@@ -821,7 +821,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameters of each generator's vendor PSCAD model (UDM), as PSCAD takes them. Filled in for each inverter it stands for (DETAILED: each node): {UNITS} units, {MVA} their MVA, {P_MW} {Q_MVAR} their P and Q where it connects, {P_PU} {Q_PU} on {MVA}, {UNIT_MVA} {UNIT_P_MW} {UNIT_Q_MVAR} one unit's, {V_PU} {V_KV} {KV} {ANGLE} the voltage there, its base and PSCAD angle, {P_INV_MW} {Q_INV_MVAR} {V_INV_PU} at the inverters' own terminals (a UDM on the MV side), {FREQ} -- e.g. Ninv = {UNITS}, Vt0 = {V_PU}. In the GUI, the PSCAD_Params tab shows each vendor model's parameters, read from its definition in its file, a column per generator: double-click one to change it (a choice from its list), clear it to go back to the model's own.</t>
+          <t xml:space="preserve">Parameters of each generator's vendor PSCAD model (UDM), as PSCAD takes them. Filled in for each inverter it stands for (DETAILED: each node): {UNITS} units, {MVA} their MVA, {P_MW} {Q_MVAR} their P and Q where it connects, {P_PU} {Q_PU} on {MVA}, {UNIT_MVA} {UNIT_P_MW} {UNIT_Q_MVAR} one unit's, {V_PU} {V_KV} {KV} {ANGLE} the voltage there, its base and PSCAD angle, {P_INV_MW} {Q_INV_MVAR} {V_INV_PU} at the inverters' own terminals (a UDM on the MV side), {FREQ} -- e.g. Ninv = {UNITS}, Vt0 = {V_PU}. In the GUI, the PSCAD_Params tab shows each vendor model's parameters, read from its definition in its file, a column per generator -- and, picked under Definition, those of the parts inside it (its controller ...) and its signals set by a constant, slider or switch (FreqDroop ...): double-click one to change it (a choice from its list), clear it to go back to the model's own. A part's setting is Part/Setting (Controller4/UFLevel1), a signal's its source's Value (var_switch#5/Value); they change a copy of the definition of the generator's own.</t>
         </is>
       </c>
     </row>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -216,7 +216,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMIB PLANT MODEL  |  INPUT WORKBOOK</t>
+          <t xml:space="preserve">PLANT MODEL BUILDER  |  INPUT WORKBOOK</t>
         </is>
       </c>
       <c r="B1" s="6"/>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="17.0" customHeight="1">
+    <row r="17" ht="30.0" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2118,7 +2118,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base</t>
+          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base; several (3, 5, 10): a set of models for each, named &lt;name&gt;_SCR3 ...</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -20240,7 +20240,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base</t>
+          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base; several (3, 5, 10): a set of models for each, named &lt;name&gt;_SCR3 ...</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -2118,7 +2118,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base; several (3, 5, 10): a set of models for each, named &lt;name&gt;_SCR3 ...</t>
+          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base; several values (3, 5, 10): a set of models for each, &lt;name&gt;_SCR&lt;value&gt;</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -2146,7 +2146,11 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">several values (3, 5, 10): a set of models for each, &lt;name&gt;_XR&lt;value&gt;</t>
+        </is>
+      </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -2191,7 +2195,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="17.0" customHeight="1">
+    <row r="20" ht="30.0" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2216,7 +2220,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of the SCR (with Grid X/R)</t>
+          <t xml:space="preserve">instead of the SCR (with Grid X/R); several values (3, 5, 10): a set of models for each, &lt;name&gt;_SC&lt;value&gt;</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -2318,7 +2322,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI to the substation HV bus; blank = no gen-tie (the MPTs on the POI bus)</t>
+          <t xml:space="preserve">POI to the substation HV bus; blank = no gen-tie (the MPTs on the POI bus); several values (3, 5, 10): a set of models for each, &lt;name&gt;_TIE&lt;value&gt;</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -2751,7 +2755,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="17.0" customHeight="1">
+    <row r="36" ht="30.0" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2780,7 +2784,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
+          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0); several values (3, 5, 10): a set of models for each, &lt;name&gt;_V&lt;value&gt;</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -2789,7 +2793,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="17.0" customHeight="1">
+    <row r="37" ht="30.0" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2818,7 +2822,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
+          <t xml:space="preserve">mode Q; + = into the grid (blank = 0); several values (3, 5, 10): a set of models for each, &lt;name&gt;_Q&lt;value&gt;</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -2827,7 +2831,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="17.0" customHeight="1">
+    <row r="38" ht="30.0" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2848,7 +2852,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
+          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading; several values (3, 5, 10): a set of models for each, &lt;name&gt;_PF&lt;value&gt;</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -2857,7 +2861,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="17.0" customHeight="1">
+    <row r="39" ht="30.0" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -2886,7 +2890,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
+          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0); several values (3, 5, 10): a set of models for each, &lt;name&gt;_VG&lt;value&gt;</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -2924,7 +2928,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
+          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it; several values (3, 5, 10): a set of models for each, &lt;name&gt;_P&lt;value&gt;</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -20240,7 +20244,7 @@
       <c r="E16" s="8"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base; several (3, 5, 10): a set of models for each, named &lt;name&gt;_SCR3 ...</t>
+          <t xml:space="preserve">short-circuit ratio at the POI, on the SCR base; several values (3, 5, 10): a set of models for each, &lt;name&gt;_SCR&lt;value&gt;</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -20261,7 +20265,11 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="2"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">several values (3, 5, 10): a set of models for each, &lt;name&gt;_XR&lt;value&gt;</t>
+        </is>
+      </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -20297,7 +20305,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="17.0" customHeight="1">
+    <row r="19" ht="30.0" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Grid short-circuit MVA</t>
@@ -20313,7 +20321,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">instead of the SCR (with Grid X/R)</t>
+          <t xml:space="preserve">instead of the SCR (with Grid X/R); several values (3, 5, 10): a set of models for each, &lt;name&gt;_SC&lt;value&gt;</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -20403,7 +20411,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI to the substation HV bus; blank = no gen-tie (the MPTs on the POI bus)</t>
+          <t xml:space="preserve">POI to the substation HV bus; blank = no gen-tie (the MPTs on the POI bus); several values (3, 5, 10): a set of models for each, &lt;name&gt;_TIE&lt;value&gt;</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
@@ -20763,7 +20771,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="17.0" customHeight="1">
+    <row r="37" ht="30.0" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">POI voltage</t>
@@ -20785,7 +20793,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0)</t>
+          <t xml:space="preserve">the POI voltage the plant holds (blank = 1.0); several values (3, 5, 10): a set of models for each, &lt;name&gt;_V&lt;value&gt;</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
@@ -20794,7 +20802,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="17.0" customHeight="1">
+    <row r="38" ht="30.0" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Q at POI</t>
@@ -20816,7 +20824,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode Q; + = into the grid (blank = 0)</t>
+          <t xml:space="preserve">mode Q; + = into the grid (blank = 0); several values (3, 5, 10): a set of models for each, &lt;name&gt;_Q&lt;value&gt;</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -20825,7 +20833,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="17.0" customHeight="1">
+    <row r="39" ht="30.0" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">PF at POI</t>
@@ -20839,7 +20847,7 @@
       <c r="E39" s="8"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading</t>
+          <t xml:space="preserve">mode PF; + lagging (Q into the grid), - leading; several values (3, 5, 10): a set of models for each, &lt;name&gt;_PF&lt;value&gt;</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
@@ -20848,7 +20856,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="17.0" customHeight="1">
+    <row r="40" ht="30.0" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Grid voltage</t>
@@ -20870,7 +20878,7 @@
       <c r="E40" s="8"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0)</t>
+          <t xml:space="preserve">mode V: the infinite bus (blank = 1.0); several values (3, 5, 10): a set of models for each, &lt;name&gt;_VG&lt;value&gt;</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
@@ -20899,7 +20907,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it</t>
+          <t xml:space="preserve">blank = each generator at its dispatch | a value = the dispatches scaled to deliver it; several values (3, 5, 10): a set of models for each, &lt;name&gt;_P&lt;value&gt;</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -2738,7 +2738,11 @@
         </is>
       </c>
       <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q</t>
+        </is>
+      </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q | PF | V</t>
@@ -2746,7 +2750,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage</t>
+          <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage (blank = Q)</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -3144,7 +3148,11 @@
         </is>
       </c>
       <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
+          <t xml:space="preserve">YES = a multimeter between the grid and the POI (blank = YES)</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -3254,7 +3262,11 @@
         </is>
       </c>
       <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
@@ -3262,7 +3274,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
+          <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have (blank = YES)</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -4854,7 +4866,11 @@
         </is>
       </c>
       <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">share</t>
+        </is>
+      </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">share | fixed</t>
@@ -4862,7 +4878,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
+          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q (blank = share)</t>
         </is>
       </c>
       <c r="H99" s="13" t="inlineStr">
@@ -5171,7 +5187,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="17.0" customHeight="1">
+    <row r="110" ht="56.0" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5188,7 +5204,11 @@
         </is>
       </c>
       <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEEDERS where Feeders has rows for it, else EQUIVALENT where Collector X is given, else NONE</t>
+        </is>
+      </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
@@ -5196,7 +5216,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
+          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE (blank = FEEDERS where Feeders has rows for it, else EQUIVALENT where Collector X is given, else NONE)</t>
         </is>
       </c>
       <c r="H110" s="13" t="inlineStr">
@@ -5312,7 +5332,11 @@
         </is>
       </c>
       <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu</t>
+        </is>
+      </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pu | ohm</t>
@@ -5320,7 +5344,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
+          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS (blank = pu)</t>
         </is>
       </c>
       <c r="H114" s="13" t="inlineStr">
@@ -6434,7 +6458,11 @@
         </is>
       </c>
       <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD</t>
+        </is>
+      </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LOAD | SHUNT</t>
@@ -6442,7 +6470,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor (blank = LOAD)</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -20754,7 +20782,11 @@
         </is>
       </c>
       <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q</t>
+        </is>
+      </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Q | PF | V</t>
@@ -20762,7 +20794,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage</t>
+          <t xml:space="preserve">Q: Q at the POI | PF: power factor at the POI | V: the plant holds the POI voltage with the grid at Grid voltage (blank = Q)</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
@@ -21113,7 +21145,11 @@
         </is>
       </c>
       <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
@@ -21121,7 +21157,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES = a multimeter between the grid and the POI</t>
+          <t xml:space="preserve">YES = a multimeter between the grid and the POI (blank = YES)</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -21217,7 +21253,11 @@
         </is>
       </c>
       <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">YES | NO</t>
@@ -21225,7 +21265,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have</t>
+          <t xml:space="preserve">YES = a fault on the grid side of the POI with its timed fault logic, as vendors' test cases have (blank = YES)</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -22752,7 +22792,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q</t>
+          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q (blank = share)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -22791,7 +22831,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE</t>
+          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE (blank = FEEDERS where Feeders has rows for it, else EQUIVALENT where Collector X is given, else NONE)</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -22811,7 +22851,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS</t>
+          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS (blank = pu)</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -25152,10 +25192,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="76.0" customHeight="1">
+    <row r="2" ht="88.0" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"># LOAD: constant impedance | SHUNT: + capacitor, - reactor</t>
+          <t xml:space="preserve"># LOAD: constant impedance | SHUNT: + capacitor, - reactor (blank = LOAD)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30.0" customHeight="1">
+    <row r="42" ht="56.0" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -701,11 +701,11 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">One row per main power transformer; HV winding first. Three windings: TV kV, the three impedances and their bases. Parallel units: identical units in parallel. Tie: a line of its own from HV to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="82.0" customHeight="1">
+          <t xml:space="preserve">One row per main power transformer; HV winding first. Three windings: TV kV, the three impedances and their bases. Parallel units: identical units in parallel. Tie: a line of its own from HV to it. MVA blank: the MVA of the units on it (Unit MVA x Units), following them -- the GUI's Size MPTs from the generators suggests a rating. Rate A, B, C: its normal and emergency ratings (PSS/E RATEA, RATEB, RATEC; PSLF rate1, rate2, rate3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="95.0" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -713,7 +713,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">One row per generator (PV, BESS, wind, synchronous ...): the units (count and one unit's data; the model is their aggregate), its GSU (one GSU's data and the count), its collector (FEEDERS: the WECC equivalent of its rows in Feeders; EQUIVALENT: R X B given; NONE), how it shares the POI's Q, its electrical control model in the .dyr (REEC_A: REECA1, PV and wind; REEC_C: REECCU1, BESS; REEC_D: REECDU1, PV, BESS and WT4) and its PSCAD model (vendor library and definition, or blank for a voltage source at the solved terminal voltage: a network check against PSS/E) and where the inverter connects (LV or MV side of the GSU).</t>
+          <t xml:space="preserve">One row per generator (PV, BESS, wind, synchronous ...): the units (count and one unit's data; the model is their aggregate), its GSU (one GSU's data, and Units per GSU or the GSU count -- the GUI's GSUs page: Size GSUs from the units; Rate A, B, C one GSU's), its collector (FEEDERS: the WECC equivalent of its rows in Feeders; EQUIVALENT: R X B given; NONE), how it shares the POI's Q, its electrical control model in the .dyr (REEC_A: REECA1, PV and wind; REEC_C: REECCU1, BESS; REEC_D: REECDU1, PV, BESS and WT4) and its PSCAD model (vendor library and definition, or blank for a voltage source at the solved terminal voltage: a network check against PSS/E) and where the inverter connects (LV or MV side of the GSU).</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="17.0" customHeight="1">
+    <row r="45" ht="43.0" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
@@ -737,7 +737,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable data per length (R, X in ohm; C in uF or B in uS) and the length unit they are per.</t>
+          <t xml:space="preserve">Cable data per length (R, X in ohm; C in uF or B in uS) and the length unit they are per; Rate A, B, C one cable's ratings in MVA at its collector's kV (sqrt(3) x kV x amps / 1000): a section's x its parallel cables, a collector equivalent's its sections from the collector bus together.</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="17.0" customHeight="1">
+    <row r="61" ht="30.0" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -3650,11 +3650,15 @@
         </is>
       </c>
       <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the MVA of the units on it, following them</t>
+        </is>
+      </c>
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
+          <t xml:space="preserve">the rating (3 windings: HV winding; blank = the MVA of the units on it, following them)</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -3723,7 +3727,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="17.0" customHeight="1">
+    <row r="64" ht="30.0" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -3731,29 +3735,33 @@
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV %</t>
+          <t xml:space="preserve">Rate A MVA</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_hl_pct</t>
+          <t xml:space="preserve">rate_mva</t>
         </is>
       </c>
       <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on its base MVA</t>
+          <t xml:space="preserve">normal rating: PSS/E RATEA, PSLF rate1 (blank = MVA; 3 windings: the HV winding's, the LV and TV windings' their MVA)</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30.0" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -3761,25 +3769,29 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV %</t>
+          <t xml:space="preserve">Rate B MVA</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_ht_pct</t>
+          <t xml:space="preserve">rate_b_mva</t>
         </is>
       </c>
       <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate A</t>
+        </is>
+      </c>
       <c r="F65" s="8"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">emergency rating: RATEB, rate2 (blank = Rate A; 3 windings: the HV winding's, the LV and TV windings' in proportion)</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -3791,25 +3803,29 @@
       </c>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV %</t>
+          <t xml:space="preserve">Rate C MVA</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">z_lt_pct</t>
+          <t xml:space="preserve">rate_c_mva</t>
         </is>
       </c>
       <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate B</t>
+        </is>
+      </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">RATEC, rate3 (blank = Rate B; 3 windings: as Rate B)</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -3821,24 +3837,20 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-LV base MVA</t>
+          <t xml:space="preserve">Z HV-LV %</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_hl_mva</t>
+          <t xml:space="preserve">z_hl_pct</t>
         </is>
       </c>
       <c r="D67" s="8"/>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E67" s="8"/>
       <c r="F67" s="8"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">on its base MVA</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -3855,24 +3867,20 @@
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z HV-TV base MVA</t>
+          <t xml:space="preserve">Z HV-TV %</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_ht_mva</t>
+          <t xml:space="preserve">z_ht_pct</t>
         </is>
       </c>
       <c r="D68" s="8"/>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -3889,24 +3897,20 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z LV-TV base MVA</t>
+          <t xml:space="preserve">Z LV-TV %</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_lt_mva</t>
+          <t xml:space="preserve">z_lt_pct</t>
         </is>
       </c>
       <c r="D69" s="8"/>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MVA</t>
-        </is>
-      </c>
+      <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">3 windings</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -3923,20 +3927,24 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X/R</t>
+          <t xml:space="preserve">Z HV-LV base MVA</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_r</t>
+          <t xml:space="preserve">base_hl_mva</t>
         </is>
       </c>
       <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">each impedance</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -3953,20 +3961,24 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load loss kW</t>
+          <t xml:space="preserve">Z HV-TV base MVA</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">load_loss_kw</t>
+          <t xml:space="preserve">base_ht_mva</t>
         </is>
       </c>
       <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -3983,20 +3995,24 @@
       </c>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector group</t>
+          <t xml:space="preserve">Z LV-TV base MVA</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vector</t>
+          <t xml:space="preserve">base_lt_mva</t>
         </is>
       </c>
       <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA</t>
+        </is>
+      </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
+          <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -4013,24 +4029,20 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV tap</t>
+          <t xml:space="preserve">X/R</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tap</t>
+          <t xml:space="preserve">x_r</t>
         </is>
       </c>
       <c r="D73" s="8"/>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
+          <t xml:space="preserve">each impedance</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -4047,24 +4059,20 @@
       </c>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel units</t>
+          <t xml:space="preserve">Load loss kW</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">count</t>
+          <t xml:space="preserve">load_loss_kw</t>
         </is>
       </c>
       <c r="D74" s="8"/>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E74" s="8"/>
       <c r="F74" s="8"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical units (blank = 1)</t>
+          <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -4081,24 +4089,20 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">No-load loss %</t>
+          <t xml:space="preserve">Vector group</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">nll_pct</t>
+          <t xml:space="preserve">vector</t>
         </is>
       </c>
       <c r="D75" s="8"/>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
+      <c r="E75" s="8"/>
       <c r="F75" s="8"/>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">of MVA (blank = 0)</t>
+          <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
@@ -4115,24 +4119,24 @@
       </c>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnetising current %</t>
+          <t xml:space="preserve">HV tap</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">im_pct</t>
+          <t xml:space="preserve">tap</t>
         </is>
       </c>
       <c r="D76" s="8"/>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">of MVA (blank = 0)</t>
+          <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
@@ -4149,24 +4153,24 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rating MVA</t>
+          <t xml:space="preserve">Parallel units</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_mva</t>
+          <t xml:space="preserve">count</t>
         </is>
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVA</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77" s="8"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = MVA</t>
+          <t xml:space="preserve">identical units (blank = 1)</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -4183,24 +4187,24 @@
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length</t>
+          <t xml:space="preserve">No-load loss %</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_length</t>
+          <t xml:space="preserve">nll_pct</t>
         </is>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+          <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -4217,29 +4221,33 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie length unit</t>
+          <t xml:space="preserve">Magnetising current %</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_unit</t>
+          <t xml:space="preserve">im_pct</t>
         </is>
       </c>
       <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G79" s="8"/>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">of MVA (blank = 0)</t>
+        </is>
+      </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="30.0" customHeight="1">
+    <row r="80" ht="17.0" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -4247,96 +4255,92 @@
       </c>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie values per</t>
+          <t xml:space="preserve">Tie length</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_per_unit</t>
+          <t xml:space="preserve">tie_length</t>
         </is>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km or mi, whichever matches a line of its kV</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
+        </is>
+      </c>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="17.0" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tie length unit</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_unit</t>
+        </is>
+      </c>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">km | mi | kft | m | ft</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
-        </is>
-      </c>
-      <c r="H80" s="13" t="inlineStr">
+      <c r="G81" s="8"/>
+      <c r="H81" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="30.0" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+    <row r="82" ht="30.0" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tie R per length</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tie_r_per</t>
-        </is>
-      </c>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a typical overhead line of the HV kV</t>
-        </is>
-      </c>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
-        </is>
-      </c>
-      <c r="H81" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="17.0" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MPT</t>
-        </is>
-      </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie X per length</t>
+          <t xml:space="preserve">Tie values per</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_x_per</t>
+          <t xml:space="preserve">tie_per_unit</t>
         </is>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">typical</t>
-        </is>
-      </c>
-      <c r="F82" s="8"/>
+          <t xml:space="preserve">km or mi, whichever matches a line of its kV</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm (blank = typical)</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
@@ -4345,7 +4349,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="17.0" customHeight="1">
+    <row r="83" ht="30.0" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -4353,24 +4357,24 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie B per length</t>
+          <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_b_per</t>
+          <t xml:space="preserve">tie_r_per</t>
         </is>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">typical</t>
+          <t xml:space="preserve">a typical overhead line of the HV kV</t>
         </is>
       </c>
       <c r="F83" s="8"/>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS (blank = typical)</t>
+          <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -4387,12 +4391,12 @@
       </c>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tie rating MVA</t>
+          <t xml:space="preserve">Tie X per length</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tie_rate_mva</t>
+          <t xml:space="preserve">tie_x_per</t>
         </is>
       </c>
       <c r="D84" s="8"/>
@@ -4404,7 +4408,7 @@
       <c r="F84" s="8"/>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = typical</t>
+          <t xml:space="preserve">ohm (blank = typical)</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -4413,83 +4417,87 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generators</t>
-        </is>
-      </c>
-      <c r="B85" s="7"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
+    <row r="85" ht="17.0" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPT</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tie B per length</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tie_b_per</t>
+        </is>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uS (blank = typical)</t>
+        </is>
+      </c>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="17.0" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generators</t>
+          <t xml:space="preserve">MPT</t>
         </is>
       </c>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Tie rating MVA</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">tie_rate_mva</t>
         </is>
       </c>
       <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">typical</t>
+        </is>
+      </c>
       <c r="F86" s="8"/>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
+          <t xml:space="preserve">blank = typical</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30.0" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
-        </is>
-      </c>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
-        </is>
-      </c>
-      <c r="H87" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
     </row>
     <row r="88" ht="17.0" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
@@ -4499,24 +4507,20 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine ID</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D88" s="8"/>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E88" s="8"/>
       <c r="F88" s="8"/>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">generator name. Its buses: &lt;name&gt;:MV (GSU HV), &lt;name&gt; or &lt;name&gt;:LV (terminal)</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
@@ -4525,7 +4529,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="17.0" customHeight="1">
+    <row r="89" ht="30.0" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4533,20 +4537,24 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Type</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PV | BESS | WT4 | WT3 | SYNC | USER</t>
+        </is>
+      </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
+          <t xml:space="preserve">PV BESS WT4 WT3 SYNC USER (USER: Dyr_Records only)</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
@@ -4563,20 +4571,24 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F90" s="8"/>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number of units</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4593,24 +4605,20 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit MVA</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_mva</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D91" s="8"/>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from P and Q</t>
-        </is>
-      </c>
+      <c r="E91" s="8"/>
       <c r="F91" s="8"/>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit (blank = from P and Q)</t>
+          <t xml:space="preserve">the bus its collector starts from: MPT1 (LV), MPT1:TV, a shared collector, HV, POI</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -4627,18 +4635,22 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmax MW</t>
+          <t xml:space="preserve">Units</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmax_mw</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number of units</t>
+        </is>
+      </c>
       <c r="H92" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -4653,24 +4665,24 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Pmin MW</t>
+          <t xml:space="preserve">Unit MVA</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pmin_mw</t>
+          <t xml:space="preserve">unit_mva</t>
         </is>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">from P and Q</t>
         </is>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
+          <t xml:space="preserve">one unit (blank = from P and Q)</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
@@ -4687,26 +4699,18 @@
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmax MVAr</t>
+          <t xml:space="preserve">Unit Pmax MW</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmax_mvar</t>
+          <t xml:space="preserve">unit_pmax_mw</t>
         </is>
       </c>
       <c r="D94" s="8"/>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from Unit PF</t>
-        </is>
-      </c>
+      <c r="E94" s="8"/>
       <c r="F94" s="8"/>
-      <c r="G94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = from Unit PF</t>
-        </is>
-      </c>
+      <c r="G94" s="8"/>
       <c r="H94" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -4721,24 +4725,24 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Qmin MVAr</t>
+          <t xml:space="preserve">Unit Pmin MW</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_qmin_mvar</t>
+          <t xml:space="preserve">unit_pmin_mw</t>
         </is>
       </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Qmax</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F95" s="8"/>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = -Qmax</t>
+          <t xml:space="preserve">BESS charging: negative (blank = 0)</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
@@ -4755,24 +4759,24 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit PF</t>
+          <t xml:space="preserve">Unit Qmax MVAr</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_pf</t>
+          <t xml:space="preserve">unit_qmax_mvar</t>
         </is>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95</t>
+          <t xml:space="preserve">from Unit PF</t>
         </is>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
+          <t xml:space="preserve">blank = from Unit PF</t>
         </is>
       </c>
       <c r="H96" s="13" t="inlineStr">
@@ -4789,24 +4793,24 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminal kV</t>
+          <t xml:space="preserve">Unit Qmin MVAr</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kv</t>
+          <t xml:space="preserve">unit_qmin_mvar</t>
         </is>
       </c>
       <c r="D97" s="8"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">-Qmax</t>
         </is>
       </c>
       <c r="F97" s="8"/>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = GSU LV kV</t>
+          <t xml:space="preserve">blank = -Qmax</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
@@ -4815,7 +4819,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="30.0" customHeight="1">
+    <row r="98" ht="17.0" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4823,24 +4827,24 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dispatch MW</t>
+          <t xml:space="preserve">Unit PF</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">dispatch_mw</t>
+          <t xml:space="preserve">unit_pf</t>
         </is>
       </c>
       <c r="D98" s="8"/>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax (BESS charging: negative</t>
+          <t xml:space="preserve">0.95</t>
         </is>
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
+          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
         </is>
       </c>
       <c r="H98" s="13" t="inlineStr">
@@ -4857,28 +4861,24 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode</t>
+          <t xml:space="preserve">Terminal kV</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mode</t>
+          <t xml:space="preserve">kv</t>
         </is>
       </c>
       <c r="D99" s="8"/>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">share</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share | fixed</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GSU LV kV</t>
+        </is>
+      </c>
+      <c r="F99" s="8"/>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q (blank = share)</t>
+          <t xml:space="preserve">blank = GSU LV kV</t>
         </is>
       </c>
       <c r="H99" s="13" t="inlineStr">
@@ -4887,7 +4887,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="17.0" customHeight="1">
+    <row r="100" ht="30.0" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4895,24 +4895,24 @@
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Dispatch MW</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_q_mvar</t>
+          <t xml:space="preserve">dispatch_mw</t>
         </is>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Pmax (BESS charging: negative</t>
         </is>
       </c>
       <c r="F100" s="8"/>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
+          <t xml:space="preserve">this generator's total; blank = Pmax (BESS charging: negative)</t>
         </is>
       </c>
       <c r="H100" s="13" t="inlineStr">
@@ -4929,20 +4929,28 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed PF</t>
+          <t xml:space="preserve">Q mode</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed_pf</t>
+          <t xml:space="preserve">q_mode</t>
         </is>
       </c>
       <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">share</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">share | fixed</t>
+        </is>
+      </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
+          <t xml:space="preserve">share: holds the POI with the other share generators | fixed: its own Q (blank = share)</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
@@ -4959,24 +4967,24 @@
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU count</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_count</t>
+          <t xml:space="preserve">fixed_q_mvar</t>
         </is>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = Units</t>
+          <t xml:space="preserve">Q mode fixed (blank = 0)</t>
         </is>
       </c>
       <c r="H102" s="13" t="inlineStr">
@@ -4985,7 +4993,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="30.0" customHeight="1">
+    <row r="103" ht="17.0" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4993,24 +5001,20 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU MVA</t>
+          <t xml:space="preserve">Fixed PF</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_mva</t>
+          <t xml:space="preserve">fixed_pf</t>
         </is>
       </c>
       <c r="D103" s="8"/>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no GSU (units on the MV bus</t>
-        </is>
-      </c>
+      <c r="E103" s="8"/>
       <c r="F103" s="8"/>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
+          <t xml:space="preserve">Q mode fixed, instead of Fixed Q (+ lagging)</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
@@ -5027,25 +5031,33 @@
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV kV</t>
+          <t xml:space="preserve">Units per GSU</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_hv_kv</t>
+          <t xml:space="preserve">gsu_units</t>
         </is>
       </c>
       <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units / GSU count</t>
+        </is>
+      </c>
       <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the units on one GSU (blank = Units / GSU count; both blank: 1)</t>
+        </is>
+      </c>
       <c r="H104" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="17.0" customHeight="1">
+    <row r="105" ht="43.0" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5053,25 +5065,33 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU LV kV</t>
+          <t xml:space="preserve">GSU count</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_lv_kv</t>
+          <t xml:space="preserve">gsu_count</t>
         </is>
       </c>
       <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units / Units per GSU, rounded up (that blank too: Units, a GSU each</t>
+        </is>
+      </c>
       <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = Units / Units per GSU, rounded up (that blank too: Units, a GSU each)</t>
+        </is>
+      </c>
       <c r="H105" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="17.0" customHeight="1">
+    <row r="106" ht="30.0" customHeight="1">
       <c r="A106" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5079,20 +5099,24 @@
       </c>
       <c r="B106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU Z %</t>
+          <t xml:space="preserve">GSU MVA</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_z_pct</t>
+          <t xml:space="preserve">gsu_mva</t>
         </is>
       </c>
       <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no GSU (units on the MV bus</t>
+        </is>
+      </c>
       <c r="F106" s="8"/>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on GSU MVA</t>
+          <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
         </is>
       </c>
       <c r="H106" s="13" t="inlineStr">
@@ -5109,21 +5133,29 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU X/R</t>
+          <t xml:space="preserve">GSU Rate A MVA</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_x_r</t>
+          <t xml:space="preserve">gsu_rate_a_mva</t>
         </is>
       </c>
       <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSU MVA</t>
+        </is>
+      </c>
       <c r="F107" s="8"/>
-      <c r="G107" s="8"/>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one GSU's normal rating: RATEA, rate1 (blank = GSU MVA)</t>
+        </is>
+      </c>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -5135,21 +5167,29 @@
       </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU vector group</t>
+          <t xml:space="preserve">GSU Rate B MVA</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_vector</t>
+          <t xml:space="preserve">gsu_rate_b_mva</t>
         </is>
       </c>
       <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate A</t>
+        </is>
+      </c>
       <c r="F108" s="8"/>
-      <c r="G108" s="8"/>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one GSU's emergency rating: RATEB, rate2 (blank = Rate A)</t>
+        </is>
+      </c>
       <c r="H108" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -5161,33 +5201,33 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSU HV tap</t>
+          <t xml:space="preserve">GSU Rate C MVA</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gsu_tap</t>
+          <t xml:space="preserve">gsu_rate_c_mva</t>
         </is>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">Rate B</t>
         </is>
       </c>
       <c r="F109" s="8"/>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">one GSU's: RATEC, rate3 (blank = Rate B)</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="56.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="17.0" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5195,30 +5235,18 @@
       </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">GSU HV kV</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">gsu_hv_kv</t>
         </is>
       </c>
       <c r="D110" s="8"/>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS where Feeders has rows for it, else EQUIVALENT where Collector X is given, else NONE</t>
-        </is>
-      </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE (blank = FEEDERS where Feeders has rows for it, else EQUIVALENT where Collector X is given, else NONE)</t>
-        </is>
-      </c>
+      <c r="E110" s="8"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8"/>
       <c r="H110" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5233,22 +5261,18 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector R</t>
+          <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_r</t>
+          <t xml:space="preserve">gsu_lv_kv</t>
         </is>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIVALENT</t>
-        </is>
-      </c>
+      <c r="G111" s="8"/>
       <c r="H111" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5263,12 +5287,12 @@
       </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector X</t>
+          <t xml:space="preserve">GSU Z %</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_x</t>
+          <t xml:space="preserve">gsu_z_pct</t>
         </is>
       </c>
       <c r="D112" s="8"/>
@@ -5276,7 +5300,7 @@
       <c r="F112" s="8"/>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EQUIVALENT</t>
+          <t xml:space="preserve">on GSU MVA</t>
         </is>
       </c>
       <c r="H112" s="13" t="inlineStr">
@@ -5293,22 +5317,18 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector B</t>
+          <t xml:space="preserve">GSU X/R</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_b</t>
+          <t xml:space="preserve">gsu_x_r</t>
         </is>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EQUIVALENT, total charging</t>
-        </is>
-      </c>
+      <c r="G113" s="8"/>
       <c r="H113" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5323,30 +5343,18 @@
       </c>
       <c r="B114" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector units</t>
+          <t xml:space="preserve">GSU vector group</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">coll_units</t>
+          <t xml:space="preserve">gsu_vector</t>
         </is>
       </c>
       <c r="D114" s="8"/>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu | ohm</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS (blank = pu)</t>
-        </is>
-      </c>
+      <c r="E114" s="8"/>
+      <c r="F114" s="8"/>
+      <c r="G114" s="8"/>
       <c r="H114" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5361,29 +5369,33 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZSORCE X pu</t>
+          <t xml:space="preserve">GSU HV tap</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zsorce_x</t>
+          <t xml:space="preserve">gsu_tap</t>
         </is>
       </c>
       <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F115" s="8"/>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H115" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="56.0" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5391,29 +5403,37 @@
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WMOD</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wmod</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEEDERS where Feeders has rows for it, else EQUIVALENT where Collector X is given, else NONE</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEEDERS | EQUIVALENT | NONE</t>
+        </is>
+      </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
+          <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE (blank = FEEDERS where Feeders has rows for it, else EQUIVALENT where Collector X is given, else NONE)</t>
         </is>
       </c>
       <c r="H116" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="43.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="17.0" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5421,37 +5441,29 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converter model</t>
+          <t xml:space="preserve">Collector R</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">regc</t>
+          <t xml:space="preserve">coll_r</t>
         </is>
       </c>
       <c r="D117" s="8"/>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REGC_A</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REGC_A | REGC_B</t>
-        </is>
-      </c>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGC_A: a current source, the standard | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (ZSORCE X its Xe) -- PV, BESS, WT4; .dyr REGCA1 / REGCBU1, .dyd regc_a / regc_b (blank = REGC_A)</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="17.0" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5459,33 +5471,25 @@
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical control</t>
+          <t xml:space="preserve">Collector X</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">reec</t>
+          <t xml:space="preserve">coll_x</t>
         </is>
       </c>
       <c r="D118" s="8"/>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
-        </is>
-      </c>
+      <c r="E118" s="8"/>
+      <c r="F118" s="8"/>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REEC_A: PV, WT | REEC_C: BESS (state of charge) | REEC_D: PV, BESS, WT4, the newest (voltage-dependent limits, momentary cessation) -- .dyr and .dyd alike (blank = REEC_A, BESS REEC_C)</t>
+          <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
       <c r="H118" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5497,29 +5501,25 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD library</t>
+          <t xml:space="preserve">Collector B</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_library</t>
+          <t xml:space="preserve">coll_b</t>
         </is>
       </c>
       <c r="D119" s="8"/>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
+      <c r="E119" s="8"/>
       <c r="F119" s="8"/>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
+          <t xml:space="preserve">EQUIVALENT, total charging</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5531,29 +5531,33 @@
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD definition</t>
+          <t xml:space="preserve">Collector units</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_definition</t>
+          <t xml:space="preserve">coll_units</t>
         </is>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a source: network check</t>
-        </is>
-      </c>
-      <c r="F120" s="8"/>
+          <t xml:space="preserve">pu</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pu | ohm</t>
+        </is>
+      </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
+          <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS (blank = pu)</t>
         </is>
       </c>
       <c r="H120" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -5565,33 +5569,29 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD AC port</t>
+          <t xml:space="preserve">ZSORCE X pu</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_ac_port</t>
+          <t xml:space="preserve">zsorce_x</t>
         </is>
       </c>
       <c r="D121" s="8"/>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its 3-phase port</t>
-        </is>
-      </c>
+      <c r="E121" s="8"/>
       <c r="F121" s="8"/>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+          <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="17.0" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5599,12 +5599,12 @@
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD source case</t>
+          <t xml:space="preserve">WMOD</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_source</t>
+          <t xml:space="preserve">wmod</t>
         </is>
       </c>
       <c r="D122" s="8"/>
@@ -5612,16 +5612,16 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
+          <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="43.0" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5629,29 +5629,33 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD component ID</t>
+          <t xml:space="preserve">Converter model</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_component_id</t>
+          <t xml:space="preserve">regc</t>
         </is>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="F123" s="8"/>
+          <t xml:space="preserve">REGC_A</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGC_A | REGC_B</t>
+        </is>
+      </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
+          <t xml:space="preserve">REGC_A: a current source, the standard | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (ZSORCE X its Xe) -- PV, BESS, WT4; .dyr REGCA1 / REGCBU1, .dyd regc_a / regc_b (blank = REGC_A)</t>
         </is>
       </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -5663,237 +5667,253 @@
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD inverter at</t>
+          <t xml:space="preserve">Electrical control</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_inv_at</t>
+          <t xml:space="preserve">reec</t>
         </is>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV</t>
+          <t xml:space="preserve">REEC_A, BESS REEC_C</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV | MV</t>
+          <t xml:space="preserve">REEC_A | REEC_C | REEC_D</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
+          <t xml:space="preserve">REEC_A: PV, WT | REEC_C: BESS (state of charge) | REEC_D: PV, BESS, WT4, the newest (voltage-dependent limits, momentary cessation) -- .dyr and .dyd alike (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="17.0" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD library</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_library</t>
+        </is>
+      </c>
+      <c r="D125" s="8"/>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F125" s="8"/>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
     </row>
     <row r="126" ht="17.0" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeders</t>
+          <t xml:space="preserve">Generators</t>
         </is>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">pscad_definition</t>
         </is>
       </c>
       <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a source: network check</t>
+        </is>
+      </c>
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
+          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
     <row r="127" ht="17.0" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeders</t>
+          <t xml:space="preserve">Generators</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeder</t>
+          <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">feeder</t>
+          <t xml:space="preserve">pscad_ac_port</t>
         </is>
       </c>
       <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its 3-phase port</t>
+        </is>
+      </c>
       <c r="F127" s="8"/>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">feeder name</t>
+          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="30.0" customHeight="1">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeders</t>
+          <t xml:space="preserve">Generators</t>
         </is>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copies</t>
+          <t xml:space="preserve">PSCAD source case</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">copies</t>
+          <t xml:space="preserve">pscad_source</t>
         </is>
       </c>
       <c r="D128" s="8"/>
-      <c r="E128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
+      <c r="E128" s="8"/>
       <c r="F128" s="8"/>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
+          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="30.0" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeders</t>
+          <t xml:space="preserve">Generators</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section</t>
+          <t xml:space="preserve">PSCAD component ID</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">section</t>
+          <t xml:space="preserve">pscad_component_id</t>
         </is>
       </c>
       <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
+        </is>
+      </c>
       <c r="F129" s="8"/>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
     <row r="130" ht="30.0" customHeight="1">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeders</t>
+          <t xml:space="preserve">Generators</t>
         </is>
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">From section</t>
+          <t xml:space="preserve">PSCAD inverter at</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_section</t>
+          <t xml:space="preserve">pscad_inv_at</t>
         </is>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the one before (daisy chain</t>
-        </is>
-      </c>
-      <c r="F130" s="8"/>
+          <t xml:space="preserve">LV</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV | MV</t>
+        </is>
+      </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+          <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="17.0" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B131" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cable</t>
-        </is>
-      </c>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from Cables</t>
-        </is>
-      </c>
-      <c r="H131" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B131" s="7"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
     </row>
     <row r="132" ht="17.0" customHeight="1">
       <c r="A132" s="8" t="inlineStr">
@@ -5903,18 +5923,22 @@
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">length</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
-      <c r="G132" s="8"/>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
+        </is>
+      </c>
       <c r="H132" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -5929,28 +5953,20 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Feeder</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">feeder</t>
         </is>
       </c>
       <c r="D133" s="8"/>
-      <c r="E133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+      <c r="E133" s="8"/>
+      <c r="F133" s="8"/>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = km</t>
+          <t xml:space="preserve">feeder name</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
@@ -5967,20 +5983,24 @@
       </c>
       <c r="B134" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units at end</t>
+          <t xml:space="preserve">Copies</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">copies</t>
         </is>
       </c>
       <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F134" s="8"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units tapped at the far end</t>
+          <t xml:space="preserve">identical feeders (blank = 1)</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
@@ -5997,12 +6017,12 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units of</t>
+          <t xml:space="preserve">Section</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units_of</t>
+          <t xml:space="preserve">section</t>
         </is>
       </c>
       <c r="D135" s="8"/>
@@ -6010,7 +6030,7 @@
       <c r="F135" s="8"/>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
+          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
         </is>
       </c>
       <c r="H135" s="13" t="inlineStr">
@@ -6019,7 +6039,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="17.0" customHeight="1">
+    <row r="136" ht="30.0" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -6027,24 +6047,24 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel cables</t>
+          <t xml:space="preserve">From section</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parallel</t>
+          <t xml:space="preserve">from_section</t>
         </is>
       </c>
       <c r="D136" s="8"/>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">the one before (daisy chain</t>
         </is>
       </c>
       <c r="F136" s="8"/>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6061,24 +6081,20 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R ohm</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_ohm</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D137" s="8"/>
-      <c r="E137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable x Length</t>
-        </is>
-      </c>
+      <c r="E137" s="8"/>
       <c r="F137" s="8"/>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
+          <t xml:space="preserve">from Cables</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
@@ -6095,26 +6111,18 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X ohm</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_ohm</t>
+          <t xml:space="preserve">length</t>
         </is>
       </c>
       <c r="D138" s="8"/>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable x Length</t>
-        </is>
-      </c>
+      <c r="E138" s="8"/>
       <c r="F138" s="8"/>
-      <c r="G138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
-        </is>
-      </c>
+      <c r="G138" s="8"/>
       <c r="H138" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -6129,24 +6137,28 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B uS</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_us</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable x Length</t>
-        </is>
-      </c>
-      <c r="F139" s="8"/>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
+          <t xml:space="preserve">blank = km</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
@@ -6155,34 +6167,50 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B140" s="7"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
+    <row r="140" ht="17.0" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Units at end</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">units</t>
+        </is>
+      </c>
+      <c r="D140" s="8"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="8"/>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">units tapped at the far end</t>
+        </is>
+      </c>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="17.0" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">Units of</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">units_of</t>
         </is>
       </c>
       <c r="D141" s="8"/>
@@ -6190,7 +6218,7 @@
       <c r="F141" s="8"/>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable type</t>
+          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
@@ -6202,29 +6230,29 @@
     <row r="142" ht="17.0" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">Parallel cables</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">parallel</t>
         </is>
       </c>
       <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+      <c r="E142" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F142" s="8"/>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -6236,25 +6264,29 @@
     <row r="143" ht="17.0" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R per length</t>
+          <t xml:space="preserve">R ohm</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_per</t>
+          <t xml:space="preserve">r_ohm</t>
         </is>
       </c>
       <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
       <c r="F143" s="8"/>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
+          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr">
@@ -6266,25 +6298,29 @@
     <row r="144" ht="17.0" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">X ohm</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">x_ohm</t>
         </is>
       </c>
       <c r="D144" s="8"/>
-      <c r="E144" s="8"/>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
       <c r="F144" s="8"/>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
@@ -6296,25 +6332,29 @@
     <row r="145" ht="17.0" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">B uS</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">b_us</t>
         </is>
       </c>
       <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
+      <c r="E145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
       <c r="F145" s="8"/>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H145" s="13" t="inlineStr">
@@ -6323,72 +6363,76 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="17.0" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B146" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B per length</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b_per</t>
-        </is>
-      </c>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
-      <c r="G146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">uS, instead of C</t>
-        </is>
-      </c>
-      <c r="H146" s="13" t="inlineStr">
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+    </row>
+    <row r="147" ht="17.0" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cable</t>
+        </is>
+      </c>
+      <c r="D147" s="8"/>
+      <c r="E147" s="8"/>
+      <c r="F147" s="8"/>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cable type</t>
+        </is>
+      </c>
+      <c r="H147" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
-    </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B147" s="7"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
     </row>
     <row r="148" ht="17.0" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
-      <c r="F148" s="8"/>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
+          <t xml:space="preserve">the values are per</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
@@ -6400,17 +6444,17 @@
     <row r="149" ht="17.0" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D149" s="8"/>
@@ -6418,7 +6462,7 @@
       <c r="F149" s="8"/>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H149" s="13" t="inlineStr">
@@ -6427,50 +6471,58 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loads_Shunts</t>
-        </is>
-      </c>
-      <c r="B150" s="7"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-      <c r="G150" s="7"/>
-      <c r="H150" s="7"/>
+    <row r="150" ht="17.0" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X per length</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x_per</t>
+        </is>
+      </c>
+      <c r="D150" s="8"/>
+      <c r="E150" s="8"/>
+      <c r="F150" s="8"/>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ohm</t>
+        </is>
+      </c>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="17.0" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t xml:space="preserve">C per length</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">c_per</t>
         </is>
       </c>
       <c r="D151" s="8"/>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD</t>
-        </is>
-      </c>
-      <c r="F151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
+      <c r="E151" s="8"/>
+      <c r="F151" s="8"/>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor (blank = LOAD)</t>
+          <t xml:space="preserve">uF</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -6482,17 +6534,17 @@
     <row r="152" ht="17.0" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">At bus</t>
+          <t xml:space="preserve">B per length</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at</t>
+          <t xml:space="preserve">b_per</t>
         </is>
       </c>
       <c r="D152" s="8"/>
@@ -6500,7 +6552,7 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+          <t xml:space="preserve">uS, instead of C</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -6509,96 +6561,112 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="17.0" customHeight="1">
+    <row r="153" ht="30.0" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MW</t>
+          <t xml:space="preserve">Rate A MVA</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mw</t>
+          <t xml:space="preserve">rate_a_mva</t>
         </is>
       </c>
       <c r="D153" s="8"/>
-      <c r="E153" s="8"/>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
       <c r="F153" s="8"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
+          <t xml:space="preserve">one cable's normal rating at its collector's kV (sqrt(3) x kV x amps / 1000): RATEA, rate1 -- a section's: x its parallel cables (blank = none)</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
     <row r="154" ht="17.0" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">Rate B MVA</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">rate_b_mva</t>
         </is>
       </c>
       <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate A</t>
+        </is>
+      </c>
       <c r="F154" s="8"/>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">one cable's emergency rating: RATEB, rate2 (blank = Rate A)</t>
         </is>
       </c>
       <c r="H154" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
     <row r="155" ht="17.0" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Rate C MVA</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">rate_c_mva</t>
         </is>
       </c>
       <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate B</t>
+        </is>
+      </c>
       <c r="F155" s="8"/>
-      <c r="G155" s="8"/>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one cable's: RATEC, rate3 (blank = Rate B)</t>
+        </is>
+      </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B156" s="7"/>
@@ -6609,20 +6677,20 @@
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" ht="30.0" customHeight="1">
+    <row r="157" ht="17.0" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">machine</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D157" s="8"/>
@@ -6630,7 +6698,7 @@
       <c r="F157" s="8"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
+          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
@@ -6642,29 +6710,25 @@
     <row r="158" ht="17.0" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine ID</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D158" s="8"/>
-      <c r="E158" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its generator's</t>
-        </is>
-      </c>
+      <c r="E158" s="8"/>
       <c r="F158" s="8"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its generator's</t>
+          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
@@ -6673,66 +6737,50 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="30.0" customHeight="1">
-      <c r="A159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B159" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pgen MW</t>
-        </is>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pgen_mw</t>
-        </is>
-      </c>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
-        </is>
-      </c>
-      <c r="F159" s="8"/>
-      <c r="G159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
-        </is>
-      </c>
-      <c r="H159" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B159" s="7"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
     </row>
     <row r="160" ht="17.0" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax MW</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmax_mw</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmax</t>
-        </is>
-      </c>
-      <c r="F160" s="8"/>
+          <t xml:space="preserve">LOAD</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor (blank = LOAD)</t>
         </is>
       </c>
       <c r="H160" s="13" t="inlineStr">
@@ -6744,29 +6792,25 @@
     <row r="161" ht="17.0" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmin MW</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmin_mw</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D161" s="8"/>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its units x Unit Pmin</t>
-        </is>
-      </c>
+      <c r="E161" s="8"/>
       <c r="F161" s="8"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
@@ -6778,29 +6822,25 @@
     <row r="162" ht="17.0" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B162" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmax MVAr</t>
+          <t xml:space="preserve">MW</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmax_mvar</t>
+          <t xml:space="preserve">mw</t>
         </is>
       </c>
       <c r="D162" s="8"/>
-      <c r="E162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its units x Unit Qmax</t>
-        </is>
-      </c>
+      <c r="E162" s="8"/>
       <c r="F162" s="8"/>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
         </is>
       </c>
       <c r="H162" s="13" t="inlineStr">
@@ -6812,29 +6852,25 @@
     <row r="163" ht="17.0" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmin MVAr</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmin_mvar</t>
+          <t xml:space="preserve">mvar</t>
         </is>
       </c>
       <c r="D163" s="8"/>
-      <c r="E163" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its units x Unit Qmin</t>
-        </is>
-      </c>
+      <c r="E163" s="8"/>
       <c r="F163" s="8"/>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
         </is>
       </c>
       <c r="H163" s="13" t="inlineStr">
@@ -6843,110 +6879,102 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="30.0" customHeight="1">
+    <row r="164" ht="17.0" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D164" s="8"/>
+      <c r="E164" s="8"/>
+      <c r="F164" s="8"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B164" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
-        </is>
-      </c>
-      <c r="C164" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">q_mvar</t>
-        </is>
-      </c>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">as its generator's Q mode</t>
-        </is>
-      </c>
-      <c r="F164" s="8"/>
-      <c r="G164" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
-        </is>
-      </c>
-      <c r="H164" s="13" t="inlineStr">
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
+      <c r="H165" s="7"/>
+    </row>
+    <row r="166" ht="30.0" customHeight="1">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine</t>
+        </is>
+      </c>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
+      <c r="D166" s="8"/>
+      <c r="E166" s="8"/>
+      <c r="F166" s="8"/>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
+        </is>
+      </c>
+      <c r="H166" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
-    </row>
-    <row r="165" ht="17.0" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B165" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MBASE MVA</t>
-        </is>
-      </c>
-      <c r="C165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mbase_mva</t>
-        </is>
-      </c>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its units x Unit MVA</t>
-        </is>
-      </c>
-      <c r="F165" s="8"/>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = its units x Unit MVA</t>
-        </is>
-      </c>
-      <c r="H165" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B166" s="7"/>
-      <c r="C166" s="7"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
-      <c r="G166" s="7"/>
-      <c r="H166" s="7"/>
     </row>
     <row r="167" ht="17.0" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bus</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its generator's</t>
+        </is>
+      </c>
       <c r="F167" s="8"/>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H167" s="13" t="inlineStr">
@@ -6955,32 +6983,32 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="17.0" customHeight="1">
+    <row r="168" ht="30.0" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B168" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H168" s="13" t="inlineStr">
@@ -6989,32 +7017,32 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="30.0" customHeight="1">
+    <row r="169" ht="17.0" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Pmax MW</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">pmax_mw</t>
         </is>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
+          <t xml:space="preserve">its units x Unit Pmax</t>
         </is>
       </c>
       <c r="F169" s="8"/>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
         </is>
       </c>
       <c r="H169" s="13" t="inlineStr">
@@ -7023,140 +7051,180 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B170" s="7"/>
-      <c r="C170" s="7"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
-      <c r="G170" s="7"/>
-      <c r="H170" s="7"/>
+    <row r="170" ht="17.0" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B170" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pmin MW</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pmin_mw</t>
+        </is>
+      </c>
+      <c r="D170" s="8"/>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Pmin</t>
+        </is>
+      </c>
+      <c r="F170" s="8"/>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+        </is>
+      </c>
+      <c r="H170" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="17.0" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Qmax</t>
+        </is>
+      </c>
       <c r="F171" s="8"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="17.0" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Model</t>
+          <t xml:space="preserve">Qmin MVAr</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">model</t>
+          <t xml:space="preserve">qmin_mvar</t>
         </is>
       </c>
       <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Qmin</t>
+        </is>
+      </c>
       <c r="F172" s="8"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="30.0" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">q_mvar</t>
         </is>
       </c>
       <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as its generator's Q mode</t>
+        </is>
+      </c>
       <c r="F173" s="8"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
         </is>
       </c>
       <c r="H173" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="174" ht="17.0" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">MBASE MVA</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">mbase_mva</t>
         </is>
       </c>
       <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit MVA</t>
+        </is>
+      </c>
       <c r="F174" s="8"/>
-      <c r="G174" s="8"/>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit MVA</t>
+        </is>
+      </c>
       <c r="H174" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B175" s="7"/>
@@ -7170,121 +7238,129 @@
     <row r="176" ht="17.0" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Bus</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">bus</t>
         </is>
       </c>
       <c r="D176" s="8"/>
-      <c r="E176" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the plant</t>
-        </is>
-      </c>
+      <c r="E176" s="8"/>
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the plant</t>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
         </is>
       </c>
       <c r="H176" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="177" ht="17.0" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record</t>
+          <t xml:space="preserve">Number</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">record</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic</t>
+        </is>
+      </c>
       <c r="F177" s="8"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
+          <t xml:space="preserve">blank = automatic</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="18" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B178" s="7"/>
-      <c r="C178" s="7"/>
-      <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
-      <c r="F178" s="7"/>
-      <c r="G178" s="7"/>
-      <c r="H178" s="7"/>
-    </row>
-    <row r="179" ht="17.0" customHeight="1">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B179" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generator</t>
-        </is>
-      </c>
-      <c r="C179" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generator</t>
-        </is>
-      </c>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
-      <c r="G179" s="8"/>
-      <c r="H179" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="30.0" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D178" s="8"/>
+      <c r="E178" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
+      <c r="F178" s="8"/>
+      <c r="G178" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
+        </is>
+      </c>
+      <c r="H178" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
+      <c r="G179" s="7"/>
+      <c r="H179" s="7"/>
     </row>
     <row r="180" ht="17.0" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D180" s="8"/>
@@ -7292,29 +7368,29 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="30.0" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Model</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">model</t>
         </is>
       </c>
       <c r="D181" s="8"/>
@@ -7322,196 +7398,268 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
         </is>
       </c>
       <c r="H181" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
-        </is>
-      </c>
-      <c r="B182" s="7"/>
-      <c r="C182" s="7"/>
-      <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
-      <c r="F182" s="7"/>
-      <c r="G182" s="7"/>
-      <c r="H182" s="7"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="8"/>
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="17.0" customHeight="1">
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B182" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
+      <c r="D182" s="8"/>
+      <c r="E182" s="8"/>
+      <c r="F182" s="8"/>
+      <c r="G182" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
+        </is>
+      </c>
+      <c r="H182" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="17.0" customHeight="1">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C183" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D183" s="8"/>
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
-      <c r="G183" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H183" s="8"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="8"/>
-      <c r="B184" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POI</t>
-        </is>
-      </c>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
-      <c r="F184" s="8"/>
-      <c r="G184" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the point of interconnection</t>
-        </is>
-      </c>
-      <c r="H184" s="8"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="8"/>
+      <c r="G183" s="8"/>
+      <c r="H183" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="7"/>
+      <c r="H184" s="7"/>
+    </row>
+    <row r="185" ht="17.0" customHeight="1">
+      <c r="A185" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV</t>
-        </is>
-      </c>
-      <c r="C185" s="8"/>
+          <t xml:space="preserve">Generator</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator</t>
+        </is>
+      </c>
       <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
+      <c r="E185" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the plant</t>
+        </is>
+      </c>
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
-        </is>
-      </c>
-      <c r="H185" s="8"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="8"/>
+          <t xml:space="preserve">blank = the plant</t>
+        </is>
+      </c>
+      <c r="H185" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="17.0" customHeight="1">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Records</t>
+        </is>
+      </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
-        </is>
-      </c>
-      <c r="C186" s="8"/>
+          <t xml:space="preserve">Record</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">record</t>
+        </is>
+      </c>
       <c r="D186" s="8"/>
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
-        </is>
-      </c>
-      <c r="H186" s="8"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="8"/>
-      <c r="B187" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
-        </is>
-      </c>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
-      <c r="F187" s="8"/>
-      <c r="G187" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
-        </is>
-      </c>
-      <c r="H187" s="8"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="8"/>
+          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
+        </is>
+      </c>
+      <c r="H186" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B187" s="7"/>
+      <c r="C187" s="7"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
+    </row>
+    <row r="188" ht="17.0" customHeight="1">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
-        </is>
-      </c>
-      <c r="C188" s="8"/>
+          <t xml:space="preserve">Generator</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator</t>
+        </is>
+      </c>
       <c r="D188" s="8"/>
       <c r="E188" s="8"/>
       <c r="F188" s="8"/>
-      <c r="G188" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
-        </is>
-      </c>
-      <c r="H188" s="8"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="8"/>
+      <c r="G188" s="8"/>
+      <c r="H188" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="17.0" customHeight="1">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
-        </is>
-      </c>
-      <c r="C189" s="8"/>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
       <c r="F189" s="8"/>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
-        </is>
-      </c>
-      <c r="H189" s="8"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="8"/>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H189" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="17.0" customHeight="1">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B190" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
-        </is>
-      </c>
-      <c r="C190" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D190" s="8"/>
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
-        </is>
-      </c>
-      <c r="H190" s="8"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="8"/>
-      <c r="B191" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
-        </is>
-      </c>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
-      <c r="G191" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a generator's terminal</t>
-        </is>
-      </c>
-      <c r="H191" s="8"/>
+          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+        </is>
+      </c>
+      <c r="H190" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
+        </is>
+      </c>
+      <c r="B191" s="7"/>
+      <c r="C191" s="7"/>
+      <c r="D191" s="7"/>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="7"/>
+      <c r="H191" s="7"/>
     </row>
     <row r="192">
       <c r="A192" s="8"/>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C192" s="8"/>
@@ -7520,7 +7668,7 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H192" s="8"/>
@@ -7529,7 +7677,7 @@
       <c r="A193" s="8"/>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C193" s="8"/>
@@ -7538,34 +7686,34 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" ht="18" customHeight="1">
-      <c r="A194" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
-        </is>
-      </c>
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="7"/>
-      <c r="H194" s="7"/>
+    <row r="194">
+      <c r="A194" s="8"/>
+      <c r="B194" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HV</t>
+        </is>
+      </c>
+      <c r="C194" s="8"/>
+      <c r="D194" s="8"/>
+      <c r="E194" s="8"/>
+      <c r="F194" s="8"/>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
+        </is>
+      </c>
+      <c r="H194" s="8"/>
     </row>
     <row r="195">
-      <c r="A195" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A195" s="8"/>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNITS}</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -7574,24 +7722,16 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H195" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">an MPT's LV winding</t>
+        </is>
+      </c>
+      <c r="H195" s="8"/>
     </row>
     <row r="196">
-      <c r="A196" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A196" s="8"/>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -7600,24 +7740,16 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
-        </is>
-      </c>
-      <c r="H196" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+        </is>
+      </c>
+      <c r="H196" s="8"/>
     </row>
     <row r="197">
-      <c r="A197" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A197" s="8"/>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_MW}</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C197" s="8"/>
@@ -7626,24 +7758,16 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
-        </is>
-      </c>
-      <c r="H197" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+        </is>
+      </c>
+      <c r="H197" s="8"/>
     </row>
     <row r="198">
-      <c r="A198" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A198" s="8"/>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C198" s="8"/>
@@ -7652,24 +7776,16 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
-        </is>
-      </c>
-      <c r="H198" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">a shared collector's far end</t>
+        </is>
+      </c>
+      <c r="H198" s="8"/>
     </row>
     <row r="199">
-      <c r="A199" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A199" s="8"/>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C199" s="8"/>
@@ -7678,24 +7794,16 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
-        </is>
-      </c>
-      <c r="H199" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">a generator's GSU HV side</t>
+        </is>
+      </c>
+      <c r="H199" s="8"/>
     </row>
     <row r="200">
-      <c r="A200" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A200" s="8"/>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
         </is>
       </c>
       <c r="C200" s="8"/>
@@ -7704,24 +7812,16 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
-        </is>
-      </c>
-      <c r="H200" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">a generator's terminal</t>
+        </is>
+      </c>
+      <c r="H200" s="8"/>
     </row>
     <row r="201">
-      <c r="A201" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A201" s="8"/>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C201" s="8"/>
@@ -7730,24 +7830,16 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
-        </is>
-      </c>
-      <c r="H201" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H201" s="8"/>
     </row>
     <row r="202">
-      <c r="A202" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A202" s="8"/>
       <c r="B202" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
         </is>
       </c>
       <c r="C202" s="8"/>
@@ -7756,40 +7848,24 @@
       <c r="F202" s="8"/>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
-        </is>
-      </c>
-      <c r="H202" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B203" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
-        </is>
-      </c>
-      <c r="C203" s="8"/>
-      <c r="D203" s="8"/>
-      <c r="E203" s="8"/>
-      <c r="F203" s="8"/>
-      <c r="G203" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
-        </is>
-      </c>
-      <c r="H203" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+        </is>
+      </c>
+      <c r="H202" s="8"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
+        </is>
+      </c>
+      <c r="B203" s="7"/>
+      <c r="C203" s="7"/>
+      <c r="D203" s="7"/>
+      <c r="E203" s="7"/>
+      <c r="F203" s="7"/>
+      <c r="G203" s="7"/>
+      <c r="H203" s="7"/>
     </row>
     <row r="204">
       <c r="A204" s="8" t="inlineStr">
@@ -7799,7 +7875,7 @@
       </c>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C204" s="8"/>
@@ -7808,7 +7884,7 @@
       <c r="F204" s="8"/>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H204" s="13" t="inlineStr">
@@ -7825,7 +7901,7 @@
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C205" s="8"/>
@@ -7834,7 +7910,7 @@
       <c r="F205" s="8"/>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H205" s="13" t="inlineStr">
@@ -7851,7 +7927,7 @@
       </c>
       <c r="B206" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C206" s="8"/>
@@ -7860,7 +7936,7 @@
       <c r="F206" s="8"/>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H206" s="13" t="inlineStr">
@@ -7877,7 +7953,7 @@
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C207" s="8"/>
@@ -7886,7 +7962,7 @@
       <c r="F207" s="8"/>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H207" s="13" t="inlineStr">
@@ -7903,7 +7979,7 @@
       </c>
       <c r="B208" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C208" s="8"/>
@@ -7912,7 +7988,7 @@
       <c r="F208" s="8"/>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H208" s="13" t="inlineStr">
@@ -7929,7 +8005,7 @@
       </c>
       <c r="B209" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C209" s="8"/>
@@ -7938,7 +8014,7 @@
       <c r="F209" s="8"/>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H209" s="13" t="inlineStr">
@@ -7955,7 +8031,7 @@
       </c>
       <c r="B210" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C210" s="8"/>
@@ -7964,7 +8040,7 @@
       <c r="F210" s="8"/>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H210" s="13" t="inlineStr">
@@ -7981,7 +8057,7 @@
       </c>
       <c r="B211" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C211" s="8"/>
@@ -7990,10 +8066,244 @@
       <c r="F211" s="8"/>
       <c r="G211" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">one unit's P (MW)</t>
+        </is>
+      </c>
+      <c r="H211" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B212" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+        </is>
+      </c>
+      <c r="C212" s="8"/>
+      <c r="D212" s="8"/>
+      <c r="E212" s="8"/>
+      <c r="F212" s="8"/>
+      <c r="G212" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
+        </is>
+      </c>
+      <c r="H212" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B213" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_PU}</t>
+        </is>
+      </c>
+      <c r="C213" s="8"/>
+      <c r="D213" s="8"/>
+      <c r="E213" s="8"/>
+      <c r="F213" s="8"/>
+      <c r="G213" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
+        </is>
+      </c>
+      <c r="H213" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B214" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_KV}</t>
+        </is>
+      </c>
+      <c r="C214" s="8"/>
+      <c r="D214" s="8"/>
+      <c r="E214" s="8"/>
+      <c r="F214" s="8"/>
+      <c r="G214" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the same in kV</t>
+        </is>
+      </c>
+      <c r="H214" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B215" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{KV}</t>
+        </is>
+      </c>
+      <c r="C215" s="8"/>
+      <c r="D215" s="8"/>
+      <c r="E215" s="8"/>
+      <c r="F215" s="8"/>
+      <c r="G215" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">that bus's base kV</t>
+        </is>
+      </c>
+      <c r="H215" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B216" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{ANGLE}</t>
+        </is>
+      </c>
+      <c r="C216" s="8"/>
+      <c r="D216" s="8"/>
+      <c r="E216" s="8"/>
+      <c r="F216" s="8"/>
+      <c r="G216" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+        </is>
+      </c>
+      <c r="H216" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B217" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{FREQ}</t>
+        </is>
+      </c>
+      <c r="C217" s="8"/>
+      <c r="D217" s="8"/>
+      <c r="E217" s="8"/>
+      <c r="F217" s="8"/>
+      <c r="G217" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frequency (Hz)</t>
+        </is>
+      </c>
+      <c r="H217" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B218" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{P_INV_MW}</t>
+        </is>
+      </c>
+      <c r="C218" s="8"/>
+      <c r="D218" s="8"/>
+      <c r="E218" s="8"/>
+      <c r="F218" s="8"/>
+      <c r="G218" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+        </is>
+      </c>
+      <c r="H218" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B219" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
+        </is>
+      </c>
+      <c r="C219" s="8"/>
+      <c r="D219" s="8"/>
+      <c r="E219" s="8"/>
+      <c r="F219" s="8"/>
+      <c r="G219" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H219" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B220" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C220" s="8"/>
+      <c r="D220" s="8"/>
+      <c r="E220" s="8"/>
+      <c r="F220" s="8"/>
+      <c r="G220" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H211" s="13" t="inlineStr">
+      <c r="H220" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -8005,33 +8315,33 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A125:H125"/>
-    <mergeCell ref="A140:H140"/>
-    <mergeCell ref="A147:H147"/>
-    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A131:H131"/>
+    <mergeCell ref="A146:H146"/>
     <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A166:H166"/>
-    <mergeCell ref="A170:H170"/>
+    <mergeCell ref="A159:H159"/>
+    <mergeCell ref="A165:H165"/>
     <mergeCell ref="A175:H175"/>
-    <mergeCell ref="A178:H178"/>
-    <mergeCell ref="A182:H182"/>
-    <mergeCell ref="A194:H194"/>
+    <mergeCell ref="A179:H179"/>
+    <mergeCell ref="A184:H184"/>
+    <mergeCell ref="A187:H187"/>
+    <mergeCell ref="A191:H191"/>
+    <mergeCell ref="A203:H203"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
     <hyperlink ref="A55" location="'MPT'!A1" display="MPT"/>
-    <hyperlink ref="A85" location="'Generators'!A1" display="Generators"/>
-    <hyperlink ref="A125" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A140" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A147" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A150" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A156" location="'Machines'!A1" display="Machines"/>
-    <hyperlink ref="A166" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A170" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A175" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A178" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A194" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A87" location="'Generators'!A1" display="Generators"/>
+    <hyperlink ref="A131" location="'Feeders'!A1" display="Feeders"/>
+    <hyperlink ref="A146" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A156" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A159" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A165" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A175" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A179" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A184" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A187" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A203" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -20753,7 +21063,7 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
@@ -21534,6 +21844,8 @@
     <col min="27" max="27" width="10" customWidth="1"/>
     <col min="28" max="28" width="10" customWidth="1"/>
     <col min="29" max="29" width="10" customWidth="1"/>
+    <col min="30" max="30" width="10" customWidth="1"/>
+    <col min="31" max="31" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -21579,111 +21891,121 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rate A MVA</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate B MVA</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate C MVA</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Z HV-LV %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z HV-TV %</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z LV-TV %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z HV-LV base MVA</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z HV-TV base MVA</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Z LV-TV base MVA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">X/R</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Load loss kW</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Vector group</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">HV tap</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Parallel units</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No-load loss %</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Magnetising current %</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rating MVA</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie length</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie length unit</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie values per</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie R per length</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie X per length</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie B per length</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tie rating MVA</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="100.0" customHeight="1">
+    <row r="2" ht="132.0" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"># MPT name. Its buses: &lt;name&gt; or &lt;name&gt;:LV (LV winding), &lt;name&gt;:TV (tertiary)</t>
@@ -21703,7 +22025,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the rating (3 windings: HV winding)</t>
+          <t xml:space="preserve">the rating (3 windings: HV winding; blank = the MVA of the units on it, following them)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -21718,101 +22040,111 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">normal rating: PSS/E RATEA, PSLF rate1 (blank = MVA; 3 windings: the HV winding's, the LV and TV windings' their MVA)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emergency rating: RATEB, rate2 (blank = Rate A; 3 windings: the HV winding's, the LV and TV windings' in proportion)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RATEC, rate3 (blank = Rate B; 3 windings: as Rate B)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">on its base MVA</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3 windings</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3 windings</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = MVA</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">each impedance</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2 windings, at MVA: instead of X/R</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">YNd1, YNd11, Dyn1, YNyn0, YNd1d1 ...</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HV winding ratio, 1.025 = +2.5 % (blank = 1)</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">identical units (blank = 1)</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">of MVA (blank = 0)</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = MVA</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
         </is>
       </c>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm (blank = a typical overhead line of the HV kV)</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ohm (blank = typical)</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">uS (blank = typical)</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = typical</t>
         </is>
@@ -21842,32 +22174,32 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3">
-        <v>10.0</v>
+        <v>225.0</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>10.0</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="3">
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3">
         <v>45.0</v>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">YNd1</t>
         </is>
       </c>
-      <c r="R3" s="3">
+      <c r="U3" s="3">
         <v>1.0</v>
       </c>
-      <c r="S3" s="3">
+      <c r="V3" s="3">
         <v>1</v>
-      </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3">
-        <v>225.0</v>
       </c>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
@@ -21876,6 +22208,8 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3"/>
@@ -21907,6 +22241,8 @@
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
@@ -21938,6 +22274,8 @@
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3"/>
@@ -21969,6 +22307,8 @@
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3"/>
@@ -22000,6 +22340,8 @@
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3"/>
@@ -22031,6 +22373,8 @@
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3"/>
@@ -22062,6 +22406,8 @@
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
@@ -22093,6 +22439,8 @@
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3"/>
@@ -22124,6 +22472,8 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
@@ -22155,6 +22505,8 @@
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -22186,6 +22538,8 @@
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -22217,6 +22571,8 @@
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -22248,6 +22604,8 @@
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -22279,6 +22637,8 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -22310,6 +22670,8 @@
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -22341,6 +22703,8 @@
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -22372,6 +22736,8 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -22403,6 +22769,8 @@
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -22434,6 +22802,8 @@
       <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -22465,16 +22835,18 @@
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B500">
       <formula1>"2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X3:X500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z3:Z500">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y3:Y500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA3:AA500">
       <formula1>"km,mi,kft,m,ft"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22523,12 +22895,16 @@
     <col min="31" max="31" width="10" customWidth="1"/>
     <col min="32" max="32" width="10" customWidth="1"/>
     <col min="33" max="33" width="10" customWidth="1"/>
-    <col min="34" max="34" width="18" customWidth="1"/>
-    <col min="35" max="35" width="16" customWidth="1"/>
+    <col min="34" max="34" width="10" customWidth="1"/>
+    <col min="35" max="35" width="10" customWidth="1"/>
     <col min="36" max="36" width="10" customWidth="1"/>
-    <col min="37" max="37" width="18" customWidth="1"/>
-    <col min="38" max="38" width="10" customWidth="1"/>
-    <col min="39" max="39" width="10" customWidth="1"/>
+    <col min="37" max="37" width="10" customWidth="1"/>
+    <col min="38" max="38" width="18" customWidth="1"/>
+    <col min="39" max="39" width="16" customWidth="1"/>
+    <col min="40" max="40" width="10" customWidth="1"/>
+    <col min="41" max="41" width="18" customWidth="1"/>
+    <col min="42" max="42" width="10" customWidth="1"/>
+    <col min="43" max="43" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -22614,115 +22990,135 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Units per GSU</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">GSU count</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GSU MVA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSU Rate A MVA</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSU Rate B MVA</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GSU Rate C MVA</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GSU HV kV</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GSU LV kV</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GSU Z %</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GSU X/R</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GSU vector group</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">GSU HV tap</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Collector</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Collector R</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Collector X</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Collector B</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Collector units</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">ZSORCE X pu</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">WMOD</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Converter model</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Electrical control</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD source case</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD component ID</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD inverter at</t>
         </is>
@@ -22807,99 +23203,119 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = Units</t>
+          <t xml:space="preserve">the units on one GSU (blank = Units / GSU count; both blank: 1)</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">blank = Units / Units per GSU, rounded up (that blank too: Units, a GSU each)</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">one GSU; blank = no GSU (units on the MV bus)</t>
         </is>
       </c>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one GSU's normal rating: RATEA, rate1 (blank = GSU MVA)</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">one GSU's emergency rating: RATEB, rate2 (blank = Rate A)</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one GSU's: RATEC, rate3 (blank = Rate B)</t>
+        </is>
+      </c>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">on GSU MVA</t>
         </is>
       </c>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FEEDERS: WECC equivalent of its Feeders rows | EQUIVALENT: R X B here | NONE (blank = FEEDERS where Feeders has rows for it, else EQUIVALENT where Collector X is given, else NONE)</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIVALENT</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUIVALENT, total charging</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">pu: system base at collector kV | ohm: R X in ohm, B in uS (blank = pu)</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">on MBASE (blank: inverters 9999, SYNC X''d)</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blank: inverters 1, SYNC 0</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">REGC_A: a current source, the standard | REGC_B: a voltage source behind ZSORCE R + jX, for weak grids (ZSORCE X its Xe) -- PV, BESS, WT4; .dyr REGCA1 / REGCBU1, .dyd regc_a / regc_b (blank = REGC_A)</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">REEC_A: PV, WT | REEC_C: BESS (state of charge) | REEC_D: PV, BESS, WT4, the newest (voltage-dependent limits, momentary cessation) -- .dyr and .dyd alike (blank = REEC_A, BESS REEC_C)</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr">
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
@@ -22957,50 +23373,54 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
-      <c r="R3" s="3">
+      <c r="R3" s="3"/>
+      <c r="S3" s="3">
         <v>4.2</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3">
         <v>34.5</v>
       </c>
-      <c r="T3" s="3">
+      <c r="X3" s="3">
         <v>0.63</v>
       </c>
-      <c r="U3" s="3">
+      <c r="Y3" s="3">
         <v>6.5</v>
       </c>
-      <c r="V3" s="3">
+      <c r="Z3" s="3">
         <v>8.0</v>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">YNd1</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">FEEDERS</t>
         </is>
       </c>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
-      <c r="AG3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_A</t>
-        </is>
-      </c>
+      <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_A</t>
+        </is>
+      </c>
       <c r="AL3" s="3"/>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AM3" s="3"/>
+      <c r="AN3" s="3"/>
+      <c r="AO3" s="3"/>
+      <c r="AP3" s="3"/>
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">LV</t>
         </is>
@@ -23058,50 +23478,54 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
-      <c r="R4" s="3">
+      <c r="R4" s="3"/>
+      <c r="S4" s="3">
         <v>4.4</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3">
         <v>34.5</v>
       </c>
-      <c r="T4" s="3">
+      <c r="X4" s="3">
         <v>0.69</v>
       </c>
-      <c r="U4" s="3">
+      <c r="Y4" s="3">
         <v>6.0</v>
       </c>
-      <c r="V4" s="3">
+      <c r="Z4" s="3">
         <v>7.0</v>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">YNd1</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">FEEDERS</t>
         </is>
       </c>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">REEC_C</t>
-        </is>
-      </c>
+      <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
-      <c r="AK4" s="3"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REEC_C</t>
+        </is>
+      </c>
       <c r="AL4" s="3"/>
-      <c r="AM4" s="3" t="inlineStr">
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+      <c r="AO4" s="3"/>
+      <c r="AP4" s="3"/>
+      <c r="AQ4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">LV</t>
         </is>
@@ -23147,6 +23571,10 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
+      <c r="AN5" s="3"/>
+      <c r="AO5" s="3"/>
+      <c r="AP5" s="3"/>
+      <c r="AQ5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3"/>
@@ -23188,6 +23616,10 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3"/>
@@ -23229,6 +23661,10 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+      <c r="AO7" s="3"/>
+      <c r="AP7" s="3"/>
+      <c r="AQ7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3"/>
@@ -23270,6 +23706,10 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3"/>
@@ -23311,6 +23751,10 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+      <c r="AO9" s="3"/>
+      <c r="AP9" s="3"/>
+      <c r="AQ9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
@@ -23352,6 +23796,10 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
+      <c r="AQ10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3"/>
@@ -23393,6 +23841,10 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
@@ -23434,6 +23886,10 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="3"/>
+      <c r="AQ12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -23475,6 +23931,10 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
+      <c r="AN13" s="3"/>
+      <c r="AO13" s="3"/>
+      <c r="AP13" s="3"/>
+      <c r="AQ13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -23516,6 +23976,10 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="3"/>
+      <c r="AQ14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -23557,6 +24021,10 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -23598,6 +24066,10 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -23639,6 +24111,10 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
+      <c r="AN17" s="3"/>
+      <c r="AO17" s="3"/>
+      <c r="AP17" s="3"/>
+      <c r="AQ17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -23680,6 +24156,10 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
+      <c r="AQ18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -23721,6 +24201,10 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -23762,6 +24246,10 @@
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
+      <c r="AN20" s="3"/>
+      <c r="AO20" s="3"/>
+      <c r="AP20" s="3"/>
+      <c r="AQ20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -23803,6 +24291,10 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
       <c r="AM21" s="3"/>
+      <c r="AN21" s="3"/>
+      <c r="AO21" s="3"/>
+      <c r="AP21" s="3"/>
+      <c r="AQ21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -23844,6 +24336,10 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
       <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="3"/>
+      <c r="AQ22" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="7">
@@ -23853,19 +24349,19 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N3:N500">
       <formula1>"share,fixed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y3:Y500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC3:AC500">
       <formula1>"FEEDERS,EQUIVALENT,NONE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC3:AC500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AG3:AG500">
       <formula1>"pu,ohm"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF3:AF500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AJ3:AJ500">
       <formula1>"REGC_A,REGC_B"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AG3:AG500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AK3:AK500">
       <formula1>"REEC_A,REEC_C,REEC_D"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AM3:AM500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AQ3:AQ500">
       <formula1>"LV,MV"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24735,6 +25231,9 @@
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -24768,8 +25267,23 @@
           <t xml:space="preserve">B per length</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="40.0" customHeight="1">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate A MVA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate B MVA</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate C MVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="132.0" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"># cable type</t>
@@ -24798,6 +25312,21 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">uS, instead of C</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one cable's normal rating at its collector's kV (sqrt(3) x kV x amps / 1000): RATEA, rate1 -- a section's: x its parallel cables (blank = none)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one cable's emergency rating: RATEB, rate2 (blank = Rate A)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one cable's: RATEC, rate3 (blank = Rate B)</t>
         </is>
       </c>
     </row>
@@ -24822,6 +25351,9 @@
         <v>0.39</v>
       </c>
       <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -24844,6 +25376,9 @@
         <v>0.3</v>
       </c>
       <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -24866,6 +25401,9 @@
         <v>0.22</v>
       </c>
       <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -24888,6 +25426,9 @@
         <v>0.17</v>
       </c>
       <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3"/>
@@ -24896,6 +25437,9 @@
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3"/>
@@ -24904,6 +25448,9 @@
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3"/>
@@ -24912,6 +25459,9 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
@@ -24920,6 +25470,9 @@
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3"/>
@@ -24928,6 +25481,9 @@
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
@@ -24936,6 +25492,9 @@
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -24944,6 +25503,9 @@
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -24952,6 +25514,9 @@
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -24960,6 +25525,9 @@
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -24968,6 +25536,9 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -24976,6 +25547,9 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -24984,6 +25558,9 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -24992,6 +25569,9 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -25000,6 +25580,9 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -25008,6 +25591,9 @@
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -25016,6 +25602,9 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -717,7 +717,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="82.0" customHeight="1">
+    <row r="44" ht="108.0" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -725,7 +725,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">The collector feeders section by section from the collector bus out: cable, length and the units tapped at the section's far end. A daisy chain needs no From section; a lateral names the section it leaves from (its far end); 0 = straight from the collector bus. Copies: identical feeders. WECC equivalent: Zeq = sum(Zi Wi^2) / W^2, Beq = sum(Bi), Wi = MW of the units downstream of section i. R ohm, X ohm, B uS: a section's own values (its parallel cables together) in place of Cable x Length -- the GUI's Fill R, X, B from cables shows them to change; Clear R, X, B goes back. A section with R and X needs no cable.</t>
+          <t xml:space="preserve">The collector feeders section by section from the collector bus out: cable, length and the units tapped at the section's far end. A daisy chain needs no From section; a lateral names the section it leaves from (its far end); 0 = straight from the collector bus. Copies: identical feeders. The feeders on an MPT: those of the generators on it -- the GUI's Feeders on each MPT sets how many each has (its units spread over them), and they follow a generator's Units when it changes. WECC equivalent: Zeq = sum(Zi Wi^2) / W^2, Beq = sum(Bi), Wi = MW of the units downstream of section i. R ohm, X ohm, B uS: a section's own values (its parallel cables together) in place of Cable x Length -- the GUI's Fill R, X, B from cables shows them to change; Clear R, X, B goes back. A section with R and X needs no cable.</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="17.0" customHeight="1">
+    <row r="134" ht="30.0" customHeight="1">
       <c r="A134" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -6000,7 +6000,7 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
+          <t xml:space="preserve">identical feeders: how many of this feeder (blank = 1) -- an MPT's feeders are those of the generators on it (GUI: MPT or Feeders page, Feeders on each MPT)</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
@@ -6148,17 +6148,17 @@
       <c r="D139" s="8"/>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = km</t>
+          <t xml:space="preserve">blank = ft</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
@@ -6424,7 +6424,11 @@
         </is>
       </c>
       <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">km | mi | kft | m | ft</t>
@@ -6432,7 +6436,7 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per</t>
+          <t xml:space="preserve">the values are per (blank = km)</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
@@ -24466,7 +24470,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="124.0" customHeight="1">
+    <row r="2" ht="132.0" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"># the generator (its own collector) or a shared collector</t>
@@ -24479,7 +24483,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">identical feeders (blank = 1)</t>
+          <t xml:space="preserve">identical feeders: how many of this feeder (blank = 1) -- an MPT's feeders are those of the generators on it (GUI: MPT or Feeders page, Feeders on each MPT)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -24500,7 +24504,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = km</t>
+          <t xml:space="preserve">blank = ft</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -24558,11 +24562,11 @@
         </is>
       </c>
       <c r="G3" s="3">
-        <v>1.6</v>
+        <v>5250</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I3" s="3">
@@ -24598,11 +24602,11 @@
         </is>
       </c>
       <c r="G4" s="3">
-        <v>0.4</v>
+        <v>1300</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I4" s="3">
@@ -24638,11 +24642,11 @@
         </is>
       </c>
       <c r="G5" s="3">
-        <v>0.4</v>
+        <v>1300</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I5" s="3">
@@ -24678,11 +24682,11 @@
         </is>
       </c>
       <c r="G6" s="3">
-        <v>0.4</v>
+        <v>1300</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I6" s="3">
@@ -24718,11 +24722,11 @@
         </is>
       </c>
       <c r="G7" s="3">
-        <v>0.4</v>
+        <v>1300</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I7" s="3">
@@ -24758,11 +24762,11 @@
         </is>
       </c>
       <c r="G8" s="3">
-        <v>0.4</v>
+        <v>1300</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I8" s="3">
@@ -24798,11 +24802,11 @@
         </is>
       </c>
       <c r="G9" s="3">
-        <v>0.8</v>
+        <v>2600</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I9" s="3">
@@ -24838,11 +24842,11 @@
         </is>
       </c>
       <c r="G10" s="3">
-        <v>0.15</v>
+        <v>500</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I10" s="3">
@@ -24878,11 +24882,11 @@
         </is>
       </c>
       <c r="G11" s="3">
-        <v>0.15</v>
+        <v>500</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I11" s="3">
@@ -24918,11 +24922,11 @@
         </is>
       </c>
       <c r="G12" s="3">
-        <v>0.15</v>
+        <v>500</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I12" s="3">
@@ -24958,11 +24962,11 @@
         </is>
       </c>
       <c r="G13" s="3">
-        <v>0.15</v>
+        <v>500</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I13" s="3">
@@ -24998,11 +25002,11 @@
         </is>
       </c>
       <c r="G14" s="3">
-        <v>0.15</v>
+        <v>500</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="I14" s="3">
@@ -25209,7 +25213,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H3:H500">
-      <formula1>"km,mi,kft,m,ft"</formula1>
+      <formula1>"ft,kft,m,km,mi"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -25291,7 +25295,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per</t>
+          <t xml:space="preserve">the values are per (blank = km)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -2350,17 +2350,17 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km, mi, kft, m, ft (blank = km)</t>
+          <t xml:space="preserve">ft, kft, m, km, mi (blank = ft)</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -4298,13 +4298,21 @@
         </is>
       </c>
       <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ft</t>
+        </is>
+      </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
-      <c r="G81" s="8"/>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = ft</t>
+        </is>
+      </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -4751,7 +4759,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="17.0" customHeight="1">
+    <row r="96" ht="43.0" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4770,13 +4778,13 @@
       <c r="D96" s="8"/>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Unit PF</t>
+          <t xml:space="preserve">the MVA left at full P: sqrt(Unit MVA^2 - Pmax^2</t>
         </is>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = from Unit PF</t>
+          <t xml:space="preserve">blank = the MVA left at full P: sqrt(Unit MVA^2 - Pmax^2), or from Unit PF</t>
         </is>
       </c>
       <c r="H96" s="13" t="inlineStr">
@@ -4819,7 +4827,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="17.0" customHeight="1">
+    <row r="98" ht="30.0" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -4838,13 +4846,13 @@
       <c r="D98" s="8"/>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95</t>
+          <t xml:space="preserve">0.95 where Unit MVA is blank too</t>
         </is>
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
+          <t xml:space="preserve">Q at Pmax when Qmax is blank, instead of from Unit MVA (blank = 0.95 where Unit MVA is blank too)</t>
         </is>
       </c>
       <c r="H98" s="13" t="inlineStr">
@@ -20742,7 +20750,7 @@
         </is>
       </c>
       <c r="B23" s="3">
-        <v>5.0</v>
+        <v>16400</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="inlineStr">
@@ -20770,23 +20778,23 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">km, mi, kft, m, ft (blank = km)</t>
+          <t xml:space="preserve">ft, kft, m, km, mi (blank = ft)</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -21777,7 +21785,7 @@
       <formula1>"YES,NO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B24">
-      <formula1>"km,mi,kft,m,ft"</formula1>
+      <formula1>"ft,kft,m,km,mi"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B25">
       <formula1>"km,mi,kft,m,ft"</formula1>
@@ -22127,7 +22135,11 @@
           <t xml:space="preserve">a line of its own from HV to this MPT (blank = none)</t>
         </is>
       </c>
-      <c r="Z2" s="2"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = ft</t>
+        </is>
+      </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
@@ -22848,7 +22860,7 @@
       <formula1>"2,3"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z3:Z500">
-      <formula1>"km,mi,kft,m,ft"</formula1>
+      <formula1>"ft,kft,m,km,mi"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA3:AA500">
       <formula1>"km,mi,kft,m,ft"</formula1>
@@ -23167,7 +23179,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = from Unit PF</t>
+          <t xml:space="preserve">blank = the MVA left at full P: sqrt(Unit MVA^2 - Pmax^2), or from Unit PF</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -23177,7 +23189,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q at Pmax when Qmax is blank (blank = 0.95)</t>
+          <t xml:space="preserve">Q at Pmax when Qmax is blank, instead of from Unit MVA (blank = 0.95 where Unit MVA is blank too)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any parameter of the WECC-approved generic models, by generator, model and PSS/E name or position (ICON2, CON14) -- IB for the infinite bus, PLANT for the plant controller. Inverters: REGCA1 (REGC_A) + REECA1 / REECCU1 / REECDU1 (REEC_A / C / D) + REPCA1 (REPC_A) or REAX4BU1 (with PLNTBU1, REPC_B); WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1; SYNC: GENROU SEXS TGOV1. REECCU1, REECDU1, PLNTBU1, REAX4BU1 (and REGCAU1, REPCAU1) are user models: the WECC user-model DLL must be loaded for the PSS/E check (ADDLIB_IDV / DLLS in the script). The report lists every model's parameters with the values used. In the GUI, the Dyr_Params tab shows every model's parameters with the values the .dyr gets, a column per generator: double-click one to change it (it becomes a row here), clear it to go back to the default.</t>
+          <t xml:space="preserve">Any parameter of the WECC-approved generic models, by generator, model and PSS/E name or position (ICON2, CON14) -- IB for the infinite bus, PLANT for the plant controller. Inverters: REGCA1 (REGC_A) + REECA1 / REECCU1 / REECDU1 (REEC_A / C / D) + REPCA1 (REPC_A) or REAX4BU1 (with PLNTBU1, REPC_B); WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1; SYNC: its Machine, Exciter and Governor models (Generators; blank: GENROU SEXS TGOV1). REECCU1, REECDU1, PLNTBU1, REAX4BU1 (and REGCAU1, REPCAU1) are user models: the WECC user-model DLL must be loaded for the PSS/E check (ADDLIB_IDV / DLLS in the script). The report lists every model's parameters with the values used. In the GUI, the Dyr_Params tab shows every model's parameters with the values the .dyr gets, a column per generator: double-click one to change it (it becomes a row here), clear it to go back to the default.</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: its machine (GENROU, GENSAL), exciter (SEXS, IEEET1, ESST1A, EXST1), governor (TGOV1, HYGOV, GAST, IEEEG1) | IB: GENCLS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" ht="17.0" customHeight="1">
+    <row r="5" ht="43.0" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Plant</t>
@@ -1686,11 +1686,15 @@
         </is>
       </c>
       <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from the generators: PV100, Hybrid_PV100_BESS50 </t>
+        </is>
+      </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">model name: file names and the PSCAD case (letters, digits, _)</t>
+          <t xml:space="preserve">model name: file names and the PSCAD case (letters, digits, _; blank = from the generators: PV100, Hybrid_PV100_BESS50 ...)</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -5713,33 +5717,37 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD library</t>
+          <t xml:space="preserve">Machine model</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_library</t>
+          <t xml:space="preserve">sync_machine</t>
         </is>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
-      <c r="F125" s="8"/>
+          <t xml:space="preserve">GENROU</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GENROU | GENSAL</t>
+        </is>
+      </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
+          <t xml:space="preserve">SYNC: GENROU round rotor (steam, gas) | GENSAL salient pole (hydro) (blank = GENROU)</t>
         </is>
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="30.0" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5747,33 +5755,37 @@
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD definition</t>
+          <t xml:space="preserve">Exciter model</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_definition</t>
+          <t xml:space="preserve">sync_exciter</t>
         </is>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a source: network check</t>
-        </is>
-      </c>
-      <c r="F126" s="8"/>
+          <t xml:space="preserve">SEXS</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEXS | IEEET1 | ESST1A | EXST1 | NONE</t>
+        </is>
+      </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
+          <t xml:space="preserve">SYNC: SEXS simplified | IEEET1 DC (IEEE type 1) | ESST1A static, bus-fed | EXST1 static (older form) | NONE: constant field voltage (blank = SEXS)</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="30.0" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5781,33 +5793,37 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD AC port</t>
+          <t xml:space="preserve">Governor model</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_ac_port</t>
+          <t xml:space="preserve">sync_governor</t>
         </is>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its 3-phase port</t>
-        </is>
-      </c>
-      <c r="F127" s="8"/>
+          <t xml:space="preserve">TGOV1</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TGOV1 | HYGOV | GAST | IEEEG1 | NONE</t>
+        </is>
+      </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
+          <t xml:space="preserve">SYNC: TGOV1 steam | HYGOV hydro | GAST gas | IEEEG1 steam, multi-stage | NONE: constant mechanical power (blank = TGOV1)</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="30.0" customHeight="1">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="17.0" customHeight="1">
       <c r="A128" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5815,20 +5831,24 @@
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD source case</t>
+          <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_source</t>
+          <t xml:space="preserve">pscad_library</t>
         </is>
       </c>
       <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
       <c r="F128" s="8"/>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
+          <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
@@ -5837,7 +5857,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="30.0" customHeight="1">
+    <row r="129" ht="17.0" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5845,24 +5865,24 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD component ID</t>
+          <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_component_id</t>
+          <t xml:space="preserve">pscad_definition</t>
         </is>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
+          <t xml:space="preserve">a source: network check</t>
         </is>
       </c>
       <c r="F129" s="8"/>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
+          <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -5871,7 +5891,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="30.0" customHeight="1">
+    <row r="130" ht="17.0" customHeight="1">
       <c r="A130" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Generators</t>
@@ -5879,28 +5899,24 @@
       </c>
       <c r="B130" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD inverter at</t>
+          <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pscad_inv_at</t>
+          <t xml:space="preserve">pscad_ac_port</t>
         </is>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV</t>
-        </is>
-      </c>
-      <c r="F130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LV | MV</t>
-        </is>
-      </c>
+          <t xml:space="preserve">its 3-phase port</t>
+        </is>
+      </c>
+      <c r="F130" s="8"/>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
+          <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
@@ -5909,113 +5925,121 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-    </row>
-    <row r="132" ht="17.0" customHeight="1">
+    <row r="131" ht="30.0" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD source case</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_source</t>
+        </is>
+      </c>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="30.0" customHeight="1">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feeders</t>
+          <t xml:space="preserve">Generators</t>
         </is>
       </c>
       <c r="B132" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collector</t>
+          <t xml:space="preserve">PSCAD component ID</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">collector</t>
+          <t xml:space="preserve">pscad_component_id</t>
         </is>
       </c>
       <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the definition, its values from PSCAD_Params</t>
+        </is>
+      </c>
       <c r="F132" s="8"/>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
+          <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
         </is>
       </c>
       <c r="H132" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="17.0" customHeight="1">
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="30.0" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Generators</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD inverter at</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pscad_inv_at</t>
+        </is>
+      </c>
+      <c r="D133" s="8"/>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV | MV</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Feeders</t>
         </is>
       </c>
-      <c r="B133" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeder</t>
-        </is>
-      </c>
-      <c r="C133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feeder</t>
-        </is>
-      </c>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feeder name</t>
-        </is>
-      </c>
-      <c r="H133" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="30.0" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Feeders</t>
-        </is>
-      </c>
-      <c r="B134" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Copies</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copies</t>
-        </is>
-      </c>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">identical feeders: how many of this feeder (blank = 1) -- an MPT's feeders are those of the generators on it (GUI: MPT or Feeders page, Feeders on each MPT)</t>
-        </is>
-      </c>
-      <c r="H134" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B134" s="7"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
     </row>
     <row r="135" ht="17.0" customHeight="1">
       <c r="A135" s="8" t="inlineStr">
@@ -6025,12 +6049,12 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Section</t>
+          <t xml:space="preserve">Collector</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">section</t>
+          <t xml:space="preserve">collector</t>
         </is>
       </c>
       <c r="D135" s="8"/>
@@ -6038,7 +6062,7 @@
       <c r="F135" s="8"/>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+          <t xml:space="preserve">the generator (its own collector) or a shared collector</t>
         </is>
       </c>
       <c r="H135" s="13" t="inlineStr">
@@ -6047,7 +6071,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="30.0" customHeight="1">
+    <row r="136" ht="17.0" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -6055,24 +6079,20 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">From section</t>
+          <t xml:space="preserve">Feeder</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_section</t>
+          <t xml:space="preserve">feeder</t>
         </is>
       </c>
       <c r="D136" s="8"/>
-      <c r="E136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the one before (daisy chain</t>
-        </is>
-      </c>
+      <c r="E136" s="8"/>
       <c r="F136" s="8"/>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
+          <t xml:space="preserve">feeder name</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
@@ -6081,7 +6101,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="17.0" customHeight="1">
+    <row r="137" ht="30.0" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -6089,20 +6109,24 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">Copies</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">copies</t>
         </is>
       </c>
       <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="F137" s="8"/>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">from Cables</t>
+          <t xml:space="preserve">identical feeders: how many of this feeder (blank = 1) -- an MPT's feeders are those of the generators on it (GUI: MPT or Feeders page, Feeders on each MPT)</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
@@ -6119,25 +6143,29 @@
       </c>
       <c r="B138" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length</t>
+          <t xml:space="preserve">Section</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">length</t>
+          <t xml:space="preserve">section</t>
         </is>
       </c>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
-      <c r="G138" s="8"/>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1, 2, 3 ... from the collector bus out</t>
+        </is>
+      </c>
       <c r="H138" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="17.0" customHeight="1">
+    <row r="139" ht="30.0" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Feeders</t>
@@ -6145,28 +6173,24 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">From section</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">from_section</t>
         </is>
       </c>
       <c r="D139" s="8"/>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ft</t>
-        </is>
-      </c>
-      <c r="F139" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ft | kft | m | km | mi</t>
-        </is>
-      </c>
+          <t xml:space="preserve">the one before (daisy chain</t>
+        </is>
+      </c>
+      <c r="F139" s="8"/>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = ft</t>
+          <t xml:space="preserve">blank = the one before (daisy chain) | 0 = the collector bus | n = a lateral off the end of section n</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
@@ -6183,12 +6207,12 @@
       </c>
       <c r="B140" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units at end</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D140" s="8"/>
@@ -6196,7 +6220,7 @@
       <c r="F140" s="8"/>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units tapped at the far end</t>
+          <t xml:space="preserve">from Cables</t>
         </is>
       </c>
       <c r="H140" s="13" t="inlineStr">
@@ -6213,22 +6237,18 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Units of</t>
+          <t xml:space="preserve">Length</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">units_of</t>
+          <t xml:space="preserve">length</t>
         </is>
       </c>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
-        </is>
-      </c>
+      <c r="G141" s="8"/>
       <c r="H141" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
@@ -6243,24 +6263,28 @@
       </c>
       <c r="B142" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallel cables</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parallel</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D142" s="8"/>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F142" s="8"/>
+          <t xml:space="preserve">ft</t>
+        </is>
+      </c>
+      <c r="F142" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
+        </is>
+      </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = 1</t>
+          <t xml:space="preserve">blank = ft</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
@@ -6277,24 +6301,20 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R ohm</t>
+          <t xml:space="preserve">Units at end</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">r_ohm</t>
+          <t xml:space="preserve">units</t>
         </is>
       </c>
       <c r="D143" s="8"/>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable x Length</t>
-        </is>
-      </c>
+      <c r="E143" s="8"/>
       <c r="F143" s="8"/>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
+          <t xml:space="preserve">units tapped at the far end</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr">
@@ -6311,24 +6331,20 @@
       </c>
       <c r="B144" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X ohm</t>
+          <t xml:space="preserve">Units of</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_ohm</t>
+          <t xml:space="preserve">units_of</t>
         </is>
       </c>
       <c r="D144" s="8"/>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cable x Length</t>
-        </is>
-      </c>
+      <c r="E144" s="8"/>
       <c r="F144" s="8"/>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
+          <t xml:space="preserve">shared collectors: whose units (repeat the section for another generator's)</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
@@ -6345,24 +6361,24 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B uS</t>
+          <t xml:space="preserve">Parallel cables</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_us</t>
+          <t xml:space="preserve">parallel</t>
         </is>
       </c>
       <c r="D145" s="8"/>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable x Length</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F145" s="8"/>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
+          <t xml:space="preserve">blank = 1</t>
         </is>
       </c>
       <c r="H145" s="13" t="inlineStr">
@@ -6371,42 +6387,66 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cables</t>
-        </is>
-      </c>
-      <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
+    <row r="146" ht="17.0" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feeders</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R ohm</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">r_ohm</t>
+        </is>
+      </c>
+      <c r="D146" s="8"/>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
+      <c r="F146" s="8"/>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the section's R, its parallel cables together (blank = Cable x Length)</t>
+        </is>
+      </c>
+      <c r="H146" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="17.0" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable</t>
+          <t xml:space="preserve">X ohm</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable</t>
+          <t xml:space="preserve">x_ohm</t>
         </is>
       </c>
       <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
       <c r="F147" s="8"/>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">cable type</t>
+          <t xml:space="preserve">the section's X (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
@@ -6418,33 +6458,29 @@
     <row r="148" ht="17.0" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cables</t>
+          <t xml:space="preserve">Feeders</t>
         </is>
       </c>
       <c r="B148" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Length unit</t>
+          <t xml:space="preserve">B uS</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit</t>
+          <t xml:space="preserve">b_us</t>
         </is>
       </c>
       <c r="D148" s="8"/>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
-        </is>
-      </c>
-      <c r="F148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Cable x Length</t>
+        </is>
+      </c>
+      <c r="F148" s="8"/>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per (blank = km)</t>
+          <t xml:space="preserve">the section's charging B, total (blank = Cable x Length)</t>
         </is>
       </c>
       <c r="H148" s="13" t="inlineStr">
@@ -6453,35 +6489,19 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="17.0" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
         </is>
       </c>
-      <c r="B149" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R per length</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">r_per</t>
-        </is>
-      </c>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
-      <c r="F149" s="8"/>
-      <c r="G149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ohm, at operating temperature</t>
-        </is>
-      </c>
-      <c r="H149" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
     </row>
     <row r="150" ht="17.0" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
@@ -6491,12 +6511,12 @@
       </c>
       <c r="B150" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">X per length</t>
+          <t xml:space="preserve">Cable</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">x_per</t>
+          <t xml:space="preserve">cable</t>
         </is>
       </c>
       <c r="D150" s="8"/>
@@ -6504,7 +6524,7 @@
       <c r="F150" s="8"/>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ohm</t>
+          <t xml:space="preserve">cable type</t>
         </is>
       </c>
       <c r="H150" s="13" t="inlineStr">
@@ -6521,20 +6541,28 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">Length unit</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">unit</t>
         </is>
       </c>
       <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
-      <c r="F151" s="8"/>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">km | mi | kft | m | ft</t>
+        </is>
+      </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">the values are per (blank = km)</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -6551,12 +6579,12 @@
       </c>
       <c r="B152" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">R per length</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">r_per</t>
         </is>
       </c>
       <c r="D152" s="8"/>
@@ -6564,7 +6592,7 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS, instead of C</t>
+          <t xml:space="preserve">ohm, at operating temperature</t>
         </is>
       </c>
       <c r="H152" s="13" t="inlineStr">
@@ -6573,7 +6601,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="30.0" customHeight="1">
+    <row r="153" ht="17.0" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Cables</t>
@@ -6581,29 +6609,25 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate A MVA</t>
+          <t xml:space="preserve">X per length</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_a_mva</t>
+          <t xml:space="preserve">x_per</t>
         </is>
       </c>
       <c r="D153" s="8"/>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none</t>
-        </is>
-      </c>
+      <c r="E153" s="8"/>
       <c r="F153" s="8"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one cable's normal rating at its collector's kV (sqrt(3) x kV x amps / 1000): RATEA, rate1 -- a section's: x its parallel cables (blank = none)</t>
+          <t xml:space="preserve">ohm</t>
         </is>
       </c>
       <c r="H153" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6615,29 +6639,25 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate B MVA</t>
+          <t xml:space="preserve">C per length</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_b_mva</t>
+          <t xml:space="preserve">c_per</t>
         </is>
       </c>
       <c r="D154" s="8"/>
-      <c r="E154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate A</t>
-        </is>
-      </c>
+      <c r="E154" s="8"/>
       <c r="F154" s="8"/>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one cable's emergency rating: RATEB, rate2 (blank = Rate A)</t>
+          <t xml:space="preserve">uF</t>
         </is>
       </c>
       <c r="H154" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
@@ -6649,110 +6669,134 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rate C MVA</t>
+          <t xml:space="preserve">B per length</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rate_c_mva</t>
+          <t xml:space="preserve">b_per</t>
         </is>
       </c>
       <c r="D155" s="8"/>
-      <c r="E155" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rate B</t>
-        </is>
-      </c>
+      <c r="E155" s="8"/>
       <c r="F155" s="8"/>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one cable's: RATEC, rate3 (blank = Rate B)</t>
+          <t xml:space="preserve">uS, instead of C</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="30.0" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cables</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate A MVA</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rate_a_mva</t>
+        </is>
+      </c>
+      <c r="D156" s="8"/>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none</t>
+        </is>
+      </c>
+      <c r="F156" s="8"/>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one cable's normal rating at its collector's kV (sqrt(3) x kV x amps / 1000): RATEA, rate1 -- a section's: x its parallel cables (blank = none)</t>
+        </is>
+      </c>
+      <c r="H156" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
-    </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Collectors</t>
-        </is>
-      </c>
-      <c r="B156" s="7"/>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
-      <c r="G156" s="7"/>
-      <c r="H156" s="7"/>
     </row>
     <row r="157" ht="17.0" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">Rate B MVA</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">rate_b_mva</t>
         </is>
       </c>
       <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate A</t>
+        </is>
+      </c>
       <c r="F157" s="8"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
+          <t xml:space="preserve">one cable's emergency rating: RATEB, rate2 (blank = Rate A)</t>
         </is>
       </c>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
     <row r="158" ht="17.0" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Collectors</t>
+          <t xml:space="preserve">Cables</t>
         </is>
       </c>
       <c r="B158" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connect to</t>
+          <t xml:space="preserve">Rate C MVA</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">connect</t>
+          <t xml:space="preserve">rate_c_mva</t>
         </is>
       </c>
       <c r="D158" s="8"/>
-      <c r="E158" s="8"/>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rate B</t>
+        </is>
+      </c>
       <c r="F158" s="8"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
+          <t xml:space="preserve">one cable's: RATEC, rate3 (blank = Rate B)</t>
         </is>
       </c>
       <c r="H158" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B159" s="7"/>
@@ -6766,33 +6810,25 @@
     <row r="160" ht="17.0" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B160" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kind</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D160" s="8"/>
-      <c r="E160" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD</t>
-        </is>
-      </c>
-      <c r="F160" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD | SHUNT</t>
-        </is>
-      </c>
+      <c r="E160" s="8"/>
+      <c r="F160" s="8"/>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor (blank = LOAD)</t>
+          <t xml:space="preserve">shared collector: its far-end bus has this name</t>
         </is>
       </c>
       <c r="H160" s="13" t="inlineStr">
@@ -6804,17 +6840,17 @@
     <row r="161" ht="17.0" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loads_Shunts</t>
+          <t xml:space="preserve">Collectors</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">At bus</t>
+          <t xml:space="preserve">Connect to</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at</t>
+          <t xml:space="preserve">connect</t>
         </is>
       </c>
       <c r="D161" s="8"/>
@@ -6822,7 +6858,7 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+          <t xml:space="preserve">the bus it starts from (MPT1, MPT1:TV ...)</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
@@ -6831,35 +6867,19 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="17.0" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
-      <c r="B162" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MW</t>
-        </is>
-      </c>
-      <c r="C162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mw</t>
-        </is>
-      </c>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
-      <c r="F162" s="8"/>
-      <c r="G162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOAD, at 1 pu</t>
-        </is>
-      </c>
-      <c r="H162" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
     </row>
     <row r="163" ht="17.0" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
@@ -6869,20 +6889,28 @@
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MVAr</t>
+          <t xml:space="preserve">Kind</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mvar</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD</t>
+        </is>
+      </c>
+      <c r="F163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD | SHUNT</t>
+        </is>
+      </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
+          <t xml:space="preserve">LOAD: constant impedance | SHUNT: + capacitor, - reactor (blank = LOAD)</t>
         </is>
       </c>
       <c r="H163" s="13" t="inlineStr">
@@ -6899,52 +6927,72 @@
       </c>
       <c r="B164" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Name</t>
+          <t xml:space="preserve">At bus</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">at</t>
         </is>
       </c>
       <c r="D164" s="8"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
-      <c r="G164" s="8"/>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POI, HV, MPT1, MPT1:TV, PV:MV, PV ...</t>
+        </is>
+      </c>
       <c r="H164" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
-      <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
-    </row>
-    <row r="166" ht="30.0" customHeight="1">
+    <row r="165" ht="17.0" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MW</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mw</t>
+        </is>
+      </c>
+      <c r="D165" s="8"/>
+      <c r="E165" s="8"/>
+      <c r="F165" s="8"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAD, at 1 pu</t>
+        </is>
+      </c>
+      <c r="H165" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="17.0" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machines</t>
+          <t xml:space="preserve">Loads_Shunts</t>
         </is>
       </c>
       <c r="B166" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine</t>
+          <t xml:space="preserve">MVAr</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">machine</t>
+          <t xml:space="preserve">mvar</t>
         </is>
       </c>
       <c r="D166" s="8"/>
@@ -6952,7 +7000,7 @@
       <c r="F166" s="8"/>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
+          <t xml:space="preserve">at 1 pu: LOAD + inductive | SHUNT + capacitive</t>
         </is>
       </c>
       <c r="H166" s="13" t="inlineStr">
@@ -6964,97 +7012,65 @@
     <row r="167" ht="17.0" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Loads_Shunts</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D167" s="8"/>
+      <c r="E167" s="8"/>
+      <c r="F167" s="8"/>
+      <c r="G167" s="8"/>
+      <c r="H167" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B167" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machine ID</t>
-        </is>
-      </c>
-      <c r="C167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its generator's</t>
-        </is>
-      </c>
-      <c r="F167" s="8"/>
-      <c r="G167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = its generator's</t>
-        </is>
-      </c>
-      <c r="H167" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="30.0" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
+      <c r="H168" s="7"/>
+    </row>
+    <row r="169" ht="30.0" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
         </is>
       </c>
-      <c r="B168" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pgen MW</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pgen_mw</t>
-        </is>
-      </c>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
-        </is>
-      </c>
-      <c r="F168" s="8"/>
-      <c r="G168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
-        </is>
-      </c>
-      <c r="H168" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="17.0" customHeight="1">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Machines</t>
-        </is>
-      </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmax MW</t>
+          <t xml:space="preserve">Machine</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmax_mw</t>
+          <t xml:space="preserve">machine</t>
         </is>
       </c>
       <c r="D169" s="8"/>
-      <c r="E169" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its units x Unit Pmax</t>
-        </is>
-      </c>
+      <c r="E169" s="8"/>
       <c r="F169" s="8"/>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmax</t>
+          <t xml:space="preserve">DETAILED model: a machine, &lt;generator&gt;_&lt;feeder&gt;_S&lt;section&gt; (the GUI lists them); its values in place of its share of its generator's</t>
         </is>
       </c>
       <c r="H169" s="13" t="inlineStr">
@@ -7071,24 +7087,24 @@
       </c>
       <c r="B170" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pmin MW</t>
+          <t xml:space="preserve">Machine ID</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pmin_mw</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Pmin</t>
+          <t xml:space="preserve">its generator's</t>
         </is>
       </c>
       <c r="F170" s="8"/>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Pmin</t>
+          <t xml:space="preserve">blank = its generator's</t>
         </is>
       </c>
       <c r="H170" s="13" t="inlineStr">
@@ -7097,7 +7113,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="17.0" customHeight="1">
+    <row r="171" ht="30.0" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -7105,24 +7121,24 @@
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmax MVAr</t>
+          <t xml:space="preserve">Pgen MW</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmax_mvar</t>
+          <t xml:space="preserve">pgen_mw</t>
         </is>
       </c>
       <c r="D171" s="8"/>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmax</t>
+          <t xml:space="preserve">its share of its generator's Dispatch MW</t>
         </is>
       </c>
       <c r="F171" s="8"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmax</t>
+          <t xml:space="preserve">its dispatch (blank = its share of its generator's Dispatch MW)</t>
         </is>
       </c>
       <c r="H171" s="13" t="inlineStr">
@@ -7139,24 +7155,24 @@
       </c>
       <c r="B172" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qmin MVAr</t>
+          <t xml:space="preserve">Pmax MW</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">qmin_mvar</t>
+          <t xml:space="preserve">pmax_mw</t>
         </is>
       </c>
       <c r="D172" s="8"/>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit Qmin</t>
+          <t xml:space="preserve">its units x Unit Pmax</t>
         </is>
       </c>
       <c r="F172" s="8"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+          <t xml:space="preserve">blank = its units x Unit Pmax</t>
         </is>
       </c>
       <c r="H172" s="13" t="inlineStr">
@@ -7165,7 +7181,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="30.0" customHeight="1">
+    <row r="173" ht="17.0" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Machines</t>
@@ -7173,24 +7189,24 @@
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fixed Q MVAr</t>
+          <t xml:space="preserve">Pmin MW</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">q_mvar</t>
+          <t xml:space="preserve">pmin_mw</t>
         </is>
       </c>
       <c r="D173" s="8"/>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">as its generator's Q mode</t>
+          <t xml:space="preserve">its units x Unit Pmin</t>
         </is>
       </c>
       <c r="F173" s="8"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
+          <t xml:space="preserve">blank = its units x Unit Pmin</t>
         </is>
       </c>
       <c r="H173" s="13" t="inlineStr">
@@ -7207,24 +7223,24 @@
       </c>
       <c r="B174" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBASE MVA</t>
+          <t xml:space="preserve">Qmax MVAr</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mbase_mva</t>
+          <t xml:space="preserve">qmax_mvar</t>
         </is>
       </c>
       <c r="D174" s="8"/>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its units x Unit MVA</t>
+          <t xml:space="preserve">its units x Unit Qmax</t>
         </is>
       </c>
       <c r="F174" s="8"/>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = its units x Unit MVA</t>
+          <t xml:space="preserve">blank = its units x Unit Qmax</t>
         </is>
       </c>
       <c r="H174" s="13" t="inlineStr">
@@ -7233,42 +7249,66 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bus_Numbers</t>
-        </is>
-      </c>
-      <c r="B175" s="7"/>
-      <c r="C175" s="7"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
-      <c r="G175" s="7"/>
-      <c r="H175" s="7"/>
-    </row>
-    <row r="176" ht="17.0" customHeight="1">
+    <row r="175" ht="17.0" customHeight="1">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machines</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qmin MVAr</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">qmin_mvar</t>
+        </is>
+      </c>
+      <c r="D175" s="8"/>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its units x Unit Qmin</t>
+        </is>
+      </c>
+      <c r="F175" s="8"/>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = its units x Unit Qmin</t>
+        </is>
+      </c>
+      <c r="H175" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="30.0" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus</t>
+          <t xml:space="preserve">Fixed Q MVAr</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bus</t>
+          <t xml:space="preserve">q_mvar</t>
         </is>
       </c>
       <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">as its generator's Q mode</t>
+        </is>
+      </c>
       <c r="F176" s="8"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+          <t xml:space="preserve">a value: this Q, fixed (blank = as its generator's Q mode)</t>
         </is>
       </c>
       <c r="H176" s="13" t="inlineStr">
@@ -7280,29 +7320,29 @@
     <row r="177" ht="17.0" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus_Numbers</t>
+          <t xml:space="preserve">Machines</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number</t>
+          <t xml:space="preserve">MBASE MVA</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">mbase_mva</t>
         </is>
       </c>
       <c r="D177" s="8"/>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">automatic</t>
+          <t xml:space="preserve">its units x Unit MVA</t>
         </is>
       </c>
       <c r="F177" s="8"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = automatic</t>
+          <t xml:space="preserve">blank = its units x Unit MVA</t>
         </is>
       </c>
       <c r="H177" s="13" t="inlineStr">
@@ -7311,143 +7351,131 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="30.0" customHeight="1">
-      <c r="A178" s="8" t="inlineStr">
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
-      <c r="B178" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Name</t>
-        </is>
-      </c>
-      <c r="C178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">automatic (12 characters at most</t>
-        </is>
-      </c>
-      <c r="F178" s="8"/>
-      <c r="G178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
-        </is>
-      </c>
-      <c r="H178" s="13" t="inlineStr">
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="7"/>
+    </row>
+    <row r="179" ht="17.0" customHeight="1">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus_Numbers</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bus</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bus</t>
+        </is>
+      </c>
+      <c r="D179" s="8"/>
+      <c r="E179" s="8"/>
+      <c r="F179" s="8"/>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its role: IB, POI, HV, MPT1:LV, PV:MV, PV:LV ...</t>
+        </is>
+      </c>
+      <c r="H179" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
-    </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Params</t>
-        </is>
-      </c>
-      <c r="B179" s="7"/>
-      <c r="C179" s="7"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
-      <c r="G179" s="7"/>
-      <c r="H179" s="7"/>
     </row>
     <row r="180" ht="17.0" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B180" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Number</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
+      <c r="E180" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic</t>
+        </is>
+      </c>
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+          <t xml:space="preserve">blank = automatic</t>
         </is>
       </c>
       <c r="H180" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
         </is>
       </c>
     </row>
     <row r="181" ht="30.0" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Params</t>
+          <t xml:space="preserve">Bus_Numbers</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Model</t>
+          <t xml:space="preserve">Name</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">model</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">automatic (12 characters at most</t>
+        </is>
+      </c>
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: GENROU SEXS TGOV1 | IB: GENCLS</t>
+          <t xml:space="preserve">blank = automatic (12 characters at most)</t>
         </is>
       </c>
       <c r="H181" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="17.0" customHeight="1">
-      <c r="A182" s="8" t="inlineStr">
+          <t xml:space="preserve">PSS/E + PSLF + PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
-      <c r="B182" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parameter</t>
-        </is>
-      </c>
-      <c r="C182" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parameter</t>
-        </is>
-      </c>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
-      <c r="F182" s="8"/>
-      <c r="G182" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
-        </is>
-      </c>
-      <c r="H182" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSS/E + PSLF</t>
-        </is>
-      </c>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
+      <c r="G182" s="7"/>
+      <c r="H182" s="7"/>
     </row>
     <row r="183" ht="17.0" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
@@ -7457,106 +7485,118 @@
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value</t>
+          <t xml:space="preserve">Generator</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">generator</t>
         </is>
       </c>
       <c r="D183" s="8"/>
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
-      <c r="G183" s="8"/>
+      <c r="G183" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IB: the infinite bus | PLANT: the plant controller (REPC_B)</t>
+        </is>
+      </c>
       <c r="H183" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dyr_Records</t>
-        </is>
-      </c>
-      <c r="B184" s="7"/>
-      <c r="C184" s="7"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
-      <c r="G184" s="7"/>
-      <c r="H184" s="7"/>
+    <row r="184" ht="43.0" customHeight="1">
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dyr_Params</t>
+        </is>
+      </c>
+      <c r="B184" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Model</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">model</t>
+        </is>
+      </c>
+      <c r="D184" s="8"/>
+      <c r="E184" s="8"/>
+      <c r="F184" s="8"/>
+      <c r="G184" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REGCA1 (REGCAU1) | REECA1 REECCU1 REECDU1 | REPCA1 (REPCAU1) or REAX4BU1 | PLANT: PLNTBU1 | WT3: + WTDTA1 WTARA1 WTPTA1 WTTQA1 | SYNC: its machine (GENROU, GENSAL), exciter (SEXS, IEEET1, ESST1A, EXST1), governor (TGOV1, HYGOV, GAST, IEEEG1) | IB: GENCLS</t>
+        </is>
+      </c>
+      <c r="H184" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSS/E + PSLF</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="17.0" customHeight="1">
       <c r="A185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator</t>
+          <t xml:space="preserve">Parameter</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">generator</t>
+          <t xml:space="preserve">parameter</t>
         </is>
       </c>
       <c r="D185" s="8"/>
-      <c r="E185" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the plant</t>
-        </is>
-      </c>
+      <c r="E185" s="8"/>
       <c r="F185" s="8"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank = the plant</t>
+          <t xml:space="preserve">PSS/E name (the report lists them all) or position: ICON2, CON14</t>
         </is>
       </c>
       <c r="H185" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
     <row r="186" ht="17.0" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyr_Records</t>
+          <t xml:space="preserve">Dyr_Params</t>
         </is>
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record</t>
+          <t xml:space="preserve">Value</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">record</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="D186" s="8"/>
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
-      <c r="G186" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
-        </is>
-      </c>
+      <c r="G186" s="8"/>
       <c r="H186" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSS/E</t>
+          <t xml:space="preserve">PSS/E + PSLF</t>
         </is>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B187" s="7"/>
@@ -7570,7 +7610,7 @@
     <row r="188" ht="17.0" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B188" s="12" t="inlineStr">
@@ -7584,29 +7624,37 @@
         </is>
       </c>
       <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the plant</t>
+        </is>
+      </c>
       <c r="F188" s="8"/>
-      <c r="G188" s="8"/>
+      <c r="G188" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank = the plant</t>
+        </is>
+      </c>
       <c r="H188" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD</t>
+          <t xml:space="preserve">PSS/E</t>
         </is>
       </c>
     </row>
     <row r="189" ht="17.0" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PSCAD_Params</t>
+          <t xml:space="preserve">Dyr_Records</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter</t>
+          <t xml:space="preserve">Record</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">parameter</t>
+          <t xml:space="preserve">record</t>
         </is>
       </c>
       <c r="D189" s="8"/>
@@ -7614,118 +7662,134 @@
       <c r="F189" s="8"/>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the vendor model's parameter name</t>
+          <t xml:space="preserve">.dyr text ending in / -- {BUS} {ID} {MBASE} {POI} {IB} {HV} {MV} {&lt;bus role&gt;} are filled in</t>
         </is>
       </c>
       <c r="H189" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">PSS/E</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B190" s="7"/>
+      <c r="C190" s="7"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+    </row>
+    <row r="191" ht="17.0" customHeight="1">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generator</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generator</t>
+        </is>
+      </c>
+      <c r="D191" s="8"/>
+      <c r="E191" s="8"/>
+      <c r="F191" s="8"/>
+      <c r="G191" s="8"/>
+      <c r="H191" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="17.0" customHeight="1">
-      <c r="A190" s="8" t="inlineStr">
+    <row r="192" ht="17.0" customHeight="1">
+      <c r="A192" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD_Params</t>
         </is>
       </c>
-      <c r="B190" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value</t>
-        </is>
-      </c>
-      <c r="C190" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">value</t>
-        </is>
-      </c>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
-      <c r="F190" s="8"/>
-      <c r="G190" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
-        </is>
-      </c>
-      <c r="H190" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
-        </is>
-      </c>
-      <c r="B191" s="7"/>
-      <c r="C191" s="7"/>
-      <c r="D191" s="7"/>
-      <c r="E191" s="7"/>
-      <c r="F191" s="7"/>
-      <c r="G191" s="7"/>
-      <c r="H191" s="7"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="8"/>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">IB</t>
-        </is>
-      </c>
-      <c r="C192" s="8"/>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter</t>
+        </is>
+      </c>
       <c r="D192" s="8"/>
       <c r="E192" s="8"/>
       <c r="F192" s="8"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the infinite bus</t>
-        </is>
-      </c>
-      <c r="H192" s="8"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="8"/>
+          <t xml:space="preserve">the vendor model's parameter name</t>
+        </is>
+      </c>
+      <c r="H192" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="17.0" customHeight="1">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">POI</t>
-        </is>
-      </c>
-      <c r="C193" s="8"/>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
       <c r="D193" s="8"/>
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the point of interconnection</t>
-        </is>
-      </c>
-      <c r="H193" s="8"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="8"/>
-      <c r="B194" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HV</t>
-        </is>
-      </c>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
-      <c r="F194" s="8"/>
-      <c r="G194" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
-        </is>
-      </c>
-      <c r="H194" s="8"/>
+          <t xml:space="preserve">as PSCAD takes it (0.63 [kV], 40, {UNITS}, {P_PU} ...)</t>
+        </is>
+      </c>
+      <c r="H193" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUS NAMES -- Connect to, At, Bus_Numbers and {&lt;bus&gt;} in Dyr_Records take these</t>
+        </is>
+      </c>
+      <c r="B194" s="7"/>
+      <c r="C194" s="7"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
+      <c r="G194" s="7"/>
+      <c r="H194" s="7"/>
     </row>
     <row r="195">
       <c r="A195" s="8"/>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
+          <t xml:space="preserve">IB</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -7734,7 +7798,7 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT's LV winding</t>
+          <t xml:space="preserve">the infinite bus</t>
         </is>
       </c>
       <c r="H195" s="8"/>
@@ -7743,7 +7807,7 @@
       <c r="A196" s="8"/>
       <c r="B196" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
+          <t xml:space="preserve">POI</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -7752,7 +7816,7 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
+          <t xml:space="preserve">the point of interconnection</t>
         </is>
       </c>
       <c r="H196" s="8"/>
@@ -7761,7 +7825,7 @@
       <c r="A197" s="8"/>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
+          <t xml:space="preserve">HV</t>
         </is>
       </c>
       <c r="C197" s="8"/>
@@ -7770,7 +7834,7 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
+          <t xml:space="preserve">the gen-tie's plant end (the POI when there is no gen-tie)</t>
         </is>
       </c>
       <c r="H197" s="8"/>
@@ -7779,7 +7843,7 @@
       <c r="A198" s="8"/>
       <c r="B198" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;</t>
+          <t xml:space="preserve">&lt;MPT&gt; or &lt;MPT&gt;:LV</t>
         </is>
       </c>
       <c r="C198" s="8"/>
@@ -7788,7 +7852,7 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a shared collector's far end</t>
+          <t xml:space="preserve">an MPT's LV winding</t>
         </is>
       </c>
       <c r="H198" s="8"/>
@@ -7797,7 +7861,7 @@
       <c r="A199" s="8"/>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;:MV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:TV</t>
         </is>
       </c>
       <c r="C199" s="8"/>
@@ -7806,7 +7870,7 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's GSU HV side</t>
+          <t xml:space="preserve">a 3-winding MPT's tertiary</t>
         </is>
       </c>
       <c r="H199" s="8"/>
@@ -7815,7 +7879,7 @@
       <c r="A200" s="8"/>
       <c r="B200" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+          <t xml:space="preserve">&lt;MPT&gt;:HV</t>
         </is>
       </c>
       <c r="C200" s="8"/>
@@ -7824,7 +7888,7 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">a generator's terminal</t>
+          <t xml:space="preserve">an MPT with a tie line of its own: its HV end</t>
         </is>
       </c>
       <c r="H200" s="8"/>
@@ -7833,7 +7897,7 @@
       <c r="A201" s="8"/>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
+          <t xml:space="preserve">&lt;collector&gt;</t>
         </is>
       </c>
       <c r="C201" s="8"/>
@@ -7842,7 +7906,7 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+          <t xml:space="preserve">a shared collector's far end</t>
         </is>
       </c>
       <c r="H201" s="8"/>
@@ -7851,7 +7915,7 @@
       <c r="A202" s="8"/>
       <c r="B202" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
+          <t xml:space="preserve">&lt;generator&gt;:MV</t>
         </is>
       </c>
       <c r="C202" s="8"/>
@@ -7860,34 +7924,34 @@
       <c r="F202" s="8"/>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+          <t xml:space="preserve">a generator's GSU HV side</t>
         </is>
       </c>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
-        </is>
-      </c>
-      <c r="B203" s="7"/>
-      <c r="C203" s="7"/>
-      <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="7"/>
-      <c r="G203" s="7"/>
-      <c r="H203" s="7"/>
+    <row r="203">
+      <c r="A203" s="8"/>
+      <c r="B203" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;generator&gt; or &lt;generator&gt;:LV</t>
+        </is>
+      </c>
+      <c r="C203" s="8"/>
+      <c r="D203" s="8"/>
+      <c r="E203" s="8"/>
+      <c r="F203" s="8"/>
+      <c r="G203" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a generator's terminal</t>
+        </is>
+      </c>
+      <c r="H203" s="8"/>
     </row>
     <row r="204">
-      <c r="A204" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A204" s="8"/>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNITS}</t>
+          <t xml:space="preserve">&lt;collector&gt;_&lt;feeder&gt;_S&lt;n&gt;</t>
         </is>
       </c>
       <c r="C204" s="8"/>
@@ -7896,24 +7960,16 @@
       <c r="F204" s="8"/>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the units the inverter stands for</t>
-        </is>
-      </c>
-      <c r="H204" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the far end of feeder section n</t>
+        </is>
+      </c>
+      <c r="H204" s="8"/>
     </row>
     <row r="205">
-      <c r="A205" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
+      <c r="A205" s="8"/>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{MVA}</t>
+          <t xml:space="preserve">&lt;generator&gt;_&lt;feeder&gt;_S&lt;n&gt;:LV</t>
         </is>
       </c>
       <c r="C205" s="8"/>
@@ -7922,40 +7978,24 @@
       <c r="F205" s="8"/>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their MVA</t>
-        </is>
-      </c>
-      <c r="H205" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD_Params</t>
-        </is>
-      </c>
-      <c r="B206" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{P_MW}</t>
-        </is>
-      </c>
-      <c r="C206" s="8"/>
-      <c r="D206" s="8"/>
-      <c r="E206" s="8"/>
-      <c r="F206" s="8"/>
-      <c r="G206" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">their P where the inverter connects (MW)</t>
-        </is>
-      </c>
-      <c r="H206" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PSCAD</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DETAILED: the terminal of the units at that node</t>
+        </is>
+      </c>
+      <c r="H205" s="8"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params PLACEHOLDERS -- filled in for each inverter a vendor model stands for</t>
+        </is>
+      </c>
+      <c r="B206" s="7"/>
+      <c r="C206" s="7"/>
+      <c r="D206" s="7"/>
+      <c r="E206" s="7"/>
+      <c r="F206" s="7"/>
+      <c r="G206" s="7"/>
+      <c r="H206" s="7"/>
     </row>
     <row r="207">
       <c r="A207" s="8" t="inlineStr">
@@ -7965,7 +8005,7 @@
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_MVAR}</t>
+          <t xml:space="preserve">{UNITS}</t>
         </is>
       </c>
       <c r="C207" s="8"/>
@@ -7974,7 +8014,7 @@
       <c r="F207" s="8"/>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">their Q there (MVAr)</t>
+          <t xml:space="preserve">the units the inverter stands for</t>
         </is>
       </c>
       <c r="H207" s="13" t="inlineStr">
@@ -7991,7 +8031,7 @@
       </c>
       <c r="B208" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_PU}</t>
+          <t xml:space="preserve">{MVA}</t>
         </is>
       </c>
       <c r="C208" s="8"/>
@@ -8000,7 +8040,7 @@
       <c r="F208" s="8"/>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P on {MVA}</t>
+          <t xml:space="preserve">their MVA</t>
         </is>
       </c>
       <c r="H208" s="13" t="inlineStr">
@@ -8017,7 +8057,7 @@
       </c>
       <c r="B209" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_PU}</t>
+          <t xml:space="preserve">{P_MW}</t>
         </is>
       </c>
       <c r="C209" s="8"/>
@@ -8026,7 +8066,7 @@
       <c r="F209" s="8"/>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q on {MVA}</t>
+          <t xml:space="preserve">their P where the inverter connects (MW)</t>
         </is>
       </c>
       <c r="H209" s="13" t="inlineStr">
@@ -8043,7 +8083,7 @@
       </c>
       <c r="B210" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_MVA}</t>
+          <t xml:space="preserve">{Q_MVAR}</t>
         </is>
       </c>
       <c r="C210" s="8"/>
@@ -8052,7 +8092,7 @@
       <c r="F210" s="8"/>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's MVA</t>
+          <t xml:space="preserve">their Q there (MVAr)</t>
         </is>
       </c>
       <c r="H210" s="13" t="inlineStr">
@@ -8069,7 +8109,7 @@
       </c>
       <c r="B211" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_P_MW}</t>
+          <t xml:space="preserve">{P_PU}</t>
         </is>
       </c>
       <c r="C211" s="8"/>
@@ -8078,7 +8118,7 @@
       <c r="F211" s="8"/>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's P (MW)</t>
+          <t xml:space="preserve">P on {MVA}</t>
         </is>
       </c>
       <c r="H211" s="13" t="inlineStr">
@@ -8095,7 +8135,7 @@
       </c>
       <c r="B212" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
+          <t xml:space="preserve">{Q_PU}</t>
         </is>
       </c>
       <c r="C212" s="8"/>
@@ -8104,7 +8144,7 @@
       <c r="F212" s="8"/>
       <c r="G212" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">one unit's Q (MVAr)</t>
+          <t xml:space="preserve">Q on {MVA}</t>
         </is>
       </c>
       <c r="H212" s="13" t="inlineStr">
@@ -8121,7 +8161,7 @@
       </c>
       <c r="B213" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_PU}</t>
+          <t xml:space="preserve">{UNIT_MVA}</t>
         </is>
       </c>
       <c r="C213" s="8"/>
@@ -8130,7 +8170,7 @@
       <c r="F213" s="8"/>
       <c r="G213" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the voltage where it connects (pu)</t>
+          <t xml:space="preserve">one unit's MVA</t>
         </is>
       </c>
       <c r="H213" s="13" t="inlineStr">
@@ -8147,7 +8187,7 @@
       </c>
       <c r="B214" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_KV}</t>
+          <t xml:space="preserve">{UNIT_P_MW}</t>
         </is>
       </c>
       <c r="C214" s="8"/>
@@ -8156,7 +8196,7 @@
       <c r="F214" s="8"/>
       <c r="G214" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same in kV</t>
+          <t xml:space="preserve">one unit's P (MW)</t>
         </is>
       </c>
       <c r="H214" s="13" t="inlineStr">
@@ -8173,7 +8213,7 @@
       </c>
       <c r="B215" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{KV}</t>
+          <t xml:space="preserve">{UNIT_Q_MVAR}</t>
         </is>
       </c>
       <c r="C215" s="8"/>
@@ -8182,7 +8222,7 @@
       <c r="F215" s="8"/>
       <c r="G215" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">that bus's base kV</t>
+          <t xml:space="preserve">one unit's Q (MVAr)</t>
         </is>
       </c>
       <c r="H215" s="13" t="inlineStr">
@@ -8199,7 +8239,7 @@
       </c>
       <c r="B216" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{ANGLE}</t>
+          <t xml:space="preserve">{V_PU}</t>
         </is>
       </c>
       <c r="C216" s="8"/>
@@ -8208,7 +8248,7 @@
       <c r="F216" s="8"/>
       <c r="G216" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
+          <t xml:space="preserve">the voltage where it connects (pu)</t>
         </is>
       </c>
       <c r="H216" s="13" t="inlineStr">
@@ -8225,7 +8265,7 @@
       </c>
       <c r="B217" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{FREQ}</t>
+          <t xml:space="preserve">{V_KV}</t>
         </is>
       </c>
       <c r="C217" s="8"/>
@@ -8234,7 +8274,7 @@
       <c r="F217" s="8"/>
       <c r="G217" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency (Hz)</t>
+          <t xml:space="preserve">the same in kV</t>
         </is>
       </c>
       <c r="H217" s="13" t="inlineStr">
@@ -8251,7 +8291,7 @@
       </c>
       <c r="B218" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{P_INV_MW}</t>
+          <t xml:space="preserve">{KV}</t>
         </is>
       </c>
       <c r="C218" s="8"/>
@@ -8260,7 +8300,7 @@
       <c r="F218" s="8"/>
       <c r="G218" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+          <t xml:space="preserve">that bus's base kV</t>
         </is>
       </c>
       <c r="H218" s="13" t="inlineStr">
@@ -8277,7 +8317,7 @@
       </c>
       <c r="B219" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{Q_INV_MVAR}</t>
+          <t xml:space="preserve">{ANGLE}</t>
         </is>
       </c>
       <c r="C219" s="8"/>
@@ -8286,7 +8326,7 @@
       <c r="F219" s="8"/>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q there (MVAr)</t>
+          <t xml:space="preserve">its PSCAD angle (deg, the transformers' phase shifts included)</t>
         </is>
       </c>
       <c r="H219" s="13" t="inlineStr">
@@ -8303,7 +8343,7 @@
       </c>
       <c r="B220" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">{V_INV_PU}</t>
+          <t xml:space="preserve">{FREQ}</t>
         </is>
       </c>
       <c r="C220" s="8"/>
@@ -8312,10 +8352,88 @@
       <c r="F220" s="8"/>
       <c r="G220" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">frequency (Hz)</t>
+        </is>
+      </c>
+      <c r="H220" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B221" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{P_INV_MW}</t>
+        </is>
+      </c>
+      <c r="C221" s="8"/>
+      <c r="D221" s="8"/>
+      <c r="E221" s="8"/>
+      <c r="F221" s="8"/>
+      <c r="G221" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P at the inverters' own terminals (MW; a UDM on the MV side)</t>
+        </is>
+      </c>
+      <c r="H221" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B222" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{Q_INV_MVAR}</t>
+        </is>
+      </c>
+      <c r="C222" s="8"/>
+      <c r="D222" s="8"/>
+      <c r="E222" s="8"/>
+      <c r="F222" s="8"/>
+      <c r="G222" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q there (MVAr)</t>
+        </is>
+      </c>
+      <c r="H222" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSCAD_Params</t>
+        </is>
+      </c>
+      <c r="B223" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{V_INV_PU}</t>
+        </is>
+      </c>
+      <c r="C223" s="8"/>
+      <c r="D223" s="8"/>
+      <c r="E223" s="8"/>
+      <c r="F223" s="8"/>
+      <c r="G223" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">the voltage there (pu)</t>
         </is>
       </c>
-      <c r="H220" s="13" t="inlineStr">
+      <c r="H223" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD</t>
         </is>
@@ -8328,32 +8446,32 @@
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A55:H55"/>
     <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A131:H131"/>
-    <mergeCell ref="A146:H146"/>
-    <mergeCell ref="A156:H156"/>
+    <mergeCell ref="A134:H134"/>
+    <mergeCell ref="A149:H149"/>
     <mergeCell ref="A159:H159"/>
-    <mergeCell ref="A165:H165"/>
-    <mergeCell ref="A175:H175"/>
-    <mergeCell ref="A179:H179"/>
-    <mergeCell ref="A184:H184"/>
+    <mergeCell ref="A162:H162"/>
+    <mergeCell ref="A168:H168"/>
+    <mergeCell ref="A178:H178"/>
+    <mergeCell ref="A182:H182"/>
     <mergeCell ref="A187:H187"/>
-    <mergeCell ref="A191:H191"/>
-    <mergeCell ref="A203:H203"/>
+    <mergeCell ref="A190:H190"/>
+    <mergeCell ref="A194:H194"/>
+    <mergeCell ref="A206:H206"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'Plant'!A1" display="Plant"/>
     <hyperlink ref="A55" location="'MPT'!A1" display="MPT"/>
     <hyperlink ref="A87" location="'Generators'!A1" display="Generators"/>
-    <hyperlink ref="A131" location="'Feeders'!A1" display="Feeders"/>
-    <hyperlink ref="A146" location="'Cables'!A1" display="Cables"/>
-    <hyperlink ref="A156" location="'Collectors'!A1" display="Collectors"/>
-    <hyperlink ref="A159" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
-    <hyperlink ref="A165" location="'Machines'!A1" display="Machines"/>
-    <hyperlink ref="A175" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
-    <hyperlink ref="A179" location="'Dyr_Params'!A1" display="Dyr_Params"/>
-    <hyperlink ref="A184" location="'Dyr_Records'!A1" display="Dyr_Records"/>
-    <hyperlink ref="A187" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
-    <hyperlink ref="A203" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A134" location="'Feeders'!A1" display="Feeders"/>
+    <hyperlink ref="A149" location="'Cables'!A1" display="Cables"/>
+    <hyperlink ref="A159" location="'Collectors'!A1" display="Collectors"/>
+    <hyperlink ref="A162" location="'Loads_Shunts'!A1" display="Loads_Shunts"/>
+    <hyperlink ref="A168" location="'Machines'!A1" display="Machines"/>
+    <hyperlink ref="A178" location="'Bus_Numbers'!A1" display="Bus_Numbers"/>
+    <hyperlink ref="A182" location="'Dyr_Params'!A1" display="Dyr_Params"/>
+    <hyperlink ref="A187" location="'Dyr_Records'!A1" display="Dyr_Records"/>
+    <hyperlink ref="A190" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
+    <hyperlink ref="A206" location="'PSCAD_Params'!A1" display="PSCAD_Params"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -18375,7 +18493,7 @@
     <row r="388" ht="18" customHeight="1">
       <c r="A388" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GENROU -- synchronous machine, round rotor (type SYNC)</t>
+          <t xml:space="preserve">GENROU -- synchronous machine, round rotor (type SYNC; Machine model)</t>
         </is>
       </c>
       <c r="B388" s="7"/>
@@ -18751,7 +18869,7 @@
     <row r="403" ht="18" customHeight="1">
       <c r="A403" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEXS -- simplified excitation system (type SYNC)</t>
+          <t xml:space="preserve">SEXS -- simplified excitation system (type SYNC; Exciter model)</t>
         </is>
       </c>
       <c r="B403" s="7"/>
@@ -18919,7 +19037,7 @@
     <row r="410" ht="18" customHeight="1">
       <c r="A410" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TGOV1 -- steam turbine-governor (type SYNC)</t>
+          <t xml:space="preserve">TGOV1 -- steam turbine-governor (type SYNC; Governor model)</t>
         </is>
       </c>
       <c r="B410" s="7"/>
@@ -19117,7 +19235,7 @@
     <row r="418" ht="18" customHeight="1">
       <c r="A418" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT -- </t>
+          <t xml:space="preserve">GENSAL -- synchronous machine, salient pole: hydro (type SYNC; Machine model)</t>
         </is>
       </c>
       <c r="B418" s="7"/>
@@ -19129,7 +19247,7 @@
     <row r="419">
       <c r="A419" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B419" s="8" t="inlineStr">
@@ -19139,19 +19257,23 @@
       </c>
       <c r="C419" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">vref</t>
+          <t xml:space="preserve">Tdop</t>
         </is>
       </c>
       <c r="D419" s="8">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="E419" s="8"/>
-      <c r="F419" s="8"/>
+      <c r="F419" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T'do (s)</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B420" s="8" t="inlineStr">
@@ -19161,19 +19283,23 @@
       </c>
       <c r="C420" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp1</t>
+          <t xml:space="preserve">Tdopp</t>
         </is>
       </c>
       <c r="D420" s="8">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E420" s="8"/>
-      <c r="F420" s="8"/>
+      <c r="F420" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T''do (s)</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B421" s="8" t="inlineStr">
@@ -19183,19 +19309,23 @@
       </c>
       <c r="C421" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp2</t>
+          <t xml:space="preserve">Tqopp</t>
         </is>
       </c>
       <c r="D421" s="8">
-        <v>0.175</v>
+        <v>0.1</v>
       </c>
       <c r="E421" s="8"/>
-      <c r="F421" s="8"/>
+      <c r="F421" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T''qo (s)</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B422" s="8" t="inlineStr">
@@ -19205,19 +19335,23 @@
       </c>
       <c r="C422" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp3</t>
+          <t xml:space="preserve">H</t>
         </is>
       </c>
       <c r="D422" s="8">
-        <v>0.15</v>
+        <v>3.0</v>
       </c>
       <c r="E422" s="8"/>
-      <c r="F422" s="8"/>
+      <c r="F422" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inertia constant (s; 0 = infinite bus)</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B423" s="8" t="inlineStr">
@@ -19227,19 +19361,23 @@
       </c>
       <c r="C423" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp4</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="D423" s="8">
-        <v>0.1</v>
+        <v>0.0</v>
       </c>
       <c r="E423" s="8"/>
-      <c r="F423" s="8"/>
+      <c r="F423" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">damping (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B424" s="8" t="inlineStr">
@@ -19249,19 +19387,23 @@
       </c>
       <c r="C424" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp5</t>
+          <t xml:space="preserve">Xd</t>
         </is>
       </c>
       <c r="D424" s="8">
-        <v>-0.55</v>
+        <v>1.0</v>
       </c>
       <c r="E424" s="8"/>
-      <c r="F424" s="8"/>
+      <c r="F424" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xd (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B425" s="8" t="inlineStr">
@@ -19271,19 +19413,23 @@
       </c>
       <c r="C425" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp6</t>
+          <t xml:space="preserve">Xq</t>
         </is>
       </c>
       <c r="D425" s="8">
-        <v>-0.35</v>
+        <v>0.6</v>
       </c>
       <c r="E425" s="8"/>
-      <c r="F425" s="8"/>
+      <c r="F425" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xq (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B426" s="8" t="inlineStr">
@@ -19293,19 +19439,23 @@
       </c>
       <c r="C426" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp7</t>
+          <t xml:space="preserve">Xdp</t>
         </is>
       </c>
       <c r="D426" s="8">
-        <v>-0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E426" s="8"/>
-      <c r="F426" s="8"/>
+      <c r="F426" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X'd (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B427" s="8" t="inlineStr">
@@ -19315,19 +19465,23 @@
       </c>
       <c r="C427" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp8</t>
+          <t xml:space="preserve">Xdpp</t>
         </is>
       </c>
       <c r="D427" s="8">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E427" s="8"/>
-      <c r="F427" s="8"/>
+      <c r="F427" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X''d (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B428" s="8" t="inlineStr">
@@ -19337,19 +19491,23 @@
       </c>
       <c r="C428" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp9</t>
+          <t xml:space="preserve">Xl</t>
         </is>
       </c>
       <c r="D428" s="8">
-        <v>0.0</v>
+        <v>0.15</v>
       </c>
       <c r="E428" s="8"/>
-      <c r="F428" s="8"/>
+      <c r="F428" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leakage reactance (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B429" s="8" t="inlineStr">
@@ -19359,19 +19517,23 @@
       </c>
       <c r="C429" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dvtrp10</t>
+          <t xml:space="preserve">S1</t>
         </is>
       </c>
       <c r="D429" s="8">
-        <v>0.0</v>
+        <v>0.1</v>
       </c>
       <c r="E429" s="8"/>
-      <c r="F429" s="8"/>
+      <c r="F429" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saturation at 1.0 pu</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">GENSAL</t>
         </is>
       </c>
       <c r="B430" s="8" t="inlineStr">
@@ -19381,733 +19543,3411 @@
       </c>
       <c r="C430" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp1</t>
+          <t xml:space="preserve">S12</t>
         </is>
       </c>
       <c r="D430" s="8">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
       <c r="E430" s="8"/>
-      <c r="F430" s="8"/>
-    </row>
-    <row r="431">
-      <c r="A431" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LHVRT</t>
-        </is>
-      </c>
-      <c r="B431" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CON13</t>
-        </is>
-      </c>
-      <c r="C431" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dttrp2</t>
-        </is>
-      </c>
-      <c r="D431" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="E431" s="8"/>
-      <c r="F431" s="8"/>
+      <c r="F430" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saturation at 1.2 pu</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="18" customHeight="1">
+      <c r="A431" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEET1 -- IEEE type 1 excitation system: a DC exciter (type SYNC; Exciter model)</t>
+        </is>
+      </c>
+      <c r="B431" s="7"/>
+      <c r="C431" s="7"/>
+      <c r="D431" s="7"/>
+      <c r="E431" s="7"/>
+      <c r="F431" s="7"/>
     </row>
     <row r="432">
       <c r="A432" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B432" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON14</t>
+          <t xml:space="preserve">CON1</t>
         </is>
       </c>
       <c r="C432" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp3</t>
+          <t xml:space="preserve">TR</t>
         </is>
       </c>
       <c r="D432" s="8">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="E432" s="8"/>
-      <c r="F432" s="8"/>
+      <c r="F432" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voltage measurement time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B433" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON15</t>
+          <t xml:space="preserve">CON2</t>
         </is>
       </c>
       <c r="C433" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp4</t>
+          <t xml:space="preserve">KA</t>
         </is>
       </c>
       <c r="D433" s="8">
-        <v>1.0</v>
+        <v>400.0</v>
       </c>
       <c r="E433" s="8"/>
-      <c r="F433" s="8"/>
+      <c r="F433" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voltage regulator gain</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B434" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON16</t>
+          <t xml:space="preserve">CON3</t>
         </is>
       </c>
       <c r="C434" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp5</t>
+          <t xml:space="preserve">TA</t>
         </is>
       </c>
       <c r="D434" s="8">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="E434" s="8"/>
-      <c r="F434" s="8"/>
+      <c r="F434" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B435" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON17</t>
+          <t xml:space="preserve">CON4</t>
         </is>
       </c>
       <c r="C435" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp6</t>
+          <t xml:space="preserve">VRMAX</t>
         </is>
       </c>
       <c r="D435" s="8">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="E435" s="8"/>
-      <c r="F435" s="8"/>
+      <c r="F435" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator output, upper (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B436" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON18</t>
+          <t xml:space="preserve">CON5</t>
         </is>
       </c>
       <c r="C436" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp7</t>
+          <t xml:space="preserve">VRMIN</t>
         </is>
       </c>
       <c r="D436" s="8">
-        <v>2.0</v>
+        <v>-7.3</v>
       </c>
       <c r="E436" s="8"/>
-      <c r="F436" s="8"/>
+      <c r="F436" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator output, lower (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B437" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON19</t>
+          <t xml:space="preserve">CON6</t>
         </is>
       </c>
       <c r="C437" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp8</t>
+          <t xml:space="preserve">KE</t>
         </is>
       </c>
       <c r="D437" s="8">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E437" s="8"/>
-      <c r="F437" s="8"/>
+      <c r="F437" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exciter constant (self-excited field)</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B438" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON20</t>
+          <t xml:space="preserve">CON7</t>
         </is>
       </c>
       <c r="C438" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp9</t>
+          <t xml:space="preserve">TE</t>
         </is>
       </c>
       <c r="D438" s="8">
-        <v>0.0</v>
+        <v>0.8</v>
       </c>
       <c r="E438" s="8"/>
-      <c r="F438" s="8"/>
+      <c r="F438" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exciter time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B439" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON21</t>
+          <t xml:space="preserve">CON8</t>
         </is>
       </c>
       <c r="C439" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp10</t>
+          <t xml:space="preserve">KF</t>
         </is>
       </c>
       <c r="D439" s="8">
-        <v>0.0</v>
+        <v>0.03</v>
       </c>
       <c r="E439" s="8"/>
-      <c r="F439" s="8"/>
+      <c r="F439" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rate feedback gain</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHVRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B440" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON22</t>
+          <t xml:space="preserve">CON9</t>
         </is>
       </c>
       <c r="C440" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">alarm</t>
+          <t xml:space="preserve">TF</t>
         </is>
       </c>
       <c r="D440" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E440" s="8"/>
+      <c r="F440" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rate feedback time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEET1</t>
+        </is>
+      </c>
+      <c r="B441" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON10</t>
+        </is>
+      </c>
+      <c r="C441" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Switch</t>
+        </is>
+      </c>
+      <c r="D441" s="8">
         <v>0</v>
       </c>
-      <c r="E440" s="8"/>
-      <c r="F440" s="8"/>
-    </row>
-    <row r="441" ht="18" customHeight="1">
-      <c r="A441" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LHFRT -- </t>
-        </is>
-      </c>
-      <c r="B441" s="7"/>
-      <c r="C441" s="7"/>
-      <c r="D441" s="7"/>
-      <c r="E441" s="7"/>
-      <c r="F441" s="7"/>
+      <c r="E441" s="8"/>
+      <c r="F441" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (PSS/E's switch, not used)</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B442" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON1</t>
+          <t xml:space="preserve">CON11</t>
         </is>
       </c>
       <c r="C442" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">fref</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="D442" s="8">
-        <v>60.0</v>
+        <v>3.0</v>
       </c>
       <c r="E442" s="8"/>
-      <c r="F442" s="8"/>
+      <c r="F442" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field voltage of the first saturation point (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B443" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON2</t>
+          <t xml:space="preserve">CON12</t>
         </is>
       </c>
       <c r="C443" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp1</t>
+          <t xml:space="preserve">SE1</t>
         </is>
       </c>
       <c r="D443" s="8">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="E443" s="8"/>
-      <c r="F443" s="8"/>
+      <c r="F443" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saturation at E1</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B444" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON3</t>
+          <t xml:space="preserve">CON13</t>
         </is>
       </c>
       <c r="C444" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp2</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="D444" s="8">
-        <v>1.6</v>
+        <v>4.0</v>
       </c>
       <c r="E444" s="8"/>
-      <c r="F444" s="8"/>
+      <c r="F444" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field voltage of the second saturation point (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">IEEET1</t>
         </is>
       </c>
       <c r="B445" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON4</t>
+          <t xml:space="preserve">CON14</t>
         </is>
       </c>
       <c r="C445" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp3</t>
+          <t xml:space="preserve">SE2</t>
         </is>
       </c>
       <c r="D445" s="8">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E445" s="8"/>
-      <c r="F445" s="8"/>
-    </row>
-    <row r="446">
-      <c r="A446" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LHFRT</t>
-        </is>
-      </c>
-      <c r="B446" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CON5</t>
-        </is>
-      </c>
-      <c r="C446" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dftrp4</t>
-        </is>
-      </c>
-      <c r="D446" s="8">
-        <v>-3.0</v>
-      </c>
-      <c r="E446" s="8"/>
-      <c r="F446" s="8"/>
+      <c r="F445" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saturation at E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="18" customHeight="1">
+      <c r="A446" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESST1A -- IEEE ST1A static excitation system, fed from the terminals (type SYNC; Exciter model)</t>
+        </is>
+      </c>
+      <c r="B446" s="7"/>
+      <c r="C446" s="7"/>
+      <c r="D446" s="7"/>
+      <c r="E446" s="7"/>
+      <c r="F446" s="7"/>
     </row>
     <row r="447">
       <c r="A447" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B447" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON6</t>
+          <t xml:space="preserve">ICON1</t>
         </is>
       </c>
       <c r="C447" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp5</t>
+          <t xml:space="preserve">UEL</t>
         </is>
       </c>
       <c r="D447" s="8">
-        <v>-2.7</v>
+        <v>1</v>
       </c>
       <c r="E447" s="8"/>
-      <c r="F447" s="8"/>
+      <c r="F447" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where the underexcitation limiter acts: 1, 2 or 3</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B448" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON7</t>
+          <t xml:space="preserve">ICON2</t>
         </is>
       </c>
       <c r="C448" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp6</t>
+          <t xml:space="preserve">VOS</t>
         </is>
       </c>
       <c r="D448" s="8">
-        <v>-2.2</v>
+        <v>1</v>
       </c>
       <c r="E448" s="8"/>
-      <c r="F448" s="8"/>
+      <c r="F448" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where the stabilizer acts: 1 or 2</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B449" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON8</t>
+          <t xml:space="preserve">CON1</t>
         </is>
       </c>
       <c r="C449" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp7</t>
+          <t xml:space="preserve">TR</t>
         </is>
       </c>
       <c r="D449" s="8">
-        <v>-1.6</v>
+        <v>0.02</v>
       </c>
       <c r="E449" s="8"/>
-      <c r="F449" s="8"/>
+      <c r="F449" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voltage measurement time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B450" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON9</t>
+          <t xml:space="preserve">CON2</t>
         </is>
       </c>
       <c r="C450" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp8</t>
+          <t xml:space="preserve">VIMAX</t>
         </is>
       </c>
       <c r="D450" s="8">
-        <v>-0.6</v>
+        <v>999.0</v>
       </c>
       <c r="E450" s="8"/>
-      <c r="F450" s="8"/>
+      <c r="F450" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator input error, upper (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B451" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON10</t>
+          <t xml:space="preserve">CON3</t>
         </is>
       </c>
       <c r="C451" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp9</t>
+          <t xml:space="preserve">VIMIN</t>
         </is>
       </c>
       <c r="D451" s="8">
-        <v>0.0</v>
+        <v>-999.0</v>
       </c>
       <c r="E451" s="8"/>
-      <c r="F451" s="8"/>
+      <c r="F451" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator input error, lower (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B452" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON11</t>
+          <t xml:space="preserve">CON4</t>
         </is>
       </c>
       <c r="C452" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dftrp10</t>
+          <t xml:space="preserve">TC</t>
         </is>
       </c>
       <c r="D452" s="8">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E452" s="8"/>
-      <c r="F452" s="8"/>
+      <c r="F452" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B453" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON12</t>
+          <t xml:space="preserve">CON5</t>
         </is>
       </c>
       <c r="C453" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp1</t>
+          <t xml:space="preserve">TB</t>
         </is>
       </c>
       <c r="D453" s="8">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E453" s="8"/>
-      <c r="F453" s="8"/>
+      <c r="F453" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lag time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B454" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON13</t>
+          <t xml:space="preserve">CON6</t>
         </is>
       </c>
       <c r="C454" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp2</t>
+          <t xml:space="preserve">TC1</t>
         </is>
       </c>
       <c r="D454" s="8">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="E454" s="8"/>
-      <c r="F454" s="8"/>
+      <c r="F454" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">second lead time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B455" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON14</t>
+          <t xml:space="preserve">CON7</t>
         </is>
       </c>
       <c r="C455" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp3</t>
+          <t xml:space="preserve">TB1</t>
         </is>
       </c>
       <c r="D455" s="8">
-        <v>180.0</v>
+        <v>0.0</v>
       </c>
       <c r="E455" s="8"/>
-      <c r="F455" s="8"/>
+      <c r="F455" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">second lag time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B456" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON15</t>
+          <t xml:space="preserve">CON8</t>
         </is>
       </c>
       <c r="C456" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp4</t>
+          <t xml:space="preserve">KA</t>
         </is>
       </c>
       <c r="D456" s="8">
-        <v>0.0</v>
+        <v>210.0</v>
       </c>
       <c r="E456" s="8"/>
-      <c r="F456" s="8"/>
+      <c r="F456" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voltage regulator gain</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B457" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON16</t>
+          <t xml:space="preserve">CON9</t>
         </is>
       </c>
       <c r="C457" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp5</t>
+          <t xml:space="preserve">TA</t>
         </is>
       </c>
       <c r="D457" s="8">
-        <v>0.75</v>
+        <v>0.0</v>
       </c>
       <c r="E457" s="8"/>
-      <c r="F457" s="8"/>
+      <c r="F457" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator time constant (s)</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B458" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON17</t>
+          <t xml:space="preserve">CON10</t>
         </is>
       </c>
       <c r="C458" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp6</t>
+          <t xml:space="preserve">VAMAX</t>
         </is>
       </c>
       <c r="D458" s="8">
-        <v>7.5</v>
+        <v>999.0</v>
       </c>
       <c r="E458" s="8"/>
-      <c r="F458" s="8"/>
+      <c r="F458" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amplifier output, upper (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B459" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON18</t>
+          <t xml:space="preserve">CON11</t>
         </is>
       </c>
       <c r="C459" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp7</t>
+          <t xml:space="preserve">VAMIN</t>
         </is>
       </c>
       <c r="D459" s="8">
-        <v>30.0</v>
+        <v>-999.0</v>
       </c>
       <c r="E459" s="8"/>
-      <c r="F459" s="8"/>
+      <c r="F459" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amplifier output, lower (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B460" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON19</t>
+          <t xml:space="preserve">CON12</t>
         </is>
       </c>
       <c r="C460" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp8</t>
+          <t xml:space="preserve">VRMAX</t>
         </is>
       </c>
       <c r="D460" s="8">
-        <v>180.0</v>
+        <v>6.43</v>
       </c>
       <c r="E460" s="8"/>
-      <c r="F460" s="8"/>
+      <c r="F460" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator output, upper (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B461" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON20</t>
+          <t xml:space="preserve">CON13</t>
         </is>
       </c>
       <c r="C461" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp9</t>
+          <t xml:space="preserve">VRMIN</t>
         </is>
       </c>
       <c r="D461" s="8">
-        <v>0.0</v>
+        <v>-6.0</v>
       </c>
       <c r="E461" s="8"/>
-      <c r="F461" s="8"/>
+      <c r="F461" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator output, lower (pu)</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LHFRT</t>
+          <t xml:space="preserve">ESST1A</t>
         </is>
       </c>
       <c r="B462" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON21</t>
+          <t xml:space="preserve">CON14</t>
         </is>
       </c>
       <c r="C462" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dttrp10</t>
+          <t xml:space="preserve">KC</t>
         </is>
       </c>
       <c r="D462" s="8">
-        <v>0.0</v>
+        <v>0.038</v>
       </c>
       <c r="E462" s="8"/>
-      <c r="F462" s="8"/>
+      <c r="F462" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rectifier loading factor (commutating reactance)</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">ESST1A</t>
+        </is>
+      </c>
+      <c r="B463" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON15</t>
+        </is>
+      </c>
+      <c r="C463" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KF</t>
+        </is>
+      </c>
+      <c r="D463" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E463" s="8"/>
+      <c r="F463" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rate feedback gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESST1A</t>
+        </is>
+      </c>
+      <c r="B464" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON16</t>
+        </is>
+      </c>
+      <c r="C464" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TF</t>
+        </is>
+      </c>
+      <c r="D464" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E464" s="8"/>
+      <c r="F464" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rate feedback time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESST1A</t>
+        </is>
+      </c>
+      <c r="B465" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON17</t>
+        </is>
+      </c>
+      <c r="C465" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KLR</t>
+        </is>
+      </c>
+      <c r="D465" s="8">
+        <v>4.54</v>
+      </c>
+      <c r="E465" s="8"/>
+      <c r="F465" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field current limiter gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESST1A</t>
+        </is>
+      </c>
+      <c r="B466" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON18</t>
+        </is>
+      </c>
+      <c r="C466" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ILR</t>
+        </is>
+      </c>
+      <c r="D466" s="8">
+        <v>4.4</v>
+      </c>
+      <c r="E466" s="8"/>
+      <c r="F466" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field current limit (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="18" customHeight="1">
+      <c r="A467" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1 -- IEEE ST1 static excitation system, the older form (type SYNC; Exciter model)</t>
+        </is>
+      </c>
+      <c r="B467" s="7"/>
+      <c r="C467" s="7"/>
+      <c r="D467" s="7"/>
+      <c r="E467" s="7"/>
+      <c r="F467" s="7"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B468" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON1</t>
+        </is>
+      </c>
+      <c r="C468" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TR</t>
+        </is>
+      </c>
+      <c r="D468" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="E468" s="8"/>
+      <c r="F468" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voltage measurement time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B469" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON2</t>
+        </is>
+      </c>
+      <c r="C469" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIMAX</t>
+        </is>
+      </c>
+      <c r="D469" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E469" s="8"/>
+      <c r="F469" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator input error, upper (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B470" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON3</t>
+        </is>
+      </c>
+      <c r="C470" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIMIN</t>
+        </is>
+      </c>
+      <c r="D470" s="8">
+        <v>-0.2</v>
+      </c>
+      <c r="E470" s="8"/>
+      <c r="F470" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator input error, lower (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B471" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON4</t>
+        </is>
+      </c>
+      <c r="C471" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC</t>
+        </is>
+      </c>
+      <c r="D471" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E471" s="8"/>
+      <c r="F471" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lead time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B472" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON5</t>
+        </is>
+      </c>
+      <c r="C472" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TB</t>
+        </is>
+      </c>
+      <c r="D472" s="8">
+        <v>10.0</v>
+      </c>
+      <c r="E472" s="8"/>
+      <c r="F472" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lag time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B473" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON6</t>
+        </is>
+      </c>
+      <c r="C473" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KA</t>
+        </is>
+      </c>
+      <c r="D473" s="8">
+        <v>200.0</v>
+      </c>
+      <c r="E473" s="8"/>
+      <c r="F473" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voltage regulator gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B474" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON7</t>
+        </is>
+      </c>
+      <c r="C474" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TA</t>
+        </is>
+      </c>
+      <c r="D474" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="E474" s="8"/>
+      <c r="F474" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B475" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON8</t>
+        </is>
+      </c>
+      <c r="C475" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VRMAX</t>
+        </is>
+      </c>
+      <c r="D475" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="E475" s="8"/>
+      <c r="F475" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator output, upper (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B476" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON9</t>
+        </is>
+      </c>
+      <c r="C476" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VRMIN</t>
+        </is>
+      </c>
+      <c r="D476" s="8">
+        <v>-5.0</v>
+      </c>
+      <c r="E476" s="8"/>
+      <c r="F476" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regulator output, lower (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B477" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON10</t>
+        </is>
+      </c>
+      <c r="C477" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KC</t>
+        </is>
+      </c>
+      <c r="D477" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="E477" s="8"/>
+      <c r="F477" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rectifier loading factor (commutating reactance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B478" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON11</t>
+        </is>
+      </c>
+      <c r="C478" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KF</t>
+        </is>
+      </c>
+      <c r="D478" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E478" s="8"/>
+      <c r="F478" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rate feedback gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EXST1</t>
+        </is>
+      </c>
+      <c r="B479" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON12</t>
+        </is>
+      </c>
+      <c r="C479" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TF</t>
+        </is>
+      </c>
+      <c r="D479" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E479" s="8"/>
+      <c r="F479" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rate feedback time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="18" customHeight="1">
+      <c r="A480" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV -- hydro turbine-governor with its penstock (type SYNC; Governor model)</t>
+        </is>
+      </c>
+      <c r="B480" s="7"/>
+      <c r="C480" s="7"/>
+      <c r="D480" s="7"/>
+      <c r="E480" s="7"/>
+      <c r="F480" s="7"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B481" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON1</t>
+        </is>
+      </c>
+      <c r="C481" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R</t>
+        </is>
+      </c>
+      <c r="D481" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="E481" s="8"/>
+      <c r="F481" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">permanent droop (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B482" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON2</t>
+        </is>
+      </c>
+      <c r="C482" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">r</t>
+        </is>
+      </c>
+      <c r="D482" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="E482" s="8"/>
+      <c r="F482" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">temporary droop (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B483" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON3</t>
+        </is>
+      </c>
+      <c r="C483" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tr</t>
+        </is>
+      </c>
+      <c r="D483" s="8">
+        <v>5.0</v>
+      </c>
+      <c r="E483" s="8"/>
+      <c r="F483" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B484" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON4</t>
+        </is>
+      </c>
+      <c r="C484" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tf</t>
+        </is>
+      </c>
+      <c r="D484" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="E484" s="8"/>
+      <c r="F484" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">filter time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B485" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON5</t>
+        </is>
+      </c>
+      <c r="C485" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tg</t>
+        </is>
+      </c>
+      <c r="D485" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E485" s="8"/>
+      <c r="F485" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate servo time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B486" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON6</t>
+        </is>
+      </c>
+      <c r="C486" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VELM</t>
+        </is>
+      </c>
+      <c r="D486" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E486" s="8"/>
+      <c r="F486" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate velocity limit (pu/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B487" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON7</t>
+        </is>
+      </c>
+      <c r="C487" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GMAX</t>
+        </is>
+      </c>
+      <c r="D487" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E487" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
+        </is>
+      </c>
+      <c r="F487" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate opening, upper (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B488" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON8</t>
+        </is>
+      </c>
+      <c r="C488" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GMIN</t>
+        </is>
+      </c>
+      <c r="D488" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E488" s="8"/>
+      <c r="F488" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate opening, lower (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B489" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON9</t>
+        </is>
+      </c>
+      <c r="C489" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TW</t>
+        </is>
+      </c>
+      <c r="D489" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E489" s="8"/>
+      <c r="F489" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">water inertia time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B490" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON10</t>
+        </is>
+      </c>
+      <c r="C490" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At</t>
+        </is>
+      </c>
+      <c r="D490" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="E490" s="8"/>
+      <c r="F490" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turbine gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B491" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON11</t>
+        </is>
+      </c>
+      <c r="C491" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dturb</t>
+        </is>
+      </c>
+      <c r="D491" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E491" s="8"/>
+      <c r="F491" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turbine damping (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HYGOV</t>
+        </is>
+      </c>
+      <c r="B492" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON12</t>
+        </is>
+      </c>
+      <c r="C492" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">qNL</t>
+        </is>
+      </c>
+      <c r="D492" s="8">
+        <v>0.08</v>
+      </c>
+      <c r="E492" s="8"/>
+      <c r="F492" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no-load flow (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="18" customHeight="1">
+      <c r="A493" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST -- gas turbine-governor (type SYNC; Governor model)</t>
+        </is>
+      </c>
+      <c r="B493" s="7"/>
+      <c r="C493" s="7"/>
+      <c r="D493" s="7"/>
+      <c r="E493" s="7"/>
+      <c r="F493" s="7"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B494" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON1</t>
+        </is>
+      </c>
+      <c r="C494" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R</t>
+        </is>
+      </c>
+      <c r="D494" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="E494" s="8"/>
+      <c r="F494" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">droop (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B495" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON2</t>
+        </is>
+      </c>
+      <c r="C495" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T1</t>
+        </is>
+      </c>
+      <c r="D495" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E495" s="8"/>
+      <c r="F495" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuel valve time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B496" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON3</t>
+        </is>
+      </c>
+      <c r="C496" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T2</t>
+        </is>
+      </c>
+      <c r="D496" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E496" s="8"/>
+      <c r="F496" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuel system time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B497" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON4</t>
+        </is>
+      </c>
+      <c r="C497" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T3</t>
+        </is>
+      </c>
+      <c r="D497" s="8">
+        <v>3.0</v>
+      </c>
+      <c r="E497" s="8"/>
+      <c r="F497" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">load limit time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B498" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON5</t>
+        </is>
+      </c>
+      <c r="C498" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AT</t>
+        </is>
+      </c>
+      <c r="D498" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E498" s="8"/>
+      <c r="F498" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">load limit (ambient temperature) (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B499" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON6</t>
+        </is>
+      </c>
+      <c r="C499" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KT</t>
+        </is>
+      </c>
+      <c r="D499" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="E499" s="8"/>
+      <c r="F499" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">load limit feedback gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B500" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON7</t>
+        </is>
+      </c>
+      <c r="C500" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VMAX</t>
+        </is>
+      </c>
+      <c r="D500" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E500" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
+        </is>
+      </c>
+      <c r="F500" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuel valve, upper (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B501" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON8</t>
+        </is>
+      </c>
+      <c r="C501" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VMIN</t>
+        </is>
+      </c>
+      <c r="D501" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E501" s="8"/>
+      <c r="F501" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuel valve, lower (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAST</t>
+        </is>
+      </c>
+      <c r="B502" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON9</t>
+        </is>
+      </c>
+      <c r="C502" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dturb</t>
+        </is>
+      </c>
+      <c r="D502" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E502" s="8"/>
+      <c r="F502" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turbine damping (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="18" customHeight="1">
+      <c r="A503" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1 -- IEEE type 1 steam turbine-governor, its stages (type SYNC; Governor model)</t>
+        </is>
+      </c>
+      <c r="B503" s="7"/>
+      <c r="C503" s="7"/>
+      <c r="D503" s="7"/>
+      <c r="E503" s="7"/>
+      <c r="F503" s="7"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B504" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICON1</t>
+        </is>
+      </c>
+      <c r="C504" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IBUS</t>
+        </is>
+      </c>
+      <c r="D504" s="8">
+        <v>0</v>
+      </c>
+      <c r="E504" s="8"/>
+      <c r="F504" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a cross-compound unit's low-pressure machine bus (0 = none)</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B505" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICON2</t>
+        </is>
+      </c>
+      <c r="C505" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
+      <c r="D505" s="8">
+        <v>0</v>
+      </c>
+      <c r="E505" s="8"/>
+      <c r="F505" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its machine (0 = none)</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B506" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON1</t>
+        </is>
+      </c>
+      <c r="C506" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="D506" s="8">
+        <v>20.0</v>
+      </c>
+      <c r="E506" s="8"/>
+      <c r="F506" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor gain, 1 / droop</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B507" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON2</t>
+        </is>
+      </c>
+      <c r="C507" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T1</t>
+        </is>
+      </c>
+      <c r="D507" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E507" s="8"/>
+      <c r="F507" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor lag time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B508" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON3</t>
+        </is>
+      </c>
+      <c r="C508" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T2</t>
+        </is>
+      </c>
+      <c r="D508" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E508" s="8"/>
+      <c r="F508" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">governor lead time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B509" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON4</t>
+        </is>
+      </c>
+      <c r="C509" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T3</t>
+        </is>
+      </c>
+      <c r="D509" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E509" s="8"/>
+      <c r="F509" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valve positioner time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B510" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON5</t>
+        </is>
+      </c>
+      <c r="C510" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uo</t>
+        </is>
+      </c>
+      <c r="D510" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E510" s="8"/>
+      <c r="F510" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valve opening rate (pu/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B511" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON6</t>
+        </is>
+      </c>
+      <c r="C511" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uc</t>
+        </is>
+      </c>
+      <c r="D511" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="E511" s="8"/>
+      <c r="F511" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valve closing rate (pu/s, negative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B512" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON7</t>
+        </is>
+      </c>
+      <c r="C512" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMAX</t>
+        </is>
+      </c>
+      <c r="D512" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E512" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">auto</t>
+        </is>
+      </c>
+      <c r="F512" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valve opening, upper (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B513" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON8</t>
+        </is>
+      </c>
+      <c r="C513" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMIN</t>
+        </is>
+      </c>
+      <c r="D513" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E513" s="8"/>
+      <c r="F513" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">valve opening, lower (pu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B514" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON9</t>
+        </is>
+      </c>
+      <c r="C514" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T4</t>
+        </is>
+      </c>
+      <c r="D514" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="E514" s="8"/>
+      <c r="F514" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 1 time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B515" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON10</t>
+        </is>
+      </c>
+      <c r="C515" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K1</t>
+        </is>
+      </c>
+      <c r="D515" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="E515" s="8"/>
+      <c r="F515" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 1's share of its power (high-pressure machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B516" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON11</t>
+        </is>
+      </c>
+      <c r="C516" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K2</t>
+        </is>
+      </c>
+      <c r="D516" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E516" s="8"/>
+      <c r="F516" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 1's share of its power (low-pressure machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B517" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON12</t>
+        </is>
+      </c>
+      <c r="C517" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T5</t>
+        </is>
+      </c>
+      <c r="D517" s="8">
+        <v>7.0</v>
+      </c>
+      <c r="E517" s="8"/>
+      <c r="F517" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 2 time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B518" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON13</t>
+        </is>
+      </c>
+      <c r="C518" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K3</t>
+        </is>
+      </c>
+      <c r="D518" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="E518" s="8"/>
+      <c r="F518" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 2's share of its power (high-pressure machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B519" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON14</t>
+        </is>
+      </c>
+      <c r="C519" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K4</t>
+        </is>
+      </c>
+      <c r="D519" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E519" s="8"/>
+      <c r="F519" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 2's share of its power (low-pressure machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B520" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON15</t>
+        </is>
+      </c>
+      <c r="C520" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T6</t>
+        </is>
+      </c>
+      <c r="D520" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E520" s="8"/>
+      <c r="F520" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 3 time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B521" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON16</t>
+        </is>
+      </c>
+      <c r="C521" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K5</t>
+        </is>
+      </c>
+      <c r="D521" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="E521" s="8"/>
+      <c r="F521" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 3's share of its power (high-pressure machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B522" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON17</t>
+        </is>
+      </c>
+      <c r="C522" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K6</t>
+        </is>
+      </c>
+      <c r="D522" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E522" s="8"/>
+      <c r="F522" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 3's share of its power (low-pressure machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B523" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON18</t>
+        </is>
+      </c>
+      <c r="C523" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T7</t>
+        </is>
+      </c>
+      <c r="D523" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E523" s="8"/>
+      <c r="F523" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 4 time constant (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B524" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON19</t>
+        </is>
+      </c>
+      <c r="C524" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K7</t>
+        </is>
+      </c>
+      <c r="D524" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E524" s="8"/>
+      <c r="F524" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 4's share of its power (high-pressure machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEEEG1</t>
+        </is>
+      </c>
+      <c r="B525" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON20</t>
+        </is>
+      </c>
+      <c r="C525" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K8</t>
+        </is>
+      </c>
+      <c r="D525" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E525" s="8"/>
+      <c r="F525" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage 4's share of its power (low-pressure machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="18" customHeight="1">
+      <c r="A526" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT -- </t>
+        </is>
+      </c>
+      <c r="B526" s="7"/>
+      <c r="C526" s="7"/>
+      <c r="D526" s="7"/>
+      <c r="E526" s="7"/>
+      <c r="F526" s="7"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B527" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON1</t>
+        </is>
+      </c>
+      <c r="C527" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vref</t>
+        </is>
+      </c>
+      <c r="D527" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E527" s="8"/>
+      <c r="F527" s="8"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B528" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON2</t>
+        </is>
+      </c>
+      <c r="C528" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp1</t>
+        </is>
+      </c>
+      <c r="D528" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E528" s="8"/>
+      <c r="F528" s="8"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B529" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON3</t>
+        </is>
+      </c>
+      <c r="C529" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp2</t>
+        </is>
+      </c>
+      <c r="D529" s="8">
+        <v>0.175</v>
+      </c>
+      <c r="E529" s="8"/>
+      <c r="F529" s="8"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B530" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON4</t>
+        </is>
+      </c>
+      <c r="C530" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp3</t>
+        </is>
+      </c>
+      <c r="D530" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="E530" s="8"/>
+      <c r="F530" s="8"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B531" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON5</t>
+        </is>
+      </c>
+      <c r="C531" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp4</t>
+        </is>
+      </c>
+      <c r="D531" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E531" s="8"/>
+      <c r="F531" s="8"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B532" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON6</t>
+        </is>
+      </c>
+      <c r="C532" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp5</t>
+        </is>
+      </c>
+      <c r="D532" s="8">
+        <v>-0.55</v>
+      </c>
+      <c r="E532" s="8"/>
+      <c r="F532" s="8"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B533" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON7</t>
+        </is>
+      </c>
+      <c r="C533" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp6</t>
+        </is>
+      </c>
+      <c r="D533" s="8">
+        <v>-0.35</v>
+      </c>
+      <c r="E533" s="8"/>
+      <c r="F533" s="8"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B534" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON8</t>
+        </is>
+      </c>
+      <c r="C534" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp7</t>
+        </is>
+      </c>
+      <c r="D534" s="8">
+        <v>-0.25</v>
+      </c>
+      <c r="E534" s="8"/>
+      <c r="F534" s="8"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B535" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON9</t>
+        </is>
+      </c>
+      <c r="C535" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp8</t>
+        </is>
+      </c>
+      <c r="D535" s="8">
+        <v>-0.1</v>
+      </c>
+      <c r="E535" s="8"/>
+      <c r="F535" s="8"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B536" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON10</t>
+        </is>
+      </c>
+      <c r="C536" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp9</t>
+        </is>
+      </c>
+      <c r="D536" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E536" s="8"/>
+      <c r="F536" s="8"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B537" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON11</t>
+        </is>
+      </c>
+      <c r="C537" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dvtrp10</t>
+        </is>
+      </c>
+      <c r="D537" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E537" s="8"/>
+      <c r="F537" s="8"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B538" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON12</t>
+        </is>
+      </c>
+      <c r="C538" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp1</t>
+        </is>
+      </c>
+      <c r="D538" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E538" s="8"/>
+      <c r="F538" s="8"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B539" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON13</t>
+        </is>
+      </c>
+      <c r="C539" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp2</t>
+        </is>
+      </c>
+      <c r="D539" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E539" s="8"/>
+      <c r="F539" s="8"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B540" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON14</t>
+        </is>
+      </c>
+      <c r="C540" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp3</t>
+        </is>
+      </c>
+      <c r="D540" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E540" s="8"/>
+      <c r="F540" s="8"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B541" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON15</t>
+        </is>
+      </c>
+      <c r="C541" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp4</t>
+        </is>
+      </c>
+      <c r="D541" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="E541" s="8"/>
+      <c r="F541" s="8"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B542" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON16</t>
+        </is>
+      </c>
+      <c r="C542" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp5</t>
+        </is>
+      </c>
+      <c r="D542" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="E542" s="8"/>
+      <c r="F542" s="8"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B543" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON17</t>
+        </is>
+      </c>
+      <c r="C543" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp6</t>
+        </is>
+      </c>
+      <c r="D543" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="E543" s="8"/>
+      <c r="F543" s="8"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B544" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON18</t>
+        </is>
+      </c>
+      <c r="C544" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp7</t>
+        </is>
+      </c>
+      <c r="D544" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="E544" s="8"/>
+      <c r="F544" s="8"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B545" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON19</t>
+        </is>
+      </c>
+      <c r="C545" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp8</t>
+        </is>
+      </c>
+      <c r="D545" s="8">
+        <v>3.0</v>
+      </c>
+      <c r="E545" s="8"/>
+      <c r="F545" s="8"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B546" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON20</t>
+        </is>
+      </c>
+      <c r="C546" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp9</t>
+        </is>
+      </c>
+      <c r="D546" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E546" s="8"/>
+      <c r="F546" s="8"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B547" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON21</t>
+        </is>
+      </c>
+      <c r="C547" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp10</t>
+        </is>
+      </c>
+      <c r="D547" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E547" s="8"/>
+      <c r="F547" s="8"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHVRT</t>
+        </is>
+      </c>
+      <c r="B548" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON22</t>
+        </is>
+      </c>
+      <c r="C548" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alarm</t>
+        </is>
+      </c>
+      <c r="D548" s="8">
+        <v>0</v>
+      </c>
+      <c r="E548" s="8"/>
+      <c r="F548" s="8"/>
+    </row>
+    <row r="549" ht="18" customHeight="1">
+      <c r="A549" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT -- </t>
+        </is>
+      </c>
+      <c r="B549" s="7"/>
+      <c r="C549" s="7"/>
+      <c r="D549" s="7"/>
+      <c r="E549" s="7"/>
+      <c r="F549" s="7"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">LHFRT</t>
         </is>
       </c>
-      <c r="B463" s="8" t="inlineStr">
+      <c r="B550" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON1</t>
+        </is>
+      </c>
+      <c r="C550" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fref</t>
+        </is>
+      </c>
+      <c r="D550" s="8">
+        <v>60.0</v>
+      </c>
+      <c r="E550" s="8"/>
+      <c r="F550" s="8"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B551" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON2</t>
+        </is>
+      </c>
+      <c r="C551" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp1</t>
+        </is>
+      </c>
+      <c r="D551" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="E551" s="8"/>
+      <c r="F551" s="8"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B552" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON3</t>
+        </is>
+      </c>
+      <c r="C552" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp2</t>
+        </is>
+      </c>
+      <c r="D552" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="E552" s="8"/>
+      <c r="F552" s="8"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B553" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON4</t>
+        </is>
+      </c>
+      <c r="C553" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp3</t>
+        </is>
+      </c>
+      <c r="D553" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E553" s="8"/>
+      <c r="F553" s="8"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B554" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON5</t>
+        </is>
+      </c>
+      <c r="C554" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp4</t>
+        </is>
+      </c>
+      <c r="D554" s="8">
+        <v>-3.0</v>
+      </c>
+      <c r="E554" s="8"/>
+      <c r="F554" s="8"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B555" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON6</t>
+        </is>
+      </c>
+      <c r="C555" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp5</t>
+        </is>
+      </c>
+      <c r="D555" s="8">
+        <v>-2.7</v>
+      </c>
+      <c r="E555" s="8"/>
+      <c r="F555" s="8"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B556" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON7</t>
+        </is>
+      </c>
+      <c r="C556" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp6</t>
+        </is>
+      </c>
+      <c r="D556" s="8">
+        <v>-2.2</v>
+      </c>
+      <c r="E556" s="8"/>
+      <c r="F556" s="8"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B557" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON8</t>
+        </is>
+      </c>
+      <c r="C557" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp7</t>
+        </is>
+      </c>
+      <c r="D557" s="8">
+        <v>-1.6</v>
+      </c>
+      <c r="E557" s="8"/>
+      <c r="F557" s="8"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B558" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON9</t>
+        </is>
+      </c>
+      <c r="C558" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp8</t>
+        </is>
+      </c>
+      <c r="D558" s="8">
+        <v>-0.6</v>
+      </c>
+      <c r="E558" s="8"/>
+      <c r="F558" s="8"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B559" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON10</t>
+        </is>
+      </c>
+      <c r="C559" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp9</t>
+        </is>
+      </c>
+      <c r="D559" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E559" s="8"/>
+      <c r="F559" s="8"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B560" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON11</t>
+        </is>
+      </c>
+      <c r="C560" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dftrp10</t>
+        </is>
+      </c>
+      <c r="D560" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E560" s="8"/>
+      <c r="F560" s="8"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B561" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON12</t>
+        </is>
+      </c>
+      <c r="C561" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp1</t>
+        </is>
+      </c>
+      <c r="D561" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E561" s="8"/>
+      <c r="F561" s="8"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B562" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON13</t>
+        </is>
+      </c>
+      <c r="C562" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp2</t>
+        </is>
+      </c>
+      <c r="D562" s="8">
+        <v>30.0</v>
+      </c>
+      <c r="E562" s="8"/>
+      <c r="F562" s="8"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B563" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON14</t>
+        </is>
+      </c>
+      <c r="C563" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp3</t>
+        </is>
+      </c>
+      <c r="D563" s="8">
+        <v>180.0</v>
+      </c>
+      <c r="E563" s="8"/>
+      <c r="F563" s="8"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B564" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON15</t>
+        </is>
+      </c>
+      <c r="C564" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp4</t>
+        </is>
+      </c>
+      <c r="D564" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E564" s="8"/>
+      <c r="F564" s="8"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B565" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON16</t>
+        </is>
+      </c>
+      <c r="C565" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp5</t>
+        </is>
+      </c>
+      <c r="D565" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E565" s="8"/>
+      <c r="F565" s="8"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B566" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON17</t>
+        </is>
+      </c>
+      <c r="C566" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp6</t>
+        </is>
+      </c>
+      <c r="D566" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="E566" s="8"/>
+      <c r="F566" s="8"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B567" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON18</t>
+        </is>
+      </c>
+      <c r="C567" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp7</t>
+        </is>
+      </c>
+      <c r="D567" s="8">
+        <v>30.0</v>
+      </c>
+      <c r="E567" s="8"/>
+      <c r="F567" s="8"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B568" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON19</t>
+        </is>
+      </c>
+      <c r="C568" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp8</t>
+        </is>
+      </c>
+      <c r="D568" s="8">
+        <v>180.0</v>
+      </c>
+      <c r="E568" s="8"/>
+      <c r="F568" s="8"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B569" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON20</t>
+        </is>
+      </c>
+      <c r="C569" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp9</t>
+        </is>
+      </c>
+      <c r="D569" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E569" s="8"/>
+      <c r="F569" s="8"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B570" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CON21</t>
+        </is>
+      </c>
+      <c r="C570" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dttrp10</t>
+        </is>
+      </c>
+      <c r="D570" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="E570" s="8"/>
+      <c r="F570" s="8"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LHFRT</t>
+        </is>
+      </c>
+      <c r="B571" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">CON22</t>
         </is>
       </c>
-      <c r="C463" s="12" t="inlineStr">
+      <c r="C571" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">alarm</t>
         </is>
       </c>
-      <c r="D463" s="8">
+      <c r="D571" s="8">
         <v>0</v>
       </c>
-      <c r="E463" s="8"/>
-      <c r="F463" s="8"/>
+      <c r="E571" s="8"/>
+      <c r="F571" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="29">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -20129,7 +22969,14 @@
     <mergeCell ref="A403:F403"/>
     <mergeCell ref="A410:F410"/>
     <mergeCell ref="A418:F418"/>
-    <mergeCell ref="A441:F441"/>
+    <mergeCell ref="A431:F431"/>
+    <mergeCell ref="A446:F446"/>
+    <mergeCell ref="A467:F467"/>
+    <mergeCell ref="A480:F480"/>
+    <mergeCell ref="A493:F493"/>
+    <mergeCell ref="A503:F503"/>
+    <mergeCell ref="A526:F526"/>
+    <mergeCell ref="A549:F549"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -20203,7 +23050,7 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
     </row>
-    <row r="3" ht="17.0" customHeight="1">
+    <row r="3" ht="43.0" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
@@ -20215,11 +23062,15 @@
         </is>
       </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from the generators: PV100, Hybrid_PV100_BESS50 </t>
+        </is>
+      </c>
       <c r="E3" s="8"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">model name: file names and the PSCAD case (letters, digits, _)</t>
+          <t xml:space="preserve">model name: file names and the PSCAD case (letters, digits, _; blank = from the generators: PV100, Hybrid_PV100_BESS50 ...)</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
@@ -22915,12 +25766,15 @@
     <col min="35" max="35" width="10" customWidth="1"/>
     <col min="36" max="36" width="10" customWidth="1"/>
     <col min="37" max="37" width="10" customWidth="1"/>
-    <col min="38" max="38" width="18" customWidth="1"/>
-    <col min="39" max="39" width="16" customWidth="1"/>
+    <col min="38" max="38" width="10" customWidth="1"/>
+    <col min="39" max="39" width="10" customWidth="1"/>
     <col min="40" max="40" width="10" customWidth="1"/>
     <col min="41" max="41" width="18" customWidth="1"/>
-    <col min="42" max="42" width="10" customWidth="1"/>
+    <col min="42" max="42" width="16" customWidth="1"/>
     <col min="43" max="43" width="10" customWidth="1"/>
+    <col min="44" max="44" width="18" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -23111,30 +25965,45 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Machine model</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exciter model</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governor model</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">PSCAD library</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD definition</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD AC port</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD source case</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD component ID</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PSCAD inverter at</t>
         </is>
@@ -23308,30 +26177,45 @@
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">SYNC: GENROU round rotor (steam, gas) | GENSAL salient pole (hydro) (blank = GENROU)</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYNC: SEXS simplified | IEEET1 DC (IEEE type 1) | ESST1A static, bus-fed | EXST1 static (older form) | NONE: constant field voltage (blank = SEXS)</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYNC: TGOV1 steam | HYGOV hydro | GAST gas | IEEEG1 steam, multi-stage | NONE: constant mechanical power (blank = TGOV1)</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">vendor library .pslx (blank = none)</t>
         </is>
       </c>
-      <c r="AM2" s="2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">vendor model, library:name (blank = a source: network check)</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">its AC port (blank = its 3-phase port)</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">the OEM's PSCAD model (.pscx / .pslx) the UDM comes from: its PSCAD definition added to the case (GUI: Pick UDM from OEM model)</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">a UDM placed in the source case: copied with its settings instead (blank = the definition, its values from PSCAD_Params)</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LV: the inverter (your UDM or the stand-in source) on the GSU's LV side, the GSU built | MV: on its HV side, for a UDM with its GSU inside (blank = LV)</t>
         </is>
@@ -23436,7 +26320,10 @@
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">LV</t>
         </is>
@@ -23541,7 +26428,10 @@
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
       <c r="AP4" s="3"/>
-      <c r="AQ4" s="3" t="inlineStr">
+      <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">LV</t>
         </is>
@@ -23591,6 +26481,9 @@
       <c r="AO5" s="3"/>
       <c r="AP5" s="3"/>
       <c r="AQ5" s="3"/>
+      <c r="AR5" s="3"/>
+      <c r="AS5" s="3"/>
+      <c r="AT5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3"/>
@@ -23636,6 +26529,9 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
       <c r="AQ6" s="3"/>
+      <c r="AR6" s="3"/>
+      <c r="AS6" s="3"/>
+      <c r="AT6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3"/>
@@ -23681,6 +26577,9 @@
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
       <c r="AQ7" s="3"/>
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="3"/>
+      <c r="AT7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3"/>
@@ -23726,6 +26625,9 @@
       <c r="AO8" s="3"/>
       <c r="AP8" s="3"/>
       <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="3"/>
@@ -23771,6 +26673,9 @@
       <c r="AO9" s="3"/>
       <c r="AP9" s="3"/>
       <c r="AQ9" s="3"/>
+      <c r="AR9" s="3"/>
+      <c r="AS9" s="3"/>
+      <c r="AT9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
@@ -23816,6 +26721,9 @@
       <c r="AO10" s="3"/>
       <c r="AP10" s="3"/>
       <c r="AQ10" s="3"/>
+      <c r="AR10" s="3"/>
+      <c r="AS10" s="3"/>
+      <c r="AT10" s="3"/>
     </row>
     <row r="11">
       <c r="A11" s="3"/>
@@ -23861,6 +26769,9 @@
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
       <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
+      <c r="AS11" s="3"/>
+      <c r="AT11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
@@ -23906,6 +26817,9 @@
       <c r="AO12" s="3"/>
       <c r="AP12" s="3"/>
       <c r="AQ12" s="3"/>
+      <c r="AR12" s="3"/>
+      <c r="AS12" s="3"/>
+      <c r="AT12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3"/>
@@ -23951,6 +26865,9 @@
       <c r="AO13" s="3"/>
       <c r="AP13" s="3"/>
       <c r="AQ13" s="3"/>
+      <c r="AR13" s="3"/>
+      <c r="AS13" s="3"/>
+      <c r="AT13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3"/>
@@ -23996,6 +26913,9 @@
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
       <c r="AQ14" s="3"/>
+      <c r="AR14" s="3"/>
+      <c r="AS14" s="3"/>
+      <c r="AT14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -24041,6 +26961,9 @@
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
       <c r="AQ15" s="3"/>
+      <c r="AR15" s="3"/>
+      <c r="AS15" s="3"/>
+      <c r="AT15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -24086,6 +27009,9 @@
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
+      <c r="AS16" s="3"/>
+      <c r="AT16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -24131,6 +27057,9 @@
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
       <c r="AQ17" s="3"/>
+      <c r="AR17" s="3"/>
+      <c r="AS17" s="3"/>
+      <c r="AT17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -24176,6 +27105,9 @@
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
       <c r="AQ18" s="3"/>
+      <c r="AR18" s="3"/>
+      <c r="AS18" s="3"/>
+      <c r="AT18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -24221,6 +27153,9 @@
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="3"/>
+      <c r="AT19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -24266,6 +27201,9 @@
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
       <c r="AQ20" s="3"/>
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="3"/>
+      <c r="AT20" s="3"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -24311,6 +27249,9 @@
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
       <c r="AQ21" s="3"/>
+      <c r="AR21" s="3"/>
+      <c r="AS21" s="3"/>
+      <c r="AT21" s="3"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -24356,9 +27297,12 @@
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
       <c r="AQ22" s="3"/>
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="3"/>
+      <c r="AT22" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B500">
       <formula1>"PV,BESS,WT4,WT3,SYNC,USER"</formula1>
     </dataValidation>
@@ -24377,7 +27321,16 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AK3:AK500">
       <formula1>"REEC_A,REEC_C,REEC_D"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AQ3:AQ500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AL3:AL500">
+      <formula1>"GENROU,GENSAL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AM3:AM500">
+      <formula1>"SEXS,IEEET1,ESST1A,EXST1,NONE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AN3:AN500">
+      <formula1>"TGOV1,HYGOV,GAST,IEEEG1,NONE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AT3:AT500">
       <formula1>"LV,MV"</formula1>
     </dataValidation>
   </dataValidations>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="56.0" customHeight="1">
+    <row r="42" ht="82.0" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -701,7 +701,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">One row per main power transformer; HV winding first. Three windings: TV kV, the three impedances and their bases. Parallel units: identical units in parallel. Tie: a line of its own from HV to it. MVA blank: the MVA of the units on it (Unit MVA x Units), following them -- the GUI's Size MPTs from the generators suggests a rating. Rate A, B, C: its normal and emergency ratings (PSS/E RATEA, RATEB, RATEC; PSLF rate1, rate2, rate3).</t>
+          <t xml:space="preserve">One row per main power transformer; HV winding first. Three windings: TV kV (blank: the LV's, a split LV winding), the LV and TV MVA (blank: the MVA shared out by the units on each), the three impedances (Z HV-TV blank: Z HV-LV; Z LV-TV blank: 1.8 x Z HV-LV, a split LV winding's) and their bases. Parallel units: identical units in parallel. Tie: a line of its own from HV to it. MVA blank: the MVA of the units on it (Unit MVA x Units), following them -- the GUI's Size MPTs from the generators suggests a rating. Rate A, B, C: its normal and emergency ratings (PSS/E RATEA, RATEB, RATEC; PSLF rate1, rate2, rate3).</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="17.0" customHeight="1">
+    <row r="62" ht="56.0" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -3688,11 +3688,15 @@
         </is>
       </c>
       <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA x the LV units' share of the units on LV and TV -- none on TV: MVA</t>
+        </is>
+      </c>
       <c r="F62" s="8"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">3 windings (blank = MVA x the LV units' share of the units on LV and TV -- none on TV: MVA)</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -3701,7 +3705,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="17.0" customHeight="1">
+    <row r="63" ht="56.0" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -3718,11 +3722,15 @@
         </is>
       </c>
       <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVA x the TV units' share -- none on it: MVA/2 on a split LV winding (TV kV the LV's</t>
+        </is>
+      </c>
       <c r="F63" s="8"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">3 windings (blank = MVA x the TV units' share -- none on it: MVA/2 on a split LV winding (TV kV the LV's), MVA/3 a tertiary)</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -3880,11 +3888,15 @@
         </is>
       </c>
       <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z HV-LV</t>
+        </is>
+      </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">3 windings, on its base MVA (blank = Z HV-LV)</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -3893,7 +3905,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="17.0" customHeight="1">
+    <row r="69" ht="30.0" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -3910,11 +3922,15 @@
         </is>
       </c>
       <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.8 x Z HV-LV, a split LV winding's</t>
+        </is>
+      </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">3 windings, on its base MVA (blank = 1.8 x Z HV-LV, a split LV winding's)</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -24893,12 +24909,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">3 windings (blank = MVA x the LV units' share of the units on LV and TV -- none on TV: MVA)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">3 windings (blank = MVA x the TV units' share -- none on it: MVA/2 on a split LV winding (TV kV the LV's), MVA/3 a tertiary)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -24923,12 +24939,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">3 windings, on its base MVA (blank = Z HV-LV)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 windings</t>
+          <t xml:space="preserve">3 windings, on its base MVA (blank = 1.8 x Z HV-LV, a split LV winding's)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable data per length (R, X in ohm; C in uF or B in uS) and the length unit they are per; Rate A, B, C one cable's ratings in MVA at its collector's kV (sqrt(3) x kV x amps / 1000): a section's x its parallel cables, a collector equivalent's its sections from the collector bus together.</t>
+          <t xml:space="preserve">Cable data per length (R, X in ohm; B in uS, or C in uF instead -- the GUI's C to B turns C into B) and the length unit they are per; Rate A, B, C one cable's ratings in MVA at its collector's kV (sqrt(3) x kV x amps / 1000): a section's x its parallel cables, a collector equivalent's its sections from the collector bus together.</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="B154" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C per length</t>
+          <t xml:space="preserve">B per length</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">c_per</t>
+          <t xml:space="preserve">b_per</t>
         </is>
       </c>
       <c r="D154" s="8"/>
@@ -6668,7 +6668,7 @@
       <c r="F154" s="8"/>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">uS, the charging susceptance (GUI: Cables page, C to B)</t>
         </is>
       </c>
       <c r="H154" s="13" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">B per length</t>
+          <t xml:space="preserve">C per length</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">b_per</t>
+          <t xml:space="preserve">c_per</t>
         </is>
       </c>
       <c r="D155" s="8"/>
@@ -6698,7 +6698,7 @@
       <c r="F155" s="8"/>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS, instead of C</t>
+          <t xml:space="preserve">uF, instead of B (B = 2 pi f C)</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
@@ -28244,12 +28244,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">B per length</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">C per length</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B per length</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -28291,12 +28291,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">uF</t>
+          <t xml:space="preserve">uS, the charging susceptance (GUI: Cables page, C to B)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">uS, instead of C</t>
+          <t xml:space="preserve">uF, instead of B (B = 2 pi f C)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -28333,7 +28333,7 @@
         <v>0.105</v>
       </c>
       <c r="E3" s="3">
-        <v>0.39</v>
+        <v>147.027</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -28358,7 +28358,7 @@
         <v>0.118</v>
       </c>
       <c r="E4" s="3">
-        <v>0.3</v>
+        <v>113.097</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -28383,7 +28383,7 @@
         <v>0.133</v>
       </c>
       <c r="E5" s="3">
-        <v>0.22</v>
+        <v>82.938</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -28408,7 +28408,7 @@
         <v>0.148</v>
       </c>
       <c r="E6" s="3">
-        <v>0.17</v>
+        <v>64.0885</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>

--- a/smib/SMIB_INPUT_TEMPLATE.xlsx
+++ b/smib/SMIB_INPUT_TEMPLATE.xlsx
@@ -2392,17 +2392,17 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km or mi, whichever matches a line of the POI kV</t>
+          <t xml:space="preserve">ft, kft, km or mi, whichever matches a line of the POI kV</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the length R, X, B, C below are per: km, mi, kft, m, ft (blank = km or mi, whichever matches a line of the POI kV)</t>
+          <t xml:space="preserve">the length R, X, B, C below are per: ft, kft, m, km, mi (blank = ft, kft, km or mi, whichever matches a line of the POI kV)</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -4339,7 +4339,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="30.0" customHeight="1">
+    <row r="82" ht="43.0" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">MPT</t>
@@ -4358,17 +4358,17 @@
       <c r="D82" s="8"/>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km or mi, whichever matches a line of its kV</t>
+          <t xml:space="preserve">ft, kft, km or mi, whichever matches a line of its kV</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = ft, kft, km or mi, whichever matches a line of its kV)</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
@@ -6568,17 +6568,17 @@
       <c r="D151" s="8"/>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per (blank = km)</t>
+          <t xml:space="preserve">the values are per (blank = ft)</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -23678,23 +23678,23 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km or mi, whichever matches a line of the POI kV</t>
+          <t xml:space="preserve">ft, kft, km or mi, whichever matches a line of the POI kV</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">km | mi | kft | m | ft</t>
+          <t xml:space="preserve">ft | kft | m | km | mi</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the length R, X, B, C below are per: km, mi, kft, m, ft (blank = km or mi, whichever matches a line of the POI kV)</t>
+          <t xml:space="preserve">the length R, X, B, C below are per: ft, kft, m, km, mi (blank = ft, kft, km or mi, whichever matches a line of the POI kV)</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -23710,7 +23710,7 @@
         </is>
       </c>
       <c r="B26" s="3">
-        <v>0.072</v>
+        <v>2.19456e-05</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         </is>
       </c>
       <c r="B27" s="3">
-        <v>0.495</v>
+        <v>0.000150876</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         </is>
       </c>
       <c r="B28" s="3">
-        <v>3.35</v>
+        <v>0.00102108</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
       <formula1>"ft,kft,m,km,mi"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B25">
-      <formula1>"km,mi,kft,m,ft"</formula1>
+      <formula1>"ft,kft,m,km,mi"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B36">
       <formula1>"Q,PF,V"</formula1>
@@ -25009,7 +25009,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the length R, X, B are per (blank = km or mi, whichever matches a line of its kV)</t>
+          <t xml:space="preserve">the length R, X, B are per (blank = ft, kft, km or mi, whichever matches a line of its kV)</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -25730,7 +25730,7 @@
       <formula1>"ft,kft,m,km,mi"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA3:AA500">
-      <formula1>"km,mi,kft,m,ft"</formula1>
+      <formula1>"ft,kft,m,km,mi"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -28276,7 +28276,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">the values are per (blank = km)</t>
+          <t xml:space="preserve">the values are per (blank = ft)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -28323,17 +28323,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="C3" s="3">
-        <v>0.046</v>
+        <v>1.40208e-05</v>
       </c>
       <c r="D3" s="3">
-        <v>0.105</v>
+        <v>3.2004e-05</v>
       </c>
       <c r="E3" s="3">
-        <v>147.027</v>
+        <v>0.0448138296</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -28348,17 +28348,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="C4" s="3">
-        <v>0.09</v>
+        <v>2.7432e-05</v>
       </c>
       <c r="D4" s="3">
-        <v>0.118</v>
+        <v>3.59664e-05</v>
       </c>
       <c r="E4" s="3">
-        <v>113.097</v>
+        <v>0.0344719656</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -28373,17 +28373,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="C5" s="3">
-        <v>0.201</v>
+        <v>6.12648e-05</v>
       </c>
       <c r="D5" s="3">
-        <v>0.133</v>
+        <v>4.05384e-05</v>
       </c>
       <c r="E5" s="3">
-        <v>82.938</v>
+        <v>0.0252795024</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -28398,17 +28398,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">km</t>
+          <t xml:space="preserve">ft</t>
         </is>
       </c>
       <c r="C6" s="3">
-        <v>0.404</v>
+        <v>0.0001231392</v>
       </c>
       <c r="D6" s="3">
-        <v>0.148</v>
+        <v>4.51104e-05</v>
       </c>
       <c r="E6" s="3">
-        <v>64.0885</v>
+        <v>0.0195341748</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -28594,7 +28594,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B3:B500">
-      <formula1>"km,mi,kft,m,ft"</formula1>
+      <formula1>"ft,kft,m,km,mi"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
